--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="288">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,12 @@
     <t>['33']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['5', '45+5', '50', '80']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -799,9 +805,6 @@
     <t>['37', '63']</t>
   </si>
   <si>
-    <t>['62']</t>
-  </si>
-  <si>
     <t>['65', '69']</t>
   </si>
   <si>
@@ -872,6 +875,9 @@
   </si>
   <si>
     <t>['48', '63']</t>
+  </si>
+  <si>
+    <t>['52']</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1901,7 +1907,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1979,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -2519,7 +2525,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2803,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ8">
         <v>1.56</v>
@@ -2931,7 +2937,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3137,7 +3143,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3218,7 +3224,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3343,7 +3349,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3549,7 +3555,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3755,7 +3761,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3961,7 +3967,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4167,7 +4173,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4373,7 +4379,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5609,7 +5615,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5687,7 +5693,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>2.33</v>
@@ -5896,7 +5902,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR23">
         <v>2.07</v>
@@ -6099,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ24">
         <v>0.67</v>
@@ -6227,7 +6233,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6433,7 +6439,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6639,7 +6645,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6720,7 +6726,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR27">
         <v>0.72</v>
@@ -6845,7 +6851,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7257,7 +7263,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7544,7 +7550,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ31">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR31">
         <v>1.66</v>
@@ -7669,7 +7675,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7875,7 +7881,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8287,7 +8293,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8777,7 +8783,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37">
         <v>1.56</v>
@@ -8905,7 +8911,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9111,7 +9117,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9398,7 +9404,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9729,7 +9735,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10347,7 +10353,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10553,7 +10559,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10965,7 +10971,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11377,7 +11383,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11455,7 +11461,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50">
         <v>1.89</v>
@@ -11661,7 +11667,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ51">
         <v>0.5600000000000001</v>
@@ -12076,7 +12082,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ53">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR53">
         <v>1.28</v>
@@ -12201,7 +12207,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12407,7 +12413,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13025,7 +13031,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13231,7 +13237,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13437,7 +13443,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13643,7 +13649,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13930,7 +13936,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR62">
         <v>1.9</v>
@@ -14261,7 +14267,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14339,10 +14345,10 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR64">
         <v>1.8</v>
@@ -14673,7 +14679,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14957,7 +14963,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ67">
         <v>1.89</v>
@@ -16115,7 +16121,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16321,7 +16327,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17429,7 +17435,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ79">
         <v>0.33</v>
@@ -17557,7 +17563,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17841,7 +17847,7 @@
         <v>0.25</v>
       </c>
       <c r="AP81">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>0.5600000000000001</v>
@@ -18050,7 +18056,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ82">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR82">
         <v>1.3</v>
@@ -18999,7 +19005,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19205,7 +19211,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19411,7 +19417,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19492,7 +19498,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ89">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19617,7 +19623,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19823,7 +19829,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20235,7 +20241,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20441,7 +20447,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20647,7 +20653,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20725,7 +20731,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ95">
         <v>1.56</v>
@@ -20853,7 +20859,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21471,7 +21477,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21677,7 +21683,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21883,7 +21889,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -21964,7 +21970,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR101">
         <v>1.68</v>
@@ -22089,7 +22095,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22295,7 +22301,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22579,7 +22585,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ104">
         <v>0.33</v>
@@ -22707,7 +22713,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22788,7 +22794,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ105">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR105">
         <v>1.93</v>
@@ -23325,7 +23331,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23406,7 +23412,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ108">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR108">
         <v>1.61</v>
@@ -23531,7 +23537,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23943,7 +23949,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24433,7 +24439,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -24561,7 +24567,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24973,7 +24979,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25179,7 +25185,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25466,7 +25472,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ118">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR118">
         <v>1.58</v>
@@ -25591,7 +25597,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26003,7 +26009,7 @@
         <v>107</v>
       </c>
       <c r="P121" t="s">
-        <v>261</v>
+        <v>204</v>
       </c>
       <c r="Q121">
         <v>3.5</v>
@@ -26209,7 +26215,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26415,7 +26421,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26702,7 +26708,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR124">
         <v>1.68</v>
@@ -26827,7 +26833,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26905,7 +26911,7 @@
         <v>0.86</v>
       </c>
       <c r="AP125">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125">
         <v>1.11</v>
@@ -27239,7 +27245,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27445,7 +27451,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27857,7 +27863,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28269,7 +28275,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28681,7 +28687,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28887,7 +28893,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -28965,7 +28971,7 @@
         <v>1.5</v>
       </c>
       <c r="AP135">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ135">
         <v>1.44</v>
@@ -29093,7 +29099,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29299,7 +29305,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29505,7 +29511,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29789,7 +29795,7 @@
         <v>1.43</v>
       </c>
       <c r="AP139">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ139">
         <v>1.22</v>
@@ -29917,7 +29923,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30123,7 +30129,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30204,7 +30210,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ141">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR141">
         <v>1.53</v>
@@ -30822,7 +30828,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31643,7 +31649,7 @@
         <v>0.75</v>
       </c>
       <c r="AP148">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ148">
         <v>0.67</v>
@@ -31771,7 +31777,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31977,7 +31983,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32183,7 +32189,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32389,7 +32395,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33007,7 +33013,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33419,7 +33425,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q157">
         <v>2.63</v>
@@ -33500,7 +33506,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ157">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR157">
         <v>1.39</v>
@@ -33625,7 +33631,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34037,7 +34043,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34243,7 +34249,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34655,7 +34661,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -34812,6 +34818,418 @@
       </c>
       <c r="BP163">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7450811</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45688.58333333334</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>72</v>
+      </c>
+      <c r="H164" t="s">
+        <v>78</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164" t="s">
+        <v>204</v>
+      </c>
+      <c r="P164" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q164">
+        <v>2.88</v>
+      </c>
+      <c r="R164">
+        <v>2.25</v>
+      </c>
+      <c r="S164">
+        <v>3.5</v>
+      </c>
+      <c r="T164">
+        <v>1.33</v>
+      </c>
+      <c r="U164">
+        <v>3.15</v>
+      </c>
+      <c r="V164">
+        <v>2.54</v>
+      </c>
+      <c r="W164">
+        <v>1.48</v>
+      </c>
+      <c r="X164">
+        <v>6.25</v>
+      </c>
+      <c r="Y164">
+        <v>1.1</v>
+      </c>
+      <c r="Z164">
+        <v>2.1</v>
+      </c>
+      <c r="AA164">
+        <v>3.2</v>
+      </c>
+      <c r="AB164">
+        <v>3.47</v>
+      </c>
+      <c r="AC164">
+        <v>1.02</v>
+      </c>
+      <c r="AD164">
+        <v>11</v>
+      </c>
+      <c r="AE164">
+        <v>1.18</v>
+      </c>
+      <c r="AF164">
+        <v>3.88</v>
+      </c>
+      <c r="AG164">
+        <v>1.71</v>
+      </c>
+      <c r="AH164">
+        <v>2.06</v>
+      </c>
+      <c r="AI164">
+        <v>1.57</v>
+      </c>
+      <c r="AJ164">
+        <v>2.25</v>
+      </c>
+      <c r="AK164">
+        <v>1.32</v>
+      </c>
+      <c r="AL164">
+        <v>1.28</v>
+      </c>
+      <c r="AM164">
+        <v>1.69</v>
+      </c>
+      <c r="AN164">
+        <v>1.33</v>
+      </c>
+      <c r="AO164">
+        <v>0.44</v>
+      </c>
+      <c r="AP164">
+        <v>1.5</v>
+      </c>
+      <c r="AQ164">
+        <v>0.4</v>
+      </c>
+      <c r="AR164">
+        <v>1.72</v>
+      </c>
+      <c r="AS164">
+        <v>1.3</v>
+      </c>
+      <c r="AT164">
+        <v>3.02</v>
+      </c>
+      <c r="AU164">
+        <v>6</v>
+      </c>
+      <c r="AV164">
+        <v>2</v>
+      </c>
+      <c r="AW164">
+        <v>9</v>
+      </c>
+      <c r="AX164">
+        <v>9</v>
+      </c>
+      <c r="AY164">
+        <v>20</v>
+      </c>
+      <c r="AZ164">
+        <v>11</v>
+      </c>
+      <c r="BA164">
+        <v>6</v>
+      </c>
+      <c r="BB164">
+        <v>6</v>
+      </c>
+      <c r="BC164">
+        <v>12</v>
+      </c>
+      <c r="BD164">
+        <v>1.84</v>
+      </c>
+      <c r="BE164">
+        <v>6.4</v>
+      </c>
+      <c r="BF164">
+        <v>2.17</v>
+      </c>
+      <c r="BG164">
+        <v>1.33</v>
+      </c>
+      <c r="BH164">
+        <v>2.88</v>
+      </c>
+      <c r="BI164">
+        <v>1.57</v>
+      </c>
+      <c r="BJ164">
+        <v>2.16</v>
+      </c>
+      <c r="BK164">
+        <v>2.2</v>
+      </c>
+      <c r="BL164">
+        <v>1.72</v>
+      </c>
+      <c r="BM164">
+        <v>2.45</v>
+      </c>
+      <c r="BN164">
+        <v>1.45</v>
+      </c>
+      <c r="BO164">
+        <v>3.15</v>
+      </c>
+      <c r="BP164">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7450814</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45688.6875</v>
+      </c>
+      <c r="F165">
+        <v>19</v>
+      </c>
+      <c r="G165" t="s">
+        <v>76</v>
+      </c>
+      <c r="H165" t="s">
+        <v>82</v>
+      </c>
+      <c r="I165">
+        <v>2</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>2</v>
+      </c>
+      <c r="L165">
+        <v>4</v>
+      </c>
+      <c r="M165">
+        <v>1</v>
+      </c>
+      <c r="N165">
+        <v>5</v>
+      </c>
+      <c r="O165" t="s">
+        <v>205</v>
+      </c>
+      <c r="P165" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q165">
+        <v>2.05</v>
+      </c>
+      <c r="R165">
+        <v>2.4</v>
+      </c>
+      <c r="S165">
+        <v>5.5</v>
+      </c>
+      <c r="T165">
+        <v>1.29</v>
+      </c>
+      <c r="U165">
+        <v>3.4</v>
+      </c>
+      <c r="V165">
+        <v>2.43</v>
+      </c>
+      <c r="W165">
+        <v>1.52</v>
+      </c>
+      <c r="X165">
+        <v>5.95</v>
+      </c>
+      <c r="Y165">
+        <v>1.11</v>
+      </c>
+      <c r="Z165">
+        <v>1.61</v>
+      </c>
+      <c r="AA165">
+        <v>3.7</v>
+      </c>
+      <c r="AB165">
+        <v>5.36</v>
+      </c>
+      <c r="AC165">
+        <v>1.01</v>
+      </c>
+      <c r="AD165">
+        <v>12</v>
+      </c>
+      <c r="AE165">
+        <v>1.15</v>
+      </c>
+      <c r="AF165">
+        <v>4.33</v>
+      </c>
+      <c r="AG165">
+        <v>1.63</v>
+      </c>
+      <c r="AH165">
+        <v>2.19</v>
+      </c>
+      <c r="AI165">
+        <v>1.75</v>
+      </c>
+      <c r="AJ165">
+        <v>2</v>
+      </c>
+      <c r="AK165">
+        <v>1.11</v>
+      </c>
+      <c r="AL165">
+        <v>1.18</v>
+      </c>
+      <c r="AM165">
+        <v>2.58</v>
+      </c>
+      <c r="AN165">
+        <v>2.67</v>
+      </c>
+      <c r="AO165">
+        <v>1</v>
+      </c>
+      <c r="AP165">
+        <v>2.7</v>
+      </c>
+      <c r="AQ165">
+        <v>0.9</v>
+      </c>
+      <c r="AR165">
+        <v>2.02</v>
+      </c>
+      <c r="AS165">
+        <v>1.4</v>
+      </c>
+      <c r="AT165">
+        <v>3.42</v>
+      </c>
+      <c r="AU165">
+        <v>10</v>
+      </c>
+      <c r="AV165">
+        <v>9</v>
+      </c>
+      <c r="AW165">
+        <v>10</v>
+      </c>
+      <c r="AX165">
+        <v>4</v>
+      </c>
+      <c r="AY165">
+        <v>24</v>
+      </c>
+      <c r="AZ165">
+        <v>15</v>
+      </c>
+      <c r="BA165">
+        <v>7</v>
+      </c>
+      <c r="BB165">
+        <v>7</v>
+      </c>
+      <c r="BC165">
+        <v>14</v>
+      </c>
+      <c r="BD165">
+        <v>1.44</v>
+      </c>
+      <c r="BE165">
+        <v>6.75</v>
+      </c>
+      <c r="BF165">
+        <v>3.15</v>
+      </c>
+      <c r="BG165">
+        <v>1.34</v>
+      </c>
+      <c r="BH165">
+        <v>2.85</v>
+      </c>
+      <c r="BI165">
+        <v>1.58</v>
+      </c>
+      <c r="BJ165">
+        <v>2.14</v>
+      </c>
+      <c r="BK165">
+        <v>2.38</v>
+      </c>
+      <c r="BL165">
+        <v>1.72</v>
+      </c>
+      <c r="BM165">
+        <v>2.48</v>
+      </c>
+      <c r="BN165">
+        <v>1.44</v>
+      </c>
+      <c r="BO165">
+        <v>3.2</v>
+      </c>
+      <c r="BP165">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="290">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -634,6 +634,15 @@
     <t>['5', '45+5', '50', '80']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['5', '7', '10', '33', '45']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -641,9 +650,6 @@
   </si>
   <si>
     <t>['32', '87']</t>
-  </si>
-  <si>
-    <t>['73']</t>
   </si>
   <si>
     <t>['10', '56']</t>
@@ -1239,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1573,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ2">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1782,7 +1788,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ3">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1907,7 +1913,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -1988,7 +1994,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2191,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5">
         <v>1.11</v>
@@ -2400,7 +2406,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ6">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2525,7 +2531,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2603,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ7">
         <v>1.22</v>
@@ -2937,7 +2943,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3015,10 +3021,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3143,7 +3149,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3349,7 +3355,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3555,7 +3561,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3761,7 +3767,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3967,7 +3973,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4173,7 +4179,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4379,7 +4385,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5284,7 +5290,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ20">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR20">
         <v>0.84</v>
@@ -5487,7 +5493,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ21">
         <v>0.5600000000000001</v>
@@ -5615,7 +5621,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5696,7 +5702,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR22">
         <v>2.03</v>
@@ -5899,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ23">
         <v>0.4</v>
@@ -6108,7 +6114,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ24">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR24">
         <v>1.69</v>
@@ -6233,7 +6239,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6311,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>1.11</v>
@@ -6439,7 +6445,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6645,7 +6651,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6723,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ27">
         <v>0.9</v>
@@ -6851,7 +6857,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7263,7 +7269,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7547,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ31">
         <v>0.4</v>
@@ -7675,7 +7681,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7756,7 +7762,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ32">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR32">
         <v>1.13</v>
@@ -7881,7 +7887,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8293,7 +8299,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8580,7 +8586,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ36">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR36">
         <v>1.51</v>
@@ -8911,7 +8917,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -8989,7 +8995,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ38">
         <v>2.11</v>
@@ -9117,7 +9123,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9401,7 +9407,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ40">
         <v>0.9</v>
@@ -9735,7 +9741,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9816,7 +9822,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10019,10 +10025,10 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ43">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10353,7 +10359,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10434,7 +10440,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR45">
         <v>1.15</v>
@@ -10559,7 +10565,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10640,7 +10646,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ46">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR46">
         <v>1.21</v>
@@ -10843,10 +10849,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR47">
         <v>1.43</v>
@@ -10971,7 +10977,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11049,7 +11055,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ48">
         <v>1.56</v>
@@ -11258,7 +11264,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ49">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11383,7 +11389,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12207,7 +12213,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12413,7 +12419,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13031,7 +13037,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13237,7 +13243,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13315,10 +13321,10 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ59">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR59">
         <v>1.38</v>
@@ -13443,7 +13449,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13649,7 +13655,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13727,7 +13733,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ61">
         <v>0.33</v>
@@ -13933,7 +13939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ62">
         <v>0.9</v>
@@ -14139,7 +14145,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63">
         <v>1.56</v>
@@ -14267,7 +14273,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14554,7 +14560,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR65">
         <v>1.09</v>
@@ -14679,7 +14685,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14757,7 +14763,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ66">
         <v>0.5600000000000001</v>
@@ -15172,7 +15178,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ68">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR68">
         <v>1.44</v>
@@ -15378,7 +15384,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ69">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -15584,7 +15590,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ70">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15993,7 +15999,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ72">
         <v>1.44</v>
@@ -16121,7 +16127,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16327,7 +16333,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16405,10 +16411,10 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ74">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -16817,7 +16823,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ76">
         <v>1.22</v>
@@ -17232,7 +17238,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ78">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR78">
         <v>1.53</v>
@@ -17563,7 +17569,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17641,7 +17647,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ80">
         <v>1.89</v>
@@ -18262,7 +18268,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ83">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR83">
         <v>1.5</v>
@@ -18465,7 +18471,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>0.33</v>
@@ -18880,7 +18886,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR86">
         <v>1.54</v>
@@ -19005,7 +19011,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19211,7 +19217,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19417,7 +19423,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19495,7 +19501,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ89">
         <v>0.4</v>
@@ -19623,7 +19629,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19829,7 +19835,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20116,7 +20122,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ92">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -20241,7 +20247,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20322,7 +20328,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ93">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR93">
         <v>1.66</v>
@@ -20447,7 +20453,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20525,10 +20531,10 @@
         <v>0.2</v>
       </c>
       <c r="AP94">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ94">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR94">
         <v>1.85</v>
@@ -20653,7 +20659,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20859,7 +20865,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21143,7 +21149,7 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ97">
         <v>1.22</v>
@@ -21349,7 +21355,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ98">
         <v>1.44</v>
@@ -21477,7 +21483,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21683,7 +21689,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21889,7 +21895,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -21967,7 +21973,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ101">
         <v>0.9</v>
@@ -22095,7 +22101,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22301,7 +22307,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22379,7 +22385,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ103">
         <v>1.56</v>
@@ -22713,7 +22719,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22791,7 +22797,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ105">
         <v>0.4</v>
@@ -23206,7 +23212,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ107">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23331,7 +23337,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23537,7 +23543,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23618,7 +23624,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ109">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -23821,10 +23827,10 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ110">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR110">
         <v>1.69</v>
@@ -23949,7 +23955,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24027,7 +24033,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ111">
         <v>1.56</v>
@@ -24236,7 +24242,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ112">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR112">
         <v>1.59</v>
@@ -24442,7 +24448,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR113">
         <v>1.89</v>
@@ -24567,7 +24573,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24648,7 +24654,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ114">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR114">
         <v>1.55</v>
@@ -24851,7 +24857,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ115">
         <v>1.11</v>
@@ -24979,7 +24985,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25185,7 +25191,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25597,7 +25603,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -25675,7 +25681,7 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ119">
         <v>0.5600000000000001</v>
@@ -26215,7 +26221,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26293,7 +26299,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ122">
         <v>1.89</v>
@@ -26421,7 +26427,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26833,7 +26839,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27245,7 +27251,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27451,7 +27457,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27529,10 +27535,10 @@
         <v>0.5</v>
       </c>
       <c r="AP128">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27738,7 +27744,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ129">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR129">
         <v>1.39</v>
@@ -27863,7 +27869,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -27941,7 +27947,7 @@
         <v>1.17</v>
       </c>
       <c r="AP130">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ130">
         <v>1.22</v>
@@ -28150,7 +28156,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ131">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28275,7 +28281,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28562,7 +28568,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ133">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR133">
         <v>1.65</v>
@@ -28687,7 +28693,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28765,10 +28771,10 @@
         <v>2.43</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ134">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR134">
         <v>1.7</v>
@@ -28893,7 +28899,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29099,7 +29105,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29305,7 +29311,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29383,7 +29389,7 @@
         <v>0.29</v>
       </c>
       <c r="AP137">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ137">
         <v>0.33</v>
@@ -29511,7 +29517,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29923,7 +29929,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30129,7 +30135,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30619,7 +30625,7 @@
         <v>1.38</v>
       </c>
       <c r="AP143">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ143">
         <v>1.22</v>
@@ -31031,10 +31037,10 @@
         <v>0.63</v>
       </c>
       <c r="AP145">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ145">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR145">
         <v>1.63</v>
@@ -31446,7 +31452,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ147">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR147">
         <v>1.42</v>
@@ -31652,7 +31658,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ148">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR148">
         <v>1.73</v>
@@ -31777,7 +31783,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31858,7 +31864,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ149">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AR149">
         <v>1.41</v>
@@ -31983,7 +31989,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32189,7 +32195,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32267,7 +32273,7 @@
         <v>2.14</v>
       </c>
       <c r="AP151">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ151">
         <v>1.89</v>
@@ -32395,7 +32401,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32679,10 +32685,10 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR153">
         <v>1.63</v>
@@ -33013,7 +33019,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33091,7 +33097,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ155">
         <v>1.56</v>
@@ -33425,7 +33431,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q157">
         <v>2.63</v>
@@ -33631,7 +33637,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34043,7 +34049,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34249,7 +34255,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34661,7 +34667,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -34742,7 +34748,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ163">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR163">
         <v>1.52</v>
@@ -35073,7 +35079,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35230,6 +35236,1036 @@
       </c>
       <c r="BP165">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7450816</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45689.44791666666</v>
+      </c>
+      <c r="F166">
+        <v>19</v>
+      </c>
+      <c r="G166" t="s">
+        <v>77</v>
+      </c>
+      <c r="H166" t="s">
+        <v>80</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>2</v>
+      </c>
+      <c r="O166" t="s">
+        <v>206</v>
+      </c>
+      <c r="P166" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q166">
+        <v>2.3</v>
+      </c>
+      <c r="R166">
+        <v>2.38</v>
+      </c>
+      <c r="S166">
+        <v>4.5</v>
+      </c>
+      <c r="T166">
+        <v>1.3</v>
+      </c>
+      <c r="U166">
+        <v>3.25</v>
+      </c>
+      <c r="V166">
+        <v>2.3</v>
+      </c>
+      <c r="W166">
+        <v>1.55</v>
+      </c>
+      <c r="X166">
+        <v>5</v>
+      </c>
+      <c r="Y166">
+        <v>1.13</v>
+      </c>
+      <c r="Z166">
+        <v>1.73</v>
+      </c>
+      <c r="AA166">
+        <v>3.59</v>
+      </c>
+      <c r="AB166">
+        <v>4.7</v>
+      </c>
+      <c r="AC166">
+        <v>1.04</v>
+      </c>
+      <c r="AD166">
+        <v>10</v>
+      </c>
+      <c r="AE166">
+        <v>1.2</v>
+      </c>
+      <c r="AF166">
+        <v>4.33</v>
+      </c>
+      <c r="AG166">
+        <v>1.57</v>
+      </c>
+      <c r="AH166">
+        <v>2.15</v>
+      </c>
+      <c r="AI166">
+        <v>1.57</v>
+      </c>
+      <c r="AJ166">
+        <v>2.38</v>
+      </c>
+      <c r="AK166">
+        <v>1.18</v>
+      </c>
+      <c r="AL166">
+        <v>1.22</v>
+      </c>
+      <c r="AM166">
+        <v>2.1</v>
+      </c>
+      <c r="AN166">
+        <v>1.56</v>
+      </c>
+      <c r="AO166">
+        <v>0.67</v>
+      </c>
+      <c r="AP166">
+        <v>1.5</v>
+      </c>
+      <c r="AQ166">
+        <v>0.7</v>
+      </c>
+      <c r="AR166">
+        <v>1.68</v>
+      </c>
+      <c r="AS166">
+        <v>1.24</v>
+      </c>
+      <c r="AT166">
+        <v>2.92</v>
+      </c>
+      <c r="AU166">
+        <v>4</v>
+      </c>
+      <c r="AV166">
+        <v>7</v>
+      </c>
+      <c r="AW166">
+        <v>9</v>
+      </c>
+      <c r="AX166">
+        <v>4</v>
+      </c>
+      <c r="AY166">
+        <v>16</v>
+      </c>
+      <c r="AZ166">
+        <v>14</v>
+      </c>
+      <c r="BA166">
+        <v>3</v>
+      </c>
+      <c r="BB166">
+        <v>2</v>
+      </c>
+      <c r="BC166">
+        <v>5</v>
+      </c>
+      <c r="BD166">
+        <v>1.49</v>
+      </c>
+      <c r="BE166">
+        <v>7</v>
+      </c>
+      <c r="BF166">
+        <v>2.9</v>
+      </c>
+      <c r="BG166">
+        <v>1.33</v>
+      </c>
+      <c r="BH166">
+        <v>2.88</v>
+      </c>
+      <c r="BI166">
+        <v>1.58</v>
+      </c>
+      <c r="BJ166">
+        <v>2.15</v>
+      </c>
+      <c r="BK166">
+        <v>2</v>
+      </c>
+      <c r="BL166">
+        <v>1.72</v>
+      </c>
+      <c r="BM166">
+        <v>2.45</v>
+      </c>
+      <c r="BN166">
+        <v>1.44</v>
+      </c>
+      <c r="BO166">
+        <v>3.2</v>
+      </c>
+      <c r="BP166">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7450810</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45689.5625</v>
+      </c>
+      <c r="F167">
+        <v>19</v>
+      </c>
+      <c r="G167" t="s">
+        <v>75</v>
+      </c>
+      <c r="H167" t="s">
+        <v>86</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167" t="s">
+        <v>95</v>
+      </c>
+      <c r="P167" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q167">
+        <v>4</v>
+      </c>
+      <c r="R167">
+        <v>2.05</v>
+      </c>
+      <c r="S167">
+        <v>3</v>
+      </c>
+      <c r="T167">
+        <v>1.44</v>
+      </c>
+      <c r="U167">
+        <v>2.6</v>
+      </c>
+      <c r="V167">
+        <v>3</v>
+      </c>
+      <c r="W167">
+        <v>1.33</v>
+      </c>
+      <c r="X167">
+        <v>7</v>
+      </c>
+      <c r="Y167">
+        <v>1.06</v>
+      </c>
+      <c r="Z167">
+        <v>3.36</v>
+      </c>
+      <c r="AA167">
+        <v>3.17</v>
+      </c>
+      <c r="AB167">
+        <v>2.19</v>
+      </c>
+      <c r="AC167">
+        <v>1.07</v>
+      </c>
+      <c r="AD167">
+        <v>8</v>
+      </c>
+      <c r="AE167">
+        <v>1.38</v>
+      </c>
+      <c r="AF167">
+        <v>3</v>
+      </c>
+      <c r="AG167">
+        <v>2.1</v>
+      </c>
+      <c r="AH167">
+        <v>1.67</v>
+      </c>
+      <c r="AI167">
+        <v>1.91</v>
+      </c>
+      <c r="AJ167">
+        <v>1.91</v>
+      </c>
+      <c r="AK167">
+        <v>1.62</v>
+      </c>
+      <c r="AL167">
+        <v>1.28</v>
+      </c>
+      <c r="AM167">
+        <v>1.33</v>
+      </c>
+      <c r="AN167">
+        <v>1.33</v>
+      </c>
+      <c r="AO167">
+        <v>2.33</v>
+      </c>
+      <c r="AP167">
+        <v>1.3</v>
+      </c>
+      <c r="AQ167">
+        <v>2.2</v>
+      </c>
+      <c r="AR167">
+        <v>1.71</v>
+      </c>
+      <c r="AS167">
+        <v>1.43</v>
+      </c>
+      <c r="AT167">
+        <v>3.14</v>
+      </c>
+      <c r="AU167">
+        <v>4</v>
+      </c>
+      <c r="AV167">
+        <v>3</v>
+      </c>
+      <c r="AW167">
+        <v>8</v>
+      </c>
+      <c r="AX167">
+        <v>6</v>
+      </c>
+      <c r="AY167">
+        <v>14</v>
+      </c>
+      <c r="AZ167">
+        <v>10</v>
+      </c>
+      <c r="BA167">
+        <v>4</v>
+      </c>
+      <c r="BB167">
+        <v>2</v>
+      </c>
+      <c r="BC167">
+        <v>6</v>
+      </c>
+      <c r="BD167">
+        <v>2.18</v>
+      </c>
+      <c r="BE167">
+        <v>6.4</v>
+      </c>
+      <c r="BF167">
+        <v>1.84</v>
+      </c>
+      <c r="BG167">
+        <v>1.35</v>
+      </c>
+      <c r="BH167">
+        <v>2.8</v>
+      </c>
+      <c r="BI167">
+        <v>1.61</v>
+      </c>
+      <c r="BJ167">
+        <v>2.1</v>
+      </c>
+      <c r="BK167">
+        <v>2.38</v>
+      </c>
+      <c r="BL167">
+        <v>1.85</v>
+      </c>
+      <c r="BM167">
+        <v>2.55</v>
+      </c>
+      <c r="BN167">
+        <v>1.42</v>
+      </c>
+      <c r="BO167">
+        <v>3.3</v>
+      </c>
+      <c r="BP167">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7450817</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45689.67708333334</v>
+      </c>
+      <c r="F168">
+        <v>19</v>
+      </c>
+      <c r="G168" t="s">
+        <v>73</v>
+      </c>
+      <c r="H168" t="s">
+        <v>83</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>1</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>1</v>
+      </c>
+      <c r="O168" t="s">
+        <v>207</v>
+      </c>
+      <c r="P168" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q168">
+        <v>2.4</v>
+      </c>
+      <c r="R168">
+        <v>2.38</v>
+      </c>
+      <c r="S168">
+        <v>4.33</v>
+      </c>
+      <c r="T168">
+        <v>1.3</v>
+      </c>
+      <c r="U168">
+        <v>3.25</v>
+      </c>
+      <c r="V168">
+        <v>2.3</v>
+      </c>
+      <c r="W168">
+        <v>1.55</v>
+      </c>
+      <c r="X168">
+        <v>5</v>
+      </c>
+      <c r="Y168">
+        <v>1.13</v>
+      </c>
+      <c r="Z168">
+        <v>1.64</v>
+      </c>
+      <c r="AA168">
+        <v>3.67</v>
+      </c>
+      <c r="AB168">
+        <v>5.3</v>
+      </c>
+      <c r="AC168">
+        <v>1.04</v>
+      </c>
+      <c r="AD168">
+        <v>10</v>
+      </c>
+      <c r="AE168">
+        <v>1.22</v>
+      </c>
+      <c r="AF168">
+        <v>4.2</v>
+      </c>
+      <c r="AG168">
+        <v>1.61</v>
+      </c>
+      <c r="AH168">
+        <v>2.1</v>
+      </c>
+      <c r="AI168">
+        <v>1.57</v>
+      </c>
+      <c r="AJ168">
+        <v>2.38</v>
+      </c>
+      <c r="AK168">
+        <v>1.22</v>
+      </c>
+      <c r="AL168">
+        <v>1.25</v>
+      </c>
+      <c r="AM168">
+        <v>1.91</v>
+      </c>
+      <c r="AN168">
+        <v>2.44</v>
+      </c>
+      <c r="AO168">
+        <v>0.67</v>
+      </c>
+      <c r="AP168">
+        <v>2.5</v>
+      </c>
+      <c r="AQ168">
+        <v>0.6</v>
+      </c>
+      <c r="AR168">
+        <v>1.8</v>
+      </c>
+      <c r="AS168">
+        <v>1.43</v>
+      </c>
+      <c r="AT168">
+        <v>3.23</v>
+      </c>
+      <c r="AU168">
+        <v>9</v>
+      </c>
+      <c r="AV168">
+        <v>2</v>
+      </c>
+      <c r="AW168">
+        <v>8</v>
+      </c>
+      <c r="AX168">
+        <v>7</v>
+      </c>
+      <c r="AY168">
+        <v>19</v>
+      </c>
+      <c r="AZ168">
+        <v>12</v>
+      </c>
+      <c r="BA168">
+        <v>9</v>
+      </c>
+      <c r="BB168">
+        <v>5</v>
+      </c>
+      <c r="BC168">
+        <v>14</v>
+      </c>
+      <c r="BD168">
+        <v>1.5</v>
+      </c>
+      <c r="BE168">
+        <v>6.75</v>
+      </c>
+      <c r="BF168">
+        <v>2.9</v>
+      </c>
+      <c r="BG168">
+        <v>1.21</v>
+      </c>
+      <c r="BH168">
+        <v>3.65</v>
+      </c>
+      <c r="BI168">
+        <v>1.4</v>
+      </c>
+      <c r="BJ168">
+        <v>2.63</v>
+      </c>
+      <c r="BK168">
+        <v>1.91</v>
+      </c>
+      <c r="BL168">
+        <v>2.04</v>
+      </c>
+      <c r="BM168">
+        <v>1.93</v>
+      </c>
+      <c r="BN168">
+        <v>1.77</v>
+      </c>
+      <c r="BO168">
+        <v>2.55</v>
+      </c>
+      <c r="BP168">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7450812</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45690.34375</v>
+      </c>
+      <c r="F169">
+        <v>19</v>
+      </c>
+      <c r="G169" t="s">
+        <v>87</v>
+      </c>
+      <c r="H169" t="s">
+        <v>79</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="M169">
+        <v>1</v>
+      </c>
+      <c r="N169">
+        <v>2</v>
+      </c>
+      <c r="O169" t="s">
+        <v>202</v>
+      </c>
+      <c r="P169" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q169">
+        <v>2.1</v>
+      </c>
+      <c r="R169">
+        <v>2.3</v>
+      </c>
+      <c r="S169">
+        <v>6</v>
+      </c>
+      <c r="T169">
+        <v>1.33</v>
+      </c>
+      <c r="U169">
+        <v>3</v>
+      </c>
+      <c r="V169">
+        <v>2.55</v>
+      </c>
+      <c r="W169">
+        <v>1.45</v>
+      </c>
+      <c r="X169">
+        <v>5.75</v>
+      </c>
+      <c r="Y169">
+        <v>1.1</v>
+      </c>
+      <c r="Z169">
+        <v>1.5</v>
+      </c>
+      <c r="AA169">
+        <v>4.2</v>
+      </c>
+      <c r="AB169">
+        <v>6</v>
+      </c>
+      <c r="AC169">
+        <v>1.05</v>
+      </c>
+      <c r="AD169">
+        <v>9.5</v>
+      </c>
+      <c r="AE169">
+        <v>1.25</v>
+      </c>
+      <c r="AF169">
+        <v>3.75</v>
+      </c>
+      <c r="AG169">
+        <v>1.8</v>
+      </c>
+      <c r="AH169">
+        <v>1.94</v>
+      </c>
+      <c r="AI169">
+        <v>1.95</v>
+      </c>
+      <c r="AJ169">
+        <v>1.8</v>
+      </c>
+      <c r="AK169">
+        <v>1.12</v>
+      </c>
+      <c r="AL169">
+        <v>1.18</v>
+      </c>
+      <c r="AM169">
+        <v>2.4</v>
+      </c>
+      <c r="AN169">
+        <v>1.78</v>
+      </c>
+      <c r="AO169">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP169">
+        <v>1.7</v>
+      </c>
+      <c r="AQ169">
+        <v>0.6</v>
+      </c>
+      <c r="AR169">
+        <v>1.91</v>
+      </c>
+      <c r="AS169">
+        <v>1.01</v>
+      </c>
+      <c r="AT169">
+        <v>2.92</v>
+      </c>
+      <c r="AU169">
+        <v>7</v>
+      </c>
+      <c r="AV169">
+        <v>3</v>
+      </c>
+      <c r="AW169">
+        <v>11</v>
+      </c>
+      <c r="AX169">
+        <v>4</v>
+      </c>
+      <c r="AY169">
+        <v>22</v>
+      </c>
+      <c r="AZ169">
+        <v>7</v>
+      </c>
+      <c r="BA169">
+        <v>5</v>
+      </c>
+      <c r="BB169">
+        <v>6</v>
+      </c>
+      <c r="BC169">
+        <v>11</v>
+      </c>
+      <c r="BD169">
+        <v>1.24</v>
+      </c>
+      <c r="BE169">
+        <v>8</v>
+      </c>
+      <c r="BF169">
+        <v>4.3</v>
+      </c>
+      <c r="BG169">
+        <v>1.23</v>
+      </c>
+      <c r="BH169">
+        <v>3.5</v>
+      </c>
+      <c r="BI169">
+        <v>1.41</v>
+      </c>
+      <c r="BJ169">
+        <v>2.55</v>
+      </c>
+      <c r="BK169">
+        <v>2.1</v>
+      </c>
+      <c r="BL169">
+        <v>2.05</v>
+      </c>
+      <c r="BM169">
+        <v>2.05</v>
+      </c>
+      <c r="BN169">
+        <v>1.7</v>
+      </c>
+      <c r="BO169">
+        <v>2.55</v>
+      </c>
+      <c r="BP169">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7450813</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45690.44791666666</v>
+      </c>
+      <c r="F170">
+        <v>19</v>
+      </c>
+      <c r="G170" t="s">
+        <v>70</v>
+      </c>
+      <c r="H170" t="s">
+        <v>81</v>
+      </c>
+      <c r="I170">
+        <v>5</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>5</v>
+      </c>
+      <c r="L170">
+        <v>5</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>5</v>
+      </c>
+      <c r="O170" t="s">
+        <v>208</v>
+      </c>
+      <c r="P170" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q170">
+        <v>2.3</v>
+      </c>
+      <c r="R170">
+        <v>2.38</v>
+      </c>
+      <c r="S170">
+        <v>4.5</v>
+      </c>
+      <c r="T170">
+        <v>1.28</v>
+      </c>
+      <c r="U170">
+        <v>3.3</v>
+      </c>
+      <c r="V170">
+        <v>2.3</v>
+      </c>
+      <c r="W170">
+        <v>1.55</v>
+      </c>
+      <c r="X170">
+        <v>5</v>
+      </c>
+      <c r="Y170">
+        <v>1.13</v>
+      </c>
+      <c r="Z170">
+        <v>1.73</v>
+      </c>
+      <c r="AA170">
+        <v>3.96</v>
+      </c>
+      <c r="AB170">
+        <v>4.2</v>
+      </c>
+      <c r="AC170">
+        <v>1.04</v>
+      </c>
+      <c r="AD170">
+        <v>10</v>
+      </c>
+      <c r="AE170">
+        <v>1.2</v>
+      </c>
+      <c r="AF170">
+        <v>4.33</v>
+      </c>
+      <c r="AG170">
+        <v>1.55</v>
+      </c>
+      <c r="AH170">
+        <v>2.2</v>
+      </c>
+      <c r="AI170">
+        <v>1.62</v>
+      </c>
+      <c r="AJ170">
+        <v>2.2</v>
+      </c>
+      <c r="AK170">
+        <v>1.2</v>
+      </c>
+      <c r="AL170">
+        <v>1.2</v>
+      </c>
+      <c r="AM170">
+        <v>2.05</v>
+      </c>
+      <c r="AN170">
+        <v>2</v>
+      </c>
+      <c r="AO170">
+        <v>1</v>
+      </c>
+      <c r="AP170">
+        <v>2.1</v>
+      </c>
+      <c r="AQ170">
+        <v>0.9</v>
+      </c>
+      <c r="AR170">
+        <v>1.79</v>
+      </c>
+      <c r="AS170">
+        <v>1.45</v>
+      </c>
+      <c r="AT170">
+        <v>3.24</v>
+      </c>
+      <c r="AU170">
+        <v>10</v>
+      </c>
+      <c r="AV170">
+        <v>3</v>
+      </c>
+      <c r="AW170">
+        <v>3</v>
+      </c>
+      <c r="AX170">
+        <v>3</v>
+      </c>
+      <c r="AY170">
+        <v>13</v>
+      </c>
+      <c r="AZ170">
+        <v>6</v>
+      </c>
+      <c r="BA170">
+        <v>7</v>
+      </c>
+      <c r="BB170">
+        <v>2</v>
+      </c>
+      <c r="BC170">
+        <v>9</v>
+      </c>
+      <c r="BD170">
+        <v>1.63</v>
+      </c>
+      <c r="BE170">
+        <v>6.5</v>
+      </c>
+      <c r="BF170">
+        <v>2.55</v>
+      </c>
+      <c r="BG170">
+        <v>1.32</v>
+      </c>
+      <c r="BH170">
+        <v>2.9</v>
+      </c>
+      <c r="BI170">
+        <v>1.56</v>
+      </c>
+      <c r="BJ170">
+        <v>2.18</v>
+      </c>
+      <c r="BK170">
+        <v>2.38</v>
+      </c>
+      <c r="BL170">
+        <v>1.85</v>
+      </c>
+      <c r="BM170">
+        <v>2.43</v>
+      </c>
+      <c r="BN170">
+        <v>1.45</v>
+      </c>
+      <c r="BO170">
+        <v>3.15</v>
+      </c>
+      <c r="BP170">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="291">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,9 @@
     <t>['5', '7', '10', '33', '45']</t>
   </si>
   <si>
+    <t>['40']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -868,9 +871,6 @@
     <t>['13']</t>
   </si>
   <si>
-    <t>['40']</t>
-  </si>
-  <si>
     <t>['32', '74']</t>
   </si>
   <si>
@@ -884,6 +884,9 @@
   </si>
   <si>
     <t>['52']</t>
+  </si>
+  <si>
+    <t>['22']</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP170"/>
+  <dimension ref="A1:BP171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1913,7 +1916,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2200,7 +2203,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ5">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2403,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0.6</v>
@@ -2531,7 +2534,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2943,7 +2946,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3355,7 +3358,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3561,7 +3564,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3767,7 +3770,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3973,7 +3976,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4179,7 +4182,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4385,7 +4388,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5621,7 +5624,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6239,7 +6242,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6320,7 +6323,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR25">
         <v>1</v>
@@ -6445,7 +6448,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6523,7 +6526,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>1.22</v>
@@ -6651,7 +6654,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6857,7 +6860,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7269,7 +7272,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7681,7 +7684,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7887,7 +7890,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8299,7 +8302,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8917,7 +8920,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9123,7 +9126,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9616,7 +9619,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ41">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR41">
         <v>2.02</v>
@@ -9741,7 +9744,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9819,7 +9822,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
         <v>0.9</v>
@@ -10359,7 +10362,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10565,7 +10568,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10977,7 +10980,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11389,7 +11392,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12213,7 +12216,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12419,7 +12422,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12706,7 +12709,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ56">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -13037,7 +13040,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13243,7 +13246,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13449,7 +13452,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13527,7 +13530,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>1.56</v>
@@ -13655,7 +13658,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14273,7 +14276,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14685,7 +14688,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15587,7 +15590,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>2.2</v>
@@ -15796,7 +15799,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ71">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16127,7 +16130,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16333,7 +16336,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17569,7 +17572,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18677,7 +18680,7 @@
         <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ85">
         <v>1.56</v>
@@ -19011,7 +19014,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19217,7 +19220,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19423,7 +19426,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19629,7 +19632,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19835,7 +19838,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -19916,7 +19919,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ91">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20247,7 +20250,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20453,7 +20456,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20659,7 +20662,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20865,7 +20868,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21483,7 +21486,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21689,7 +21692,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21895,7 +21898,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22101,7 +22104,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22307,7 +22310,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22719,7 +22722,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23337,7 +23340,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23543,7 +23546,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23955,7 +23958,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24573,7 +24576,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24860,7 +24863,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ115">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -24985,7 +24988,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25191,7 +25194,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25269,7 +25272,7 @@
         <v>1.4</v>
       </c>
       <c r="AP117">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>1.22</v>
@@ -25603,7 +25606,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26221,7 +26224,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26427,7 +26430,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26711,7 +26714,7 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ124">
         <v>0.9</v>
@@ -26839,7 +26842,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26920,7 +26923,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ125">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR125">
         <v>1.75</v>
@@ -27251,7 +27254,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27457,7 +27460,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27869,7 +27872,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28281,7 +28284,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28693,7 +28696,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28899,7 +28902,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29105,7 +29108,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29311,7 +29314,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29517,7 +29520,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29929,7 +29932,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30007,7 +30010,7 @@
         <v>2.57</v>
       </c>
       <c r="AP140">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ140">
         <v>2.11</v>
@@ -30135,7 +30138,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30422,7 +30425,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ142">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR142">
         <v>1.61</v>
@@ -31783,7 +31786,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31989,7 +31992,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32195,7 +32198,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32401,7 +32404,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33019,7 +33022,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33431,7 +33434,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>284</v>
+        <v>209</v>
       </c>
       <c r="Q157">
         <v>2.63</v>
@@ -35172,22 +35175,22 @@
         <v>3.42</v>
       </c>
       <c r="AU165">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV165">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW165">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX165">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY165">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ165">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA165">
         <v>7</v>
@@ -36266,6 +36269,212 @@
       </c>
       <c r="BP170">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7450815</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45690.5625</v>
+      </c>
+      <c r="F171">
+        <v>19</v>
+      </c>
+      <c r="G171" t="s">
+        <v>74</v>
+      </c>
+      <c r="H171" t="s">
+        <v>85</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>2</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>2</v>
+      </c>
+      <c r="O171" t="s">
+        <v>209</v>
+      </c>
+      <c r="P171" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q171">
+        <v>2.1</v>
+      </c>
+      <c r="R171">
+        <v>2.3</v>
+      </c>
+      <c r="S171">
+        <v>6</v>
+      </c>
+      <c r="T171">
+        <v>1.33</v>
+      </c>
+      <c r="U171">
+        <v>3.1</v>
+      </c>
+      <c r="V171">
+        <v>2.45</v>
+      </c>
+      <c r="W171">
+        <v>1.48</v>
+      </c>
+      <c r="X171">
+        <v>5.75</v>
+      </c>
+      <c r="Y171">
+        <v>1.1</v>
+      </c>
+      <c r="Z171">
+        <v>1.51</v>
+      </c>
+      <c r="AA171">
+        <v>4.2</v>
+      </c>
+      <c r="AB171">
+        <v>5.9</v>
+      </c>
+      <c r="AC171">
+        <v>1.05</v>
+      </c>
+      <c r="AD171">
+        <v>9.5</v>
+      </c>
+      <c r="AE171">
+        <v>1.25</v>
+      </c>
+      <c r="AF171">
+        <v>3.8</v>
+      </c>
+      <c r="AG171">
+        <v>1.77</v>
+      </c>
+      <c r="AH171">
+        <v>1.98</v>
+      </c>
+      <c r="AI171">
+        <v>1.95</v>
+      </c>
+      <c r="AJ171">
+        <v>1.8</v>
+      </c>
+      <c r="AK171">
+        <v>1.11</v>
+      </c>
+      <c r="AL171">
+        <v>1.18</v>
+      </c>
+      <c r="AM171">
+        <v>2.55</v>
+      </c>
+      <c r="AN171">
+        <v>2.11</v>
+      </c>
+      <c r="AO171">
+        <v>1.11</v>
+      </c>
+      <c r="AP171">
+        <v>2</v>
+      </c>
+      <c r="AQ171">
+        <v>1.1</v>
+      </c>
+      <c r="AR171">
+        <v>1.72</v>
+      </c>
+      <c r="AS171">
+        <v>1.47</v>
+      </c>
+      <c r="AT171">
+        <v>3.19</v>
+      </c>
+      <c r="AU171">
+        <v>4</v>
+      </c>
+      <c r="AV171">
+        <v>2</v>
+      </c>
+      <c r="AW171">
+        <v>3</v>
+      </c>
+      <c r="AX171">
+        <v>3</v>
+      </c>
+      <c r="AY171">
+        <v>14</v>
+      </c>
+      <c r="AZ171">
+        <v>9</v>
+      </c>
+      <c r="BA171">
+        <v>4</v>
+      </c>
+      <c r="BB171">
+        <v>4</v>
+      </c>
+      <c r="BC171">
+        <v>8</v>
+      </c>
+      <c r="BD171">
+        <v>1.44</v>
+      </c>
+      <c r="BE171">
+        <v>6.75</v>
+      </c>
+      <c r="BF171">
+        <v>3.15</v>
+      </c>
+      <c r="BG171">
+        <v>1.36</v>
+      </c>
+      <c r="BH171">
+        <v>2.75</v>
+      </c>
+      <c r="BI171">
+        <v>1.64</v>
+      </c>
+      <c r="BJ171">
+        <v>2.05</v>
+      </c>
+      <c r="BK171">
+        <v>2.38</v>
+      </c>
+      <c r="BL171">
+        <v>1.85</v>
+      </c>
+      <c r="BM171">
+        <v>2.63</v>
+      </c>
+      <c r="BN171">
+        <v>1.38</v>
+      </c>
+      <c r="BO171">
+        <v>3.45</v>
+      </c>
+      <c r="BP171">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="292">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -888,6 +888,9 @@
   <si>
     <t>['22']</t>
   </si>
+  <si>
+    <t>['14', '26', '85']</t>
+  </si>
 </sst>
 </file>
 
@@ -1248,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1788,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ3">
         <v>0.7</v>
@@ -2615,7 +2618,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ7">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -6529,7 +6532,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -9616,7 +9619,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ41">
         <v>1.1</v>
@@ -10237,7 +10240,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ44">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -11882,7 +11885,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ52">
         <v>1.44</v>
@@ -12297,7 +12300,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ54">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR54">
         <v>1.89</v>
@@ -16623,7 +16626,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ75">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -20946,7 +20949,7 @@
         <v>2.4</v>
       </c>
       <c r="AP96">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ96">
         <v>2.11</v>
@@ -21155,7 +21158,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ97">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21567,7 +21570,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ99">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR99">
         <v>1.36</v>
@@ -23418,7 +23421,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ108">
         <v>0.4</v>
@@ -24242,7 +24245,7 @@
         <v>2.67</v>
       </c>
       <c r="AP112">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ112">
         <v>2.2</v>
@@ -26099,7 +26102,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ121">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR121">
         <v>1.57</v>
@@ -28362,7 +28365,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ132">
         <v>1.56</v>
@@ -30631,7 +30634,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ143">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR143">
         <v>1.98</v>
@@ -31452,7 +31455,7 @@
         <v>0.25</v>
       </c>
       <c r="AP147">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ147">
         <v>0.6</v>
@@ -34748,7 +34751,7 @@
         <v>0.75</v>
       </c>
       <c r="AP163">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ163">
         <v>0.9</v>
@@ -36475,6 +36478,212 @@
       </c>
       <c r="BP171">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7450818</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45691.625</v>
+      </c>
+      <c r="F172">
+        <v>19</v>
+      </c>
+      <c r="G172" t="s">
+        <v>71</v>
+      </c>
+      <c r="H172" t="s">
+        <v>84</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>2</v>
+      </c>
+      <c r="K172">
+        <v>3</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <v>3</v>
+      </c>
+      <c r="N172">
+        <v>4</v>
+      </c>
+      <c r="O172" t="s">
+        <v>149</v>
+      </c>
+      <c r="P172" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q172">
+        <v>3.6</v>
+      </c>
+      <c r="R172">
+        <v>1.91</v>
+      </c>
+      <c r="S172">
+        <v>3.6</v>
+      </c>
+      <c r="T172">
+        <v>1.58</v>
+      </c>
+      <c r="U172">
+        <v>2.26</v>
+      </c>
+      <c r="V172">
+        <v>3.6</v>
+      </c>
+      <c r="W172">
+        <v>1.25</v>
+      </c>
+      <c r="X172">
+        <v>9.5</v>
+      </c>
+      <c r="Y172">
+        <v>1.03</v>
+      </c>
+      <c r="Z172">
+        <v>2.73</v>
+      </c>
+      <c r="AA172">
+        <v>2.88</v>
+      </c>
+      <c r="AB172">
+        <v>2.81</v>
+      </c>
+      <c r="AC172">
+        <v>1.11</v>
+      </c>
+      <c r="AD172">
+        <v>6.5</v>
+      </c>
+      <c r="AE172">
+        <v>1.48</v>
+      </c>
+      <c r="AF172">
+        <v>2.37</v>
+      </c>
+      <c r="AG172">
+        <v>2.56</v>
+      </c>
+      <c r="AH172">
+        <v>1.45</v>
+      </c>
+      <c r="AI172">
+        <v>2.1</v>
+      </c>
+      <c r="AJ172">
+        <v>1.67</v>
+      </c>
+      <c r="AK172">
+        <v>1.42</v>
+      </c>
+      <c r="AL172">
+        <v>1.33</v>
+      </c>
+      <c r="AM172">
+        <v>1.45</v>
+      </c>
+      <c r="AN172">
+        <v>0.78</v>
+      </c>
+      <c r="AO172">
+        <v>1.22</v>
+      </c>
+      <c r="AP172">
+        <v>0.7</v>
+      </c>
+      <c r="AQ172">
+        <v>1.4</v>
+      </c>
+      <c r="AR172">
+        <v>1.47</v>
+      </c>
+      <c r="AS172">
+        <v>1.31</v>
+      </c>
+      <c r="AT172">
+        <v>2.78</v>
+      </c>
+      <c r="AU172">
+        <v>7</v>
+      </c>
+      <c r="AV172">
+        <v>9</v>
+      </c>
+      <c r="AW172">
+        <v>3</v>
+      </c>
+      <c r="AX172">
+        <v>6</v>
+      </c>
+      <c r="AY172">
+        <v>11</v>
+      </c>
+      <c r="AZ172">
+        <v>17</v>
+      </c>
+      <c r="BA172">
+        <v>5</v>
+      </c>
+      <c r="BB172">
+        <v>2</v>
+      </c>
+      <c r="BC172">
+        <v>7</v>
+      </c>
+      <c r="BD172">
+        <v>1.95</v>
+      </c>
+      <c r="BE172">
+        <v>6.1</v>
+      </c>
+      <c r="BF172">
+        <v>2.07</v>
+      </c>
+      <c r="BG172">
+        <v>1.53</v>
+      </c>
+      <c r="BH172">
+        <v>2.25</v>
+      </c>
+      <c r="BI172">
+        <v>1.89</v>
+      </c>
+      <c r="BJ172">
+        <v>1.75</v>
+      </c>
+      <c r="BK172">
+        <v>2.45</v>
+      </c>
+      <c r="BL172">
+        <v>1.45</v>
+      </c>
+      <c r="BM172">
+        <v>3.25</v>
+      </c>
+      <c r="BN172">
+        <v>1.26</v>
+      </c>
+      <c r="BO172">
+        <v>4.4</v>
+      </c>
+      <c r="BP172">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="293">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,9 @@
     <t>['40']</t>
   </si>
   <si>
+    <t>['22', '29']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1251,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1919,7 +1922,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2537,7 +2540,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2949,7 +2952,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3233,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ10">
         <v>0.9</v>
@@ -3361,7 +3364,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3567,7 +3570,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3773,7 +3776,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3851,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ13">
         <v>1.22</v>
@@ -3979,7 +3982,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4060,7 +4063,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ14">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4185,7 +4188,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4391,7 +4394,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5627,7 +5630,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6245,7 +6248,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6451,7 +6454,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6657,7 +6660,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6863,7 +6866,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7275,7 +7278,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7687,7 +7690,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7893,7 +7896,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8305,7 +8308,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8923,7 +8926,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9129,7 +9132,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9747,7 +9750,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10237,7 +10240,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ44">
         <v>1.4</v>
@@ -10365,7 +10368,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10571,7 +10574,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10983,7 +10986,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11395,7 +11398,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11476,7 +11479,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR50">
         <v>1.73</v>
@@ -12219,7 +12222,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12425,7 +12428,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12503,7 +12506,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ55">
         <v>1.56</v>
@@ -13043,7 +13046,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13249,7 +13252,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13455,7 +13458,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13661,7 +13664,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14279,7 +14282,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14691,7 +14694,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14978,7 +14981,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ67">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR67">
         <v>1.96</v>
@@ -16133,7 +16136,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16339,7 +16342,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17035,7 +17038,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ77">
         <v>1.56</v>
@@ -17575,7 +17578,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17656,7 +17659,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ80">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR80">
         <v>1.47</v>
@@ -19017,7 +19020,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19223,7 +19226,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19304,7 +19307,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ88">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR88">
         <v>1.53</v>
@@ -19429,7 +19432,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19635,7 +19638,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19841,7 +19844,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20125,7 +20128,7 @@
         <v>0.8</v>
       </c>
       <c r="AP92">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ92">
         <v>0.7</v>
@@ -20253,7 +20256,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20459,7 +20462,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20665,7 +20668,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20871,7 +20874,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21489,7 +21492,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21695,7 +21698,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21901,7 +21904,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22107,7 +22110,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22188,7 +22191,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ102">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR102">
         <v>1.67</v>
@@ -22313,7 +22316,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22725,7 +22728,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23343,7 +23346,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23549,7 +23552,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23961,7 +23964,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24579,7 +24582,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24657,7 +24660,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ114">
         <v>0.6</v>
@@ -24991,7 +24994,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25197,7 +25200,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25609,7 +25612,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26227,7 +26230,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26308,7 +26311,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ122">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR122">
         <v>2.04</v>
@@ -26433,7 +26436,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26845,7 +26848,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27257,7 +27260,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27463,7 +27466,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27875,7 +27878,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28287,7 +28290,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28571,7 +28574,7 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ133">
         <v>0.6</v>
@@ -28699,7 +28702,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28905,7 +28908,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29111,7 +29114,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29317,7 +29320,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29523,7 +29526,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29935,7 +29938,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30141,7 +30144,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31789,7 +31792,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31995,7 +31998,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32201,7 +32204,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32282,7 +32285,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ151">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR151">
         <v>1.81</v>
@@ -32407,7 +32410,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32485,7 +32488,7 @@
         <v>1.29</v>
       </c>
       <c r="AP152">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ152">
         <v>1.44</v>
@@ -33025,7 +33028,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33643,7 +33646,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34055,7 +34058,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34136,7 +34139,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ160">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR160">
         <v>1.51</v>
@@ -34261,7 +34264,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34673,7 +34676,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35085,7 +35088,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36321,7 +36324,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36527,7 +36530,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36684,6 +36687,212 @@
       </c>
       <c r="BP172">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7450826</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45695.58333333334</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>78</v>
+      </c>
+      <c r="H173" t="s">
+        <v>70</v>
+      </c>
+      <c r="I173">
+        <v>2</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>3</v>
+      </c>
+      <c r="L173">
+        <v>2</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>3</v>
+      </c>
+      <c r="O173" t="s">
+        <v>210</v>
+      </c>
+      <c r="P173" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q173">
+        <v>3</v>
+      </c>
+      <c r="R173">
+        <v>2.2</v>
+      </c>
+      <c r="S173">
+        <v>2.95</v>
+      </c>
+      <c r="T173">
+        <v>1.31</v>
+      </c>
+      <c r="U173">
+        <v>3.1</v>
+      </c>
+      <c r="V173">
+        <v>2.4</v>
+      </c>
+      <c r="W173">
+        <v>1.5</v>
+      </c>
+      <c r="X173">
+        <v>5.75</v>
+      </c>
+      <c r="Y173">
+        <v>1.12</v>
+      </c>
+      <c r="Z173">
+        <v>2.34</v>
+      </c>
+      <c r="AA173">
+        <v>3.68</v>
+      </c>
+      <c r="AB173">
+        <v>2.7</v>
+      </c>
+      <c r="AC173">
+        <v>1.05</v>
+      </c>
+      <c r="AD173">
+        <v>9.5</v>
+      </c>
+      <c r="AE173">
+        <v>1.22</v>
+      </c>
+      <c r="AF173">
+        <v>4</v>
+      </c>
+      <c r="AG173">
+        <v>1.67</v>
+      </c>
+      <c r="AH173">
+        <v>2</v>
+      </c>
+      <c r="AI173">
+        <v>1.57</v>
+      </c>
+      <c r="AJ173">
+        <v>2.2</v>
+      </c>
+      <c r="AK173">
+        <v>1.5</v>
+      </c>
+      <c r="AL173">
+        <v>1.28</v>
+      </c>
+      <c r="AM173">
+        <v>1.47</v>
+      </c>
+      <c r="AN173">
+        <v>1.67</v>
+      </c>
+      <c r="AO173">
+        <v>1.89</v>
+      </c>
+      <c r="AP173">
+        <v>1.8</v>
+      </c>
+      <c r="AQ173">
+        <v>1.7</v>
+      </c>
+      <c r="AR173">
+        <v>1.71</v>
+      </c>
+      <c r="AS173">
+        <v>1.28</v>
+      </c>
+      <c r="AT173">
+        <v>2.99</v>
+      </c>
+      <c r="AU173">
+        <v>3</v>
+      </c>
+      <c r="AV173">
+        <v>3</v>
+      </c>
+      <c r="AW173">
+        <v>3</v>
+      </c>
+      <c r="AX173">
+        <v>3</v>
+      </c>
+      <c r="AY173">
+        <v>6</v>
+      </c>
+      <c r="AZ173">
+        <v>7</v>
+      </c>
+      <c r="BA173">
+        <v>3</v>
+      </c>
+      <c r="BB173">
+        <v>5</v>
+      </c>
+      <c r="BC173">
+        <v>8</v>
+      </c>
+      <c r="BD173">
+        <v>2.2</v>
+      </c>
+      <c r="BE173">
+        <v>6.4</v>
+      </c>
+      <c r="BF173">
+        <v>1.81</v>
+      </c>
+      <c r="BG173">
+        <v>1.33</v>
+      </c>
+      <c r="BH173">
+        <v>2.85</v>
+      </c>
+      <c r="BI173">
+        <v>1.58</v>
+      </c>
+      <c r="BJ173">
+        <v>2.14</v>
+      </c>
+      <c r="BK173">
+        <v>1.95</v>
+      </c>
+      <c r="BL173">
+        <v>1.71</v>
+      </c>
+      <c r="BM173">
+        <v>2.48</v>
+      </c>
+      <c r="BN173">
+        <v>1.44</v>
+      </c>
+      <c r="BO173">
+        <v>3.25</v>
+      </c>
+      <c r="BP173">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -649,6 +649,9 @@
     <t>['22', '29']</t>
   </si>
   <si>
+    <t>['8', '48', '61']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1254,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1922,7 +1925,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2206,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ5">
         <v>1.1</v>
@@ -2540,7 +2543,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2827,7 +2830,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ8">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2952,7 +2955,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3364,7 +3367,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3445,7 +3448,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ11">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3570,7 +3573,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3776,7 +3779,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3982,7 +3985,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4188,7 +4191,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4394,7 +4397,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5630,7 +5633,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6248,7 +6251,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6454,7 +6457,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6660,7 +6663,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6866,7 +6869,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6947,7 +6950,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ28">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR28">
         <v>2.08</v>
@@ -7278,7 +7281,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7562,7 +7565,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ31">
         <v>0.4</v>
@@ -7690,7 +7693,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7896,7 +7899,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8308,7 +8311,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8926,7 +8929,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9132,7 +9135,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9416,7 +9419,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ40">
         <v>0.9</v>
@@ -9750,7 +9753,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10368,7 +10371,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10574,7 +10577,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10986,7 +10989,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11067,7 +11070,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ48">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR48">
         <v>0.96</v>
@@ -11398,7 +11401,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12222,7 +12225,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12428,7 +12431,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13046,7 +13049,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13252,7 +13255,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13458,7 +13461,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13664,7 +13667,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13742,7 +13745,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ61">
         <v>0.33</v>
@@ -14157,7 +14160,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -14282,7 +14285,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14694,7 +14697,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -16008,7 +16011,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ72">
         <v>1.44</v>
@@ -16136,7 +16139,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16342,7 +16345,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17578,7 +17581,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18689,7 +18692,7 @@
         <v>2</v>
       </c>
       <c r="AQ85">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR85">
         <v>1.53</v>
@@ -19020,7 +19023,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19226,7 +19229,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19432,7 +19435,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19638,7 +19641,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19844,7 +19847,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20256,7 +20259,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20462,7 +20465,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20668,7 +20671,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20874,7 +20877,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21158,7 +21161,7 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ97">
         <v>1.4</v>
@@ -21492,7 +21495,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21698,7 +21701,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21904,7 +21907,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22110,7 +22113,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22316,7 +22319,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22728,7 +22731,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23346,7 +23349,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23552,7 +23555,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23836,7 +23839,7 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ110">
         <v>0.6</v>
@@ -23964,7 +23967,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24582,7 +24585,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24994,7 +24997,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25075,7 +25078,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ116">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR116">
         <v>1.38</v>
@@ -25200,7 +25203,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25612,7 +25615,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26230,7 +26233,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26436,7 +26439,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26848,7 +26851,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27260,7 +27263,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27466,7 +27469,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27544,7 +27547,7 @@
         <v>0.5</v>
       </c>
       <c r="AP128">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ128">
         <v>0.9</v>
@@ -27878,7 +27881,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28290,7 +28293,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28371,7 +28374,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ132">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR132">
         <v>1.49</v>
@@ -28702,7 +28705,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28908,7 +28911,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29114,7 +29117,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29320,7 +29323,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29526,7 +29529,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29938,7 +29941,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30144,7 +30147,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31792,7 +31795,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31998,7 +32001,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32079,7 +32082,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ150">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR150">
         <v>1.43</v>
@@ -32204,7 +32207,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32282,7 +32285,7 @@
         <v>2.14</v>
       </c>
       <c r="AP151">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ151">
         <v>1.7</v>
@@ -32410,7 +32413,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33028,7 +33031,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33646,7 +33649,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34058,7 +34061,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34264,7 +34267,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34676,7 +34679,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35088,7 +35091,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35784,7 +35787,7 @@
         <v>0.67</v>
       </c>
       <c r="AP168">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ168">
         <v>0.6</v>
@@ -36324,7 +36327,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36530,7 +36533,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36893,6 +36896,212 @@
       </c>
       <c r="BP173">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7450822</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45695.6875</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>73</v>
+      </c>
+      <c r="H174" t="s">
+        <v>87</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>3</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>3</v>
+      </c>
+      <c r="O174" t="s">
+        <v>211</v>
+      </c>
+      <c r="P174" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q174">
+        <v>2.55</v>
+      </c>
+      <c r="R174">
+        <v>2.1</v>
+      </c>
+      <c r="S174">
+        <v>3.8</v>
+      </c>
+      <c r="T174">
+        <v>1.35</v>
+      </c>
+      <c r="U174">
+        <v>2.95</v>
+      </c>
+      <c r="V174">
+        <v>2.5</v>
+      </c>
+      <c r="W174">
+        <v>1.47</v>
+      </c>
+      <c r="X174">
+        <v>6</v>
+      </c>
+      <c r="Y174">
+        <v>1.11</v>
+      </c>
+      <c r="Z174">
+        <v>1.81</v>
+      </c>
+      <c r="AA174">
+        <v>3.76</v>
+      </c>
+      <c r="AB174">
+        <v>4</v>
+      </c>
+      <c r="AC174">
+        <v>1.05</v>
+      </c>
+      <c r="AD174">
+        <v>9.5</v>
+      </c>
+      <c r="AE174">
+        <v>1.25</v>
+      </c>
+      <c r="AF174">
+        <v>3.8</v>
+      </c>
+      <c r="AG174">
+        <v>1.79</v>
+      </c>
+      <c r="AH174">
+        <v>1.95</v>
+      </c>
+      <c r="AI174">
+        <v>1.63</v>
+      </c>
+      <c r="AJ174">
+        <v>2.1</v>
+      </c>
+      <c r="AK174">
+        <v>1.28</v>
+      </c>
+      <c r="AL174">
+        <v>1.3</v>
+      </c>
+      <c r="AM174">
+        <v>1.73</v>
+      </c>
+      <c r="AN174">
+        <v>2.5</v>
+      </c>
+      <c r="AO174">
+        <v>1.56</v>
+      </c>
+      <c r="AP174">
+        <v>2.55</v>
+      </c>
+      <c r="AQ174">
+        <v>1.4</v>
+      </c>
+      <c r="AR174">
+        <v>1.83</v>
+      </c>
+      <c r="AS174">
+        <v>1.38</v>
+      </c>
+      <c r="AT174">
+        <v>3.21</v>
+      </c>
+      <c r="AU174">
+        <v>5</v>
+      </c>
+      <c r="AV174">
+        <v>8</v>
+      </c>
+      <c r="AW174">
+        <v>6</v>
+      </c>
+      <c r="AX174">
+        <v>5</v>
+      </c>
+      <c r="AY174">
+        <v>15</v>
+      </c>
+      <c r="AZ174">
+        <v>15</v>
+      </c>
+      <c r="BA174">
+        <v>4</v>
+      </c>
+      <c r="BB174">
+        <v>0</v>
+      </c>
+      <c r="BC174">
+        <v>4</v>
+      </c>
+      <c r="BD174">
+        <v>1.72</v>
+      </c>
+      <c r="BE174">
+        <v>6.4</v>
+      </c>
+      <c r="BF174">
+        <v>2.4</v>
+      </c>
+      <c r="BG174">
+        <v>1.33</v>
+      </c>
+      <c r="BH174">
+        <v>2.85</v>
+      </c>
+      <c r="BI174">
+        <v>1.58</v>
+      </c>
+      <c r="BJ174">
+        <v>2.14</v>
+      </c>
+      <c r="BK174">
+        <v>1.94</v>
+      </c>
+      <c r="BL174">
+        <v>1.71</v>
+      </c>
+      <c r="BM174">
+        <v>2.48</v>
+      </c>
+      <c r="BN174">
+        <v>1.44</v>
+      </c>
+      <c r="BO174">
+        <v>3.3</v>
+      </c>
+      <c r="BP174">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="296">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -652,6 +652,12 @@
     <t>['8', '48', '61']</t>
   </si>
   <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -868,9 +874,6 @@
     <t>['49', '59', '78', '82']</t>
   </si>
   <si>
-    <t>['54']</t>
-  </si>
-  <si>
     <t>['12', '63']</t>
   </si>
   <si>
@@ -896,6 +899,9 @@
   </si>
   <si>
     <t>['14', '26', '85']</t>
+  </si>
+  <si>
+    <t>['19', '65']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP174"/>
+  <dimension ref="A1:BP176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1925,7 +1931,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2543,7 +2549,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2955,7 +2961,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3367,7 +3373,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3573,7 +3579,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3779,7 +3785,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3860,7 +3866,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ13">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR13">
         <v>1.41</v>
@@ -3985,7 +3991,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4063,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14">
         <v>1.7</v>
@@ -4191,7 +4197,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4397,7 +4403,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4684,7 +4690,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ17">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5093,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19">
         <v>2.11</v>
@@ -5633,7 +5639,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6251,7 +6257,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6457,7 +6463,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6663,7 +6669,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6869,7 +6875,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6947,7 +6953,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ28">
         <v>1.4</v>
@@ -7153,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>1.56</v>
@@ -7281,7 +7287,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7693,7 +7699,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7899,7 +7905,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8186,7 +8192,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ34">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR34">
         <v>1.4</v>
@@ -8311,7 +8317,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8392,7 +8398,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ35">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR35">
         <v>1.34</v>
@@ -8929,7 +8935,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9135,7 +9141,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9753,7 +9759,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10371,7 +10377,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10577,7 +10583,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10989,7 +10995,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11401,7 +11407,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12225,7 +12231,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12303,7 +12309,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ54">
         <v>1.4</v>
@@ -12431,7 +12437,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12924,7 +12930,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ57">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR57">
         <v>1.6</v>
@@ -13049,7 +13055,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13127,7 +13133,7 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ58">
         <v>2.11</v>
@@ -13255,7 +13261,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13461,7 +13467,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13667,7 +13673,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13748,7 +13754,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ61">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR61">
         <v>1.79</v>
@@ -14285,7 +14291,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14697,7 +14703,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15805,7 +15811,7 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ71">
         <v>1.1</v>
@@ -16139,7 +16145,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16345,7 +16351,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16838,7 +16844,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ76">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR76">
         <v>1.53</v>
@@ -17247,7 +17253,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78">
         <v>0.6</v>
@@ -17456,7 +17462,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ79">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR79">
         <v>1.89</v>
@@ -17581,7 +17587,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18277,7 +18283,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ83">
         <v>0.6</v>
@@ -18486,7 +18492,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR84">
         <v>1.58</v>
@@ -19023,7 +19029,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19229,7 +19235,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19435,7 +19441,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19641,7 +19647,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19722,7 +19728,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ90">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR90">
         <v>1.39</v>
@@ -19847,7 +19853,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20259,7 +20265,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20337,7 +20343,7 @@
         <v>2.6</v>
       </c>
       <c r="AP93">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ93">
         <v>2.2</v>
@@ -20465,7 +20471,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20671,7 +20677,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20877,7 +20883,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21495,7 +21501,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21701,7 +21707,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21907,7 +21913,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22113,7 +22119,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22319,7 +22325,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22606,7 +22612,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -22731,7 +22737,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23015,7 +23021,7 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106">
         <v>0.5600000000000001</v>
@@ -23221,7 +23227,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ107">
         <v>0.6</v>
@@ -23349,7 +23355,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23555,7 +23561,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23967,7 +23973,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24585,7 +24591,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24997,7 +25003,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25203,7 +25209,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25284,7 +25290,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
         <v>1.54</v>
@@ -25487,7 +25493,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ118">
         <v>0.4</v>
@@ -25615,7 +25621,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26105,7 +26111,7 @@
         <v>1.43</v>
       </c>
       <c r="AP121">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ121">
         <v>1.4</v>
@@ -26233,7 +26239,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26439,7 +26445,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26851,7 +26857,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27138,7 +27144,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ126">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR126">
         <v>1.67</v>
@@ -27263,7 +27269,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27469,7 +27475,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27881,7 +27887,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -27962,7 +27968,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ130">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR130">
         <v>1.6</v>
@@ -28293,7 +28299,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28705,7 +28711,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28911,7 +28917,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29117,7 +29123,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29323,7 +29329,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29404,7 +29410,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ137">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR137">
         <v>1.82</v>
@@ -29529,7 +29535,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29816,7 +29822,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ139">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR139">
         <v>1.94</v>
@@ -29941,7 +29947,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30147,7 +30153,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30225,7 +30231,7 @@
         <v>0.14</v>
       </c>
       <c r="AP141">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ141">
         <v>0.4</v>
@@ -30431,7 +30437,7 @@
         <v>1.13</v>
       </c>
       <c r="AP142">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ142">
         <v>1.1</v>
@@ -31795,7 +31801,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32001,7 +32007,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32207,7 +32213,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32413,7 +32419,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32903,10 +32909,10 @@
         <v>1.25</v>
       </c>
       <c r="AP154">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ154">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR154">
         <v>1.51</v>
@@ -33031,7 +33037,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33318,7 +33324,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ156">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR156">
         <v>1.39</v>
@@ -33649,7 +33655,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -33727,7 +33733,7 @@
         <v>1.63</v>
       </c>
       <c r="AP158">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
         <v>1.56</v>
@@ -34061,7 +34067,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34267,7 +34273,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34679,7 +34685,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35091,7 +35097,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36327,7 +36333,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36533,7 +36539,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37101,6 +37107,418 @@
         <v>3.3</v>
       </c>
       <c r="BP174">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7450824</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45696.44791666666</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>81</v>
+      </c>
+      <c r="H175" t="s">
+        <v>71</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>1</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>212</v>
+      </c>
+      <c r="P175" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q175">
+        <v>2.88</v>
+      </c>
+      <c r="R175">
+        <v>2.1</v>
+      </c>
+      <c r="S175">
+        <v>3.75</v>
+      </c>
+      <c r="T175">
+        <v>1.44</v>
+      </c>
+      <c r="U175">
+        <v>2.63</v>
+      </c>
+      <c r="V175">
+        <v>3.25</v>
+      </c>
+      <c r="W175">
+        <v>1.33</v>
+      </c>
+      <c r="X175">
+        <v>9</v>
+      </c>
+      <c r="Y175">
+        <v>1.07</v>
+      </c>
+      <c r="Z175">
+        <v>2.41</v>
+      </c>
+      <c r="AA175">
+        <v>3.11</v>
+      </c>
+      <c r="AB175">
+        <v>3.01</v>
+      </c>
+      <c r="AC175">
+        <v>0</v>
+      </c>
+      <c r="AD175">
+        <v>0</v>
+      </c>
+      <c r="AE175">
+        <v>0</v>
+      </c>
+      <c r="AF175">
+        <v>0</v>
+      </c>
+      <c r="AG175">
+        <v>1.95</v>
+      </c>
+      <c r="AH175">
+        <v>1.73</v>
+      </c>
+      <c r="AI175">
+        <v>1.8</v>
+      </c>
+      <c r="AJ175">
+        <v>1.95</v>
+      </c>
+      <c r="AK175">
+        <v>0</v>
+      </c>
+      <c r="AL175">
+        <v>0</v>
+      </c>
+      <c r="AM175">
+        <v>0</v>
+      </c>
+      <c r="AN175">
+        <v>1.22</v>
+      </c>
+      <c r="AO175">
+        <v>0.33</v>
+      </c>
+      <c r="AP175">
+        <v>1.2</v>
+      </c>
+      <c r="AQ175">
+        <v>0.4</v>
+      </c>
+      <c r="AR175">
+        <v>1.56</v>
+      </c>
+      <c r="AS175">
+        <v>1.3</v>
+      </c>
+      <c r="AT175">
+        <v>2.86</v>
+      </c>
+      <c r="AU175">
+        <v>5</v>
+      </c>
+      <c r="AV175">
+        <v>3</v>
+      </c>
+      <c r="AW175">
+        <v>8</v>
+      </c>
+      <c r="AX175">
+        <v>10</v>
+      </c>
+      <c r="AY175">
+        <v>13</v>
+      </c>
+      <c r="AZ175">
+        <v>13</v>
+      </c>
+      <c r="BA175">
+        <v>5</v>
+      </c>
+      <c r="BB175">
+        <v>2</v>
+      </c>
+      <c r="BC175">
+        <v>7</v>
+      </c>
+      <c r="BD175">
+        <v>0</v>
+      </c>
+      <c r="BE175">
+        <v>0</v>
+      </c>
+      <c r="BF175">
+        <v>0</v>
+      </c>
+      <c r="BG175">
+        <v>0</v>
+      </c>
+      <c r="BH175">
+        <v>0</v>
+      </c>
+      <c r="BI175">
+        <v>0</v>
+      </c>
+      <c r="BJ175">
+        <v>0</v>
+      </c>
+      <c r="BK175">
+        <v>2.25</v>
+      </c>
+      <c r="BL175">
+        <v>0</v>
+      </c>
+      <c r="BM175">
+        <v>0</v>
+      </c>
+      <c r="BN175">
+        <v>0</v>
+      </c>
+      <c r="BO175">
+        <v>0</v>
+      </c>
+      <c r="BP175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7450825</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45696.5625</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>86</v>
+      </c>
+      <c r="H176" t="s">
+        <v>72</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>2</v>
+      </c>
+      <c r="N176">
+        <v>3</v>
+      </c>
+      <c r="O176" t="s">
+        <v>213</v>
+      </c>
+      <c r="P176" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q176">
+        <v>1.93</v>
+      </c>
+      <c r="R176">
+        <v>2.3</v>
+      </c>
+      <c r="S176">
+        <v>6</v>
+      </c>
+      <c r="T176">
+        <v>1.33</v>
+      </c>
+      <c r="U176">
+        <v>3</v>
+      </c>
+      <c r="V176">
+        <v>2.45</v>
+      </c>
+      <c r="W176">
+        <v>1.48</v>
+      </c>
+      <c r="X176">
+        <v>5.75</v>
+      </c>
+      <c r="Y176">
+        <v>1.1</v>
+      </c>
+      <c r="Z176">
+        <v>1.54</v>
+      </c>
+      <c r="AA176">
+        <v>4.1</v>
+      </c>
+      <c r="AB176">
+        <v>5.6</v>
+      </c>
+      <c r="AC176">
+        <v>1.05</v>
+      </c>
+      <c r="AD176">
+        <v>9.5</v>
+      </c>
+      <c r="AE176">
+        <v>1.25</v>
+      </c>
+      <c r="AF176">
+        <v>3.8</v>
+      </c>
+      <c r="AG176">
+        <v>1.79</v>
+      </c>
+      <c r="AH176">
+        <v>1.95</v>
+      </c>
+      <c r="AI176">
+        <v>1.85</v>
+      </c>
+      <c r="AJ176">
+        <v>1.83</v>
+      </c>
+      <c r="AK176">
+        <v>1.11</v>
+      </c>
+      <c r="AL176">
+        <v>1.18</v>
+      </c>
+      <c r="AM176">
+        <v>2.55</v>
+      </c>
+      <c r="AN176">
+        <v>1.67</v>
+      </c>
+      <c r="AO176">
+        <v>1.22</v>
+      </c>
+      <c r="AP176">
+        <v>1.5</v>
+      </c>
+      <c r="AQ176">
+        <v>1.4</v>
+      </c>
+      <c r="AR176">
+        <v>1.63</v>
+      </c>
+      <c r="AS176">
+        <v>1.42</v>
+      </c>
+      <c r="AT176">
+        <v>3.05</v>
+      </c>
+      <c r="AU176">
+        <v>8</v>
+      </c>
+      <c r="AV176">
+        <v>6</v>
+      </c>
+      <c r="AW176">
+        <v>8</v>
+      </c>
+      <c r="AX176">
+        <v>10</v>
+      </c>
+      <c r="AY176">
+        <v>22</v>
+      </c>
+      <c r="AZ176">
+        <v>21</v>
+      </c>
+      <c r="BA176">
+        <v>9</v>
+      </c>
+      <c r="BB176">
+        <v>4</v>
+      </c>
+      <c r="BC176">
+        <v>13</v>
+      </c>
+      <c r="BD176">
+        <v>1.46</v>
+      </c>
+      <c r="BE176">
+        <v>6.75</v>
+      </c>
+      <c r="BF176">
+        <v>3.05</v>
+      </c>
+      <c r="BG176">
+        <v>1.34</v>
+      </c>
+      <c r="BH176">
+        <v>2.85</v>
+      </c>
+      <c r="BI176">
+        <v>1.58</v>
+      </c>
+      <c r="BJ176">
+        <v>2.12</v>
+      </c>
+      <c r="BK176">
+        <v>1.95</v>
+      </c>
+      <c r="BL176">
+        <v>1.7</v>
+      </c>
+      <c r="BM176">
+        <v>2.48</v>
+      </c>
+      <c r="BN176">
+        <v>1.44</v>
+      </c>
+      <c r="BO176">
+        <v>3.25</v>
+      </c>
+      <c r="BP176">
         <v>1.26</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="296">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1263,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP176"/>
+  <dimension ref="A1:BP179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3660,7 +3660,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ12">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ15">
         <v>1.56</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ17">
         <v>0.4</v>
@@ -4893,10 +4893,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ18">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ19">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -7365,10 +7365,10 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ30">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR30">
         <v>0.86</v>
@@ -7986,7 +7986,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ33">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR33">
         <v>1.25</v>
@@ -8189,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ34">
         <v>0.4</v>
@@ -8395,7 +8395,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ35">
         <v>1.4</v>
@@ -8810,7 +8810,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ37">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR37">
         <v>1.91</v>
@@ -9016,7 +9016,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ38">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR38">
         <v>1.85</v>
@@ -10455,7 +10455,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ45">
         <v>0.9</v>
@@ -11279,7 +11279,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49">
         <v>0.6</v>
@@ -11900,7 +11900,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ52">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12103,7 +12103,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ53">
         <v>0.4</v>
@@ -13136,7 +13136,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ58">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR58">
         <v>1.71</v>
@@ -13548,7 +13548,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -15193,7 +15193,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ68">
         <v>0.6</v>
@@ -15399,7 +15399,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ69">
         <v>0.6</v>
@@ -16020,7 +16020,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ72">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16226,7 +16226,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ73">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR73">
         <v>1.47</v>
@@ -16635,7 +16635,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ75">
         <v>1.4</v>
@@ -17050,7 +17050,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ77">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR77">
         <v>1.21</v>
@@ -19107,7 +19107,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ87">
         <v>1.56</v>
@@ -19313,7 +19313,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88">
         <v>1.7</v>
@@ -19931,7 +19931,7 @@
         <v>0.6</v>
       </c>
       <c r="AP91">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ91">
         <v>1.1</v>
@@ -20758,7 +20758,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ95">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -20964,7 +20964,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ96">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21376,7 +21376,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ98">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR98">
         <v>1.72</v>
@@ -21579,7 +21579,7 @@
         <v>1.17</v>
       </c>
       <c r="AP99">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ99">
         <v>1.4</v>
@@ -21788,7 +21788,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ100">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR100">
         <v>1.26</v>
@@ -23639,7 +23639,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ109">
         <v>0.7</v>
@@ -24054,7 +24054,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ111">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR111">
         <v>1.46</v>
@@ -25081,7 +25081,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ116">
         <v>1.4</v>
@@ -26526,7 +26526,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ123">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR123">
         <v>1.23</v>
@@ -27347,10 +27347,10 @@
         <v>1.17</v>
       </c>
       <c r="AP127">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ127">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -27759,7 +27759,7 @@
         <v>0.71</v>
       </c>
       <c r="AP129">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ129">
         <v>0.7</v>
@@ -28171,7 +28171,7 @@
         <v>0.71</v>
       </c>
       <c r="AP131">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ131">
         <v>0.6</v>
@@ -28998,7 +28998,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ135">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR135">
         <v>1.91</v>
@@ -29204,7 +29204,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ136">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -30028,7 +30028,7 @@
         <v>2</v>
       </c>
       <c r="AQ140">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR140">
         <v>1.69</v>
@@ -31261,7 +31261,7 @@
         <v>1.86</v>
       </c>
       <c r="AP146">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ146">
         <v>1.56</v>
@@ -31879,7 +31879,7 @@
         <v>2.25</v>
       </c>
       <c r="AP149">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ149">
         <v>2.2</v>
@@ -32085,7 +32085,7 @@
         <v>1.38</v>
       </c>
       <c r="AP150">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ150">
         <v>1.4</v>
@@ -32500,7 +32500,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ152">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR152">
         <v>1.7</v>
@@ -33527,7 +33527,7 @@
         <v>0.5</v>
       </c>
       <c r="AP157">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ157">
         <v>0.4</v>
@@ -33736,7 +33736,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ158">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR158">
         <v>1.55</v>
@@ -33939,10 +33939,10 @@
         <v>2.25</v>
       </c>
       <c r="AP159">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ159">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR159">
         <v>1.47</v>
@@ -34354,7 +34354,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ161">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34557,7 +34557,7 @@
         <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ162">
         <v>0.5600000000000001</v>
@@ -37520,6 +37520,624 @@
       </c>
       <c r="BP176">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7450821</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45696.67708333334</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>84</v>
+      </c>
+      <c r="H177" t="s">
+        <v>74</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>1</v>
+      </c>
+      <c r="O177" t="s">
+        <v>209</v>
+      </c>
+      <c r="P177" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q177">
+        <v>4</v>
+      </c>
+      <c r="R177">
+        <v>2.05</v>
+      </c>
+      <c r="S177">
+        <v>2.88</v>
+      </c>
+      <c r="T177">
+        <v>1.5</v>
+      </c>
+      <c r="U177">
+        <v>2.5</v>
+      </c>
+      <c r="V177">
+        <v>3.4</v>
+      </c>
+      <c r="W177">
+        <v>1.3</v>
+      </c>
+      <c r="X177">
+        <v>10</v>
+      </c>
+      <c r="Y177">
+        <v>1.06</v>
+      </c>
+      <c r="Z177">
+        <v>3.18</v>
+      </c>
+      <c r="AA177">
+        <v>3.13</v>
+      </c>
+      <c r="AB177">
+        <v>2.29</v>
+      </c>
+      <c r="AC177">
+        <v>0</v>
+      </c>
+      <c r="AD177">
+        <v>0</v>
+      </c>
+      <c r="AE177">
+        <v>2.3</v>
+      </c>
+      <c r="AF177">
+        <v>1.61</v>
+      </c>
+      <c r="AG177">
+        <v>2.1</v>
+      </c>
+      <c r="AH177">
+        <v>1.61</v>
+      </c>
+      <c r="AI177">
+        <v>1.95</v>
+      </c>
+      <c r="AJ177">
+        <v>1.8</v>
+      </c>
+      <c r="AK177">
+        <v>0</v>
+      </c>
+      <c r="AL177">
+        <v>0</v>
+      </c>
+      <c r="AM177">
+        <v>0</v>
+      </c>
+      <c r="AN177">
+        <v>1.22</v>
+      </c>
+      <c r="AO177">
+        <v>1.44</v>
+      </c>
+      <c r="AP177">
+        <v>1.4</v>
+      </c>
+      <c r="AQ177">
+        <v>1.3</v>
+      </c>
+      <c r="AR177">
+        <v>1.53</v>
+      </c>
+      <c r="AS177">
+        <v>1.54</v>
+      </c>
+      <c r="AT177">
+        <v>3.07</v>
+      </c>
+      <c r="AU177">
+        <v>4</v>
+      </c>
+      <c r="AV177">
+        <v>2</v>
+      </c>
+      <c r="AW177">
+        <v>2</v>
+      </c>
+      <c r="AX177">
+        <v>4</v>
+      </c>
+      <c r="AY177">
+        <v>7</v>
+      </c>
+      <c r="AZ177">
+        <v>7</v>
+      </c>
+      <c r="BA177">
+        <v>0</v>
+      </c>
+      <c r="BB177">
+        <v>13</v>
+      </c>
+      <c r="BC177">
+        <v>13</v>
+      </c>
+      <c r="BD177">
+        <v>0</v>
+      </c>
+      <c r="BE177">
+        <v>0</v>
+      </c>
+      <c r="BF177">
+        <v>0</v>
+      </c>
+      <c r="BG177">
+        <v>0</v>
+      </c>
+      <c r="BH177">
+        <v>0</v>
+      </c>
+      <c r="BI177">
+        <v>0</v>
+      </c>
+      <c r="BJ177">
+        <v>0</v>
+      </c>
+      <c r="BK177">
+        <v>0</v>
+      </c>
+      <c r="BL177">
+        <v>0</v>
+      </c>
+      <c r="BM177">
+        <v>0</v>
+      </c>
+      <c r="BN177">
+        <v>0</v>
+      </c>
+      <c r="BO177">
+        <v>0</v>
+      </c>
+      <c r="BP177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7450819</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45697.34375</v>
+      </c>
+      <c r="F178">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>85</v>
+      </c>
+      <c r="H178" t="s">
+        <v>77</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
+        <v>206</v>
+      </c>
+      <c r="P178" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q178">
+        <v>3</v>
+      </c>
+      <c r="R178">
+        <v>2.05</v>
+      </c>
+      <c r="S178">
+        <v>3.75</v>
+      </c>
+      <c r="T178">
+        <v>1.44</v>
+      </c>
+      <c r="U178">
+        <v>2.63</v>
+      </c>
+      <c r="V178">
+        <v>3.25</v>
+      </c>
+      <c r="W178">
+        <v>1.33</v>
+      </c>
+      <c r="X178">
+        <v>9</v>
+      </c>
+      <c r="Y178">
+        <v>1.07</v>
+      </c>
+      <c r="Z178">
+        <v>2.2</v>
+      </c>
+      <c r="AA178">
+        <v>3.04</v>
+      </c>
+      <c r="AB178">
+        <v>3.47</v>
+      </c>
+      <c r="AC178">
+        <v>1.07</v>
+      </c>
+      <c r="AD178">
+        <v>8</v>
+      </c>
+      <c r="AE178">
+        <v>1.32</v>
+      </c>
+      <c r="AF178">
+        <v>3.1</v>
+      </c>
+      <c r="AG178">
+        <v>1.93</v>
+      </c>
+      <c r="AH178">
+        <v>1.77</v>
+      </c>
+      <c r="AI178">
+        <v>1.8</v>
+      </c>
+      <c r="AJ178">
+        <v>1.95</v>
+      </c>
+      <c r="AK178">
+        <v>1.35</v>
+      </c>
+      <c r="AL178">
+        <v>1.33</v>
+      </c>
+      <c r="AM178">
+        <v>1.57</v>
+      </c>
+      <c r="AN178">
+        <v>0.89</v>
+      </c>
+      <c r="AO178">
+        <v>1.56</v>
+      </c>
+      <c r="AP178">
+        <v>1.1</v>
+      </c>
+      <c r="AQ178">
+        <v>1.4</v>
+      </c>
+      <c r="AR178">
+        <v>1.4</v>
+      </c>
+      <c r="AS178">
+        <v>1.38</v>
+      </c>
+      <c r="AT178">
+        <v>2.78</v>
+      </c>
+      <c r="AU178">
+        <v>5</v>
+      </c>
+      <c r="AV178">
+        <v>2</v>
+      </c>
+      <c r="AW178">
+        <v>9</v>
+      </c>
+      <c r="AX178">
+        <v>11</v>
+      </c>
+      <c r="AY178">
+        <v>17</v>
+      </c>
+      <c r="AZ178">
+        <v>19</v>
+      </c>
+      <c r="BA178">
+        <v>4</v>
+      </c>
+      <c r="BB178">
+        <v>4</v>
+      </c>
+      <c r="BC178">
+        <v>8</v>
+      </c>
+      <c r="BD178">
+        <v>1.55</v>
+      </c>
+      <c r="BE178">
+        <v>7.3</v>
+      </c>
+      <c r="BF178">
+        <v>2.88</v>
+      </c>
+      <c r="BG178">
+        <v>1.18</v>
+      </c>
+      <c r="BH178">
+        <v>4.2</v>
+      </c>
+      <c r="BI178">
+        <v>1.39</v>
+      </c>
+      <c r="BJ178">
+        <v>2.75</v>
+      </c>
+      <c r="BK178">
+        <v>1.68</v>
+      </c>
+      <c r="BL178">
+        <v>2.02</v>
+      </c>
+      <c r="BM178">
+        <v>2.18</v>
+      </c>
+      <c r="BN178">
+        <v>1.58</v>
+      </c>
+      <c r="BO178">
+        <v>2.95</v>
+      </c>
+      <c r="BP178">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7450827</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45697.44791666666</v>
+      </c>
+      <c r="F179">
+        <v>20</v>
+      </c>
+      <c r="G179" t="s">
+        <v>82</v>
+      </c>
+      <c r="H179" t="s">
+        <v>75</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179">
+        <v>1</v>
+      </c>
+      <c r="K179">
+        <v>2</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>1</v>
+      </c>
+      <c r="N179">
+        <v>2</v>
+      </c>
+      <c r="O179" t="s">
+        <v>177</v>
+      </c>
+      <c r="P179" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q179">
+        <v>3.25</v>
+      </c>
+      <c r="R179">
+        <v>2.2</v>
+      </c>
+      <c r="S179">
+        <v>3.25</v>
+      </c>
+      <c r="T179">
+        <v>1.4</v>
+      </c>
+      <c r="U179">
+        <v>2.75</v>
+      </c>
+      <c r="V179">
+        <v>2.75</v>
+      </c>
+      <c r="W179">
+        <v>1.4</v>
+      </c>
+      <c r="X179">
+        <v>8</v>
+      </c>
+      <c r="Y179">
+        <v>1.08</v>
+      </c>
+      <c r="Z179">
+        <v>2.57</v>
+      </c>
+      <c r="AA179">
+        <v>3.25</v>
+      </c>
+      <c r="AB179">
+        <v>2.68</v>
+      </c>
+      <c r="AC179">
+        <v>1.05</v>
+      </c>
+      <c r="AD179">
+        <v>9</v>
+      </c>
+      <c r="AE179">
+        <v>1.27</v>
+      </c>
+      <c r="AF179">
+        <v>3.45</v>
+      </c>
+      <c r="AG179">
+        <v>1.82</v>
+      </c>
+      <c r="AH179">
+        <v>1.92</v>
+      </c>
+      <c r="AI179">
+        <v>1.67</v>
+      </c>
+      <c r="AJ179">
+        <v>2.1</v>
+      </c>
+      <c r="AK179">
+        <v>1.47</v>
+      </c>
+      <c r="AL179">
+        <v>1.31</v>
+      </c>
+      <c r="AM179">
+        <v>1.47</v>
+      </c>
+      <c r="AN179">
+        <v>1.78</v>
+      </c>
+      <c r="AO179">
+        <v>2.11</v>
+      </c>
+      <c r="AP179">
+        <v>1.7</v>
+      </c>
+      <c r="AQ179">
+        <v>2</v>
+      </c>
+      <c r="AR179">
+        <v>1.4</v>
+      </c>
+      <c r="AS179">
+        <v>1.57</v>
+      </c>
+      <c r="AT179">
+        <v>2.97</v>
+      </c>
+      <c r="AU179">
+        <v>6</v>
+      </c>
+      <c r="AV179">
+        <v>4</v>
+      </c>
+      <c r="AW179">
+        <v>4</v>
+      </c>
+      <c r="AX179">
+        <v>10</v>
+      </c>
+      <c r="AY179">
+        <v>10</v>
+      </c>
+      <c r="AZ179">
+        <v>16</v>
+      </c>
+      <c r="BA179">
+        <v>5</v>
+      </c>
+      <c r="BB179">
+        <v>8</v>
+      </c>
+      <c r="BC179">
+        <v>13</v>
+      </c>
+      <c r="BD179">
+        <v>1.8</v>
+      </c>
+      <c r="BE179">
+        <v>7.1</v>
+      </c>
+      <c r="BF179">
+        <v>2.3</v>
+      </c>
+      <c r="BG179">
+        <v>1.24</v>
+      </c>
+      <c r="BH179">
+        <v>3.4</v>
+      </c>
+      <c r="BI179">
+        <v>1.33</v>
+      </c>
+      <c r="BJ179">
+        <v>2.98</v>
+      </c>
+      <c r="BK179">
+        <v>1.6</v>
+      </c>
+      <c r="BL179">
+        <v>2.15</v>
+      </c>
+      <c r="BM179">
+        <v>2.02</v>
+      </c>
+      <c r="BN179">
+        <v>1.68</v>
+      </c>
+      <c r="BO179">
+        <v>2.7</v>
+      </c>
+      <c r="BP179">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="296">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1263,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP179"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ12">
         <v>1.4</v>
@@ -4278,7 +4278,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ15">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -7162,7 +7162,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR29">
         <v>2.17</v>
@@ -7777,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ32">
         <v>0.6</v>
@@ -9222,7 +9222,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ39">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR39">
         <v>1.41</v>
@@ -10661,7 +10661,7 @@
         <v>2.33</v>
       </c>
       <c r="AP46">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ46">
         <v>2.2</v>
@@ -12518,7 +12518,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ55">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR55">
         <v>1.29</v>
@@ -14575,7 +14575,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ65">
         <v>0.9</v>
@@ -18077,7 +18077,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ82">
         <v>0.9</v>
@@ -19110,7 +19110,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ87">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -21785,7 +21785,7 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ100">
         <v>1.3</v>
@@ -22406,7 +22406,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ103">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR103">
         <v>1.6</v>
@@ -25908,7 +25908,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ120">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR120">
         <v>1.38</v>
@@ -26523,7 +26523,7 @@
         <v>2.5</v>
       </c>
       <c r="AP123">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ123">
         <v>2</v>
@@ -29613,7 +29613,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ138">
         <v>0.5600000000000001</v>
@@ -31264,7 +31264,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ146">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR146">
         <v>1.5</v>
@@ -33118,7 +33118,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ155">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR155">
         <v>1.98</v>
@@ -33321,7 +33321,7 @@
         <v>0.38</v>
       </c>
       <c r="AP156">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ156">
         <v>0.4</v>
@@ -37202,10 +37202,10 @@
         <v>0</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG175">
         <v>1.95</v>
@@ -38138,6 +38138,212 @@
       </c>
       <c r="BP179">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7450820</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45697.5625</v>
+      </c>
+      <c r="F180">
+        <v>20</v>
+      </c>
+      <c r="G180" t="s">
+        <v>80</v>
+      </c>
+      <c r="H180" t="s">
+        <v>76</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+      <c r="N180">
+        <v>1</v>
+      </c>
+      <c r="O180" t="s">
+        <v>149</v>
+      </c>
+      <c r="P180" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q180">
+        <v>5</v>
+      </c>
+      <c r="R180">
+        <v>2.3</v>
+      </c>
+      <c r="S180">
+        <v>2.2</v>
+      </c>
+      <c r="T180">
+        <v>1.33</v>
+      </c>
+      <c r="U180">
+        <v>3.25</v>
+      </c>
+      <c r="V180">
+        <v>2.63</v>
+      </c>
+      <c r="W180">
+        <v>1.44</v>
+      </c>
+      <c r="X180">
+        <v>6.5</v>
+      </c>
+      <c r="Y180">
+        <v>1.11</v>
+      </c>
+      <c r="Z180">
+        <v>5.2</v>
+      </c>
+      <c r="AA180">
+        <v>3.92</v>
+      </c>
+      <c r="AB180">
+        <v>1.61</v>
+      </c>
+      <c r="AC180">
+        <v>1.04</v>
+      </c>
+      <c r="AD180">
+        <v>10</v>
+      </c>
+      <c r="AE180">
+        <v>1.23</v>
+      </c>
+      <c r="AF180">
+        <v>3.8</v>
+      </c>
+      <c r="AG180">
+        <v>1.65</v>
+      </c>
+      <c r="AH180">
+        <v>2.05</v>
+      </c>
+      <c r="AI180">
+        <v>1.75</v>
+      </c>
+      <c r="AJ180">
+        <v>2</v>
+      </c>
+      <c r="AK180">
+        <v>2.2</v>
+      </c>
+      <c r="AL180">
+        <v>1.24</v>
+      </c>
+      <c r="AM180">
+        <v>1.17</v>
+      </c>
+      <c r="AN180">
+        <v>0.89</v>
+      </c>
+      <c r="AO180">
+        <v>1.56</v>
+      </c>
+      <c r="AP180">
+        <v>1.1</v>
+      </c>
+      <c r="AQ180">
+        <v>1.4</v>
+      </c>
+      <c r="AR180">
+        <v>1.4</v>
+      </c>
+      <c r="AS180">
+        <v>1.36</v>
+      </c>
+      <c r="AT180">
+        <v>2.76</v>
+      </c>
+      <c r="AU180">
+        <v>6</v>
+      </c>
+      <c r="AV180">
+        <v>2</v>
+      </c>
+      <c r="AW180">
+        <v>13</v>
+      </c>
+      <c r="AX180">
+        <v>2</v>
+      </c>
+      <c r="AY180">
+        <v>25</v>
+      </c>
+      <c r="AZ180">
+        <v>5</v>
+      </c>
+      <c r="BA180">
+        <v>6</v>
+      </c>
+      <c r="BB180">
+        <v>4</v>
+      </c>
+      <c r="BC180">
+        <v>10</v>
+      </c>
+      <c r="BD180">
+        <v>4.05</v>
+      </c>
+      <c r="BE180">
+        <v>8.4</v>
+      </c>
+      <c r="BF180">
+        <v>1.31</v>
+      </c>
+      <c r="BG180">
+        <v>1.16</v>
+      </c>
+      <c r="BH180">
+        <v>4.5</v>
+      </c>
+      <c r="BI180">
+        <v>1.35</v>
+      </c>
+      <c r="BJ180">
+        <v>2.9</v>
+      </c>
+      <c r="BK180">
+        <v>1.62</v>
+      </c>
+      <c r="BL180">
+        <v>2.12</v>
+      </c>
+      <c r="BM180">
+        <v>2.08</v>
+      </c>
+      <c r="BN180">
+        <v>1.65</v>
+      </c>
+      <c r="BO180">
+        <v>2.78</v>
+      </c>
+      <c r="BP180">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="298">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,9 @@
     <t>['54']</t>
   </si>
   <si>
+    <t>['45']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -902,6 +905,9 @@
   </si>
   <si>
     <t>['19', '65']</t>
+  </si>
+  <si>
+    <t>['47', '56']</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1931,7 +1937,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2424,7 +2430,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2549,7 +2555,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2961,7 +2967,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3373,7 +3379,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3451,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11">
         <v>1.4</v>
@@ -3579,7 +3585,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3785,7 +3791,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3991,7 +3997,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4197,7 +4203,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4403,7 +4409,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5639,7 +5645,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6257,7 +6263,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6463,7 +6469,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6669,7 +6675,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6875,7 +6881,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7287,7 +7293,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7699,7 +7705,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7780,7 +7786,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ32">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR32">
         <v>1.13</v>
@@ -7905,7 +7911,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -7983,7 +7989,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ33">
         <v>1.3</v>
@@ -8317,7 +8323,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8601,7 +8607,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ36">
         <v>0.7</v>
@@ -8935,7 +8941,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9141,7 +9147,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9759,7 +9765,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10377,7 +10383,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10583,7 +10589,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10995,7 +11001,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11282,7 +11288,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ49">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11407,7 +11413,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12231,7 +12237,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12437,7 +12443,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12721,7 +12727,7 @@
         <v>0.67</v>
       </c>
       <c r="AP56">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ56">
         <v>1.1</v>
@@ -13055,7 +13061,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13261,7 +13267,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13467,7 +13473,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13673,7 +13679,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14291,7 +14297,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14703,7 +14709,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15402,7 +15408,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ69">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -16145,7 +16151,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16223,7 +16229,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ73">
         <v>2</v>
@@ -16351,7 +16357,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17256,7 +17262,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR78">
         <v>1.53</v>
@@ -17587,7 +17593,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -19029,7 +19035,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19235,7 +19241,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19441,7 +19447,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19647,7 +19653,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19725,7 +19731,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ90">
         <v>1.4</v>
@@ -19853,7 +19859,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20265,7 +20271,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20471,7 +20477,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20552,7 +20558,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ94">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR94">
         <v>1.85</v>
@@ -20677,7 +20683,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20883,7 +20889,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21501,7 +21507,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21707,7 +21713,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21913,7 +21919,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22119,7 +22125,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22325,7 +22331,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22737,7 +22743,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23355,7 +23361,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23561,7 +23567,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23973,7 +23979,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24591,7 +24597,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24672,7 +24678,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ114">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR114">
         <v>1.55</v>
@@ -25003,7 +25009,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25209,7 +25215,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25621,7 +25627,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -25905,7 +25911,7 @@
         <v>2.17</v>
       </c>
       <c r="AP120">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ120">
         <v>1.4</v>
@@ -26239,7 +26245,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26445,7 +26451,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26857,7 +26863,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27269,7 +27275,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27475,7 +27481,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27887,7 +27893,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28174,7 +28180,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ131">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28299,7 +28305,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28711,7 +28717,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28917,7 +28923,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29123,7 +29129,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29329,7 +29335,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29535,7 +29541,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29947,7 +29953,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30153,7 +30159,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30849,7 +30855,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ144">
         <v>0.9</v>
@@ -31058,7 +31064,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ145">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR145">
         <v>1.63</v>
@@ -31801,7 +31807,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32007,7 +32013,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32419,7 +32425,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33037,7 +33043,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33655,7 +33661,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34067,7 +34073,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34145,7 +34151,7 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ160">
         <v>1.7</v>
@@ -34273,7 +34279,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34685,7 +34691,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35097,7 +35103,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35796,7 +35802,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ168">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR168">
         <v>1.8</v>
@@ -36333,7 +36339,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36539,7 +36545,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37363,7 +37369,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37981,7 +37987,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38344,6 +38350,212 @@
       </c>
       <c r="BP180">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7450823</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45698.625</v>
+      </c>
+      <c r="F181">
+        <v>20</v>
+      </c>
+      <c r="G181" t="s">
+        <v>79</v>
+      </c>
+      <c r="H181" t="s">
+        <v>83</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="M181">
+        <v>2</v>
+      </c>
+      <c r="N181">
+        <v>3</v>
+      </c>
+      <c r="O181" t="s">
+        <v>214</v>
+      </c>
+      <c r="P181" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q181">
+        <v>3.5</v>
+      </c>
+      <c r="R181">
+        <v>2.1</v>
+      </c>
+      <c r="S181">
+        <v>3.1</v>
+      </c>
+      <c r="T181">
+        <v>1.4</v>
+      </c>
+      <c r="U181">
+        <v>2.75</v>
+      </c>
+      <c r="V181">
+        <v>3</v>
+      </c>
+      <c r="W181">
+        <v>1.36</v>
+      </c>
+      <c r="X181">
+        <v>8</v>
+      </c>
+      <c r="Y181">
+        <v>1.08</v>
+      </c>
+      <c r="Z181">
+        <v>3.1</v>
+      </c>
+      <c r="AA181">
+        <v>2.9</v>
+      </c>
+      <c r="AB181">
+        <v>2.48</v>
+      </c>
+      <c r="AC181">
+        <v>1.06</v>
+      </c>
+      <c r="AD181">
+        <v>8.5</v>
+      </c>
+      <c r="AE181">
+        <v>1.29</v>
+      </c>
+      <c r="AF181">
+        <v>3.3</v>
+      </c>
+      <c r="AG181">
+        <v>1.91</v>
+      </c>
+      <c r="AH181">
+        <v>1.83</v>
+      </c>
+      <c r="AI181">
+        <v>1.67</v>
+      </c>
+      <c r="AJ181">
+        <v>2.1</v>
+      </c>
+      <c r="AK181">
+        <v>1.5</v>
+      </c>
+      <c r="AL181">
+        <v>1.32</v>
+      </c>
+      <c r="AM181">
+        <v>1.42</v>
+      </c>
+      <c r="AN181">
+        <v>1.44</v>
+      </c>
+      <c r="AO181">
+        <v>0.6</v>
+      </c>
+      <c r="AP181">
+        <v>1.3</v>
+      </c>
+      <c r="AQ181">
+        <v>0.82</v>
+      </c>
+      <c r="AR181">
+        <v>1.46</v>
+      </c>
+      <c r="AS181">
+        <v>1.39</v>
+      </c>
+      <c r="AT181">
+        <v>2.85</v>
+      </c>
+      <c r="AU181">
+        <v>6</v>
+      </c>
+      <c r="AV181">
+        <v>5</v>
+      </c>
+      <c r="AW181">
+        <v>4</v>
+      </c>
+      <c r="AX181">
+        <v>8</v>
+      </c>
+      <c r="AY181">
+        <v>11</v>
+      </c>
+      <c r="AZ181">
+        <v>15</v>
+      </c>
+      <c r="BA181">
+        <v>6</v>
+      </c>
+      <c r="BB181">
+        <v>8</v>
+      </c>
+      <c r="BC181">
+        <v>14</v>
+      </c>
+      <c r="BD181">
+        <v>2.12</v>
+      </c>
+      <c r="BE181">
+        <v>5.95</v>
+      </c>
+      <c r="BF181">
+        <v>2.05</v>
+      </c>
+      <c r="BG181">
+        <v>1.16</v>
+      </c>
+      <c r="BH181">
+        <v>4.45</v>
+      </c>
+      <c r="BI181">
+        <v>1.34</v>
+      </c>
+      <c r="BJ181">
+        <v>2.92</v>
+      </c>
+      <c r="BK181">
+        <v>1.62</v>
+      </c>
+      <c r="BL181">
+        <v>2.1</v>
+      </c>
+      <c r="BM181">
+        <v>2.1</v>
+      </c>
+      <c r="BN181">
+        <v>1.62</v>
+      </c>
+      <c r="BO181">
+        <v>2.85</v>
+      </c>
+      <c r="BP181">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="299">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,9 @@
     <t>['45']</t>
   </si>
   <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1269,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1937,7 +1940,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2224,7 +2227,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2555,7 +2558,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2633,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ7">
         <v>1.4</v>
@@ -2839,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ8">
         <v>1.4</v>
@@ -2967,7 +2970,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3048,7 +3051,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3379,7 +3382,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3585,7 +3588,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3791,7 +3794,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3997,7 +4000,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4203,7 +4206,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4409,7 +4412,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5645,7 +5648,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5726,7 +5729,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR22">
         <v>2.03</v>
@@ -6135,7 +6138,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ24">
         <v>0.7</v>
@@ -6263,7 +6266,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6344,7 +6347,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR25">
         <v>1</v>
@@ -6469,7 +6472,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6675,7 +6678,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6753,7 +6756,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27">
         <v>0.9</v>
@@ -6881,7 +6884,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7293,7 +7296,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7705,7 +7708,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7911,7 +7914,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8323,7 +8326,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8941,7 +8944,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9147,7 +9150,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9640,7 +9643,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ41">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR41">
         <v>2.02</v>
@@ -9765,7 +9768,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10052,7 +10055,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ43">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10383,7 +10386,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10589,7 +10592,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10670,7 +10673,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ46">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR46">
         <v>1.21</v>
@@ -11001,7 +11004,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11079,7 +11082,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ48">
         <v>1.4</v>
@@ -11413,7 +11416,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11697,7 +11700,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ51">
         <v>0.5600000000000001</v>
@@ -12237,7 +12240,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12443,7 +12446,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12730,7 +12733,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ56">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -13061,7 +13064,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13267,7 +13270,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13473,7 +13476,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13679,7 +13682,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14297,7 +14300,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14709,7 +14712,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14787,7 +14790,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ66">
         <v>0.5600000000000001</v>
@@ -14993,7 +14996,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ67">
         <v>1.7</v>
@@ -15614,7 +15617,7 @@
         <v>2</v>
       </c>
       <c r="AQ70">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15820,7 +15823,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ71">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16151,7 +16154,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16357,7 +16360,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17465,7 +17468,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ79">
         <v>0.4</v>
@@ -17593,7 +17596,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -19035,7 +19038,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19241,7 +19244,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19447,7 +19450,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19525,7 +19528,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ89">
         <v>0.4</v>
@@ -19653,7 +19656,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19859,7 +19862,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -19940,7 +19943,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ91">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20271,7 +20274,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20352,7 +20355,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ93">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR93">
         <v>1.66</v>
@@ -20477,7 +20480,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20683,7 +20686,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20761,7 +20764,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ95">
         <v>1.4</v>
@@ -20889,7 +20892,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21507,7 +21510,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21713,7 +21716,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21919,7 +21922,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22125,7 +22128,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22331,7 +22334,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22409,7 +22412,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ103">
         <v>1.4</v>
@@ -22743,7 +22746,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23361,7 +23364,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23567,7 +23570,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23979,7 +23982,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24057,7 +24060,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ111">
         <v>1.4</v>
@@ -24266,7 +24269,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ112">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR112">
         <v>1.59</v>
@@ -24469,7 +24472,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ113">
         <v>0.9</v>
@@ -24597,7 +24600,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24884,7 +24887,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ115">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25009,7 +25012,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25215,7 +25218,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25627,7 +25630,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26245,7 +26248,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26451,7 +26454,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26863,7 +26866,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26944,7 +26947,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ125">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR125">
         <v>1.75</v>
@@ -27275,7 +27278,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27481,7 +27484,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27893,7 +27896,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -27971,7 +27974,7 @@
         <v>1.17</v>
       </c>
       <c r="AP130">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ130">
         <v>1.4</v>
@@ -28305,7 +28308,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28717,7 +28720,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28798,7 +28801,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ134">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR134">
         <v>1.7</v>
@@ -28923,7 +28926,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29001,7 +29004,7 @@
         <v>1.5</v>
       </c>
       <c r="AP135">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ135">
         <v>1.3</v>
@@ -29129,7 +29132,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29335,7 +29338,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29541,7 +29544,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29825,7 +29828,7 @@
         <v>1.43</v>
       </c>
       <c r="AP139">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ139">
         <v>1.4</v>
@@ -29953,7 +29956,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30159,7 +30162,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30446,7 +30449,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ142">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR142">
         <v>1.61</v>
@@ -31061,7 +31064,7 @@
         <v>0.63</v>
       </c>
       <c r="AP145">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ145">
         <v>0.82</v>
@@ -31807,7 +31810,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31888,7 +31891,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ149">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR149">
         <v>1.41</v>
@@ -32013,7 +32016,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32425,7 +32428,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33043,7 +33046,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33661,7 +33664,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34073,7 +34076,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34279,7 +34282,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34691,7 +34694,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35103,7 +35106,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35181,7 +35184,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ165">
         <v>0.9</v>
@@ -35593,10 +35596,10 @@
         <v>2.33</v>
       </c>
       <c r="AP167">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ167">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -36339,7 +36342,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36420,7 +36423,7 @@
         <v>2</v>
       </c>
       <c r="AQ171">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR171">
         <v>1.72</v>
@@ -36545,7 +36548,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37369,7 +37372,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37987,7 +37990,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38399,7 +38402,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38556,6 +38559,418 @@
       </c>
       <c r="BP181">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7450828</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45702.58333333334</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>75</v>
+      </c>
+      <c r="H182" t="s">
+        <v>85</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>2</v>
+      </c>
+      <c r="O182" t="s">
+        <v>215</v>
+      </c>
+      <c r="P182" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q182">
+        <v>2.55</v>
+      </c>
+      <c r="R182">
+        <v>2</v>
+      </c>
+      <c r="S182">
+        <v>4.2</v>
+      </c>
+      <c r="T182">
+        <v>1.44</v>
+      </c>
+      <c r="U182">
+        <v>2.6</v>
+      </c>
+      <c r="V182">
+        <v>3</v>
+      </c>
+      <c r="W182">
+        <v>1.34</v>
+      </c>
+      <c r="X182">
+        <v>8</v>
+      </c>
+      <c r="Y182">
+        <v>1.07</v>
+      </c>
+      <c r="Z182">
+        <v>1.87</v>
+      </c>
+      <c r="AA182">
+        <v>3.37</v>
+      </c>
+      <c r="AB182">
+        <v>4.2</v>
+      </c>
+      <c r="AC182">
+        <v>1.07</v>
+      </c>
+      <c r="AD182">
+        <v>8</v>
+      </c>
+      <c r="AE182">
+        <v>1.37</v>
+      </c>
+      <c r="AF182">
+        <v>2.85</v>
+      </c>
+      <c r="AG182">
+        <v>2.1</v>
+      </c>
+      <c r="AH182">
+        <v>1.67</v>
+      </c>
+      <c r="AI182">
+        <v>1.93</v>
+      </c>
+      <c r="AJ182">
+        <v>1.77</v>
+      </c>
+      <c r="AK182">
+        <v>1.25</v>
+      </c>
+      <c r="AL182">
+        <v>1.31</v>
+      </c>
+      <c r="AM182">
+        <v>1.8</v>
+      </c>
+      <c r="AN182">
+        <v>1.3</v>
+      </c>
+      <c r="AO182">
+        <v>1.1</v>
+      </c>
+      <c r="AP182">
+        <v>1.27</v>
+      </c>
+      <c r="AQ182">
+        <v>1.09</v>
+      </c>
+      <c r="AR182">
+        <v>1.68</v>
+      </c>
+      <c r="AS182">
+        <v>1.39</v>
+      </c>
+      <c r="AT182">
+        <v>3.07</v>
+      </c>
+      <c r="AU182">
+        <v>4</v>
+      </c>
+      <c r="AV182">
+        <v>3</v>
+      </c>
+      <c r="AW182">
+        <v>6</v>
+      </c>
+      <c r="AX182">
+        <v>2</v>
+      </c>
+      <c r="AY182">
+        <v>13</v>
+      </c>
+      <c r="AZ182">
+        <v>7</v>
+      </c>
+      <c r="BA182">
+        <v>8</v>
+      </c>
+      <c r="BB182">
+        <v>1</v>
+      </c>
+      <c r="BC182">
+        <v>9</v>
+      </c>
+      <c r="BD182">
+        <v>1.68</v>
+      </c>
+      <c r="BE182">
+        <v>6.4</v>
+      </c>
+      <c r="BF182">
+        <v>2.45</v>
+      </c>
+      <c r="BG182">
+        <v>1.42</v>
+      </c>
+      <c r="BH182">
+        <v>2.55</v>
+      </c>
+      <c r="BI182">
+        <v>1.73</v>
+      </c>
+      <c r="BJ182">
+        <v>1.93</v>
+      </c>
+      <c r="BK182">
+        <v>2.17</v>
+      </c>
+      <c r="BL182">
+        <v>1.57</v>
+      </c>
+      <c r="BM182">
+        <v>2.8</v>
+      </c>
+      <c r="BN182">
+        <v>1.34</v>
+      </c>
+      <c r="BO182">
+        <v>3.8</v>
+      </c>
+      <c r="BP182">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7450833</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45702.6875</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>76</v>
+      </c>
+      <c r="H183" t="s">
+        <v>86</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>1</v>
+      </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
+      <c r="O183" t="s">
+        <v>95</v>
+      </c>
+      <c r="P183" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q183">
+        <v>2.87</v>
+      </c>
+      <c r="R183">
+        <v>2</v>
+      </c>
+      <c r="S183">
+        <v>3.6</v>
+      </c>
+      <c r="T183">
+        <v>1.44</v>
+      </c>
+      <c r="U183">
+        <v>2.55</v>
+      </c>
+      <c r="V183">
+        <v>3.1</v>
+      </c>
+      <c r="W183">
+        <v>1.32</v>
+      </c>
+      <c r="X183">
+        <v>8.5</v>
+      </c>
+      <c r="Y183">
+        <v>1.06</v>
+      </c>
+      <c r="Z183">
+        <v>2.29</v>
+      </c>
+      <c r="AA183">
+        <v>3.14</v>
+      </c>
+      <c r="AB183">
+        <v>3.17</v>
+      </c>
+      <c r="AC183">
+        <v>1.02</v>
+      </c>
+      <c r="AD183">
+        <v>7.9</v>
+      </c>
+      <c r="AE183">
+        <v>1.33</v>
+      </c>
+      <c r="AF183">
+        <v>2.82</v>
+      </c>
+      <c r="AG183">
+        <v>2.05</v>
+      </c>
+      <c r="AH183">
+        <v>1.61</v>
+      </c>
+      <c r="AI183">
+        <v>1.9</v>
+      </c>
+      <c r="AJ183">
+        <v>1.77</v>
+      </c>
+      <c r="AK183">
+        <v>1.35</v>
+      </c>
+      <c r="AL183">
+        <v>1.32</v>
+      </c>
+      <c r="AM183">
+        <v>1.6</v>
+      </c>
+      <c r="AN183">
+        <v>2.7</v>
+      </c>
+      <c r="AO183">
+        <v>2.2</v>
+      </c>
+      <c r="AP183">
+        <v>2.45</v>
+      </c>
+      <c r="AQ183">
+        <v>2.27</v>
+      </c>
+      <c r="AR183">
+        <v>2.02</v>
+      </c>
+      <c r="AS183">
+        <v>1.41</v>
+      </c>
+      <c r="AT183">
+        <v>3.43</v>
+      </c>
+      <c r="AU183">
+        <v>6</v>
+      </c>
+      <c r="AV183">
+        <v>9</v>
+      </c>
+      <c r="AW183">
+        <v>5</v>
+      </c>
+      <c r="AX183">
+        <v>7</v>
+      </c>
+      <c r="AY183">
+        <v>15</v>
+      </c>
+      <c r="AZ183">
+        <v>18</v>
+      </c>
+      <c r="BA183">
+        <v>3</v>
+      </c>
+      <c r="BB183">
+        <v>5</v>
+      </c>
+      <c r="BC183">
+        <v>8</v>
+      </c>
+      <c r="BD183">
+        <v>1.79</v>
+      </c>
+      <c r="BE183">
+        <v>6.25</v>
+      </c>
+      <c r="BF183">
+        <v>2.25</v>
+      </c>
+      <c r="BG183">
+        <v>1.5</v>
+      </c>
+      <c r="BH183">
+        <v>2.33</v>
+      </c>
+      <c r="BI183">
+        <v>1.84</v>
+      </c>
+      <c r="BJ183">
+        <v>1.8</v>
+      </c>
+      <c r="BK183">
+        <v>2.38</v>
+      </c>
+      <c r="BL183">
+        <v>1.48</v>
+      </c>
+      <c r="BM183">
+        <v>3.1</v>
+      </c>
+      <c r="BN183">
+        <v>1.28</v>
+      </c>
+      <c r="BO183">
+        <v>4.2</v>
+      </c>
+      <c r="BP183">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="303">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,15 @@
     <t>['90+1']</t>
   </si>
   <si>
+    <t>['4', '59', '77']</t>
+  </si>
+  <si>
+    <t>['4', '39', '71']</t>
+  </si>
+  <si>
+    <t>['15', '35']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -911,6 +920,9 @@
   </si>
   <si>
     <t>['47', '56']</t>
+  </si>
+  <si>
+    <t>['21', '45+2']</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1621,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ2">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1812,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ3">
         <v>0.7</v>
@@ -1940,7 +1952,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2021,7 +2033,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2430,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ6">
         <v>0.82</v>
@@ -2558,7 +2570,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2970,7 +2982,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3257,7 +3269,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ10">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3382,7 +3394,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3588,7 +3600,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3794,7 +3806,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4000,7 +4012,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4206,7 +4218,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4412,7 +4424,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5317,7 +5329,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ20">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR20">
         <v>0.84</v>
@@ -5520,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ21">
         <v>0.5600000000000001</v>
@@ -5648,7 +5660,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6266,7 +6278,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6472,7 +6484,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6550,7 +6562,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ26">
         <v>1.4</v>
@@ -6678,7 +6690,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6759,7 +6771,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ27">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR27">
         <v>0.72</v>
@@ -6884,7 +6896,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7296,7 +7308,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7708,7 +7720,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7914,7 +7926,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8326,7 +8338,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8944,7 +8956,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9150,7 +9162,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9437,7 +9449,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ40">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9640,7 +9652,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ41">
         <v>1.09</v>
@@ -9768,7 +9780,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9846,10 +9858,10 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ42">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10052,7 +10064,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43">
         <v>2.27</v>
@@ -10386,7 +10398,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10467,7 +10479,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ45">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR45">
         <v>1.15</v>
@@ -10592,7 +10604,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10879,7 +10891,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR47">
         <v>1.43</v>
@@ -11004,7 +11016,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11416,7 +11428,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11906,7 +11918,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ52">
         <v>1.3</v>
@@ -12240,7 +12252,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12446,7 +12458,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13064,7 +13076,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13270,7 +13282,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13348,7 +13360,7 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ59">
         <v>0.7</v>
@@ -13476,7 +13488,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13554,7 +13566,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ60">
         <v>1.4</v>
@@ -13682,7 +13694,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13969,7 +13981,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ62">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR62">
         <v>1.9</v>
@@ -14300,7 +14312,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14381,7 +14393,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR64">
         <v>1.8</v>
@@ -14587,7 +14599,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ65">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR65">
         <v>1.09</v>
@@ -14712,7 +14724,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15205,7 +15217,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ68">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR68">
         <v>1.44</v>
@@ -15614,7 +15626,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ70">
         <v>2.27</v>
@@ -16154,7 +16166,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16360,7 +16372,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16850,7 +16862,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ76">
         <v>1.4</v>
@@ -17596,7 +17608,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18089,7 +18101,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ82">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR82">
         <v>1.3</v>
@@ -18295,7 +18307,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ83">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR83">
         <v>1.5</v>
@@ -18704,7 +18716,7 @@
         <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ85">
         <v>1.4</v>
@@ -18913,7 +18925,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ86">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR86">
         <v>1.54</v>
@@ -19038,7 +19050,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19244,7 +19256,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19450,7 +19462,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19656,7 +19668,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19862,7 +19874,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20274,7 +20286,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20480,7 +20492,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20558,7 +20570,7 @@
         <v>0.2</v>
       </c>
       <c r="AP94">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ94">
         <v>0.82</v>
@@ -20686,7 +20698,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20892,7 +20904,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -20970,7 +20982,7 @@
         <v>2.4</v>
       </c>
       <c r="AP96">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ96">
         <v>2</v>
@@ -21510,7 +21522,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21716,7 +21728,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21922,7 +21934,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22003,7 +22015,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ101">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR101">
         <v>1.68</v>
@@ -22128,7 +22140,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22334,7 +22346,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22746,7 +22758,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22824,7 +22836,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ105">
         <v>0.4</v>
@@ -23239,7 +23251,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ107">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23364,7 +23376,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23442,7 +23454,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ108">
         <v>0.4</v>
@@ -23570,7 +23582,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23857,7 +23869,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ110">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR110">
         <v>1.69</v>
@@ -23982,7 +23994,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24266,7 +24278,7 @@
         <v>2.67</v>
       </c>
       <c r="AP112">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ112">
         <v>2.27</v>
@@ -24475,7 +24487,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ113">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR113">
         <v>1.89</v>
@@ -24600,7 +24612,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25012,7 +25024,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25218,7 +25230,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25296,7 +25308,7 @@
         <v>1.4</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ117">
         <v>1.4</v>
@@ -25630,7 +25642,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26248,7 +26260,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26326,7 +26338,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ122">
         <v>1.7</v>
@@ -26454,7 +26466,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26738,10 +26750,10 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ124">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR124">
         <v>1.68</v>
@@ -26866,7 +26878,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27278,7 +27290,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27484,7 +27496,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27565,7 +27577,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ128">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27896,7 +27908,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28308,7 +28320,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28386,7 +28398,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ132">
         <v>1.4</v>
@@ -28595,7 +28607,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ133">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR133">
         <v>1.65</v>
@@ -28720,7 +28732,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28926,7 +28938,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29132,7 +29144,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29338,7 +29350,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29544,7 +29556,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29956,7 +29968,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30034,7 +30046,7 @@
         <v>2.57</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ140">
         <v>2</v>
@@ -30162,7 +30174,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30652,7 +30664,7 @@
         <v>1.38</v>
       </c>
       <c r="AP143">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ143">
         <v>1.4</v>
@@ -30861,7 +30873,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ144">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31476,10 +31488,10 @@
         <v>0.25</v>
       </c>
       <c r="AP147">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ147">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR147">
         <v>1.42</v>
@@ -31810,7 +31822,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32016,7 +32028,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32428,7 +32440,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32715,7 +32727,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ153">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR153">
         <v>1.63</v>
@@ -33046,7 +33058,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33124,7 +33136,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ155">
         <v>1.4</v>
@@ -33664,7 +33676,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34076,7 +34088,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34282,7 +34294,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34694,7 +34706,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -34772,10 +34784,10 @@
         <v>0.75</v>
       </c>
       <c r="AP163">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ163">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR163">
         <v>1.52</v>
@@ -35106,7 +35118,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35187,7 +35199,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ165">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR165">
         <v>2.02</v>
@@ -36008,10 +36020,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP169">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ169">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR169">
         <v>1.91</v>
@@ -36217,7 +36229,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ170">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36342,7 +36354,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36420,7 +36432,7 @@
         <v>1.11</v>
       </c>
       <c r="AP171">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ171">
         <v>1.09</v>
@@ -36548,7 +36560,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36626,7 +36638,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ172">
         <v>1.4</v>
@@ -37372,7 +37384,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37990,7 +38002,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38402,7 +38414,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38608,7 +38620,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -38928,10 +38940,10 @@
         <v>3</v>
       </c>
       <c r="BB183">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC183">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD183">
         <v>1.79</v>
@@ -38971,6 +38983,624 @@
       </c>
       <c r="BP183">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7450836</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45703.44791666666</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>71</v>
+      </c>
+      <c r="H184" t="s">
+        <v>82</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184">
+        <v>3</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="N184">
+        <v>3</v>
+      </c>
+      <c r="O184" t="s">
+        <v>216</v>
+      </c>
+      <c r="P184" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q184">
+        <v>2.95</v>
+      </c>
+      <c r="R184">
+        <v>2.14</v>
+      </c>
+      <c r="S184">
+        <v>3.65</v>
+      </c>
+      <c r="T184">
+        <v>1.42</v>
+      </c>
+      <c r="U184">
+        <v>2.7</v>
+      </c>
+      <c r="V184">
+        <v>2.8</v>
+      </c>
+      <c r="W184">
+        <v>1.39</v>
+      </c>
+      <c r="X184">
+        <v>6.5</v>
+      </c>
+      <c r="Y184">
+        <v>1.08</v>
+      </c>
+      <c r="Z184">
+        <v>2.3</v>
+      </c>
+      <c r="AA184">
+        <v>3.23</v>
+      </c>
+      <c r="AB184">
+        <v>3.07</v>
+      </c>
+      <c r="AC184">
+        <v>1.06</v>
+      </c>
+      <c r="AD184">
+        <v>8.5</v>
+      </c>
+      <c r="AE184">
+        <v>1.31</v>
+      </c>
+      <c r="AF184">
+        <v>3.15</v>
+      </c>
+      <c r="AG184">
+        <v>1.98</v>
+      </c>
+      <c r="AH184">
+        <v>1.77</v>
+      </c>
+      <c r="AI184">
+        <v>1.74</v>
+      </c>
+      <c r="AJ184">
+        <v>1.99</v>
+      </c>
+      <c r="AK184">
+        <v>1.36</v>
+      </c>
+      <c r="AL184">
+        <v>1.3</v>
+      </c>
+      <c r="AM184">
+        <v>1.57</v>
+      </c>
+      <c r="AN184">
+        <v>0.7</v>
+      </c>
+      <c r="AO184">
+        <v>0.9</v>
+      </c>
+      <c r="AP184">
+        <v>0.91</v>
+      </c>
+      <c r="AQ184">
+        <v>0.82</v>
+      </c>
+      <c r="AR184">
+        <v>1.49</v>
+      </c>
+      <c r="AS184">
+        <v>1.41</v>
+      </c>
+      <c r="AT184">
+        <v>2.9</v>
+      </c>
+      <c r="AU184">
+        <v>7</v>
+      </c>
+      <c r="AV184">
+        <v>4</v>
+      </c>
+      <c r="AW184">
+        <v>11</v>
+      </c>
+      <c r="AX184">
+        <v>9</v>
+      </c>
+      <c r="AY184">
+        <v>21</v>
+      </c>
+      <c r="AZ184">
+        <v>20</v>
+      </c>
+      <c r="BA184">
+        <v>2</v>
+      </c>
+      <c r="BB184">
+        <v>5</v>
+      </c>
+      <c r="BC184">
+        <v>7</v>
+      </c>
+      <c r="BD184">
+        <v>1.85</v>
+      </c>
+      <c r="BE184">
+        <v>6.1</v>
+      </c>
+      <c r="BF184">
+        <v>2.18</v>
+      </c>
+      <c r="BG184">
+        <v>1.44</v>
+      </c>
+      <c r="BH184">
+        <v>2.48</v>
+      </c>
+      <c r="BI184">
+        <v>1.75</v>
+      </c>
+      <c r="BJ184">
+        <v>1.9</v>
+      </c>
+      <c r="BK184">
+        <v>2.2</v>
+      </c>
+      <c r="BL184">
+        <v>1.55</v>
+      </c>
+      <c r="BM184">
+        <v>2.9</v>
+      </c>
+      <c r="BN184">
+        <v>1.33</v>
+      </c>
+      <c r="BO184">
+        <v>3.85</v>
+      </c>
+      <c r="BP184">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7450830</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45703.5625</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>87</v>
+      </c>
+      <c r="H185" t="s">
+        <v>81</v>
+      </c>
+      <c r="I185">
+        <v>2</v>
+      </c>
+      <c r="J185">
+        <v>2</v>
+      </c>
+      <c r="K185">
+        <v>4</v>
+      </c>
+      <c r="L185">
+        <v>3</v>
+      </c>
+      <c r="M185">
+        <v>2</v>
+      </c>
+      <c r="N185">
+        <v>5</v>
+      </c>
+      <c r="O185" t="s">
+        <v>217</v>
+      </c>
+      <c r="P185" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q185">
+        <v>2.44</v>
+      </c>
+      <c r="R185">
+        <v>2.24</v>
+      </c>
+      <c r="S185">
+        <v>4.4</v>
+      </c>
+      <c r="T185">
+        <v>1.37</v>
+      </c>
+      <c r="U185">
+        <v>2.85</v>
+      </c>
+      <c r="V185">
+        <v>2.6</v>
+      </c>
+      <c r="W185">
+        <v>1.44</v>
+      </c>
+      <c r="X185">
+        <v>6.3</v>
+      </c>
+      <c r="Y185">
+        <v>1.09</v>
+      </c>
+      <c r="Z185">
+        <v>1.82</v>
+      </c>
+      <c r="AA185">
+        <v>3.61</v>
+      </c>
+      <c r="AB185">
+        <v>4.1</v>
+      </c>
+      <c r="AC185">
+        <v>1.05</v>
+      </c>
+      <c r="AD185">
+        <v>9</v>
+      </c>
+      <c r="AE185">
+        <v>1.27</v>
+      </c>
+      <c r="AF185">
+        <v>3.45</v>
+      </c>
+      <c r="AG185">
+        <v>1.85</v>
+      </c>
+      <c r="AH185">
+        <v>1.89</v>
+      </c>
+      <c r="AI185">
+        <v>1.72</v>
+      </c>
+      <c r="AJ185">
+        <v>2.01</v>
+      </c>
+      <c r="AK185">
+        <v>1.25</v>
+      </c>
+      <c r="AL185">
+        <v>1.27</v>
+      </c>
+      <c r="AM185">
+        <v>1.82</v>
+      </c>
+      <c r="AN185">
+        <v>1.7</v>
+      </c>
+      <c r="AO185">
+        <v>0.9</v>
+      </c>
+      <c r="AP185">
+        <v>1.82</v>
+      </c>
+      <c r="AQ185">
+        <v>0.82</v>
+      </c>
+      <c r="AR185">
+        <v>1.95</v>
+      </c>
+      <c r="AS185">
+        <v>1.39</v>
+      </c>
+      <c r="AT185">
+        <v>3.34</v>
+      </c>
+      <c r="AU185">
+        <v>8</v>
+      </c>
+      <c r="AV185">
+        <v>5</v>
+      </c>
+      <c r="AW185">
+        <v>6</v>
+      </c>
+      <c r="AX185">
+        <v>4</v>
+      </c>
+      <c r="AY185">
+        <v>19</v>
+      </c>
+      <c r="AZ185">
+        <v>11</v>
+      </c>
+      <c r="BA185">
+        <v>3</v>
+      </c>
+      <c r="BB185">
+        <v>10</v>
+      </c>
+      <c r="BC185">
+        <v>13</v>
+      </c>
+      <c r="BD185">
+        <v>1.57</v>
+      </c>
+      <c r="BE185">
+        <v>6.75</v>
+      </c>
+      <c r="BF185">
+        <v>2.65</v>
+      </c>
+      <c r="BG185">
+        <v>1.23</v>
+      </c>
+      <c r="BH185">
+        <v>3.45</v>
+      </c>
+      <c r="BI185">
+        <v>1.42</v>
+      </c>
+      <c r="BJ185">
+        <v>2.55</v>
+      </c>
+      <c r="BK185">
+        <v>1.68</v>
+      </c>
+      <c r="BL185">
+        <v>1.98</v>
+      </c>
+      <c r="BM185">
+        <v>2.08</v>
+      </c>
+      <c r="BN185">
+        <v>1.61</v>
+      </c>
+      <c r="BO185">
+        <v>2.63</v>
+      </c>
+      <c r="BP185">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7450834</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45703.67708333334</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>74</v>
+      </c>
+      <c r="H186" t="s">
+        <v>79</v>
+      </c>
+      <c r="I186">
+        <v>2</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>2</v>
+      </c>
+      <c r="L186">
+        <v>2</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>2</v>
+      </c>
+      <c r="O186" t="s">
+        <v>218</v>
+      </c>
+      <c r="P186" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q186">
+        <v>1.8</v>
+      </c>
+      <c r="R186">
+        <v>2.6</v>
+      </c>
+      <c r="S186">
+        <v>7.5</v>
+      </c>
+      <c r="T186">
+        <v>1.3</v>
+      </c>
+      <c r="U186">
+        <v>3.4</v>
+      </c>
+      <c r="V186">
+        <v>2.38</v>
+      </c>
+      <c r="W186">
+        <v>1.53</v>
+      </c>
+      <c r="X186">
+        <v>6</v>
+      </c>
+      <c r="Y186">
+        <v>1.13</v>
+      </c>
+      <c r="Z186">
+        <v>1.37</v>
+      </c>
+      <c r="AA186">
+        <v>5</v>
+      </c>
+      <c r="AB186">
+        <v>7.3</v>
+      </c>
+      <c r="AC186">
+        <v>1.03</v>
+      </c>
+      <c r="AD186">
+        <v>11</v>
+      </c>
+      <c r="AE186">
+        <v>1.19</v>
+      </c>
+      <c r="AF186">
+        <v>4.3</v>
+      </c>
+      <c r="AG186">
+        <v>1.57</v>
+      </c>
+      <c r="AH186">
+        <v>2.15</v>
+      </c>
+      <c r="AI186">
+        <v>1.95</v>
+      </c>
+      <c r="AJ186">
+        <v>1.8</v>
+      </c>
+      <c r="AK186">
+        <v>1.08</v>
+      </c>
+      <c r="AL186">
+        <v>1.16</v>
+      </c>
+      <c r="AM186">
+        <v>3.1</v>
+      </c>
+      <c r="AN186">
+        <v>2</v>
+      </c>
+      <c r="AO186">
+        <v>0.6</v>
+      </c>
+      <c r="AP186">
+        <v>2.09</v>
+      </c>
+      <c r="AQ186">
+        <v>0.55</v>
+      </c>
+      <c r="AR186">
+        <v>1.66</v>
+      </c>
+      <c r="AS186">
+        <v>1.01</v>
+      </c>
+      <c r="AT186">
+        <v>2.67</v>
+      </c>
+      <c r="AU186">
+        <v>7</v>
+      </c>
+      <c r="AV186">
+        <v>3</v>
+      </c>
+      <c r="AW186">
+        <v>8</v>
+      </c>
+      <c r="AX186">
+        <v>5</v>
+      </c>
+      <c r="AY186">
+        <v>15</v>
+      </c>
+      <c r="AZ186">
+        <v>8</v>
+      </c>
+      <c r="BA186">
+        <v>10</v>
+      </c>
+      <c r="BB186">
+        <v>6</v>
+      </c>
+      <c r="BC186">
+        <v>16</v>
+      </c>
+      <c r="BD186">
+        <v>1.33</v>
+      </c>
+      <c r="BE186">
+        <v>7</v>
+      </c>
+      <c r="BF186">
+        <v>3.65</v>
+      </c>
+      <c r="BG186">
+        <v>1.33</v>
+      </c>
+      <c r="BH186">
+        <v>2.88</v>
+      </c>
+      <c r="BI186">
+        <v>1.57</v>
+      </c>
+      <c r="BJ186">
+        <v>2.17</v>
+      </c>
+      <c r="BK186">
+        <v>1.94</v>
+      </c>
+      <c r="BL186">
+        <v>1.71</v>
+      </c>
+      <c r="BM186">
+        <v>2.48</v>
+      </c>
+      <c r="BN186">
+        <v>1.44</v>
+      </c>
+      <c r="BO186">
+        <v>3.2</v>
+      </c>
+      <c r="BP186">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -39549,7 +39549,7 @@
         <v>5</v>
       </c>
       <c r="AY186">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ186">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,9 @@
     <t>['15', '35']</t>
   </si>
   <si>
+    <t>['27', '59', '69']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -923,6 +926,9 @@
   </si>
   <si>
     <t>['21', '45+2']</t>
+  </si>
+  <si>
+    <t>['54', '65']</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1618,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ2">
         <v>0.55</v>
@@ -1952,7 +1958,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2030,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4">
         <v>0.82</v>
@@ -2570,7 +2576,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2651,7 +2657,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ7">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2982,7 +2988,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3266,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ10">
         <v>0.82</v>
@@ -3394,7 +3400,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3600,7 +3606,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3681,7 +3687,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ12">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3806,7 +3812,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3884,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ13">
         <v>1.4</v>
@@ -4012,7 +4018,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4218,7 +4224,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4424,7 +4430,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4505,7 +4511,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ16">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5535,7 +5541,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ21">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5660,7 +5666,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5738,7 +5744,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ22">
         <v>2.27</v>
@@ -5944,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ23">
         <v>0.4</v>
@@ -6278,7 +6284,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6484,7 +6490,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6565,7 +6571,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6690,7 +6696,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6896,7 +6902,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7308,7 +7314,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7720,7 +7726,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7926,7 +7932,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8338,7 +8344,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8828,10 +8834,10 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ37">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR37">
         <v>1.91</v>
@@ -8956,7 +8962,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9034,7 +9040,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ38">
         <v>2</v>
@@ -9162,7 +9168,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9780,7 +9786,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10270,10 +10276,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -10398,7 +10404,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10604,7 +10610,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11016,7 +11022,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11428,7 +11434,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11506,7 +11512,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ50">
         <v>1.7</v>
@@ -11715,7 +11721,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ51">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR51">
         <v>1.7</v>
@@ -12252,7 +12258,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12333,7 +12339,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ54">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR54">
         <v>1.89</v>
@@ -12458,7 +12464,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12536,7 +12542,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ55">
         <v>1.4</v>
@@ -13076,7 +13082,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13282,7 +13288,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13488,7 +13494,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13569,7 +13575,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ60">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -13694,7 +13700,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13978,7 +13984,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ62">
         <v>0.82</v>
@@ -14312,7 +14318,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14390,7 +14396,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ64">
         <v>0.82</v>
@@ -14724,7 +14730,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14805,7 +14811,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ66">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR66">
         <v>1.22</v>
@@ -16166,7 +16172,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16372,7 +16378,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16450,7 +16456,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ74">
         <v>0.7</v>
@@ -16659,7 +16665,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ75">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -17068,10 +17074,10 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ77">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR77">
         <v>1.21</v>
@@ -17608,7 +17614,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17892,10 +17898,10 @@
         <v>0.25</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ81">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR81">
         <v>1.75</v>
@@ -19050,7 +19056,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19256,7 +19262,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19462,7 +19468,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19668,7 +19674,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19874,7 +19880,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20158,7 +20164,7 @@
         <v>0.8</v>
       </c>
       <c r="AP92">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ92">
         <v>0.7</v>
@@ -20286,7 +20292,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20492,7 +20498,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20698,7 +20704,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20779,7 +20785,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ95">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -20904,7 +20910,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21191,7 +21197,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ97">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21394,7 +21400,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ98">
         <v>1.3</v>
@@ -21522,7 +21528,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21603,7 +21609,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ99">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR99">
         <v>1.36</v>
@@ -21728,7 +21734,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21934,7 +21940,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22140,7 +22146,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22346,7 +22352,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22630,7 +22636,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ104">
         <v>0.4</v>
@@ -22758,7 +22764,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23045,7 +23051,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR106">
         <v>1.53</v>
@@ -23376,7 +23382,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23582,7 +23588,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23994,7 +24000,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24075,7 +24081,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ111">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR111">
         <v>1.46</v>
@@ -24612,7 +24618,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24690,7 +24696,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ114">
         <v>0.82</v>
@@ -24896,7 +24902,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ115">
         <v>1.09</v>
@@ -25024,7 +25030,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25230,7 +25236,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25642,7 +25648,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -25723,7 +25729,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ119">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR119">
         <v>1.67</v>
@@ -26135,7 +26141,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ121">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR121">
         <v>1.57</v>
@@ -26260,7 +26266,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26466,7 +26472,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26878,7 +26884,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26956,7 +26962,7 @@
         <v>0.86</v>
       </c>
       <c r="AP125">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ125">
         <v>1.09</v>
@@ -27290,7 +27296,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27371,7 +27377,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ127">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -27496,7 +27502,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27908,7 +27914,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28320,7 +28326,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28604,7 +28610,7 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ133">
         <v>0.55</v>
@@ -28732,7 +28738,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28810,7 +28816,7 @@
         <v>2.43</v>
       </c>
       <c r="AP134">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ134">
         <v>2.27</v>
@@ -28938,7 +28944,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29144,7 +29150,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29225,7 +29231,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ136">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29350,7 +29356,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29428,7 +29434,7 @@
         <v>0.29</v>
       </c>
       <c r="AP137">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ137">
         <v>0.4</v>
@@ -29556,7 +29562,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29637,7 +29643,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ138">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR138">
         <v>1.26</v>
@@ -29968,7 +29974,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30174,7 +30180,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30667,7 +30673,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ143">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR143">
         <v>1.98</v>
@@ -31694,7 +31700,7 @@
         <v>0.75</v>
       </c>
       <c r="AP148">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ148">
         <v>0.7</v>
@@ -31822,7 +31828,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32028,7 +32034,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32440,7 +32446,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32518,7 +32524,7 @@
         <v>1.29</v>
       </c>
       <c r="AP152">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ152">
         <v>1.3</v>
@@ -33058,7 +33064,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33676,7 +33682,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -33757,7 +33763,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ158">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR158">
         <v>1.55</v>
@@ -34088,7 +34094,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34294,7 +34300,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34581,7 +34587,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ162">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AR162">
         <v>1.43</v>
@@ -34706,7 +34712,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -34990,7 +34996,7 @@
         <v>0.44</v>
       </c>
       <c r="AP164">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ164">
         <v>0.4</v>
@@ -35118,7 +35124,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36226,7 +36232,7 @@
         <v>1</v>
       </c>
       <c r="AP170">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ170">
         <v>0.82</v>
@@ -36354,7 +36360,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36560,7 +36566,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36641,7 +36647,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ172">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR172">
         <v>1.47</v>
@@ -36844,7 +36850,7 @@
         <v>1.89</v>
       </c>
       <c r="AP173">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ173">
         <v>1.7</v>
@@ -37384,7 +37390,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37877,7 +37883,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ178">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR178">
         <v>1.4</v>
@@ -38002,7 +38008,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38414,7 +38420,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38620,7 +38626,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39143,13 +39149,13 @@
         <v>20</v>
       </c>
       <c r="BA184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB184">
         <v>5</v>
       </c>
       <c r="BC184">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD184">
         <v>1.85</v>
@@ -39238,7 +39244,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39601,6 +39607,624 @@
       </c>
       <c r="BP186">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7450835</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45704.34375</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>78</v>
+      </c>
+      <c r="H187" t="s">
+        <v>73</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="M187">
+        <v>2</v>
+      </c>
+      <c r="N187">
+        <v>3</v>
+      </c>
+      <c r="O187" t="s">
+        <v>93</v>
+      </c>
+      <c r="P187" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q187">
+        <v>3.66</v>
+      </c>
+      <c r="R187">
+        <v>2.15</v>
+      </c>
+      <c r="S187">
+        <v>2.72</v>
+      </c>
+      <c r="T187">
+        <v>1.35</v>
+      </c>
+      <c r="U187">
+        <v>2.99</v>
+      </c>
+      <c r="V187">
+        <v>2.7</v>
+      </c>
+      <c r="W187">
+        <v>1.42</v>
+      </c>
+      <c r="X187">
+        <v>6.75</v>
+      </c>
+      <c r="Y187">
+        <v>1.05</v>
+      </c>
+      <c r="Z187">
+        <v>3.31</v>
+      </c>
+      <c r="AA187">
+        <v>3.02</v>
+      </c>
+      <c r="AB187">
+        <v>2.29</v>
+      </c>
+      <c r="AC187">
+        <v>1.03</v>
+      </c>
+      <c r="AD187">
+        <v>10</v>
+      </c>
+      <c r="AE187">
+        <v>1.21</v>
+      </c>
+      <c r="AF187">
+        <v>3.6</v>
+      </c>
+      <c r="AG187">
+        <v>1.8</v>
+      </c>
+      <c r="AH187">
+        <v>1.94</v>
+      </c>
+      <c r="AI187">
+        <v>1.66</v>
+      </c>
+      <c r="AJ187">
+        <v>2.09</v>
+      </c>
+      <c r="AK187">
+        <v>1.65</v>
+      </c>
+      <c r="AL187">
+        <v>1.28</v>
+      </c>
+      <c r="AM187">
+        <v>1.34</v>
+      </c>
+      <c r="AN187">
+        <v>1.8</v>
+      </c>
+      <c r="AO187">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP187">
+        <v>1.64</v>
+      </c>
+      <c r="AQ187">
+        <v>0.8</v>
+      </c>
+      <c r="AR187">
+        <v>1.64</v>
+      </c>
+      <c r="AS187">
+        <v>1.44</v>
+      </c>
+      <c r="AT187">
+        <v>3.08</v>
+      </c>
+      <c r="AU187">
+        <v>4</v>
+      </c>
+      <c r="AV187">
+        <v>4</v>
+      </c>
+      <c r="AW187">
+        <v>6</v>
+      </c>
+      <c r="AX187">
+        <v>0</v>
+      </c>
+      <c r="AY187">
+        <v>14</v>
+      </c>
+      <c r="AZ187">
+        <v>6</v>
+      </c>
+      <c r="BA187">
+        <v>7</v>
+      </c>
+      <c r="BB187">
+        <v>5</v>
+      </c>
+      <c r="BC187">
+        <v>12</v>
+      </c>
+      <c r="BD187">
+        <v>2.25</v>
+      </c>
+      <c r="BE187">
+        <v>6.4</v>
+      </c>
+      <c r="BF187">
+        <v>1.78</v>
+      </c>
+      <c r="BG187">
+        <v>1.38</v>
+      </c>
+      <c r="BH187">
+        <v>2.65</v>
+      </c>
+      <c r="BI187">
+        <v>1.65</v>
+      </c>
+      <c r="BJ187">
+        <v>2.02</v>
+      </c>
+      <c r="BK187">
+        <v>2.06</v>
+      </c>
+      <c r="BL187">
+        <v>1.63</v>
+      </c>
+      <c r="BM187">
+        <v>2.65</v>
+      </c>
+      <c r="BN187">
+        <v>1.38</v>
+      </c>
+      <c r="BO187">
+        <v>3.5</v>
+      </c>
+      <c r="BP187">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7450829</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45704.44791666666</v>
+      </c>
+      <c r="F188">
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>72</v>
+      </c>
+      <c r="H188" t="s">
+        <v>84</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>0</v>
+      </c>
+      <c r="O188" t="s">
+        <v>95</v>
+      </c>
+      <c r="P188" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q188">
+        <v>3.34</v>
+      </c>
+      <c r="R188">
+        <v>2.05</v>
+      </c>
+      <c r="S188">
+        <v>3.14</v>
+      </c>
+      <c r="T188">
+        <v>1.43</v>
+      </c>
+      <c r="U188">
+        <v>2.66</v>
+      </c>
+      <c r="V188">
+        <v>2.99</v>
+      </c>
+      <c r="W188">
+        <v>1.35</v>
+      </c>
+      <c r="X188">
+        <v>7.3</v>
+      </c>
+      <c r="Y188">
+        <v>1.04</v>
+      </c>
+      <c r="Z188">
+        <v>2.71</v>
+      </c>
+      <c r="AA188">
+        <v>3.2</v>
+      </c>
+      <c r="AB188">
+        <v>2.58</v>
+      </c>
+      <c r="AC188">
+        <v>1.02</v>
+      </c>
+      <c r="AD188">
+        <v>7.9</v>
+      </c>
+      <c r="AE188">
+        <v>1.31</v>
+      </c>
+      <c r="AF188">
+        <v>2.93</v>
+      </c>
+      <c r="AG188">
+        <v>2.03</v>
+      </c>
+      <c r="AH188">
+        <v>1.72</v>
+      </c>
+      <c r="AI188">
+        <v>1.8</v>
+      </c>
+      <c r="AJ188">
+        <v>1.9</v>
+      </c>
+      <c r="AK188">
+        <v>1.48</v>
+      </c>
+      <c r="AL188">
+        <v>1.31</v>
+      </c>
+      <c r="AM188">
+        <v>1.44</v>
+      </c>
+      <c r="AN188">
+        <v>1.5</v>
+      </c>
+      <c r="AO188">
+        <v>1.4</v>
+      </c>
+      <c r="AP188">
+        <v>1.45</v>
+      </c>
+      <c r="AQ188">
+        <v>1.36</v>
+      </c>
+      <c r="AR188">
+        <v>1.73</v>
+      </c>
+      <c r="AS188">
+        <v>1.38</v>
+      </c>
+      <c r="AT188">
+        <v>3.11</v>
+      </c>
+      <c r="AU188">
+        <v>4</v>
+      </c>
+      <c r="AV188">
+        <v>4</v>
+      </c>
+      <c r="AW188">
+        <v>4</v>
+      </c>
+      <c r="AX188">
+        <v>11</v>
+      </c>
+      <c r="AY188">
+        <v>9</v>
+      </c>
+      <c r="AZ188">
+        <v>16</v>
+      </c>
+      <c r="BA188">
+        <v>10</v>
+      </c>
+      <c r="BB188">
+        <v>7</v>
+      </c>
+      <c r="BC188">
+        <v>17</v>
+      </c>
+      <c r="BD188">
+        <v>2.08</v>
+      </c>
+      <c r="BE188">
+        <v>6.25</v>
+      </c>
+      <c r="BF188">
+        <v>1.91</v>
+      </c>
+      <c r="BG188">
+        <v>1.46</v>
+      </c>
+      <c r="BH188">
+        <v>2.4</v>
+      </c>
+      <c r="BI188">
+        <v>1.79</v>
+      </c>
+      <c r="BJ188">
+        <v>1.85</v>
+      </c>
+      <c r="BK188">
+        <v>2.28</v>
+      </c>
+      <c r="BL188">
+        <v>1.52</v>
+      </c>
+      <c r="BM188">
+        <v>2.95</v>
+      </c>
+      <c r="BN188">
+        <v>1.32</v>
+      </c>
+      <c r="BO188">
+        <v>3.95</v>
+      </c>
+      <c r="BP188">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7450831</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45704.5625</v>
+      </c>
+      <c r="F189">
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>70</v>
+      </c>
+      <c r="H189" t="s">
+        <v>77</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>3</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>3</v>
+      </c>
+      <c r="O189" t="s">
+        <v>219</v>
+      </c>
+      <c r="P189" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q189">
+        <v>2.13</v>
+      </c>
+      <c r="R189">
+        <v>2.35</v>
+      </c>
+      <c r="S189">
+        <v>4.75</v>
+      </c>
+      <c r="T189">
+        <v>1.27</v>
+      </c>
+      <c r="U189">
+        <v>3.48</v>
+      </c>
+      <c r="V189">
+        <v>2.38</v>
+      </c>
+      <c r="W189">
+        <v>1.53</v>
+      </c>
+      <c r="X189">
+        <v>5.7</v>
+      </c>
+      <c r="Y189">
+        <v>1.08</v>
+      </c>
+      <c r="Z189">
+        <v>1.65</v>
+      </c>
+      <c r="AA189">
+        <v>4.1</v>
+      </c>
+      <c r="AB189">
+        <v>4.5</v>
+      </c>
+      <c r="AC189">
+        <v>1.01</v>
+      </c>
+      <c r="AD189">
+        <v>12</v>
+      </c>
+      <c r="AE189">
+        <v>1.13</v>
+      </c>
+      <c r="AF189">
+        <v>4.6</v>
+      </c>
+      <c r="AG189">
+        <v>1.57</v>
+      </c>
+      <c r="AH189">
+        <v>2.15</v>
+      </c>
+      <c r="AI189">
+        <v>1.6</v>
+      </c>
+      <c r="AJ189">
+        <v>2.19</v>
+      </c>
+      <c r="AK189">
+        <v>1.17</v>
+      </c>
+      <c r="AL189">
+        <v>1.21</v>
+      </c>
+      <c r="AM189">
+        <v>2.2</v>
+      </c>
+      <c r="AN189">
+        <v>2.1</v>
+      </c>
+      <c r="AO189">
+        <v>1.4</v>
+      </c>
+      <c r="AP189">
+        <v>2.18</v>
+      </c>
+      <c r="AQ189">
+        <v>1.27</v>
+      </c>
+      <c r="AR189">
+        <v>1.82</v>
+      </c>
+      <c r="AS189">
+        <v>1.37</v>
+      </c>
+      <c r="AT189">
+        <v>3.19</v>
+      </c>
+      <c r="AU189">
+        <v>7</v>
+      </c>
+      <c r="AV189">
+        <v>4</v>
+      </c>
+      <c r="AW189">
+        <v>6</v>
+      </c>
+      <c r="AX189">
+        <v>4</v>
+      </c>
+      <c r="AY189">
+        <v>16</v>
+      </c>
+      <c r="AZ189">
+        <v>11</v>
+      </c>
+      <c r="BA189">
+        <v>1</v>
+      </c>
+      <c r="BB189">
+        <v>1</v>
+      </c>
+      <c r="BC189">
+        <v>2</v>
+      </c>
+      <c r="BD189">
+        <v>1.55</v>
+      </c>
+      <c r="BE189">
+        <v>6.75</v>
+      </c>
+      <c r="BF189">
+        <v>2.7</v>
+      </c>
+      <c r="BG189">
+        <v>1.32</v>
+      </c>
+      <c r="BH189">
+        <v>2.95</v>
+      </c>
+      <c r="BI189">
+        <v>1.56</v>
+      </c>
+      <c r="BJ189">
+        <v>2.18</v>
+      </c>
+      <c r="BK189">
+        <v>1.91</v>
+      </c>
+      <c r="BL189">
+        <v>1.74</v>
+      </c>
+      <c r="BM189">
+        <v>2.4</v>
+      </c>
+      <c r="BN189">
+        <v>1.46</v>
+      </c>
+      <c r="BO189">
+        <v>3.15</v>
+      </c>
+      <c r="BP189">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -38946,10 +38946,10 @@
         <v>3</v>
       </c>
       <c r="BB183">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC183">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD183">
         <v>1.79</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="307">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,9 @@
     <t>['27', '59', '69']</t>
   </si>
   <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -929,6 +932,9 @@
   </si>
   <si>
     <t>['54', '65']</t>
+  </si>
+  <si>
+    <t>['30', '39', '55']</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1833,7 +1839,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ3">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1958,7 +1964,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2576,7 +2582,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2988,7 +2994,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3400,7 +3406,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3606,7 +3612,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3812,7 +3818,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4018,7 +4024,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4224,7 +4230,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4430,7 +4436,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4508,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16">
         <v>0.8</v>
@@ -5332,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ20">
         <v>0.55</v>
@@ -5666,7 +5672,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6159,7 +6165,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ24">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR24">
         <v>1.69</v>
@@ -6284,7 +6290,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6490,7 +6496,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6696,7 +6702,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6902,7 +6908,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7314,7 +7320,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7726,7 +7732,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7932,7 +7938,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8344,7 +8350,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8631,7 +8637,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ36">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR36">
         <v>1.51</v>
@@ -8962,7 +8968,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9168,7 +9174,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9246,7 +9252,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ39">
         <v>1.4</v>
@@ -9786,7 +9792,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10404,7 +10410,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10610,7 +10616,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11022,7 +11028,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11434,7 +11440,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12258,7 +12264,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12464,7 +12470,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12954,7 +12960,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ57">
         <v>1.4</v>
@@ -13082,7 +13088,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13288,7 +13294,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13369,7 +13375,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ59">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR59">
         <v>1.38</v>
@@ -13494,7 +13500,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13700,7 +13706,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14318,7 +14324,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14730,7 +14736,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -16172,7 +16178,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16378,7 +16384,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16459,7 +16465,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ74">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -17614,7 +17620,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18928,7 +18934,7 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ86">
         <v>0.82</v>
@@ -19056,7 +19062,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19262,7 +19268,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19468,7 +19474,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19674,7 +19680,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19880,7 +19886,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20167,7 +20173,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ92">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -20292,7 +20298,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20498,7 +20504,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20704,7 +20710,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20910,7 +20916,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21528,7 +21534,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21734,7 +21740,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21940,7 +21946,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22146,7 +22152,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22224,7 +22230,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ102">
         <v>1.7</v>
@@ -22352,7 +22358,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22764,7 +22770,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23382,7 +23388,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23588,7 +23594,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23669,7 +23675,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ109">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -24000,7 +24006,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24618,7 +24624,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25030,7 +25036,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25236,7 +25242,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25648,7 +25654,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26266,7 +26272,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26472,7 +26478,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26884,7 +26890,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27168,7 +27174,7 @@
         <v>0.33</v>
       </c>
       <c r="AP126">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ126">
         <v>0.4</v>
@@ -27296,7 +27302,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27502,7 +27508,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27789,7 +27795,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ129">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR129">
         <v>1.39</v>
@@ -27914,7 +27920,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28326,7 +28332,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28738,7 +28744,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28944,7 +28950,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29150,7 +29156,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29228,7 +29234,7 @@
         <v>1.43</v>
       </c>
       <c r="AP136">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ136">
         <v>1.27</v>
@@ -29356,7 +29362,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29562,7 +29568,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29974,7 +29980,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30180,7 +30186,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31703,7 +31709,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ148">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR148">
         <v>1.73</v>
@@ -31828,7 +31834,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32034,7 +32040,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32446,7 +32452,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33064,7 +33070,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33682,7 +33688,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34094,7 +34100,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34300,7 +34306,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34378,7 +34384,7 @@
         <v>1.25</v>
       </c>
       <c r="AP161">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ161">
         <v>1.3</v>
@@ -34712,7 +34718,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35124,7 +35130,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35411,7 +35417,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ166">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR166">
         <v>1.68</v>
@@ -36360,7 +36366,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36566,7 +36572,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37390,7 +37396,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -38008,7 +38014,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38420,7 +38426,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38626,7 +38632,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39244,7 +39250,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39656,7 +39662,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40225,6 +40231,212 @@
       </c>
       <c r="BP189">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7450832</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45705.625</v>
+      </c>
+      <c r="F190">
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>83</v>
+      </c>
+      <c r="H190" t="s">
+        <v>80</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>2</v>
+      </c>
+      <c r="K190">
+        <v>2</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>3</v>
+      </c>
+      <c r="N190">
+        <v>4</v>
+      </c>
+      <c r="O190" t="s">
+        <v>220</v>
+      </c>
+      <c r="P190" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q190">
+        <v>2.5</v>
+      </c>
+      <c r="R190">
+        <v>2.25</v>
+      </c>
+      <c r="S190">
+        <v>4.33</v>
+      </c>
+      <c r="T190">
+        <v>1.36</v>
+      </c>
+      <c r="U190">
+        <v>3</v>
+      </c>
+      <c r="V190">
+        <v>2.63</v>
+      </c>
+      <c r="W190">
+        <v>1.44</v>
+      </c>
+      <c r="X190">
+        <v>7</v>
+      </c>
+      <c r="Y190">
+        <v>1.1</v>
+      </c>
+      <c r="Z190">
+        <v>1.82</v>
+      </c>
+      <c r="AA190">
+        <v>3.55</v>
+      </c>
+      <c r="AB190">
+        <v>4.2</v>
+      </c>
+      <c r="AC190">
+        <v>1.05</v>
+      </c>
+      <c r="AD190">
+        <v>9.5</v>
+      </c>
+      <c r="AE190">
+        <v>1.23</v>
+      </c>
+      <c r="AF190">
+        <v>3.75</v>
+      </c>
+      <c r="AG190">
+        <v>1.8</v>
+      </c>
+      <c r="AH190">
+        <v>1.94</v>
+      </c>
+      <c r="AI190">
+        <v>1.7</v>
+      </c>
+      <c r="AJ190">
+        <v>2.05</v>
+      </c>
+      <c r="AK190">
+        <v>1.25</v>
+      </c>
+      <c r="AL190">
+        <v>1.26</v>
+      </c>
+      <c r="AM190">
+        <v>1.84</v>
+      </c>
+      <c r="AN190">
+        <v>1.44</v>
+      </c>
+      <c r="AO190">
+        <v>0.7</v>
+      </c>
+      <c r="AP190">
+        <v>1.3</v>
+      </c>
+      <c r="AQ190">
+        <v>0.91</v>
+      </c>
+      <c r="AR190">
+        <v>1.75</v>
+      </c>
+      <c r="AS190">
+        <v>1.26</v>
+      </c>
+      <c r="AT190">
+        <v>3.01</v>
+      </c>
+      <c r="AU190">
+        <v>10</v>
+      </c>
+      <c r="AV190">
+        <v>7</v>
+      </c>
+      <c r="AW190">
+        <v>10</v>
+      </c>
+      <c r="AX190">
+        <v>7</v>
+      </c>
+      <c r="AY190">
+        <v>22</v>
+      </c>
+      <c r="AZ190">
+        <v>18</v>
+      </c>
+      <c r="BA190">
+        <v>8</v>
+      </c>
+      <c r="BB190">
+        <v>8</v>
+      </c>
+      <c r="BC190">
+        <v>16</v>
+      </c>
+      <c r="BD190">
+        <v>1.61</v>
+      </c>
+      <c r="BE190">
+        <v>6.5</v>
+      </c>
+      <c r="BF190">
+        <v>2.55</v>
+      </c>
+      <c r="BG190">
+        <v>1.35</v>
+      </c>
+      <c r="BH190">
+        <v>2.8</v>
+      </c>
+      <c r="BI190">
+        <v>1.6</v>
+      </c>
+      <c r="BJ190">
+        <v>2.1</v>
+      </c>
+      <c r="BK190">
+        <v>1.98</v>
+      </c>
+      <c r="BL190">
+        <v>1.68</v>
+      </c>
+      <c r="BM190">
+        <v>2.55</v>
+      </c>
+      <c r="BN190">
+        <v>1.41</v>
+      </c>
+      <c r="BO190">
+        <v>3.35</v>
+      </c>
+      <c r="BP190">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="309">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,9 @@
     <t>['79']</t>
   </si>
   <si>
+    <t>['59', '71']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -935,6 +938,9 @@
   </si>
   <si>
     <t>['30', '39', '55']</t>
+  </si>
+  <si>
+    <t>['36', '53']</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1964,7 +1970,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2582,7 +2588,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2869,7 +2875,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ8">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2994,7 +3000,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3406,7 +3412,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3487,7 +3493,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ11">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3612,7 +3618,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3818,7 +3824,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4024,7 +4030,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4230,7 +4236,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4436,7 +4442,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4720,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ17">
         <v>0.4</v>
@@ -5132,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ19">
         <v>2</v>
@@ -5672,7 +5678,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5959,7 +5965,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ23">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR23">
         <v>2.07</v>
@@ -6290,7 +6296,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6496,7 +6502,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6702,7 +6708,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6908,7 +6914,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6989,7 +6995,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ28">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR28">
         <v>2.08</v>
@@ -7192,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ29">
         <v>1.4</v>
@@ -7320,7 +7326,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7607,7 +7613,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ31">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR31">
         <v>1.66</v>
@@ -7732,7 +7738,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7938,7 +7944,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8350,7 +8356,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8428,7 +8434,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ35">
         <v>1.4</v>
@@ -8968,7 +8974,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9174,7 +9180,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9792,7 +9798,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10410,7 +10416,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10616,7 +10622,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11028,7 +11034,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11109,7 +11115,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ48">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR48">
         <v>0.96</v>
@@ -11312,7 +11318,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ49">
         <v>0.82</v>
@@ -11440,7 +11446,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12139,7 +12145,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ53">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR53">
         <v>1.28</v>
@@ -12264,7 +12270,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12342,7 +12348,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ54">
         <v>1.36</v>
@@ -12470,7 +12476,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13088,7 +13094,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13294,7 +13300,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13500,7 +13506,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13706,7 +13712,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14199,7 +14205,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -14324,7 +14330,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14736,7 +14742,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15226,7 +15232,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ68">
         <v>0.55</v>
@@ -16178,7 +16184,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16384,7 +16390,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17286,7 +17292,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ78">
         <v>0.82</v>
@@ -17620,7 +17626,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18316,7 +18322,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ83">
         <v>0.55</v>
@@ -18731,7 +18737,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ85">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR85">
         <v>1.53</v>
@@ -19062,7 +19068,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19268,7 +19274,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19346,7 +19352,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
         <v>1.7</v>
@@ -19474,7 +19480,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19555,7 +19561,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ89">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19680,7 +19686,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19886,7 +19892,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20298,7 +20304,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20504,7 +20510,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20710,7 +20716,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20916,7 +20922,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21534,7 +21540,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21740,7 +21746,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21946,7 +21952,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22152,7 +22158,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22358,7 +22364,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22770,7 +22776,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22851,7 +22857,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ105">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR105">
         <v>1.93</v>
@@ -23054,7 +23060,7 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ106">
         <v>0.8</v>
@@ -23388,7 +23394,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23469,7 +23475,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ108">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR108">
         <v>1.61</v>
@@ -23594,7 +23600,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23672,7 +23678,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ109">
         <v>0.91</v>
@@ -24006,7 +24012,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24624,7 +24630,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25036,7 +25042,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25117,7 +25123,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ116">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR116">
         <v>1.38</v>
@@ -25242,7 +25248,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25526,10 +25532,10 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ118">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR118">
         <v>1.58</v>
@@ -25654,7 +25660,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26272,7 +26278,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26478,7 +26484,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26890,7 +26896,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27302,7 +27308,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27380,7 +27386,7 @@
         <v>1.17</v>
       </c>
       <c r="AP127">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ127">
         <v>1.27</v>
@@ -27508,7 +27514,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27920,7 +27926,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28332,7 +28338,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28413,7 +28419,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ132">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR132">
         <v>1.49</v>
@@ -28744,7 +28750,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28950,7 +28956,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29156,7 +29162,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29362,7 +29368,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29568,7 +29574,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29980,7 +29986,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30186,7 +30192,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30267,7 +30273,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ141">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR141">
         <v>1.53</v>
@@ -30470,7 +30476,7 @@
         <v>1.13</v>
       </c>
       <c r="AP142">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ142">
         <v>1.09</v>
@@ -31294,7 +31300,7 @@
         <v>1.86</v>
       </c>
       <c r="AP146">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ146">
         <v>1.4</v>
@@ -31834,7 +31840,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32040,7 +32046,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32121,7 +32127,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ150">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR150">
         <v>1.43</v>
@@ -32452,7 +32458,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33070,7 +33076,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33563,7 +33569,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ157">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR157">
         <v>1.39</v>
@@ -33688,7 +33694,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -33766,7 +33772,7 @@
         <v>1.63</v>
       </c>
       <c r="AP158">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ158">
         <v>1.27</v>
@@ -33972,7 +33978,7 @@
         <v>2.25</v>
       </c>
       <c r="AP159">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ159">
         <v>2</v>
@@ -34100,7 +34106,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34306,7 +34312,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34718,7 +34724,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35005,7 +35011,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ164">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR164">
         <v>1.72</v>
@@ -35130,7 +35136,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36366,7 +36372,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36572,7 +36578,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37065,7 +37071,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ174">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR174">
         <v>1.83</v>
@@ -37396,7 +37402,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37474,7 +37480,7 @@
         <v>1.22</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ176">
         <v>1.4</v>
@@ -37680,7 +37686,7 @@
         <v>1.44</v>
       </c>
       <c r="AP177">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ177">
         <v>1.3</v>
@@ -38014,7 +38020,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38426,7 +38432,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38632,7 +38638,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39250,7 +39256,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39662,7 +39668,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40280,7 +40286,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40437,6 +40443,418 @@
       </c>
       <c r="BP190">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7450842</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>84</v>
+      </c>
+      <c r="H191" t="s">
+        <v>78</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191">
+        <v>2</v>
+      </c>
+      <c r="M191">
+        <v>2</v>
+      </c>
+      <c r="N191">
+        <v>4</v>
+      </c>
+      <c r="O191" t="s">
+        <v>221</v>
+      </c>
+      <c r="P191" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q191">
+        <v>2.5</v>
+      </c>
+      <c r="R191">
+        <v>2.09</v>
+      </c>
+      <c r="S191">
+        <v>4.8</v>
+      </c>
+      <c r="T191">
+        <v>1.47</v>
+      </c>
+      <c r="U191">
+        <v>2.5</v>
+      </c>
+      <c r="V191">
+        <v>3.05</v>
+      </c>
+      <c r="W191">
+        <v>1.33</v>
+      </c>
+      <c r="X191">
+        <v>7</v>
+      </c>
+      <c r="Y191">
+        <v>1.06</v>
+      </c>
+      <c r="Z191">
+        <v>1.83</v>
+      </c>
+      <c r="AA191">
+        <v>3.4</v>
+      </c>
+      <c r="AB191">
+        <v>4.33</v>
+      </c>
+      <c r="AC191">
+        <v>1.07</v>
+      </c>
+      <c r="AD191">
+        <v>8</v>
+      </c>
+      <c r="AE191">
+        <v>1.38</v>
+      </c>
+      <c r="AF191">
+        <v>2.8</v>
+      </c>
+      <c r="AG191">
+        <v>2.1</v>
+      </c>
+      <c r="AH191">
+        <v>1.6</v>
+      </c>
+      <c r="AI191">
+        <v>1.95</v>
+      </c>
+      <c r="AJ191">
+        <v>1.77</v>
+      </c>
+      <c r="AK191">
+        <v>1.23</v>
+      </c>
+      <c r="AL191">
+        <v>1.3</v>
+      </c>
+      <c r="AM191">
+        <v>1.81</v>
+      </c>
+      <c r="AN191">
+        <v>1.4</v>
+      </c>
+      <c r="AO191">
+        <v>0.4</v>
+      </c>
+      <c r="AP191">
+        <v>1.36</v>
+      </c>
+      <c r="AQ191">
+        <v>0.45</v>
+      </c>
+      <c r="AR191">
+        <v>1.48</v>
+      </c>
+      <c r="AS191">
+        <v>1.29</v>
+      </c>
+      <c r="AT191">
+        <v>2.77</v>
+      </c>
+      <c r="AU191">
+        <v>10</v>
+      </c>
+      <c r="AV191">
+        <v>4</v>
+      </c>
+      <c r="AW191">
+        <v>18</v>
+      </c>
+      <c r="AX191">
+        <v>5</v>
+      </c>
+      <c r="AY191">
+        <v>36</v>
+      </c>
+      <c r="AZ191">
+        <v>11</v>
+      </c>
+      <c r="BA191">
+        <v>8</v>
+      </c>
+      <c r="BB191">
+        <v>2</v>
+      </c>
+      <c r="BC191">
+        <v>10</v>
+      </c>
+      <c r="BD191">
+        <v>1.65</v>
+      </c>
+      <c r="BE191">
+        <v>6.4</v>
+      </c>
+      <c r="BF191">
+        <v>2.55</v>
+      </c>
+      <c r="BG191">
+        <v>1.45</v>
+      </c>
+      <c r="BH191">
+        <v>2.45</v>
+      </c>
+      <c r="BI191">
+        <v>1.77</v>
+      </c>
+      <c r="BJ191">
+        <v>1.88</v>
+      </c>
+      <c r="BK191">
+        <v>2.25</v>
+      </c>
+      <c r="BL191">
+        <v>1.53</v>
+      </c>
+      <c r="BM191">
+        <v>2.9</v>
+      </c>
+      <c r="BN191">
+        <v>1.32</v>
+      </c>
+      <c r="BO191">
+        <v>3.9</v>
+      </c>
+      <c r="BP191">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7450844</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45709.6875</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>86</v>
+      </c>
+      <c r="H192" t="s">
+        <v>87</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>107</v>
+      </c>
+      <c r="P192" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q192">
+        <v>2.14</v>
+      </c>
+      <c r="R192">
+        <v>2.28</v>
+      </c>
+      <c r="S192">
+        <v>6.32</v>
+      </c>
+      <c r="T192">
+        <v>1.41</v>
+      </c>
+      <c r="U192">
+        <v>2.87</v>
+      </c>
+      <c r="V192">
+        <v>3.06</v>
+      </c>
+      <c r="W192">
+        <v>1.36</v>
+      </c>
+      <c r="X192">
+        <v>6.5</v>
+      </c>
+      <c r="Y192">
+        <v>1.08</v>
+      </c>
+      <c r="Z192">
+        <v>1.63</v>
+      </c>
+      <c r="AA192">
+        <v>3.75</v>
+      </c>
+      <c r="AB192">
+        <v>5.3</v>
+      </c>
+      <c r="AC192">
+        <v>1.06</v>
+      </c>
+      <c r="AD192">
+        <v>8.5</v>
+      </c>
+      <c r="AE192">
+        <v>1.33</v>
+      </c>
+      <c r="AF192">
+        <v>3</v>
+      </c>
+      <c r="AG192">
+        <v>1.95</v>
+      </c>
+      <c r="AH192">
+        <v>1.7</v>
+      </c>
+      <c r="AI192">
+        <v>2.08</v>
+      </c>
+      <c r="AJ192">
+        <v>1.68</v>
+      </c>
+      <c r="AK192">
+        <v>1.13</v>
+      </c>
+      <c r="AL192">
+        <v>1.22</v>
+      </c>
+      <c r="AM192">
+        <v>2.32</v>
+      </c>
+      <c r="AN192">
+        <v>1.5</v>
+      </c>
+      <c r="AO192">
+        <v>1.4</v>
+      </c>
+      <c r="AP192">
+        <v>1.64</v>
+      </c>
+      <c r="AQ192">
+        <v>1.27</v>
+      </c>
+      <c r="AR192">
+        <v>1.67</v>
+      </c>
+      <c r="AS192">
+        <v>1.41</v>
+      </c>
+      <c r="AT192">
+        <v>3.08</v>
+      </c>
+      <c r="AU192">
+        <v>4</v>
+      </c>
+      <c r="AV192">
+        <v>0</v>
+      </c>
+      <c r="AW192">
+        <v>9</v>
+      </c>
+      <c r="AX192">
+        <v>4</v>
+      </c>
+      <c r="AY192">
+        <v>19</v>
+      </c>
+      <c r="AZ192">
+        <v>7</v>
+      </c>
+      <c r="BA192">
+        <v>6</v>
+      </c>
+      <c r="BB192">
+        <v>3</v>
+      </c>
+      <c r="BC192">
+        <v>9</v>
+      </c>
+      <c r="BD192">
+        <v>1.49</v>
+      </c>
+      <c r="BE192">
+        <v>6.75</v>
+      </c>
+      <c r="BF192">
+        <v>2.95</v>
+      </c>
+      <c r="BG192">
+        <v>1.43</v>
+      </c>
+      <c r="BH192">
+        <v>2.5</v>
+      </c>
+      <c r="BI192">
+        <v>1.74</v>
+      </c>
+      <c r="BJ192">
+        <v>1.91</v>
+      </c>
+      <c r="BK192">
+        <v>2.2</v>
+      </c>
+      <c r="BL192">
+        <v>1.55</v>
+      </c>
+      <c r="BM192">
+        <v>2.88</v>
+      </c>
+      <c r="BN192">
+        <v>1.33</v>
+      </c>
+      <c r="BO192">
+        <v>3.85</v>
+      </c>
+      <c r="BP192">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="312">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -682,6 +682,12 @@
     <t>['59', '71']</t>
   </si>
   <si>
+    <t>['45+4', '76']</t>
+  </si>
+  <si>
+    <t>['17', '42', '54']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -941,6 +947,9 @@
   </si>
   <si>
     <t>['36', '53']</t>
+  </si>
+  <si>
+    <t>['8', '40', '53', '63']</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1970,7 +1979,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2588,7 +2597,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3000,7 +3009,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3412,7 +3421,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3618,7 +3627,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3824,7 +3833,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4030,7 +4039,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4108,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ14">
         <v>1.7</v>
@@ -4236,7 +4245,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4314,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ15">
         <v>1.4</v>
@@ -4442,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4523,7 +4532,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ16">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4729,7 +4738,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ17">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4932,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ18">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5553,7 +5562,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ21">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5678,7 +5687,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6296,7 +6305,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6502,7 +6511,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6708,7 +6717,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6914,7 +6923,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6992,7 +7001,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ28">
         <v>1.27</v>
@@ -7326,7 +7335,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7404,7 +7413,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ30">
         <v>2</v>
@@ -7738,7 +7747,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7944,7 +7953,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8025,7 +8034,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ33">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR33">
         <v>1.25</v>
@@ -8228,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ34">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR34">
         <v>1.4</v>
@@ -8356,7 +8365,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8974,7 +8983,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9180,7 +9189,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9798,7 +9807,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10416,7 +10425,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10494,7 +10503,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ45">
         <v>0.82</v>
@@ -10622,7 +10631,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11034,7 +11043,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11446,7 +11455,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11733,7 +11742,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ51">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.7</v>
@@ -11939,7 +11948,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ52">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12142,7 +12151,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ53">
         <v>0.45</v>
@@ -12270,7 +12279,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12476,7 +12485,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13094,7 +13103,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13172,7 +13181,7 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ58">
         <v>2</v>
@@ -13300,7 +13309,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13506,7 +13515,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13712,7 +13721,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13793,7 +13802,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ61">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR61">
         <v>1.79</v>
@@ -14330,7 +14339,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14742,7 +14751,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14823,7 +14832,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ66">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.22</v>
@@ -15438,7 +15447,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ69">
         <v>0.82</v>
@@ -15850,7 +15859,7 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71">
         <v>1.09</v>
@@ -16059,7 +16068,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ72">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16184,7 +16193,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16390,7 +16399,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16674,7 +16683,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ75">
         <v>1.36</v>
@@ -17501,7 +17510,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ79">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR79">
         <v>1.89</v>
@@ -17626,7 +17635,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17913,7 +17922,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ81">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.75</v>
@@ -18531,7 +18540,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR84">
         <v>1.58</v>
@@ -19068,7 +19077,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19146,7 +19155,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87">
         <v>1.4</v>
@@ -19274,7 +19283,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19480,7 +19489,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19686,7 +19695,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19892,7 +19901,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -19970,7 +19979,7 @@
         <v>0.6</v>
       </c>
       <c r="AP91">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ91">
         <v>1.09</v>
@@ -20304,7 +20313,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20382,7 +20391,7 @@
         <v>2.6</v>
       </c>
       <c r="AP93">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ93">
         <v>2.27</v>
@@ -20510,7 +20519,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20716,7 +20725,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20922,7 +20931,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21415,7 +21424,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ98">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR98">
         <v>1.72</v>
@@ -21540,7 +21549,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21618,7 +21627,7 @@
         <v>1.17</v>
       </c>
       <c r="AP99">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ99">
         <v>1.36</v>
@@ -21746,7 +21755,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21827,7 +21836,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ100">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR100">
         <v>1.26</v>
@@ -21952,7 +21961,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22158,7 +22167,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22364,7 +22373,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22651,7 +22660,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ104">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -22776,7 +22785,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23063,7 +23072,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ106">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.53</v>
@@ -23266,7 +23275,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ107">
         <v>0.55</v>
@@ -23394,7 +23403,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23600,7 +23609,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24012,7 +24021,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24630,7 +24639,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25042,7 +25051,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25120,7 +25129,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ116">
         <v>1.27</v>
@@ -25248,7 +25257,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25660,7 +25669,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -25741,7 +25750,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ119">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.67</v>
@@ -26150,7 +26159,7 @@
         <v>1.43</v>
       </c>
       <c r="AP121">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ121">
         <v>1.36</v>
@@ -26278,7 +26287,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26484,7 +26493,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26896,7 +26905,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27183,7 +27192,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ126">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR126">
         <v>1.67</v>
@@ -27308,7 +27317,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27514,7 +27523,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27798,7 +27807,7 @@
         <v>0.71</v>
       </c>
       <c r="AP129">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ129">
         <v>0.91</v>
@@ -27926,7 +27935,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28210,7 +28219,7 @@
         <v>0.71</v>
       </c>
       <c r="AP131">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ131">
         <v>0.82</v>
@@ -28338,7 +28347,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28750,7 +28759,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28956,7 +28965,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29037,7 +29046,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ135">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR135">
         <v>1.91</v>
@@ -29162,7 +29171,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29368,7 +29377,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29449,7 +29458,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ137">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR137">
         <v>1.82</v>
@@ -29574,7 +29583,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29655,7 +29664,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ138">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.26</v>
@@ -29986,7 +29995,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30192,7 +30201,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30270,7 +30279,7 @@
         <v>0.14</v>
       </c>
       <c r="AP141">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ141">
         <v>0.45</v>
@@ -31840,7 +31849,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31918,7 +31927,7 @@
         <v>2.25</v>
       </c>
       <c r="AP149">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ149">
         <v>2.27</v>
@@ -32046,7 +32055,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32124,7 +32133,7 @@
         <v>1.38</v>
       </c>
       <c r="AP150">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ150">
         <v>1.27</v>
@@ -32458,7 +32467,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32539,7 +32548,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ152">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR152">
         <v>1.7</v>
@@ -32948,7 +32957,7 @@
         <v>1.25</v>
       </c>
       <c r="AP154">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ154">
         <v>1.4</v>
@@ -33076,7 +33085,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33363,7 +33372,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ156">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR156">
         <v>1.39</v>
@@ -33566,7 +33575,7 @@
         <v>0.5</v>
       </c>
       <c r="AP157">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ157">
         <v>0.45</v>
@@ -33694,7 +33703,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34106,7 +34115,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34312,7 +34321,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34393,7 +34402,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ161">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34596,10 +34605,10 @@
         <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ162">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR162">
         <v>1.43</v>
@@ -34724,7 +34733,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35136,7 +35145,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36372,7 +36381,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36578,7 +36587,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37274,10 +37283,10 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ175">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR175">
         <v>1.56</v>
@@ -37402,7 +37411,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37689,7 +37698,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ177">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR177">
         <v>1.53</v>
@@ -37892,7 +37901,7 @@
         <v>1.56</v>
       </c>
       <c r="AP178">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ178">
         <v>1.27</v>
@@ -38020,7 +38029,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38098,7 +38107,7 @@
         <v>2.11</v>
       </c>
       <c r="AP179">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ179">
         <v>2</v>
@@ -38432,7 +38441,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38638,7 +38647,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39256,7 +39265,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39668,7 +39677,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -39749,7 +39758,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ187">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR187">
         <v>1.64</v>
@@ -40286,7 +40295,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40492,7 +40501,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40855,6 +40864,624 @@
       </c>
       <c r="BP192">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7450838</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45710.44791666666</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>85</v>
+      </c>
+      <c r="H193" t="s">
+        <v>71</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193">
+        <v>2</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>2</v>
+      </c>
+      <c r="O193" t="s">
+        <v>222</v>
+      </c>
+      <c r="P193" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q193">
+        <v>3.02</v>
+      </c>
+      <c r="R193">
+        <v>2.1</v>
+      </c>
+      <c r="S193">
+        <v>3.94</v>
+      </c>
+      <c r="T193">
+        <v>1.46</v>
+      </c>
+      <c r="U193">
+        <v>2.68</v>
+      </c>
+      <c r="V193">
+        <v>3.32</v>
+      </c>
+      <c r="W193">
+        <v>1.32</v>
+      </c>
+      <c r="X193">
+        <v>7</v>
+      </c>
+      <c r="Y193">
+        <v>1.06</v>
+      </c>
+      <c r="Z193">
+        <v>2.35</v>
+      </c>
+      <c r="AA193">
+        <v>3.09</v>
+      </c>
+      <c r="AB193">
+        <v>3.12</v>
+      </c>
+      <c r="AC193">
+        <v>1.08</v>
+      </c>
+      <c r="AD193">
+        <v>7.5</v>
+      </c>
+      <c r="AE193">
+        <v>1.39</v>
+      </c>
+      <c r="AF193">
+        <v>2.75</v>
+      </c>
+      <c r="AG193">
+        <v>2.15</v>
+      </c>
+      <c r="AH193">
+        <v>1.6</v>
+      </c>
+      <c r="AI193">
+        <v>1.89</v>
+      </c>
+      <c r="AJ193">
+        <v>1.82</v>
+      </c>
+      <c r="AK193">
+        <v>1.34</v>
+      </c>
+      <c r="AL193">
+        <v>1.33</v>
+      </c>
+      <c r="AM193">
+        <v>1.56</v>
+      </c>
+      <c r="AN193">
+        <v>1.1</v>
+      </c>
+      <c r="AO193">
+        <v>0.4</v>
+      </c>
+      <c r="AP193">
+        <v>1.27</v>
+      </c>
+      <c r="AQ193">
+        <v>0.36</v>
+      </c>
+      <c r="AR193">
+        <v>1.41</v>
+      </c>
+      <c r="AS193">
+        <v>1.32</v>
+      </c>
+      <c r="AT193">
+        <v>2.73</v>
+      </c>
+      <c r="AU193">
+        <v>6</v>
+      </c>
+      <c r="AV193">
+        <v>6</v>
+      </c>
+      <c r="AW193">
+        <v>3</v>
+      </c>
+      <c r="AX193">
+        <v>6</v>
+      </c>
+      <c r="AY193">
+        <v>11</v>
+      </c>
+      <c r="AZ193">
+        <v>13</v>
+      </c>
+      <c r="BA193">
+        <v>5</v>
+      </c>
+      <c r="BB193">
+        <v>12</v>
+      </c>
+      <c r="BC193">
+        <v>17</v>
+      </c>
+      <c r="BD193">
+        <v>1.86</v>
+      </c>
+      <c r="BE193">
+        <v>6.25</v>
+      </c>
+      <c r="BF193">
+        <v>2.17</v>
+      </c>
+      <c r="BG193">
+        <v>1.44</v>
+      </c>
+      <c r="BH193">
+        <v>2.45</v>
+      </c>
+      <c r="BI193">
+        <v>1.77</v>
+      </c>
+      <c r="BJ193">
+        <v>1.88</v>
+      </c>
+      <c r="BK193">
+        <v>2.25</v>
+      </c>
+      <c r="BL193">
+        <v>1.53</v>
+      </c>
+      <c r="BM193">
+        <v>2.95</v>
+      </c>
+      <c r="BN193">
+        <v>1.32</v>
+      </c>
+      <c r="BO193">
+        <v>3.95</v>
+      </c>
+      <c r="BP193">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7450845</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45710.5625</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>82</v>
+      </c>
+      <c r="H194" t="s">
+        <v>73</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>2</v>
+      </c>
+      <c r="K194">
+        <v>2</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>4</v>
+      </c>
+      <c r="N194">
+        <v>4</v>
+      </c>
+      <c r="O194" t="s">
+        <v>95</v>
+      </c>
+      <c r="P194" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q194">
+        <v>3.56</v>
+      </c>
+      <c r="R194">
+        <v>2.22</v>
+      </c>
+      <c r="S194">
+        <v>2.68</v>
+      </c>
+      <c r="T194">
+        <v>1.3</v>
+      </c>
+      <c r="U194">
+        <v>3.28</v>
+      </c>
+      <c r="V194">
+        <v>2.53</v>
+      </c>
+      <c r="W194">
+        <v>1.47</v>
+      </c>
+      <c r="X194">
+        <v>6.3</v>
+      </c>
+      <c r="Y194">
+        <v>1.06</v>
+      </c>
+      <c r="Z194">
+        <v>3.11</v>
+      </c>
+      <c r="AA194">
+        <v>3.52</v>
+      </c>
+      <c r="AB194">
+        <v>2.15</v>
+      </c>
+      <c r="AC194">
+        <v>1.01</v>
+      </c>
+      <c r="AD194">
+        <v>11</v>
+      </c>
+      <c r="AE194">
+        <v>1.16</v>
+      </c>
+      <c r="AF194">
+        <v>4.15</v>
+      </c>
+      <c r="AG194">
+        <v>1.65</v>
+      </c>
+      <c r="AH194">
+        <v>2</v>
+      </c>
+      <c r="AI194">
+        <v>1.57</v>
+      </c>
+      <c r="AJ194">
+        <v>2.25</v>
+      </c>
+      <c r="AK194">
+        <v>1.67</v>
+      </c>
+      <c r="AL194">
+        <v>1.27</v>
+      </c>
+      <c r="AM194">
+        <v>1.35</v>
+      </c>
+      <c r="AN194">
+        <v>1.7</v>
+      </c>
+      <c r="AO194">
+        <v>0.8</v>
+      </c>
+      <c r="AP194">
+        <v>1.55</v>
+      </c>
+      <c r="AQ194">
+        <v>1</v>
+      </c>
+      <c r="AR194">
+        <v>1.4</v>
+      </c>
+      <c r="AS194">
+        <v>1.39</v>
+      </c>
+      <c r="AT194">
+        <v>2.79</v>
+      </c>
+      <c r="AU194">
+        <v>7</v>
+      </c>
+      <c r="AV194">
+        <v>9</v>
+      </c>
+      <c r="AW194">
+        <v>5</v>
+      </c>
+      <c r="AX194">
+        <v>10</v>
+      </c>
+      <c r="AY194">
+        <v>14</v>
+      </c>
+      <c r="AZ194">
+        <v>26</v>
+      </c>
+      <c r="BA194">
+        <v>5</v>
+      </c>
+      <c r="BB194">
+        <v>7</v>
+      </c>
+      <c r="BC194">
+        <v>12</v>
+      </c>
+      <c r="BD194">
+        <v>2.23</v>
+      </c>
+      <c r="BE194">
+        <v>6.4</v>
+      </c>
+      <c r="BF194">
+        <v>1.8</v>
+      </c>
+      <c r="BG194">
+        <v>1.33</v>
+      </c>
+      <c r="BH194">
+        <v>2.88</v>
+      </c>
+      <c r="BI194">
+        <v>1.58</v>
+      </c>
+      <c r="BJ194">
+        <v>2.15</v>
+      </c>
+      <c r="BK194">
+        <v>1.94</v>
+      </c>
+      <c r="BL194">
+        <v>1.72</v>
+      </c>
+      <c r="BM194">
+        <v>2.48</v>
+      </c>
+      <c r="BN194">
+        <v>1.44</v>
+      </c>
+      <c r="BO194">
+        <v>3.3</v>
+      </c>
+      <c r="BP194">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7450843</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45710.67708333334</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>81</v>
+      </c>
+      <c r="H195" t="s">
+        <v>74</v>
+      </c>
+      <c r="I195">
+        <v>2</v>
+      </c>
+      <c r="J195">
+        <v>1</v>
+      </c>
+      <c r="K195">
+        <v>3</v>
+      </c>
+      <c r="L195">
+        <v>3</v>
+      </c>
+      <c r="M195">
+        <v>1</v>
+      </c>
+      <c r="N195">
+        <v>4</v>
+      </c>
+      <c r="O195" t="s">
+        <v>223</v>
+      </c>
+      <c r="P195" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q195">
+        <v>4.37</v>
+      </c>
+      <c r="R195">
+        <v>2.34</v>
+      </c>
+      <c r="S195">
+        <v>2.46</v>
+      </c>
+      <c r="T195">
+        <v>1.33</v>
+      </c>
+      <c r="U195">
+        <v>3.23</v>
+      </c>
+      <c r="V195">
+        <v>2.67</v>
+      </c>
+      <c r="W195">
+        <v>1.46</v>
+      </c>
+      <c r="X195">
+        <v>5.7</v>
+      </c>
+      <c r="Y195">
+        <v>1.11</v>
+      </c>
+      <c r="Z195">
+        <v>3.78</v>
+      </c>
+      <c r="AA195">
+        <v>3.72</v>
+      </c>
+      <c r="AB195">
+        <v>1.86</v>
+      </c>
+      <c r="AC195">
+        <v>1.05</v>
+      </c>
+      <c r="AD195">
+        <v>9.5</v>
+      </c>
+      <c r="AE195">
+        <v>1.23</v>
+      </c>
+      <c r="AF195">
+        <v>3.75</v>
+      </c>
+      <c r="AG195">
+        <v>1.73</v>
+      </c>
+      <c r="AH195">
+        <v>1.91</v>
+      </c>
+      <c r="AI195">
+        <v>1.65</v>
+      </c>
+      <c r="AJ195">
+        <v>2.11</v>
+      </c>
+      <c r="AK195">
+        <v>1.84</v>
+      </c>
+      <c r="AL195">
+        <v>1.25</v>
+      </c>
+      <c r="AM195">
+        <v>1.26</v>
+      </c>
+      <c r="AN195">
+        <v>1.2</v>
+      </c>
+      <c r="AO195">
+        <v>1.3</v>
+      </c>
+      <c r="AP195">
+        <v>1.36</v>
+      </c>
+      <c r="AQ195">
+        <v>1.18</v>
+      </c>
+      <c r="AR195">
+        <v>1.57</v>
+      </c>
+      <c r="AS195">
+        <v>1.51</v>
+      </c>
+      <c r="AT195">
+        <v>3.08</v>
+      </c>
+      <c r="AU195">
+        <v>6</v>
+      </c>
+      <c r="AV195">
+        <v>3</v>
+      </c>
+      <c r="AW195">
+        <v>11</v>
+      </c>
+      <c r="AX195">
+        <v>8</v>
+      </c>
+      <c r="AY195">
+        <v>19</v>
+      </c>
+      <c r="AZ195">
+        <v>14</v>
+      </c>
+      <c r="BA195">
+        <v>3</v>
+      </c>
+      <c r="BB195">
+        <v>5</v>
+      </c>
+      <c r="BC195">
+        <v>8</v>
+      </c>
+      <c r="BD195">
+        <v>2.55</v>
+      </c>
+      <c r="BE195">
+        <v>6.75</v>
+      </c>
+      <c r="BF195">
+        <v>1.6</v>
+      </c>
+      <c r="BG195">
+        <v>1.33</v>
+      </c>
+      <c r="BH195">
+        <v>2.88</v>
+      </c>
+      <c r="BI195">
+        <v>1.56</v>
+      </c>
+      <c r="BJ195">
+        <v>2.17</v>
+      </c>
+      <c r="BK195">
+        <v>1.91</v>
+      </c>
+      <c r="BL195">
+        <v>1.74</v>
+      </c>
+      <c r="BM195">
+        <v>2.45</v>
+      </c>
+      <c r="BN195">
+        <v>1.5</v>
+      </c>
+      <c r="BO195">
+        <v>3.2</v>
+      </c>
+      <c r="BP195">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="316">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,12 @@
     <t>['17', '42', '54']</t>
   </si>
   <si>
+    <t>['73', '85']</t>
+  </si>
+  <si>
+    <t>['2', '18', '79']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -950,6 +956,12 @@
   </si>
   <si>
     <t>['8', '40', '53', '63']</t>
+  </si>
+  <si>
+    <t>['18', '61']</t>
+  </si>
+  <si>
+    <t>['34', '39']</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1648,7 +1660,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ2">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1979,7 +1991,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2472,7 +2484,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ6">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2597,7 +2609,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2675,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
         <v>1.36</v>
@@ -2881,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ8">
         <v>1.27</v>
@@ -3009,7 +3021,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3421,7 +3433,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3627,7 +3639,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3705,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ12">
         <v>1.27</v>
@@ -3833,7 +3845,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4039,7 +4051,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4120,7 +4132,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ14">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4245,7 +4257,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4451,7 +4463,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5356,7 +5368,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ20">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR20">
         <v>0.84</v>
@@ -5687,7 +5699,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6177,7 +6189,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ24">
         <v>0.91</v>
@@ -6305,7 +6317,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6511,7 +6523,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6717,7 +6729,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6795,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ27">
         <v>0.82</v>
@@ -6923,7 +6935,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7335,7 +7347,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7747,7 +7759,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7825,10 +7837,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR32">
         <v>1.13</v>
@@ -7953,7 +7965,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8365,7 +8377,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8983,7 +8995,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9189,7 +9201,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9807,7 +9819,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10425,7 +10437,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10631,7 +10643,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10709,7 +10721,7 @@
         <v>2.33</v>
       </c>
       <c r="AP46">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
         <v>2.27</v>
@@ -10918,7 +10930,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR47">
         <v>1.43</v>
@@ -11043,7 +11055,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11121,7 +11133,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ48">
         <v>1.27</v>
@@ -11330,7 +11342,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ49">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11455,7 +11467,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11536,7 +11548,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ50">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR50">
         <v>1.73</v>
@@ -11739,7 +11751,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -12279,7 +12291,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12485,7 +12497,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13103,7 +13115,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13309,7 +13321,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13515,7 +13527,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13721,7 +13733,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14339,7 +14351,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14623,7 +14635,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ65">
         <v>0.82</v>
@@ -14751,7 +14763,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14829,7 +14841,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -15035,10 +15047,10 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ67">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR67">
         <v>1.96</v>
@@ -15244,7 +15256,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ68">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR68">
         <v>1.44</v>
@@ -15450,7 +15462,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ69">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -16193,7 +16205,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16399,7 +16411,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17304,7 +17316,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ78">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR78">
         <v>1.53</v>
@@ -17507,7 +17519,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ79">
         <v>0.36</v>
@@ -17635,7 +17647,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17716,7 +17728,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ80">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR80">
         <v>1.47</v>
@@ -18125,7 +18137,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
         <v>0.82</v>
@@ -18334,7 +18346,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ83">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR83">
         <v>1.5</v>
@@ -19077,7 +19089,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19283,7 +19295,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19364,7 +19376,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ88">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR88">
         <v>1.53</v>
@@ -19489,7 +19501,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19567,7 +19579,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ89">
         <v>0.45</v>
@@ -19695,7 +19707,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19901,7 +19913,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20313,7 +20325,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20519,7 +20531,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20600,7 +20612,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ94">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR94">
         <v>1.85</v>
@@ -20725,7 +20737,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20803,7 +20815,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ95">
         <v>1.27</v>
@@ -20931,7 +20943,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21549,7 +21561,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21755,7 +21767,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21833,7 +21845,7 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ100">
         <v>1.18</v>
@@ -21961,7 +21973,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22167,7 +22179,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22248,7 +22260,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ102">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR102">
         <v>1.67</v>
@@ -22373,7 +22385,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22451,7 +22463,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ103">
         <v>1.4</v>
@@ -22785,7 +22797,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23278,7 +23290,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ107">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23403,7 +23415,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23609,7 +23621,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23896,7 +23908,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ110">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR110">
         <v>1.69</v>
@@ -24021,7 +24033,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24099,7 +24111,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ111">
         <v>1.27</v>
@@ -24511,7 +24523,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ113">
         <v>0.82</v>
@@ -24639,7 +24651,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24720,7 +24732,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ114">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR114">
         <v>1.55</v>
@@ -25051,7 +25063,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25257,7 +25269,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25669,7 +25681,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26287,7 +26299,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26368,7 +26380,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ122">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR122">
         <v>2.04</v>
@@ -26493,7 +26505,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26571,7 +26583,7 @@
         <v>2.5</v>
       </c>
       <c r="AP123">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ123">
         <v>2</v>
@@ -26905,7 +26917,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27317,7 +27329,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27523,7 +27535,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27935,7 +27947,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28013,7 +28025,7 @@
         <v>1.17</v>
       </c>
       <c r="AP130">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ130">
         <v>1.4</v>
@@ -28222,7 +28234,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ131">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28347,7 +28359,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28634,7 +28646,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ133">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR133">
         <v>1.65</v>
@@ -28759,7 +28771,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28965,7 +28977,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29043,7 +29055,7 @@
         <v>1.5</v>
       </c>
       <c r="AP135">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ135">
         <v>1.18</v>
@@ -29171,7 +29183,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29377,7 +29389,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29583,7 +29595,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29661,7 +29673,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -29867,7 +29879,7 @@
         <v>1.43</v>
       </c>
       <c r="AP139">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ139">
         <v>1.4</v>
@@ -29995,7 +30007,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30201,7 +30213,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31103,10 +31115,10 @@
         <v>0.63</v>
       </c>
       <c r="AP145">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ145">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR145">
         <v>1.63</v>
@@ -31518,7 +31530,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ147">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR147">
         <v>1.42</v>
@@ -31849,7 +31861,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32055,7 +32067,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32342,7 +32354,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ151">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR151">
         <v>1.81</v>
@@ -32467,7 +32479,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33085,7 +33097,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33369,7 +33381,7 @@
         <v>0.38</v>
       </c>
       <c r="AP156">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ156">
         <v>0.36</v>
@@ -33703,7 +33715,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34115,7 +34127,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34196,7 +34208,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ160">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR160">
         <v>1.51</v>
@@ -34321,7 +34333,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34733,7 +34745,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35145,7 +35157,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35223,7 +35235,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ165">
         <v>0.82</v>
@@ -35635,7 +35647,7 @@
         <v>2.33</v>
       </c>
       <c r="AP167">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ167">
         <v>2.27</v>
@@ -35844,7 +35856,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ168">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR168">
         <v>1.8</v>
@@ -36050,7 +36062,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ169">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR169">
         <v>1.91</v>
@@ -36381,7 +36393,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36587,7 +36599,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36874,7 +36886,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ173">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR173">
         <v>1.71</v>
@@ -37411,7 +37423,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -38029,7 +38041,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38313,7 +38325,7 @@
         <v>1.56</v>
       </c>
       <c r="AP180">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ180">
         <v>1.4</v>
@@ -38441,7 +38453,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38522,7 +38534,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ181">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR181">
         <v>1.46</v>
@@ -38647,7 +38659,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -38725,7 +38737,7 @@
         <v>1.1</v>
       </c>
       <c r="AP182">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ182">
         <v>1.09</v>
@@ -38931,7 +38943,7 @@
         <v>2.2</v>
       </c>
       <c r="AP183">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ183">
         <v>2.27</v>
@@ -39265,7 +39277,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39552,7 +39564,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ186">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR186">
         <v>1.66</v>
@@ -39677,7 +39689,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40295,7 +40307,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40501,7 +40513,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41119,7 +41131,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41482,6 +41494,624 @@
       </c>
       <c r="BP195">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7450840</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45711.34375</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>80</v>
+      </c>
+      <c r="H196" t="s">
+        <v>79</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>2</v>
+      </c>
+      <c r="N196">
+        <v>2</v>
+      </c>
+      <c r="O196" t="s">
+        <v>95</v>
+      </c>
+      <c r="P196" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q196">
+        <v>2.95</v>
+      </c>
+      <c r="R196">
+        <v>2.13</v>
+      </c>
+      <c r="S196">
+        <v>3.7</v>
+      </c>
+      <c r="T196">
+        <v>1.43</v>
+      </c>
+      <c r="U196">
+        <v>2.65</v>
+      </c>
+      <c r="V196">
+        <v>2.85</v>
+      </c>
+      <c r="W196">
+        <v>1.38</v>
+      </c>
+      <c r="X196">
+        <v>7</v>
+      </c>
+      <c r="Y196">
+        <v>1.07</v>
+      </c>
+      <c r="Z196">
+        <v>2.29</v>
+      </c>
+      <c r="AA196">
+        <v>3.34</v>
+      </c>
+      <c r="AB196">
+        <v>2.99</v>
+      </c>
+      <c r="AC196">
+        <v>1.06</v>
+      </c>
+      <c r="AD196">
+        <v>8.5</v>
+      </c>
+      <c r="AE196">
+        <v>1.32</v>
+      </c>
+      <c r="AF196">
+        <v>3.1</v>
+      </c>
+      <c r="AG196">
+        <v>1.98</v>
+      </c>
+      <c r="AH196">
+        <v>1.77</v>
+      </c>
+      <c r="AI196">
+        <v>1.76</v>
+      </c>
+      <c r="AJ196">
+        <v>1.96</v>
+      </c>
+      <c r="AK196">
+        <v>1.36</v>
+      </c>
+      <c r="AL196">
+        <v>1.3</v>
+      </c>
+      <c r="AM196">
+        <v>1.58</v>
+      </c>
+      <c r="AN196">
+        <v>1.1</v>
+      </c>
+      <c r="AO196">
+        <v>0.55</v>
+      </c>
+      <c r="AP196">
+        <v>1</v>
+      </c>
+      <c r="AQ196">
+        <v>0.75</v>
+      </c>
+      <c r="AR196">
+        <v>1.46</v>
+      </c>
+      <c r="AS196">
+        <v>1</v>
+      </c>
+      <c r="AT196">
+        <v>2.46</v>
+      </c>
+      <c r="AU196">
+        <v>8</v>
+      </c>
+      <c r="AV196">
+        <v>4</v>
+      </c>
+      <c r="AW196">
+        <v>11</v>
+      </c>
+      <c r="AX196">
+        <v>8</v>
+      </c>
+      <c r="AY196">
+        <v>24</v>
+      </c>
+      <c r="AZ196">
+        <v>18</v>
+      </c>
+      <c r="BA196">
+        <v>8</v>
+      </c>
+      <c r="BB196">
+        <v>7</v>
+      </c>
+      <c r="BC196">
+        <v>15</v>
+      </c>
+      <c r="BD196">
+        <v>1.84</v>
+      </c>
+      <c r="BE196">
+        <v>6.4</v>
+      </c>
+      <c r="BF196">
+        <v>2.17</v>
+      </c>
+      <c r="BG196">
+        <v>1.4</v>
+      </c>
+      <c r="BH196">
+        <v>2.6</v>
+      </c>
+      <c r="BI196">
+        <v>1.53</v>
+      </c>
+      <c r="BJ196">
+        <v>2.35</v>
+      </c>
+      <c r="BK196">
+        <v>2.15</v>
+      </c>
+      <c r="BL196">
+        <v>1.58</v>
+      </c>
+      <c r="BM196">
+        <v>2.8</v>
+      </c>
+      <c r="BN196">
+        <v>1.35</v>
+      </c>
+      <c r="BO196">
+        <v>3.7</v>
+      </c>
+      <c r="BP196">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7450837</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45711.44791666666</v>
+      </c>
+      <c r="F197">
+        <v>22</v>
+      </c>
+      <c r="G197" t="s">
+        <v>75</v>
+      </c>
+      <c r="H197" t="s">
+        <v>70</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>2</v>
+      </c>
+      <c r="K197">
+        <v>2</v>
+      </c>
+      <c r="L197">
+        <v>2</v>
+      </c>
+      <c r="M197">
+        <v>2</v>
+      </c>
+      <c r="N197">
+        <v>4</v>
+      </c>
+      <c r="O197" t="s">
+        <v>224</v>
+      </c>
+      <c r="P197" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q197">
+        <v>2.8</v>
+      </c>
+      <c r="R197">
+        <v>2.28</v>
+      </c>
+      <c r="S197">
+        <v>3.55</v>
+      </c>
+      <c r="T197">
+        <v>1.34</v>
+      </c>
+      <c r="U197">
+        <v>3</v>
+      </c>
+      <c r="V197">
+        <v>2.45</v>
+      </c>
+      <c r="W197">
+        <v>1.48</v>
+      </c>
+      <c r="X197">
+        <v>5.7</v>
+      </c>
+      <c r="Y197">
+        <v>1.11</v>
+      </c>
+      <c r="Z197">
+        <v>2.24</v>
+      </c>
+      <c r="AA197">
+        <v>3.52</v>
+      </c>
+      <c r="AB197">
+        <v>2.94</v>
+      </c>
+      <c r="AC197">
+        <v>1.05</v>
+      </c>
+      <c r="AD197">
+        <v>9.5</v>
+      </c>
+      <c r="AE197">
+        <v>1.23</v>
+      </c>
+      <c r="AF197">
+        <v>3.85</v>
+      </c>
+      <c r="AG197">
+        <v>1.7</v>
+      </c>
+      <c r="AH197">
+        <v>1.95</v>
+      </c>
+      <c r="AI197">
+        <v>1.59</v>
+      </c>
+      <c r="AJ197">
+        <v>2.22</v>
+      </c>
+      <c r="AK197">
+        <v>1.37</v>
+      </c>
+      <c r="AL197">
+        <v>1.27</v>
+      </c>
+      <c r="AM197">
+        <v>1.61</v>
+      </c>
+      <c r="AN197">
+        <v>1.27</v>
+      </c>
+      <c r="AO197">
+        <v>1.7</v>
+      </c>
+      <c r="AP197">
+        <v>1.25</v>
+      </c>
+      <c r="AQ197">
+        <v>1.64</v>
+      </c>
+      <c r="AR197">
+        <v>1.68</v>
+      </c>
+      <c r="AS197">
+        <v>1.26</v>
+      </c>
+      <c r="AT197">
+        <v>2.94</v>
+      </c>
+      <c r="AU197">
+        <v>3</v>
+      </c>
+      <c r="AV197">
+        <v>5</v>
+      </c>
+      <c r="AW197">
+        <v>3</v>
+      </c>
+      <c r="AX197">
+        <v>8</v>
+      </c>
+      <c r="AY197">
+        <v>6</v>
+      </c>
+      <c r="AZ197">
+        <v>16</v>
+      </c>
+      <c r="BA197">
+        <v>4</v>
+      </c>
+      <c r="BB197">
+        <v>11</v>
+      </c>
+      <c r="BC197">
+        <v>15</v>
+      </c>
+      <c r="BD197">
+        <v>1.84</v>
+      </c>
+      <c r="BE197">
+        <v>6.4</v>
+      </c>
+      <c r="BF197">
+        <v>2.17</v>
+      </c>
+      <c r="BG197">
+        <v>1.34</v>
+      </c>
+      <c r="BH197">
+        <v>2.85</v>
+      </c>
+      <c r="BI197">
+        <v>1.6</v>
+      </c>
+      <c r="BJ197">
+        <v>2.12</v>
+      </c>
+      <c r="BK197">
+        <v>1.96</v>
+      </c>
+      <c r="BL197">
+        <v>1.7</v>
+      </c>
+      <c r="BM197">
+        <v>2.5</v>
+      </c>
+      <c r="BN197">
+        <v>1.42</v>
+      </c>
+      <c r="BO197">
+        <v>3.3</v>
+      </c>
+      <c r="BP197">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7450839</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45711.5625</v>
+      </c>
+      <c r="F198">
+        <v>22</v>
+      </c>
+      <c r="G198" t="s">
+        <v>76</v>
+      </c>
+      <c r="H198" t="s">
+        <v>83</v>
+      </c>
+      <c r="I198">
+        <v>2</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>3</v>
+      </c>
+      <c r="L198">
+        <v>3</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>4</v>
+      </c>
+      <c r="O198" t="s">
+        <v>225</v>
+      </c>
+      <c r="P198" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q198">
+        <v>1.95</v>
+      </c>
+      <c r="R198">
+        <v>2.4</v>
+      </c>
+      <c r="S198">
+        <v>6.5</v>
+      </c>
+      <c r="T198">
+        <v>1.33</v>
+      </c>
+      <c r="U198">
+        <v>3.25</v>
+      </c>
+      <c r="V198">
+        <v>2.5</v>
+      </c>
+      <c r="W198">
+        <v>1.5</v>
+      </c>
+      <c r="X198">
+        <v>6.5</v>
+      </c>
+      <c r="Y198">
+        <v>1.11</v>
+      </c>
+      <c r="Z198">
+        <v>1.48</v>
+      </c>
+      <c r="AA198">
+        <v>4.3</v>
+      </c>
+      <c r="AB198">
+        <v>6.2</v>
+      </c>
+      <c r="AC198">
+        <v>1.04</v>
+      </c>
+      <c r="AD198">
+        <v>10</v>
+      </c>
+      <c r="AE198">
+        <v>1.21</v>
+      </c>
+      <c r="AF198">
+        <v>4</v>
+      </c>
+      <c r="AG198">
+        <v>1.77</v>
+      </c>
+      <c r="AH198">
+        <v>1.98</v>
+      </c>
+      <c r="AI198">
+        <v>1.91</v>
+      </c>
+      <c r="AJ198">
+        <v>1.91</v>
+      </c>
+      <c r="AK198">
+        <v>1.12</v>
+      </c>
+      <c r="AL198">
+        <v>1.18</v>
+      </c>
+      <c r="AM198">
+        <v>2.32</v>
+      </c>
+      <c r="AN198">
+        <v>2.45</v>
+      </c>
+      <c r="AO198">
+        <v>0.82</v>
+      </c>
+      <c r="AP198">
+        <v>2.5</v>
+      </c>
+      <c r="AQ198">
+        <v>0.75</v>
+      </c>
+      <c r="AR198">
+        <v>1.96</v>
+      </c>
+      <c r="AS198">
+        <v>1.41</v>
+      </c>
+      <c r="AT198">
+        <v>3.37</v>
+      </c>
+      <c r="AU198">
+        <v>6</v>
+      </c>
+      <c r="AV198">
+        <v>5</v>
+      </c>
+      <c r="AW198">
+        <v>6</v>
+      </c>
+      <c r="AX198">
+        <v>9</v>
+      </c>
+      <c r="AY198">
+        <v>17</v>
+      </c>
+      <c r="AZ198">
+        <v>16</v>
+      </c>
+      <c r="BA198">
+        <v>4</v>
+      </c>
+      <c r="BB198">
+        <v>13</v>
+      </c>
+      <c r="BC198">
+        <v>17</v>
+      </c>
+      <c r="BD198">
+        <v>1.38</v>
+      </c>
+      <c r="BE198">
+        <v>7.5</v>
+      </c>
+      <c r="BF198">
+        <v>3.4</v>
+      </c>
+      <c r="BG198">
+        <v>1.21</v>
+      </c>
+      <c r="BH198">
+        <v>3.65</v>
+      </c>
+      <c r="BI198">
+        <v>1.37</v>
+      </c>
+      <c r="BJ198">
+        <v>2.7</v>
+      </c>
+      <c r="BK198">
+        <v>1.62</v>
+      </c>
+      <c r="BL198">
+        <v>2.08</v>
+      </c>
+      <c r="BM198">
+        <v>2</v>
+      </c>
+      <c r="BN198">
+        <v>1.73</v>
+      </c>
+      <c r="BO198">
+        <v>2.45</v>
+      </c>
+      <c r="BP198">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -694,6 +694,9 @@
     <t>['2', '18', '79']</t>
   </si>
   <si>
+    <t>['15', '21', '57']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -962,6 +965,9 @@
   </si>
   <si>
     <t>['34', '39']</t>
+  </si>
+  <si>
+    <t>['8', '51']</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1991,7 +1997,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2609,7 +2615,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3021,7 +3027,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3099,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ9">
         <v>2.27</v>
@@ -3433,7 +3439,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3639,7 +3645,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3845,7 +3851,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3926,7 +3932,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ13">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR13">
         <v>1.41</v>
@@ -4051,7 +4057,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4257,7 +4263,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4463,7 +4469,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5699,7 +5705,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6317,7 +6323,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6395,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ25">
         <v>1.09</v>
@@ -6523,7 +6529,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6729,7 +6735,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6935,7 +6941,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7347,7 +7353,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7759,7 +7765,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7965,7 +7971,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8377,7 +8383,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8458,7 +8464,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ35">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR35">
         <v>1.34</v>
@@ -8995,7 +9001,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9201,7 +9207,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9819,7 +9825,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10437,7 +10443,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10643,7 +10649,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10927,7 +10933,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ47">
         <v>0.75</v>
@@ -11055,7 +11061,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11467,7 +11473,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12291,7 +12297,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12497,7 +12503,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12990,7 +12996,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ57">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR57">
         <v>1.6</v>
@@ -13115,7 +13121,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13321,7 +13327,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13527,7 +13533,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13733,7 +13739,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14223,7 +14229,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ63">
         <v>1.27</v>
@@ -14351,7 +14357,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14763,7 +14769,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -16205,7 +16211,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16411,7 +16417,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16904,7 +16910,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ76">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR76">
         <v>1.53</v>
@@ -17647,7 +17653,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17725,7 +17731,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ80">
         <v>1.64</v>
@@ -18549,7 +18555,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ84">
         <v>0.36</v>
@@ -19089,7 +19095,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19295,7 +19301,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19501,7 +19507,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19707,7 +19713,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19788,7 +19794,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ90">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR90">
         <v>1.39</v>
@@ -19913,7 +19919,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20325,7 +20331,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20531,7 +20537,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20737,7 +20743,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20943,7 +20949,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21561,7 +21567,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21767,7 +21773,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21973,7 +21979,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22051,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ101">
         <v>0.82</v>
@@ -22179,7 +22185,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22385,7 +22391,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22797,7 +22803,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23415,7 +23421,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23621,7 +23627,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24033,7 +24039,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24651,7 +24657,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25063,7 +25069,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25269,7 +25275,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25350,7 +25356,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ117">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR117">
         <v>1.54</v>
@@ -25681,7 +25687,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -25759,7 +25765,7 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -26299,7 +26305,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26505,7 +26511,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26917,7 +26923,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27329,7 +27335,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27535,7 +27541,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27947,7 +27953,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28028,7 +28034,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ130">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR130">
         <v>1.6</v>
@@ -28359,7 +28365,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28771,7 +28777,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28977,7 +28983,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29183,7 +29189,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29389,7 +29395,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29595,7 +29601,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29882,7 +29888,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ139">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR139">
         <v>1.94</v>
@@ -30007,7 +30013,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30213,7 +30219,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31861,7 +31867,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32067,7 +32073,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32479,7 +32485,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32763,7 +32769,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ153">
         <v>0.82</v>
@@ -32972,7 +32978,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ154">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR154">
         <v>1.51</v>
@@ -33097,7 +33103,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33715,7 +33721,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34127,7 +34133,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34333,7 +34339,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34745,7 +34751,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35157,7 +35163,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35441,7 +35447,7 @@
         <v>0.67</v>
       </c>
       <c r="AP166">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ166">
         <v>0.91</v>
@@ -36393,7 +36399,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36599,7 +36605,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37423,7 +37429,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37504,7 +37510,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ176">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR176">
         <v>1.63</v>
@@ -38041,7 +38047,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38453,7 +38459,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38659,7 +38665,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39277,7 +39283,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39689,7 +39695,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40307,7 +40313,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40513,7 +40519,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41131,7 +41137,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41543,7 +41549,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41749,7 +41755,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42112,6 +42118,212 @@
       </c>
       <c r="BP198">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7450841</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45712.625</v>
+      </c>
+      <c r="F199">
+        <v>22</v>
+      </c>
+      <c r="G199" t="s">
+        <v>77</v>
+      </c>
+      <c r="H199" t="s">
+        <v>72</v>
+      </c>
+      <c r="I199">
+        <v>2</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>3</v>
+      </c>
+      <c r="L199">
+        <v>3</v>
+      </c>
+      <c r="M199">
+        <v>2</v>
+      </c>
+      <c r="N199">
+        <v>5</v>
+      </c>
+      <c r="O199" t="s">
+        <v>226</v>
+      </c>
+      <c r="P199" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q199">
+        <v>3</v>
+      </c>
+      <c r="R199">
+        <v>2.2</v>
+      </c>
+      <c r="S199">
+        <v>3.4</v>
+      </c>
+      <c r="T199">
+        <v>1.36</v>
+      </c>
+      <c r="U199">
+        <v>3</v>
+      </c>
+      <c r="V199">
+        <v>2.63</v>
+      </c>
+      <c r="W199">
+        <v>1.44</v>
+      </c>
+      <c r="X199">
+        <v>7</v>
+      </c>
+      <c r="Y199">
+        <v>1.1</v>
+      </c>
+      <c r="Z199">
+        <v>2.39</v>
+      </c>
+      <c r="AA199">
+        <v>3.3</v>
+      </c>
+      <c r="AB199">
+        <v>2.87</v>
+      </c>
+      <c r="AC199">
+        <v>1.06</v>
+      </c>
+      <c r="AD199">
+        <v>8.5</v>
+      </c>
+      <c r="AE199">
+        <v>1.27</v>
+      </c>
+      <c r="AF199">
+        <v>3.4</v>
+      </c>
+      <c r="AG199">
+        <v>1.85</v>
+      </c>
+      <c r="AH199">
+        <v>1.89</v>
+      </c>
+      <c r="AI199">
+        <v>1.62</v>
+      </c>
+      <c r="AJ199">
+        <v>2.2</v>
+      </c>
+      <c r="AK199">
+        <v>1.42</v>
+      </c>
+      <c r="AL199">
+        <v>1.29</v>
+      </c>
+      <c r="AM199">
+        <v>1.55</v>
+      </c>
+      <c r="AN199">
+        <v>1.5</v>
+      </c>
+      <c r="AO199">
+        <v>1.4</v>
+      </c>
+      <c r="AP199">
+        <v>1.64</v>
+      </c>
+      <c r="AQ199">
+        <v>1.27</v>
+      </c>
+      <c r="AR199">
+        <v>1.65</v>
+      </c>
+      <c r="AS199">
+        <v>1.45</v>
+      </c>
+      <c r="AT199">
+        <v>3.1</v>
+      </c>
+      <c r="AU199">
+        <v>6</v>
+      </c>
+      <c r="AV199">
+        <v>13</v>
+      </c>
+      <c r="AW199">
+        <v>7</v>
+      </c>
+      <c r="AX199">
+        <v>12</v>
+      </c>
+      <c r="AY199">
+        <v>16</v>
+      </c>
+      <c r="AZ199">
+        <v>30</v>
+      </c>
+      <c r="BA199">
+        <v>4</v>
+      </c>
+      <c r="BB199">
+        <v>11</v>
+      </c>
+      <c r="BC199">
+        <v>15</v>
+      </c>
+      <c r="BD199">
+        <v>1.77</v>
+      </c>
+      <c r="BE199">
+        <v>6.4</v>
+      </c>
+      <c r="BF199">
+        <v>2.3</v>
+      </c>
+      <c r="BG199">
+        <v>1.32</v>
+      </c>
+      <c r="BH199">
+        <v>2.9</v>
+      </c>
+      <c r="BI199">
+        <v>1.57</v>
+      </c>
+      <c r="BJ199">
+        <v>2.16</v>
+      </c>
+      <c r="BK199">
+        <v>2.05</v>
+      </c>
+      <c r="BL199">
+        <v>1.7</v>
+      </c>
+      <c r="BM199">
+        <v>2.45</v>
+      </c>
+      <c r="BN199">
+        <v>1.44</v>
+      </c>
+      <c r="BO199">
+        <v>3.2</v>
+      </c>
+      <c r="BP199">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="319">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -697,6 +697,9 @@
     <t>['15', '21', '57']</t>
   </si>
   <si>
+    <t>['90']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1329,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1997,7 +2000,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2615,7 +2618,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3027,7 +3030,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3314,7 +3317,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ10">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3439,7 +3442,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3645,7 +3648,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3851,7 +3854,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4057,7 +4060,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4135,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
         <v>1.64</v>
@@ -4263,7 +4266,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4469,7 +4472,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5168,7 +5171,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5577,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -5705,7 +5708,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6323,7 +6326,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6529,7 +6532,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6735,7 +6738,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6816,7 +6819,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ27">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR27">
         <v>0.72</v>
@@ -6941,7 +6944,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7019,7 +7022,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ28">
         <v>1.27</v>
@@ -7353,7 +7356,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7434,7 +7437,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ30">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR30">
         <v>0.86</v>
@@ -7765,7 +7768,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7971,7 +7974,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8383,7 +8386,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -9001,7 +9004,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9082,7 +9085,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR38">
         <v>1.85</v>
@@ -9207,7 +9210,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9494,7 +9497,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ40">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9825,7 +9828,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10109,7 +10112,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ43">
         <v>2.27</v>
@@ -10443,7 +10446,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10649,7 +10652,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11061,7 +11064,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11473,7 +11476,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12297,7 +12300,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12503,7 +12506,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13121,7 +13124,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13199,10 +13202,10 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR58">
         <v>1.71</v>
@@ -13327,7 +13330,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13405,7 +13408,7 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ59">
         <v>0.91</v>
@@ -13533,7 +13536,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13739,7 +13742,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14026,7 +14029,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ62">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR62">
         <v>1.9</v>
@@ -14357,7 +14360,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14438,7 +14441,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ64">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR64">
         <v>1.8</v>
@@ -14769,7 +14772,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15877,7 +15880,7 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
         <v>1.09</v>
@@ -16211,7 +16214,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16292,7 +16295,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ73">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR73">
         <v>1.47</v>
@@ -16417,7 +16420,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16907,7 +16910,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ76">
         <v>1.27</v>
@@ -17653,7 +17656,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18146,7 +18149,7 @@
         <v>1</v>
       </c>
       <c r="AQ82">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR82">
         <v>1.3</v>
@@ -19095,7 +19098,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19301,7 +19304,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19507,7 +19510,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19713,7 +19716,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19919,7 +19922,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20331,7 +20334,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20409,7 +20412,7 @@
         <v>2.6</v>
       </c>
       <c r="AP93">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ93">
         <v>2.27</v>
@@ -20537,7 +20540,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20615,7 +20618,7 @@
         <v>0.2</v>
       </c>
       <c r="AP94">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ94">
         <v>0.75</v>
@@ -20743,7 +20746,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20949,7 +20952,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21030,7 +21033,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ96">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21567,7 +21570,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21773,7 +21776,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21979,7 +21982,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22060,7 +22063,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ101">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR101">
         <v>1.68</v>
@@ -22185,7 +22188,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22391,7 +22394,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22803,7 +22806,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22881,7 +22884,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ105">
         <v>0.45</v>
@@ -23293,7 +23296,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ107">
         <v>0.75</v>
@@ -23421,7 +23424,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23627,7 +23630,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24039,7 +24042,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24657,7 +24660,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25069,7 +25072,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25275,7 +25278,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25687,7 +25690,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26177,7 +26180,7 @@
         <v>1.43</v>
       </c>
       <c r="AP121">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ121">
         <v>1.36</v>
@@ -26305,7 +26308,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26383,7 +26386,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122">
         <v>1.64</v>
@@ -26511,7 +26514,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26592,7 +26595,7 @@
         <v>1</v>
       </c>
       <c r="AQ123">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR123">
         <v>1.23</v>
@@ -26798,7 +26801,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ124">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR124">
         <v>1.68</v>
@@ -26923,7 +26926,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27335,7 +27338,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27541,7 +27544,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27953,7 +27956,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28365,7 +28368,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28777,7 +28780,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28983,7 +28986,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29189,7 +29192,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29395,7 +29398,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29601,7 +29604,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30013,7 +30016,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30094,7 +30097,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ140">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR140">
         <v>1.69</v>
@@ -30219,7 +30222,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30297,7 +30300,7 @@
         <v>0.14</v>
       </c>
       <c r="AP141">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ141">
         <v>0.45</v>
@@ -30709,7 +30712,7 @@
         <v>1.38</v>
       </c>
       <c r="AP143">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ143">
         <v>1.36</v>
@@ -30918,7 +30921,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ144">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31867,7 +31870,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32073,7 +32076,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32485,7 +32488,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32975,7 +32978,7 @@
         <v>1.25</v>
       </c>
       <c r="AP154">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ154">
         <v>1.27</v>
@@ -33103,7 +33106,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33181,7 +33184,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ155">
         <v>1.4</v>
@@ -33721,7 +33724,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34008,7 +34011,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ159">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR159">
         <v>1.47</v>
@@ -34133,7 +34136,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34339,7 +34342,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34751,7 +34754,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35163,7 +35166,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35244,7 +35247,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ165">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR165">
         <v>2.02</v>
@@ -36065,7 +36068,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP169">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ169">
         <v>0.75</v>
@@ -36399,7 +36402,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36605,7 +36608,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37301,7 +37304,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ175">
         <v>0.36</v>
@@ -37429,7 +37432,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -38047,7 +38050,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38128,7 +38131,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ179">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR179">
         <v>1.4</v>
@@ -38459,7 +38462,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38665,7 +38668,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39158,7 +39161,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ184">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR184">
         <v>1.49</v>
@@ -39283,7 +39286,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39361,7 +39364,7 @@
         <v>0.9</v>
       </c>
       <c r="AP185">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ185">
         <v>0.82</v>
@@ -39695,7 +39698,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40313,7 +40316,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40519,7 +40522,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41137,7 +41140,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41421,7 +41424,7 @@
         <v>1.3</v>
       </c>
       <c r="AP195">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ195">
         <v>1.18</v>
@@ -41549,7 +41552,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41755,7 +41758,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42167,7 +42170,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42324,6 +42327,418 @@
       </c>
       <c r="BP199">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7450852</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>81</v>
+      </c>
+      <c r="H200" t="s">
+        <v>82</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>1</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>2</v>
+      </c>
+      <c r="O200" t="s">
+        <v>227</v>
+      </c>
+      <c r="P200" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q200">
+        <v>2.65</v>
+      </c>
+      <c r="R200">
+        <v>2.22</v>
+      </c>
+      <c r="S200">
+        <v>3.85</v>
+      </c>
+      <c r="T200">
+        <v>1.37</v>
+      </c>
+      <c r="U200">
+        <v>2.85</v>
+      </c>
+      <c r="V200">
+        <v>2.6</v>
+      </c>
+      <c r="W200">
+        <v>1.44</v>
+      </c>
+      <c r="X200">
+        <v>6.3</v>
+      </c>
+      <c r="Y200">
+        <v>1.09</v>
+      </c>
+      <c r="Z200">
+        <v>2.08</v>
+      </c>
+      <c r="AA200">
+        <v>3.55</v>
+      </c>
+      <c r="AB200">
+        <v>3.26</v>
+      </c>
+      <c r="AC200">
+        <v>1.05</v>
+      </c>
+      <c r="AD200">
+        <v>9</v>
+      </c>
+      <c r="AE200">
+        <v>1.26</v>
+      </c>
+      <c r="AF200">
+        <v>3.45</v>
+      </c>
+      <c r="AG200">
+        <v>1.85</v>
+      </c>
+      <c r="AH200">
+        <v>1.89</v>
+      </c>
+      <c r="AI200">
+        <v>1.67</v>
+      </c>
+      <c r="AJ200">
+        <v>2.08</v>
+      </c>
+      <c r="AK200">
+        <v>1.32</v>
+      </c>
+      <c r="AL200">
+        <v>1.28</v>
+      </c>
+      <c r="AM200">
+        <v>1.67</v>
+      </c>
+      <c r="AN200">
+        <v>1.36</v>
+      </c>
+      <c r="AO200">
+        <v>0.82</v>
+      </c>
+      <c r="AP200">
+        <v>1.33</v>
+      </c>
+      <c r="AQ200">
+        <v>0.83</v>
+      </c>
+      <c r="AR200">
+        <v>1.6</v>
+      </c>
+      <c r="AS200">
+        <v>1.42</v>
+      </c>
+      <c r="AT200">
+        <v>3.02</v>
+      </c>
+      <c r="AU200">
+        <v>4</v>
+      </c>
+      <c r="AV200">
+        <v>3</v>
+      </c>
+      <c r="AW200">
+        <v>15</v>
+      </c>
+      <c r="AX200">
+        <v>6</v>
+      </c>
+      <c r="AY200">
+        <v>24</v>
+      </c>
+      <c r="AZ200">
+        <v>11</v>
+      </c>
+      <c r="BA200">
+        <v>8</v>
+      </c>
+      <c r="BB200">
+        <v>0</v>
+      </c>
+      <c r="BC200">
+        <v>8</v>
+      </c>
+      <c r="BD200">
+        <v>1.74</v>
+      </c>
+      <c r="BE200">
+        <v>6.4</v>
+      </c>
+      <c r="BF200">
+        <v>2.33</v>
+      </c>
+      <c r="BG200">
+        <v>1.4</v>
+      </c>
+      <c r="BH200">
+        <v>2.65</v>
+      </c>
+      <c r="BI200">
+        <v>1.66</v>
+      </c>
+      <c r="BJ200">
+        <v>2.02</v>
+      </c>
+      <c r="BK200">
+        <v>2.07</v>
+      </c>
+      <c r="BL200">
+        <v>1.63</v>
+      </c>
+      <c r="BM200">
+        <v>2.65</v>
+      </c>
+      <c r="BN200">
+        <v>1.38</v>
+      </c>
+      <c r="BO200">
+        <v>3.55</v>
+      </c>
+      <c r="BP200">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7450846</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45716.6875</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>87</v>
+      </c>
+      <c r="H201" t="s">
+        <v>75</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>1</v>
+      </c>
+      <c r="O201" t="s">
+        <v>95</v>
+      </c>
+      <c r="P201" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q201">
+        <v>3.08</v>
+      </c>
+      <c r="R201">
+        <v>2.1</v>
+      </c>
+      <c r="S201">
+        <v>3.3</v>
+      </c>
+      <c r="T201">
+        <v>1.39</v>
+      </c>
+      <c r="U201">
+        <v>2.81</v>
+      </c>
+      <c r="V201">
+        <v>2.81</v>
+      </c>
+      <c r="W201">
+        <v>1.39</v>
+      </c>
+      <c r="X201">
+        <v>6.6</v>
+      </c>
+      <c r="Y201">
+        <v>1.06</v>
+      </c>
+      <c r="Z201">
+        <v>2.6</v>
+      </c>
+      <c r="AA201">
+        <v>3.23</v>
+      </c>
+      <c r="AB201">
+        <v>2.65</v>
+      </c>
+      <c r="AC201">
+        <v>1.01</v>
+      </c>
+      <c r="AD201">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE201">
+        <v>1.26</v>
+      </c>
+      <c r="AF201">
+        <v>3.22</v>
+      </c>
+      <c r="AG201">
+        <v>1.89</v>
+      </c>
+      <c r="AH201">
+        <v>1.85</v>
+      </c>
+      <c r="AI201">
+        <v>1.72</v>
+      </c>
+      <c r="AJ201">
+        <v>2</v>
+      </c>
+      <c r="AK201">
+        <v>1.44</v>
+      </c>
+      <c r="AL201">
+        <v>1.3</v>
+      </c>
+      <c r="AM201">
+        <v>1.5</v>
+      </c>
+      <c r="AN201">
+        <v>1.82</v>
+      </c>
+      <c r="AO201">
+        <v>2</v>
+      </c>
+      <c r="AP201">
+        <v>1.67</v>
+      </c>
+      <c r="AQ201">
+        <v>2.09</v>
+      </c>
+      <c r="AR201">
+        <v>1.93</v>
+      </c>
+      <c r="AS201">
+        <v>1.58</v>
+      </c>
+      <c r="AT201">
+        <v>3.51</v>
+      </c>
+      <c r="AU201">
+        <v>4</v>
+      </c>
+      <c r="AV201">
+        <v>4</v>
+      </c>
+      <c r="AW201">
+        <v>18</v>
+      </c>
+      <c r="AX201">
+        <v>7</v>
+      </c>
+      <c r="AY201">
+        <v>34</v>
+      </c>
+      <c r="AZ201">
+        <v>14</v>
+      </c>
+      <c r="BA201">
+        <v>12</v>
+      </c>
+      <c r="BB201">
+        <v>3</v>
+      </c>
+      <c r="BC201">
+        <v>15</v>
+      </c>
+      <c r="BD201">
+        <v>1.93</v>
+      </c>
+      <c r="BE201">
+        <v>6.4</v>
+      </c>
+      <c r="BF201">
+        <v>2.07</v>
+      </c>
+      <c r="BG201">
+        <v>1.41</v>
+      </c>
+      <c r="BH201">
+        <v>2.55</v>
+      </c>
+      <c r="BI201">
+        <v>1.71</v>
+      </c>
+      <c r="BJ201">
+        <v>1.95</v>
+      </c>
+      <c r="BK201">
+        <v>2.15</v>
+      </c>
+      <c r="BL201">
+        <v>1.58</v>
+      </c>
+      <c r="BM201">
+        <v>2.8</v>
+      </c>
+      <c r="BN201">
+        <v>1.35</v>
+      </c>
+      <c r="BO201">
+        <v>3.8</v>
+      </c>
+      <c r="BP201">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="321">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -972,6 +972,12 @@
   <si>
     <t>['8', '51']</t>
   </si>
+  <si>
+    <t>['32', '68', '85']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
 </sst>
 </file>
 
@@ -1332,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2284,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ5">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2699,7 +2705,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3314,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>0.83</v>
@@ -3932,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>1.27</v>
@@ -4347,7 +4353,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ15">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4550,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -5374,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20">
         <v>0.75</v>
@@ -6407,7 +6413,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ25">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR25">
         <v>1</v>
@@ -6613,7 +6619,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ26">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -7231,7 +7237,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR29">
         <v>2.17</v>
@@ -7640,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ31">
         <v>0.45</v>
@@ -9288,10 +9294,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ39">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR39">
         <v>1.41</v>
@@ -9494,7 +9500,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ40">
         <v>0.83</v>
@@ -9703,7 +9709,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ41">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR41">
         <v>2.02</v>
@@ -10318,10 +10324,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -12381,7 +12387,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ54">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR54">
         <v>1.89</v>
@@ -12584,10 +12590,10 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ55">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR55">
         <v>1.29</v>
@@ -12793,7 +12799,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ56">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -12996,7 +13002,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ57">
         <v>1.27</v>
@@ -13820,7 +13826,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ61">
         <v>0.36</v>
@@ -15883,7 +15889,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16086,7 +16092,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ72">
         <v>1.18</v>
@@ -16707,7 +16713,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ75">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -17116,7 +17122,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ77">
         <v>1.27</v>
@@ -18970,7 +18976,7 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ86">
         <v>0.82</v>
@@ -19179,7 +19185,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ87">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -20003,7 +20009,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ91">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20206,7 +20212,7 @@
         <v>0.8</v>
       </c>
       <c r="AP92">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ92">
         <v>0.91</v>
@@ -21236,10 +21242,10 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ97">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21651,7 +21657,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ99">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR99">
         <v>1.36</v>
@@ -22266,7 +22272,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ102">
         <v>1.64</v>
@@ -22475,7 +22481,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ103">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR103">
         <v>1.6</v>
@@ -23914,7 +23920,7 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ110">
         <v>0.75</v>
@@ -24738,7 +24744,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ114">
         <v>0.75</v>
@@ -24947,7 +24953,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ115">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25977,7 +25983,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ120">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR120">
         <v>1.38</v>
@@ -26183,7 +26189,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ121">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR121">
         <v>1.57</v>
@@ -27007,7 +27013,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ125">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR125">
         <v>1.75</v>
@@ -27210,7 +27216,7 @@
         <v>0.33</v>
       </c>
       <c r="AP126">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ126">
         <v>0.36</v>
@@ -27622,7 +27628,7 @@
         <v>0.5</v>
       </c>
       <c r="AP128">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ128">
         <v>0.82</v>
@@ -28652,7 +28658,7 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
         <v>0.75</v>
@@ -29270,7 +29276,7 @@
         <v>1.43</v>
       </c>
       <c r="AP136">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ136">
         <v>1.27</v>
@@ -30509,7 +30515,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ142">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR142">
         <v>1.61</v>
@@ -30715,7 +30721,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ143">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR143">
         <v>1.98</v>
@@ -31333,7 +31339,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ146">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR146">
         <v>1.5</v>
@@ -32360,7 +32366,7 @@
         <v>2.14</v>
       </c>
       <c r="AP151">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ151">
         <v>1.64</v>
@@ -32566,7 +32572,7 @@
         <v>1.29</v>
       </c>
       <c r="AP152">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ152">
         <v>1.18</v>
@@ -33187,7 +33193,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ155">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR155">
         <v>1.98</v>
@@ -34420,7 +34426,7 @@
         <v>1.25</v>
       </c>
       <c r="AP161">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ161">
         <v>1.18</v>
@@ -35862,7 +35868,7 @@
         <v>0.67</v>
       </c>
       <c r="AP168">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ168">
         <v>0.75</v>
@@ -36483,7 +36489,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ171">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR171">
         <v>1.72</v>
@@ -36689,7 +36695,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ172">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR172">
         <v>1.47</v>
@@ -36892,7 +36898,7 @@
         <v>1.89</v>
       </c>
       <c r="AP173">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ173">
         <v>1.64</v>
@@ -37098,7 +37104,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ174">
         <v>1.27</v>
@@ -38337,7 +38343,7 @@
         <v>1</v>
       </c>
       <c r="AQ180">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR180">
         <v>1.4</v>
@@ -38749,7 +38755,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ182">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR182">
         <v>1.68</v>
@@ -39776,7 +39782,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP187">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ187">
         <v>1</v>
@@ -39985,7 +39991,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ188">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR188">
         <v>1.73</v>
@@ -40394,7 +40400,7 @@
         <v>0.7</v>
       </c>
       <c r="AP190">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ190">
         <v>0.91</v>
@@ -42739,6 +42745,624 @@
       </c>
       <c r="BP201">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7450854</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45717.44791666666</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>78</v>
+      </c>
+      <c r="H202" t="s">
+        <v>85</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>1</v>
+      </c>
+      <c r="O202" t="s">
+        <v>95</v>
+      </c>
+      <c r="P202" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q202">
+        <v>2.65</v>
+      </c>
+      <c r="R202">
+        <v>2.12</v>
+      </c>
+      <c r="S202">
+        <v>4.2</v>
+      </c>
+      <c r="T202">
+        <v>1.44</v>
+      </c>
+      <c r="U202">
+        <v>2.6</v>
+      </c>
+      <c r="V202">
+        <v>2.9</v>
+      </c>
+      <c r="W202">
+        <v>1.36</v>
+      </c>
+      <c r="X202">
+        <v>6.5</v>
+      </c>
+      <c r="Y202">
+        <v>1.08</v>
+      </c>
+      <c r="Z202">
+        <v>2.07</v>
+      </c>
+      <c r="AA202">
+        <v>3.02</v>
+      </c>
+      <c r="AB202">
+        <v>3.93</v>
+      </c>
+      <c r="AC202">
+        <v>1.07</v>
+      </c>
+      <c r="AD202">
+        <v>8</v>
+      </c>
+      <c r="AE202">
+        <v>1.34</v>
+      </c>
+      <c r="AF202">
+        <v>3</v>
+      </c>
+      <c r="AG202">
+        <v>1.95</v>
+      </c>
+      <c r="AH202">
+        <v>1.7</v>
+      </c>
+      <c r="AI202">
+        <v>1.82</v>
+      </c>
+      <c r="AJ202">
+        <v>1.89</v>
+      </c>
+      <c r="AK202">
+        <v>1.27</v>
+      </c>
+      <c r="AL202">
+        <v>1.31</v>
+      </c>
+      <c r="AM202">
+        <v>1.7</v>
+      </c>
+      <c r="AN202">
+        <v>1.64</v>
+      </c>
+      <c r="AO202">
+        <v>1.09</v>
+      </c>
+      <c r="AP202">
+        <v>1.5</v>
+      </c>
+      <c r="AQ202">
+        <v>1.25</v>
+      </c>
+      <c r="AR202">
+        <v>1.62</v>
+      </c>
+      <c r="AS202">
+        <v>1.34</v>
+      </c>
+      <c r="AT202">
+        <v>2.96</v>
+      </c>
+      <c r="AU202">
+        <v>4</v>
+      </c>
+      <c r="AV202">
+        <v>4</v>
+      </c>
+      <c r="AW202">
+        <v>10</v>
+      </c>
+      <c r="AX202">
+        <v>8</v>
+      </c>
+      <c r="AY202">
+        <v>15</v>
+      </c>
+      <c r="AZ202">
+        <v>17</v>
+      </c>
+      <c r="BA202">
+        <v>5</v>
+      </c>
+      <c r="BB202">
+        <v>3</v>
+      </c>
+      <c r="BC202">
+        <v>8</v>
+      </c>
+      <c r="BD202">
+        <v>1.72</v>
+      </c>
+      <c r="BE202">
+        <v>6.4</v>
+      </c>
+      <c r="BF202">
+        <v>2.4</v>
+      </c>
+      <c r="BG202">
+        <v>1.43</v>
+      </c>
+      <c r="BH202">
+        <v>2.5</v>
+      </c>
+      <c r="BI202">
+        <v>1.74</v>
+      </c>
+      <c r="BJ202">
+        <v>1.92</v>
+      </c>
+      <c r="BK202">
+        <v>2.18</v>
+      </c>
+      <c r="BL202">
+        <v>1.56</v>
+      </c>
+      <c r="BM202">
+        <v>2.88</v>
+      </c>
+      <c r="BN202">
+        <v>1.33</v>
+      </c>
+      <c r="BO202">
+        <v>3.85</v>
+      </c>
+      <c r="BP202">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7450850</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45717.5625</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>73</v>
+      </c>
+      <c r="H203" t="s">
+        <v>76</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>1</v>
+      </c>
+      <c r="K203">
+        <v>1</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>3</v>
+      </c>
+      <c r="N203">
+        <v>3</v>
+      </c>
+      <c r="O203" t="s">
+        <v>95</v>
+      </c>
+      <c r="P203" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q203">
+        <v>2.95</v>
+      </c>
+      <c r="R203">
+        <v>2.15</v>
+      </c>
+      <c r="S203">
+        <v>3.2</v>
+      </c>
+      <c r="T203">
+        <v>1.33</v>
+      </c>
+      <c r="U203">
+        <v>3</v>
+      </c>
+      <c r="V203">
+        <v>2.45</v>
+      </c>
+      <c r="W203">
+        <v>1.48</v>
+      </c>
+      <c r="X203">
+        <v>5.5</v>
+      </c>
+      <c r="Y203">
+        <v>1.11</v>
+      </c>
+      <c r="Z203">
+        <v>2.37</v>
+      </c>
+      <c r="AA203">
+        <v>3.4</v>
+      </c>
+      <c r="AB203">
+        <v>2.82</v>
+      </c>
+      <c r="AC203">
+        <v>1.05</v>
+      </c>
+      <c r="AD203">
+        <v>9</v>
+      </c>
+      <c r="AE203">
+        <v>1.25</v>
+      </c>
+      <c r="AF203">
+        <v>3.8</v>
+      </c>
+      <c r="AG203">
+        <v>1.77</v>
+      </c>
+      <c r="AH203">
+        <v>1.98</v>
+      </c>
+      <c r="AI203">
+        <v>1.57</v>
+      </c>
+      <c r="AJ203">
+        <v>2.25</v>
+      </c>
+      <c r="AK203">
+        <v>1.42</v>
+      </c>
+      <c r="AL203">
+        <v>1.28</v>
+      </c>
+      <c r="AM203">
+        <v>1.5</v>
+      </c>
+      <c r="AN203">
+        <v>2.55</v>
+      </c>
+      <c r="AO203">
+        <v>1.4</v>
+      </c>
+      <c r="AP203">
+        <v>2.33</v>
+      </c>
+      <c r="AQ203">
+        <v>1.55</v>
+      </c>
+      <c r="AR203">
+        <v>1.8</v>
+      </c>
+      <c r="AS203">
+        <v>1.3</v>
+      </c>
+      <c r="AT203">
+        <v>3.1</v>
+      </c>
+      <c r="AU203">
+        <v>5</v>
+      </c>
+      <c r="AV203">
+        <v>8</v>
+      </c>
+      <c r="AW203">
+        <v>9</v>
+      </c>
+      <c r="AX203">
+        <v>8</v>
+      </c>
+      <c r="AY203">
+        <v>18</v>
+      </c>
+      <c r="AZ203">
+        <v>22</v>
+      </c>
+      <c r="BA203">
+        <v>4</v>
+      </c>
+      <c r="BB203">
+        <v>4</v>
+      </c>
+      <c r="BC203">
+        <v>8</v>
+      </c>
+      <c r="BD203">
+        <v>1.91</v>
+      </c>
+      <c r="BE203">
+        <v>6.4</v>
+      </c>
+      <c r="BF203">
+        <v>2.08</v>
+      </c>
+      <c r="BG203">
+        <v>1.36</v>
+      </c>
+      <c r="BH203">
+        <v>2.75</v>
+      </c>
+      <c r="BI203">
+        <v>1.62</v>
+      </c>
+      <c r="BJ203">
+        <v>2.08</v>
+      </c>
+      <c r="BK203">
+        <v>2.02</v>
+      </c>
+      <c r="BL203">
+        <v>1.65</v>
+      </c>
+      <c r="BM203">
+        <v>2.6</v>
+      </c>
+      <c r="BN203">
+        <v>1.4</v>
+      </c>
+      <c r="BO203">
+        <v>3.4</v>
+      </c>
+      <c r="BP203">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7450848</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45717.67708333334</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>83</v>
+      </c>
+      <c r="H204" t="s">
+        <v>84</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>1</v>
+      </c>
+      <c r="O204" t="s">
+        <v>95</v>
+      </c>
+      <c r="P204" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q204">
+        <v>3.3</v>
+      </c>
+      <c r="R204">
+        <v>2</v>
+      </c>
+      <c r="S204">
+        <v>3.25</v>
+      </c>
+      <c r="T204">
+        <v>1.45</v>
+      </c>
+      <c r="U204">
+        <v>2.55</v>
+      </c>
+      <c r="V204">
+        <v>3</v>
+      </c>
+      <c r="W204">
+        <v>1.33</v>
+      </c>
+      <c r="X204">
+        <v>7</v>
+      </c>
+      <c r="Y204">
+        <v>1.06</v>
+      </c>
+      <c r="Z204">
+        <v>2.75</v>
+      </c>
+      <c r="AA204">
+        <v>3.04</v>
+      </c>
+      <c r="AB204">
+        <v>2.65</v>
+      </c>
+      <c r="AC204">
+        <v>1.09</v>
+      </c>
+      <c r="AD204">
+        <v>7</v>
+      </c>
+      <c r="AE204">
+        <v>1.42</v>
+      </c>
+      <c r="AF204">
+        <v>2.85</v>
+      </c>
+      <c r="AG204">
+        <v>2.15</v>
+      </c>
+      <c r="AH204">
+        <v>1.63</v>
+      </c>
+      <c r="AI204">
+        <v>1.85</v>
+      </c>
+      <c r="AJ204">
+        <v>1.85</v>
+      </c>
+      <c r="AK204">
+        <v>1.45</v>
+      </c>
+      <c r="AL204">
+        <v>1.3</v>
+      </c>
+      <c r="AM204">
+        <v>1.44</v>
+      </c>
+      <c r="AN204">
+        <v>1.3</v>
+      </c>
+      <c r="AO204">
+        <v>1.36</v>
+      </c>
+      <c r="AP204">
+        <v>1.18</v>
+      </c>
+      <c r="AQ204">
+        <v>1.5</v>
+      </c>
+      <c r="AR204">
+        <v>1.84</v>
+      </c>
+      <c r="AS204">
+        <v>1.39</v>
+      </c>
+      <c r="AT204">
+        <v>3.23</v>
+      </c>
+      <c r="AU204">
+        <v>4</v>
+      </c>
+      <c r="AV204">
+        <v>5</v>
+      </c>
+      <c r="AW204">
+        <v>11</v>
+      </c>
+      <c r="AX204">
+        <v>7</v>
+      </c>
+      <c r="AY204">
+        <v>18</v>
+      </c>
+      <c r="AZ204">
+        <v>15</v>
+      </c>
+      <c r="BA204">
+        <v>7</v>
+      </c>
+      <c r="BB204">
+        <v>1</v>
+      </c>
+      <c r="BC204">
+        <v>8</v>
+      </c>
+      <c r="BD204">
+        <v>2</v>
+      </c>
+      <c r="BE204">
+        <v>6.25</v>
+      </c>
+      <c r="BF204">
+        <v>1.98</v>
+      </c>
+      <c r="BG204">
+        <v>1.47</v>
+      </c>
+      <c r="BH204">
+        <v>2.4</v>
+      </c>
+      <c r="BI204">
+        <v>1.8</v>
+      </c>
+      <c r="BJ204">
+        <v>1.85</v>
+      </c>
+      <c r="BK204">
+        <v>2.3</v>
+      </c>
+      <c r="BL204">
+        <v>1.52</v>
+      </c>
+      <c r="BM204">
+        <v>3.05</v>
+      </c>
+      <c r="BN204">
+        <v>1.3</v>
+      </c>
+      <c r="BO204">
+        <v>4.1</v>
+      </c>
+      <c r="BP204">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="321">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1338,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3526,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ11">
         <v>1.27</v>
@@ -3735,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -8058,7 +8058,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ33">
         <v>1.18</v>
@@ -8676,7 +8676,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ36">
         <v>0.91</v>
@@ -8885,7 +8885,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ37">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR37">
         <v>1.91</v>
@@ -12796,7 +12796,7 @@
         <v>0.67</v>
       </c>
       <c r="AP56">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ56">
         <v>1.25</v>
@@ -13623,7 +13623,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ60">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -16298,7 +16298,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ73">
         <v>2.09</v>
@@ -17125,7 +17125,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ77">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR77">
         <v>1.21</v>
@@ -19800,7 +19800,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ90">
         <v>1.27</v>
@@ -20833,7 +20833,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ95">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -24129,7 +24129,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ111">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR111">
         <v>1.46</v>
@@ -25980,7 +25980,7 @@
         <v>2.17</v>
       </c>
       <c r="AP120">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ120">
         <v>1.55</v>
@@ -27425,7 +27425,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ127">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -29279,7 +29279,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ136">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -30924,7 +30924,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ144">
         <v>0.83</v>
@@ -33811,7 +33811,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ158">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR158">
         <v>1.55</v>
@@ -34220,7 +34220,7 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ160">
         <v>1.64</v>
@@ -37931,7 +37931,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ178">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR178">
         <v>1.4</v>
@@ -38546,7 +38546,7 @@
         <v>0.6</v>
       </c>
       <c r="AP181">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ181">
         <v>0.75</v>
@@ -40197,7 +40197,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ189">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR189">
         <v>1.82</v>
@@ -43363,6 +43363,212 @@
       </c>
       <c r="BP204">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7450851</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45718.34375</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>79</v>
+      </c>
+      <c r="H205" t="s">
+        <v>77</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>1</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>1</v>
+      </c>
+      <c r="O205" t="s">
+        <v>95</v>
+      </c>
+      <c r="P205" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q205">
+        <v>3.4</v>
+      </c>
+      <c r="R205">
+        <v>2.1</v>
+      </c>
+      <c r="S205">
+        <v>3.2</v>
+      </c>
+      <c r="T205">
+        <v>1.44</v>
+      </c>
+      <c r="U205">
+        <v>2.63</v>
+      </c>
+      <c r="V205">
+        <v>3</v>
+      </c>
+      <c r="W205">
+        <v>1.36</v>
+      </c>
+      <c r="X205">
+        <v>9</v>
+      </c>
+      <c r="Y205">
+        <v>1.07</v>
+      </c>
+      <c r="Z205">
+        <v>2.5</v>
+      </c>
+      <c r="AA205">
+        <v>3.25</v>
+      </c>
+      <c r="AB205">
+        <v>2.75</v>
+      </c>
+      <c r="AC205">
+        <v>1.08</v>
+      </c>
+      <c r="AD205">
+        <v>7.5</v>
+      </c>
+      <c r="AE205">
+        <v>1.36</v>
+      </c>
+      <c r="AF205">
+        <v>2.85</v>
+      </c>
+      <c r="AG205">
+        <v>1.94</v>
+      </c>
+      <c r="AH205">
+        <v>1.8</v>
+      </c>
+      <c r="AI205">
+        <v>1.8</v>
+      </c>
+      <c r="AJ205">
+        <v>1.95</v>
+      </c>
+      <c r="AK205">
+        <v>1.45</v>
+      </c>
+      <c r="AL205">
+        <v>1.34</v>
+      </c>
+      <c r="AM205">
+        <v>1.42</v>
+      </c>
+      <c r="AN205">
+        <v>1.3</v>
+      </c>
+      <c r="AO205">
+        <v>1.27</v>
+      </c>
+      <c r="AP205">
+        <v>1.18</v>
+      </c>
+      <c r="AQ205">
+        <v>1.42</v>
+      </c>
+      <c r="AR205">
+        <v>1.46</v>
+      </c>
+      <c r="AS205">
+        <v>1.35</v>
+      </c>
+      <c r="AT205">
+        <v>2.81</v>
+      </c>
+      <c r="AU205">
+        <v>2</v>
+      </c>
+      <c r="AV205">
+        <v>3</v>
+      </c>
+      <c r="AW205">
+        <v>4</v>
+      </c>
+      <c r="AX205">
+        <v>12</v>
+      </c>
+      <c r="AY205">
+        <v>8</v>
+      </c>
+      <c r="AZ205">
+        <v>22</v>
+      </c>
+      <c r="BA205">
+        <v>8</v>
+      </c>
+      <c r="BB205">
+        <v>4</v>
+      </c>
+      <c r="BC205">
+        <v>12</v>
+      </c>
+      <c r="BD205">
+        <v>2</v>
+      </c>
+      <c r="BE205">
+        <v>6.25</v>
+      </c>
+      <c r="BF205">
+        <v>1.98</v>
+      </c>
+      <c r="BG205">
+        <v>1.43</v>
+      </c>
+      <c r="BH205">
+        <v>2.5</v>
+      </c>
+      <c r="BI205">
+        <v>1.74</v>
+      </c>
+      <c r="BJ205">
+        <v>1.9</v>
+      </c>
+      <c r="BK205">
+        <v>2.2</v>
+      </c>
+      <c r="BL205">
+        <v>1.55</v>
+      </c>
+      <c r="BM205">
+        <v>2.9</v>
+      </c>
+      <c r="BN205">
+        <v>1.33</v>
+      </c>
+      <c r="BO205">
+        <v>3.9</v>
+      </c>
+      <c r="BP205">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="323">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -700,6 +700,12 @@
     <t>['90']</t>
   </si>
   <si>
+    <t>['35', '49', '87']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1338,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1672,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2">
         <v>0.75</v>
@@ -2006,7 +2012,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2496,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ6">
         <v>0.75</v>
@@ -2624,7 +2630,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3036,7 +3042,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3448,7 +3454,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3654,7 +3660,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3860,7 +3866,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3941,7 +3947,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ13">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR13">
         <v>1.41</v>
@@ -4066,7 +4072,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4272,7 +4278,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4478,7 +4484,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4765,7 +4771,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ17">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5714,7 +5720,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5998,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ23">
         <v>0.45</v>
@@ -6332,7 +6338,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6538,7 +6544,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6616,7 +6622,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ26">
         <v>1.5</v>
@@ -6744,7 +6750,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6950,7 +6956,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7362,7 +7368,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7774,7 +7780,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7980,7 +7986,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8267,7 +8273,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ34">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR34">
         <v>1.4</v>
@@ -8392,7 +8398,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8473,7 +8479,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ35">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR35">
         <v>1.34</v>
@@ -9010,7 +9016,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9088,7 +9094,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ38">
         <v>2.09</v>
@@ -9216,7 +9222,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9834,7 +9840,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9912,7 +9918,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ42">
         <v>0.82</v>
@@ -10452,7 +10458,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10658,7 +10664,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11070,7 +11076,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11482,7 +11488,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12306,7 +12312,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12512,7 +12518,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13005,7 +13011,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR57">
         <v>1.6</v>
@@ -13130,7 +13136,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13336,7 +13342,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13542,7 +13548,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13620,7 +13626,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ60">
         <v>1.42</v>
@@ -13748,7 +13754,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13829,7 +13835,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ61">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR61">
         <v>1.79</v>
@@ -14032,7 +14038,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ62">
         <v>0.83</v>
@@ -14366,7 +14372,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14778,7 +14784,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15680,7 +15686,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ70">
         <v>2.27</v>
@@ -16220,7 +16226,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16426,7 +16432,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16504,7 +16510,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ74">
         <v>0.91</v>
@@ -16919,7 +16925,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ76">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR76">
         <v>1.53</v>
@@ -17537,7 +17543,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ79">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR79">
         <v>1.89</v>
@@ -17662,7 +17668,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18567,7 +18573,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ84">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR84">
         <v>1.58</v>
@@ -18770,7 +18776,7 @@
         <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ85">
         <v>1.27</v>
@@ -19104,7 +19110,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19310,7 +19316,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19516,7 +19522,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19722,7 +19728,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19803,7 +19809,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ90">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR90">
         <v>1.39</v>
@@ -19928,7 +19934,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20340,7 +20346,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20546,7 +20552,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20752,7 +20758,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20958,7 +20964,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21448,7 +21454,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ98">
         <v>1.18</v>
@@ -21576,7 +21582,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21782,7 +21788,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21988,7 +21994,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22194,7 +22200,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22400,7 +22406,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22687,7 +22693,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ104">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -22812,7 +22818,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23430,7 +23436,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23636,7 +23642,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24048,7 +24054,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24666,7 +24672,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24950,7 +24956,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ115">
         <v>1.25</v>
@@ -25078,7 +25084,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25284,7 +25290,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25362,10 +25368,10 @@
         <v>1.4</v>
       </c>
       <c r="AP117">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ117">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR117">
         <v>1.54</v>
@@ -25696,7 +25702,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26314,7 +26320,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26520,7 +26526,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26804,7 +26810,7 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ124">
         <v>0.83</v>
@@ -26932,7 +26938,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27219,7 +27225,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ126">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR126">
         <v>1.67</v>
@@ -27344,7 +27350,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27550,7 +27556,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27962,7 +27968,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28043,7 +28049,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ130">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR130">
         <v>1.6</v>
@@ -28374,7 +28380,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28786,7 +28792,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28864,7 +28870,7 @@
         <v>2.43</v>
       </c>
       <c r="AP134">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ134">
         <v>2.27</v>
@@ -28992,7 +28998,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29198,7 +29204,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29404,7 +29410,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29482,10 +29488,10 @@
         <v>0.29</v>
       </c>
       <c r="AP137">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ137">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR137">
         <v>1.82</v>
@@ -29610,7 +29616,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29897,7 +29903,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ139">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR139">
         <v>1.94</v>
@@ -30022,7 +30028,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30100,7 +30106,7 @@
         <v>2.57</v>
       </c>
       <c r="AP140">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ140">
         <v>2.09</v>
@@ -30228,7 +30234,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31876,7 +31882,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32082,7 +32088,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32494,7 +32500,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32987,7 +32993,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ154">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR154">
         <v>1.51</v>
@@ -33112,7 +33118,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33399,7 +33405,7 @@
         <v>1</v>
       </c>
       <c r="AQ156">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR156">
         <v>1.39</v>
@@ -33730,7 +33736,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34142,7 +34148,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34348,7 +34354,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34760,7 +34766,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35172,7 +35178,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36280,7 +36286,7 @@
         <v>1</v>
       </c>
       <c r="AP170">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ170">
         <v>0.82</v>
@@ -36408,7 +36414,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36486,7 +36492,7 @@
         <v>1.11</v>
       </c>
       <c r="AP171">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ171">
         <v>1.25</v>
@@ -36614,7 +36620,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37313,7 +37319,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ175">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR175">
         <v>1.56</v>
@@ -37438,7 +37444,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37519,7 +37525,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ176">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR176">
         <v>1.63</v>
@@ -38056,7 +38062,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38468,7 +38474,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38674,7 +38680,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39292,7 +39298,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39576,7 +39582,7 @@
         <v>0.6</v>
       </c>
       <c r="AP186">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ186">
         <v>0.75</v>
@@ -39704,7 +39710,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40194,7 +40200,7 @@
         <v>1.4</v>
       </c>
       <c r="AP189">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ189">
         <v>1.42</v>
@@ -40322,7 +40328,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40528,7 +40534,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41021,7 +41027,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ193">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR193">
         <v>1.41</v>
@@ -41146,7 +41152,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41558,7 +41564,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41764,7 +41770,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42176,7 +42182,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42257,7 +42263,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ199">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR199">
         <v>1.65</v>
@@ -43000,7 +43006,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43206,7 +43212,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43412,7 +43418,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -43569,6 +43575,418 @@
       </c>
       <c r="BP205">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7450849</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45718.44791666666</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>74</v>
+      </c>
+      <c r="H206" t="s">
+        <v>71</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="K206">
+        <v>2</v>
+      </c>
+      <c r="L206">
+        <v>3</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>4</v>
+      </c>
+      <c r="O206" t="s">
+        <v>228</v>
+      </c>
+      <c r="P206" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q206">
+        <v>2.1</v>
+      </c>
+      <c r="R206">
+        <v>2.25</v>
+      </c>
+      <c r="S206">
+        <v>6</v>
+      </c>
+      <c r="T206">
+        <v>1.36</v>
+      </c>
+      <c r="U206">
+        <v>3</v>
+      </c>
+      <c r="V206">
+        <v>2.75</v>
+      </c>
+      <c r="W206">
+        <v>1.4</v>
+      </c>
+      <c r="X206">
+        <v>8</v>
+      </c>
+      <c r="Y206">
+        <v>1.08</v>
+      </c>
+      <c r="Z206">
+        <v>1.49</v>
+      </c>
+      <c r="AA206">
+        <v>4.2</v>
+      </c>
+      <c r="AB206">
+        <v>6.3</v>
+      </c>
+      <c r="AC206">
+        <v>1.05</v>
+      </c>
+      <c r="AD206">
+        <v>9.5</v>
+      </c>
+      <c r="AE206">
+        <v>1.27</v>
+      </c>
+      <c r="AF206">
+        <v>3.4</v>
+      </c>
+      <c r="AG206">
+        <v>1.85</v>
+      </c>
+      <c r="AH206">
+        <v>1.89</v>
+      </c>
+      <c r="AI206">
+        <v>1.95</v>
+      </c>
+      <c r="AJ206">
+        <v>1.8</v>
+      </c>
+      <c r="AK206">
+        <v>1.13</v>
+      </c>
+      <c r="AL206">
+        <v>1.21</v>
+      </c>
+      <c r="AM206">
+        <v>2.37</v>
+      </c>
+      <c r="AN206">
+        <v>2.09</v>
+      </c>
+      <c r="AO206">
+        <v>0.36</v>
+      </c>
+      <c r="AP206">
+        <v>2.17</v>
+      </c>
+      <c r="AQ206">
+        <v>0.33</v>
+      </c>
+      <c r="AR206">
+        <v>1.66</v>
+      </c>
+      <c r="AS206">
+        <v>1.35</v>
+      </c>
+      <c r="AT206">
+        <v>3.01</v>
+      </c>
+      <c r="AU206">
+        <v>7</v>
+      </c>
+      <c r="AV206">
+        <v>3</v>
+      </c>
+      <c r="AW206">
+        <v>11</v>
+      </c>
+      <c r="AX206">
+        <v>6</v>
+      </c>
+      <c r="AY206">
+        <v>23</v>
+      </c>
+      <c r="AZ206">
+        <v>13</v>
+      </c>
+      <c r="BA206">
+        <v>8</v>
+      </c>
+      <c r="BB206">
+        <v>4</v>
+      </c>
+      <c r="BC206">
+        <v>12</v>
+      </c>
+      <c r="BD206">
+        <v>1.41</v>
+      </c>
+      <c r="BE206">
+        <v>6.75</v>
+      </c>
+      <c r="BF206">
+        <v>3.3</v>
+      </c>
+      <c r="BG206">
+        <v>1.38</v>
+      </c>
+      <c r="BH206">
+        <v>2.65</v>
+      </c>
+      <c r="BI206">
+        <v>1.66</v>
+      </c>
+      <c r="BJ206">
+        <v>2.02</v>
+      </c>
+      <c r="BK206">
+        <v>2.08</v>
+      </c>
+      <c r="BL206">
+        <v>1.62</v>
+      </c>
+      <c r="BM206">
+        <v>2.65</v>
+      </c>
+      <c r="BN206">
+        <v>1.38</v>
+      </c>
+      <c r="BO206">
+        <v>3.45</v>
+      </c>
+      <c r="BP206">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7450847</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45718.5625</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>70</v>
+      </c>
+      <c r="H207" t="s">
+        <v>72</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>1</v>
+      </c>
+      <c r="O207" t="s">
+        <v>229</v>
+      </c>
+      <c r="P207" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q207">
+        <v>2.15</v>
+      </c>
+      <c r="R207">
+        <v>2.48</v>
+      </c>
+      <c r="S207">
+        <v>4.6</v>
+      </c>
+      <c r="T207">
+        <v>1.28</v>
+      </c>
+      <c r="U207">
+        <v>3.4</v>
+      </c>
+      <c r="V207">
+        <v>2.25</v>
+      </c>
+      <c r="W207">
+        <v>1.59</v>
+      </c>
+      <c r="X207">
+        <v>4.85</v>
+      </c>
+      <c r="Y207">
+        <v>1.15</v>
+      </c>
+      <c r="Z207">
+        <v>1.82</v>
+      </c>
+      <c r="AA207">
+        <v>3.83</v>
+      </c>
+      <c r="AB207">
+        <v>3.83</v>
+      </c>
+      <c r="AC207">
+        <v>1.03</v>
+      </c>
+      <c r="AD207">
+        <v>11</v>
+      </c>
+      <c r="AE207">
+        <v>1.17</v>
+      </c>
+      <c r="AF207">
+        <v>4.5</v>
+      </c>
+      <c r="AG207">
+        <v>1.57</v>
+      </c>
+      <c r="AH207">
+        <v>2.15</v>
+      </c>
+      <c r="AI207">
+        <v>1.57</v>
+      </c>
+      <c r="AJ207">
+        <v>2.26</v>
+      </c>
+      <c r="AK207">
+        <v>1.2</v>
+      </c>
+      <c r="AL207">
+        <v>1.22</v>
+      </c>
+      <c r="AM207">
+        <v>2.05</v>
+      </c>
+      <c r="AN207">
+        <v>2.18</v>
+      </c>
+      <c r="AO207">
+        <v>1.27</v>
+      </c>
+      <c r="AP207">
+        <v>2.25</v>
+      </c>
+      <c r="AQ207">
+        <v>1.17</v>
+      </c>
+      <c r="AR207">
+        <v>1.81</v>
+      </c>
+      <c r="AS207">
+        <v>1.59</v>
+      </c>
+      <c r="AT207">
+        <v>3.4</v>
+      </c>
+      <c r="AU207">
+        <v>3</v>
+      </c>
+      <c r="AV207">
+        <v>3</v>
+      </c>
+      <c r="AW207">
+        <v>13</v>
+      </c>
+      <c r="AX207">
+        <v>9</v>
+      </c>
+      <c r="AY207">
+        <v>24</v>
+      </c>
+      <c r="AZ207">
+        <v>17</v>
+      </c>
+      <c r="BA207">
+        <v>4</v>
+      </c>
+      <c r="BB207">
+        <v>0</v>
+      </c>
+      <c r="BC207">
+        <v>4</v>
+      </c>
+      <c r="BD207">
+        <v>1.54</v>
+      </c>
+      <c r="BE207">
+        <v>6.75</v>
+      </c>
+      <c r="BF207">
+        <v>2.8</v>
+      </c>
+      <c r="BG207">
+        <v>1.32</v>
+      </c>
+      <c r="BH207">
+        <v>2.95</v>
+      </c>
+      <c r="BI207">
+        <v>1.55</v>
+      </c>
+      <c r="BJ207">
+        <v>2.2</v>
+      </c>
+      <c r="BK207">
+        <v>1.92</v>
+      </c>
+      <c r="BL207">
+        <v>1.73</v>
+      </c>
+      <c r="BM207">
+        <v>2.4</v>
+      </c>
+      <c r="BN207">
+        <v>1.46</v>
+      </c>
+      <c r="BO207">
+        <v>3.15</v>
+      </c>
+      <c r="BP207">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="324">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,9 @@
     <t>['36']</t>
   </si>
   <si>
+    <t>['2', '15', '75']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1344,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1887,7 +1890,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ3">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2012,7 +2015,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2630,7 +2633,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3042,7 +3045,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3454,7 +3457,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3660,7 +3663,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3866,7 +3869,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4072,7 +4075,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4278,7 +4281,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4484,7 +4487,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5180,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ19">
         <v>2.09</v>
@@ -5720,7 +5723,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6213,7 +6216,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ24">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR24">
         <v>1.69</v>
@@ -6338,7 +6341,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6544,7 +6547,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6750,7 +6753,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6956,7 +6959,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7240,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ29">
         <v>1.55</v>
@@ -7368,7 +7371,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7780,7 +7783,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7986,7 +7989,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8398,7 +8401,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8685,7 +8688,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ36">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR36">
         <v>1.51</v>
@@ -9016,7 +9019,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9222,7 +9225,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9840,7 +9843,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10458,7 +10461,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10664,7 +10667,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11076,7 +11079,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11488,7 +11491,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12312,7 +12315,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12390,7 +12393,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ54">
         <v>1.5</v>
@@ -12518,7 +12521,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13136,7 +13139,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13342,7 +13345,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13423,7 +13426,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ59">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR59">
         <v>1.38</v>
@@ -13548,7 +13551,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13754,7 +13757,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14372,7 +14375,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14784,7 +14787,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -16226,7 +16229,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16432,7 +16435,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16513,7 +16516,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ74">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -17334,7 +17337,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
         <v>0.75</v>
@@ -17668,7 +17671,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18364,7 +18367,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ83">
         <v>0.75</v>
@@ -19110,7 +19113,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19316,7 +19319,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19522,7 +19525,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19728,7 +19731,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19934,7 +19937,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20221,7 +20224,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -20346,7 +20349,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20552,7 +20555,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20758,7 +20761,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20964,7 +20967,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21582,7 +21585,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21788,7 +21791,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21994,7 +21997,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22200,7 +22203,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22406,7 +22409,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22818,7 +22821,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23102,7 +23105,7 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23436,7 +23439,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23642,7 +23645,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23723,7 +23726,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ109">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -24054,7 +24057,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24672,7 +24675,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25084,7 +25087,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25290,7 +25293,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25574,7 +25577,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ118">
         <v>0.45</v>
@@ -25702,7 +25705,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26320,7 +26323,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26526,7 +26529,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26938,7 +26941,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27350,7 +27353,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27556,7 +27559,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27843,7 +27846,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ129">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR129">
         <v>1.39</v>
@@ -27968,7 +27971,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28380,7 +28383,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28792,7 +28795,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28998,7 +29001,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29204,7 +29207,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29410,7 +29413,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29616,7 +29619,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30028,7 +30031,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30234,7 +30237,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30518,7 +30521,7 @@
         <v>1.13</v>
       </c>
       <c r="AP142">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ142">
         <v>1.25</v>
@@ -31757,7 +31760,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ148">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR148">
         <v>1.73</v>
@@ -31882,7 +31885,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32088,7 +32091,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32500,7 +32503,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33118,7 +33121,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33736,7 +33739,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -33814,7 +33817,7 @@
         <v>1.63</v>
       </c>
       <c r="AP158">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ158">
         <v>1.42</v>
@@ -34148,7 +34151,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34354,7 +34357,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34766,7 +34769,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35178,7 +35181,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35465,7 +35468,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ166">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR166">
         <v>1.68</v>
@@ -36414,7 +36417,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36620,7 +36623,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37444,7 +37447,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37522,7 +37525,7 @@
         <v>1.22</v>
       </c>
       <c r="AP176">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ176">
         <v>1.17</v>
@@ -38062,7 +38065,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38474,7 +38477,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38680,7 +38683,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39298,7 +39301,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39710,7 +39713,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40328,7 +40331,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40409,7 +40412,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ190">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR190">
         <v>1.75</v>
@@ -40534,7 +40537,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40818,7 +40821,7 @@
         <v>1.4</v>
       </c>
       <c r="AP192">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ192">
         <v>1.27</v>
@@ -41152,7 +41155,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41564,7 +41567,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41770,7 +41773,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42182,7 +42185,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -43006,7 +43009,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43212,7 +43215,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43418,7 +43421,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -43987,6 +43990,212 @@
       </c>
       <c r="BP207">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7450853</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45719.625</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>86</v>
+      </c>
+      <c r="H208" t="s">
+        <v>80</v>
+      </c>
+      <c r="I208">
+        <v>2</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>2</v>
+      </c>
+      <c r="L208">
+        <v>3</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>4</v>
+      </c>
+      <c r="O208" t="s">
+        <v>230</v>
+      </c>
+      <c r="P208" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q208">
+        <v>1.77</v>
+      </c>
+      <c r="R208">
+        <v>2.55</v>
+      </c>
+      <c r="S208">
+        <v>8</v>
+      </c>
+      <c r="T208">
+        <v>1.31</v>
+      </c>
+      <c r="U208">
+        <v>3.2</v>
+      </c>
+      <c r="V208">
+        <v>2.45</v>
+      </c>
+      <c r="W208">
+        <v>1.49</v>
+      </c>
+      <c r="X208">
+        <v>5.7</v>
+      </c>
+      <c r="Y208">
+        <v>1.11</v>
+      </c>
+      <c r="Z208">
+        <v>1.34</v>
+      </c>
+      <c r="AA208">
+        <v>4.9</v>
+      </c>
+      <c r="AB208">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AC208">
+        <v>1.04</v>
+      </c>
+      <c r="AD208">
+        <v>10</v>
+      </c>
+      <c r="AE208">
+        <v>1.24</v>
+      </c>
+      <c r="AF208">
+        <v>3.7</v>
+      </c>
+      <c r="AG208">
+        <v>1.77</v>
+      </c>
+      <c r="AH208">
+        <v>1.98</v>
+      </c>
+      <c r="AI208">
+        <v>2.07</v>
+      </c>
+      <c r="AJ208">
+        <v>1.67</v>
+      </c>
+      <c r="AK208">
+        <v>1.08</v>
+      </c>
+      <c r="AL208">
+        <v>1.15</v>
+      </c>
+      <c r="AM208">
+        <v>2.95</v>
+      </c>
+      <c r="AN208">
+        <v>1.64</v>
+      </c>
+      <c r="AO208">
+        <v>0.91</v>
+      </c>
+      <c r="AP208">
+        <v>1.75</v>
+      </c>
+      <c r="AQ208">
+        <v>0.83</v>
+      </c>
+      <c r="AR208">
+        <v>1.66</v>
+      </c>
+      <c r="AS208">
+        <v>1.32</v>
+      </c>
+      <c r="AT208">
+        <v>2.98</v>
+      </c>
+      <c r="AU208">
+        <v>6</v>
+      </c>
+      <c r="AV208">
+        <v>4</v>
+      </c>
+      <c r="AW208">
+        <v>3</v>
+      </c>
+      <c r="AX208">
+        <v>10</v>
+      </c>
+      <c r="AY208">
+        <v>10</v>
+      </c>
+      <c r="AZ208">
+        <v>20</v>
+      </c>
+      <c r="BA208">
+        <v>1</v>
+      </c>
+      <c r="BB208">
+        <v>3</v>
+      </c>
+      <c r="BC208">
+        <v>4</v>
+      </c>
+      <c r="BD208">
+        <v>1.3</v>
+      </c>
+      <c r="BE208">
+        <v>7</v>
+      </c>
+      <c r="BF208">
+        <v>3.9</v>
+      </c>
+      <c r="BG208">
+        <v>1.38</v>
+      </c>
+      <c r="BH208">
+        <v>2.65</v>
+      </c>
+      <c r="BI208">
+        <v>1.65</v>
+      </c>
+      <c r="BJ208">
+        <v>2.02</v>
+      </c>
+      <c r="BK208">
+        <v>2.06</v>
+      </c>
+      <c r="BL208">
+        <v>1.63</v>
+      </c>
+      <c r="BM208">
+        <v>2.65</v>
+      </c>
+      <c r="BN208">
+        <v>1.38</v>
+      </c>
+      <c r="BO208">
+        <v>3.45</v>
+      </c>
+      <c r="BP208">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -709,6 +709,9 @@
     <t>['2', '15', '75']</t>
   </si>
   <si>
+    <t>['44', '80']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -986,6 +989,9 @@
   </si>
   <si>
     <t>['8']</t>
+  </si>
+  <si>
+    <t>['17']</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1684,7 +1690,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ2">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2015,7 +2021,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2633,7 +2639,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3045,7 +3051,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3457,7 +3463,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3663,7 +3669,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3869,7 +3875,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4075,7 +4081,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4281,7 +4287,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4487,7 +4493,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4977,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ18">
         <v>1.18</v>
@@ -5392,7 +5398,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ20">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR20">
         <v>0.84</v>
@@ -5723,7 +5729,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6341,7 +6347,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6547,7 +6553,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6753,7 +6759,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6959,7 +6965,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7371,7 +7377,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7449,7 +7455,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ30">
         <v>2.09</v>
@@ -7783,7 +7789,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7989,7 +7995,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8401,7 +8407,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -9019,7 +9025,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9225,7 +9231,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9843,7 +9849,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10461,7 +10467,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10667,7 +10673,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10954,7 +10960,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ47">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR47">
         <v>1.43</v>
@@ -11079,7 +11085,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11491,7 +11497,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12187,7 +12193,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ53">
         <v>0.45</v>
@@ -12315,7 +12321,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12521,7 +12527,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13139,7 +13145,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13345,7 +13351,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13551,7 +13557,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13757,7 +13763,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14375,7 +14381,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14787,7 +14793,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15280,7 +15286,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ68">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR68">
         <v>1.44</v>
@@ -15483,7 +15489,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ69">
         <v>0.75</v>
@@ -16229,7 +16235,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16435,7 +16441,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17671,7 +17677,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18370,7 +18376,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ83">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR83">
         <v>1.5</v>
@@ -19113,7 +19119,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19191,7 +19197,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ87">
         <v>1.55</v>
@@ -19319,7 +19325,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19525,7 +19531,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19731,7 +19737,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19937,7 +19943,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20349,7 +20355,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20555,7 +20561,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20761,7 +20767,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20967,7 +20973,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21585,7 +21591,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21663,7 +21669,7 @@
         <v>1.17</v>
       </c>
       <c r="AP99">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ99">
         <v>1.5</v>
@@ -21791,7 +21797,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21997,7 +22003,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22203,7 +22209,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22409,7 +22415,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22821,7 +22827,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23314,7 +23320,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ107">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23439,7 +23445,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23645,7 +23651,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23932,7 +23938,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ110">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR110">
         <v>1.69</v>
@@ -24057,7 +24063,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24675,7 +24681,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25087,7 +25093,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25293,7 +25299,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25705,7 +25711,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26323,7 +26329,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26529,7 +26535,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26941,7 +26947,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27353,7 +27359,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27559,7 +27565,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27843,7 +27849,7 @@
         <v>0.71</v>
       </c>
       <c r="AP129">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ129">
         <v>0.83</v>
@@ -27971,7 +27977,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28383,7 +28389,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28670,7 +28676,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ133">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR133">
         <v>1.65</v>
@@ -28795,7 +28801,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29001,7 +29007,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29207,7 +29213,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29413,7 +29419,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29619,7 +29625,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30031,7 +30037,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30237,7 +30243,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31554,7 +31560,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ147">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR147">
         <v>1.42</v>
@@ -31885,7 +31891,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32091,7 +32097,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32169,7 +32175,7 @@
         <v>1.38</v>
       </c>
       <c r="AP150">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ150">
         <v>1.27</v>
@@ -32503,7 +32509,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33121,7 +33127,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33739,7 +33745,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34151,7 +34157,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34357,7 +34363,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34641,7 +34647,7 @@
         <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ162">
         <v>1</v>
@@ -34769,7 +34775,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35181,7 +35187,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36086,7 +36092,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ169">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR169">
         <v>1.91</v>
@@ -36417,7 +36423,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36623,7 +36629,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37447,7 +37453,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37937,7 +37943,7 @@
         <v>1.56</v>
       </c>
       <c r="AP178">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ178">
         <v>1.42</v>
@@ -38065,7 +38071,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38477,7 +38483,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38683,7 +38689,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39301,7 +39307,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39588,7 +39594,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ186">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR186">
         <v>1.66</v>
@@ -39713,7 +39719,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40331,7 +40337,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40537,7 +40543,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41027,7 +41033,7 @@
         <v>0.4</v>
       </c>
       <c r="AP193">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ193">
         <v>0.33</v>
@@ -41155,7 +41161,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41567,7 +41573,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41648,7 +41654,7 @@
         <v>1</v>
       </c>
       <c r="AQ196">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR196">
         <v>1.46</v>
@@ -41773,7 +41779,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42185,7 +42191,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -43009,7 +43015,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43215,7 +43221,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43421,7 +43427,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -44196,6 +44202,212 @@
       </c>
       <c r="BP208">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7450857</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45723.58333333334</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>85</v>
+      </c>
+      <c r="H209" t="s">
+        <v>79</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>2</v>
+      </c>
+      <c r="L209">
+        <v>2</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>3</v>
+      </c>
+      <c r="O209" t="s">
+        <v>231</v>
+      </c>
+      <c r="P209" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q209">
+        <v>2.5</v>
+      </c>
+      <c r="R209">
+        <v>2.1</v>
+      </c>
+      <c r="S209">
+        <v>4.75</v>
+      </c>
+      <c r="T209">
+        <v>1.42</v>
+      </c>
+      <c r="U209">
+        <v>2.65</v>
+      </c>
+      <c r="V209">
+        <v>3</v>
+      </c>
+      <c r="W209">
+        <v>1.36</v>
+      </c>
+      <c r="X209">
+        <v>6.8</v>
+      </c>
+      <c r="Y209">
+        <v>1.07</v>
+      </c>
+      <c r="Z209">
+        <v>1.78</v>
+      </c>
+      <c r="AA209">
+        <v>3.51</v>
+      </c>
+      <c r="AB209">
+        <v>4.5</v>
+      </c>
+      <c r="AC209">
+        <v>1.05</v>
+      </c>
+      <c r="AD209">
+        <v>8.5</v>
+      </c>
+      <c r="AE209">
+        <v>1.32</v>
+      </c>
+      <c r="AF209">
+        <v>3</v>
+      </c>
+      <c r="AG209">
+        <v>2.05</v>
+      </c>
+      <c r="AH209">
+        <v>1.7</v>
+      </c>
+      <c r="AI209">
+        <v>1.83</v>
+      </c>
+      <c r="AJ209">
+        <v>1.85</v>
+      </c>
+      <c r="AK209">
+        <v>1.3</v>
+      </c>
+      <c r="AL209">
+        <v>1.25</v>
+      </c>
+      <c r="AM209">
+        <v>1.87</v>
+      </c>
+      <c r="AN209">
+        <v>1.27</v>
+      </c>
+      <c r="AO209">
+        <v>0.75</v>
+      </c>
+      <c r="AP209">
+        <v>1.42</v>
+      </c>
+      <c r="AQ209">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR209">
+        <v>1.41</v>
+      </c>
+      <c r="AS209">
+        <v>1.03</v>
+      </c>
+      <c r="AT209">
+        <v>2.44</v>
+      </c>
+      <c r="AU209">
+        <v>7</v>
+      </c>
+      <c r="AV209">
+        <v>3</v>
+      </c>
+      <c r="AW209">
+        <v>14</v>
+      </c>
+      <c r="AX209">
+        <v>8</v>
+      </c>
+      <c r="AY209">
+        <v>26</v>
+      </c>
+      <c r="AZ209">
+        <v>13</v>
+      </c>
+      <c r="BA209">
+        <v>3</v>
+      </c>
+      <c r="BB209">
+        <v>1</v>
+      </c>
+      <c r="BC209">
+        <v>4</v>
+      </c>
+      <c r="BD209">
+        <v>1.61</v>
+      </c>
+      <c r="BE209">
+        <v>6.4</v>
+      </c>
+      <c r="BF209">
+        <v>2.55</v>
+      </c>
+      <c r="BG209">
+        <v>1.43</v>
+      </c>
+      <c r="BH209">
+        <v>2.5</v>
+      </c>
+      <c r="BI209">
+        <v>1.74</v>
+      </c>
+      <c r="BJ209">
+        <v>1.92</v>
+      </c>
+      <c r="BK209">
+        <v>2.18</v>
+      </c>
+      <c r="BL209">
+        <v>1.56</v>
+      </c>
+      <c r="BM209">
+        <v>2.85</v>
+      </c>
+      <c r="BN209">
+        <v>1.33</v>
+      </c>
+      <c r="BO209">
+        <v>3.8</v>
+      </c>
+      <c r="BP209">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="329">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -712,6 +712,9 @@
     <t>['44', '80']</t>
   </si>
   <si>
+    <t>['21', '22', '58']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -992,6 +995,12 @@
   </si>
   <si>
     <t>['17']</t>
+  </si>
+  <si>
+    <t>['51', '90+1']</t>
+  </si>
+  <si>
+    <t>['24', '70', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1893,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ3">
         <v>0.83</v>
@@ -2021,7 +2030,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2102,7 +2111,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ4">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2639,7 +2648,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2717,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -2923,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ8">
         <v>1.27</v>
@@ -3051,7 +3060,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3132,7 +3141,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ9">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3463,7 +3472,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3669,7 +3678,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3875,7 +3884,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4081,7 +4090,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4287,7 +4296,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4493,7 +4502,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4777,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17">
         <v>0.33</v>
@@ -5729,7 +5738,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5810,7 +5819,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ22">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR22">
         <v>2.03</v>
@@ -6016,7 +6025,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ23">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR23">
         <v>2.07</v>
@@ -6219,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ24">
         <v>0.83</v>
@@ -6347,7 +6356,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6553,7 +6562,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6759,7 +6768,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6837,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ27">
         <v>0.83</v>
@@ -6965,7 +6974,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7377,7 +7386,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7664,7 +7673,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ31">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR31">
         <v>1.66</v>
@@ -7789,7 +7798,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7995,7 +8004,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8407,7 +8416,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8485,7 +8494,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ35">
         <v>1.17</v>
@@ -9025,7 +9034,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9231,7 +9240,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9721,7 +9730,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ41">
         <v>1.25</v>
@@ -9849,7 +9858,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9930,7 +9939,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ42">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10136,7 +10145,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ43">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10467,7 +10476,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10548,7 +10557,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ45">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.15</v>
@@ -10673,7 +10682,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10754,7 +10763,7 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR46">
         <v>1.21</v>
@@ -11085,7 +11094,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11163,7 +11172,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ48">
         <v>1.27</v>
@@ -11369,7 +11378,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ49">
         <v>0.75</v>
@@ -11497,7 +11506,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11781,7 +11790,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11987,7 +11996,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ52">
         <v>1.18</v>
@@ -12196,7 +12205,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ53">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR53">
         <v>1.28</v>
@@ -12321,7 +12330,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12527,7 +12536,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13145,7 +13154,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13351,7 +13360,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13557,7 +13566,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13763,7 +13772,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14381,7 +14390,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14668,7 +14677,7 @@
         <v>1</v>
       </c>
       <c r="AQ65">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.09</v>
@@ -14793,7 +14802,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14871,7 +14880,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -15077,7 +15086,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ67">
         <v>1.64</v>
@@ -15283,7 +15292,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ68">
         <v>0.6899999999999999</v>
@@ -15698,7 +15707,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ70">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -16235,7 +16244,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16441,7 +16450,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17549,7 +17558,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ79">
         <v>0.33</v>
@@ -17677,7 +17686,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18994,7 +19003,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.54</v>
@@ -19119,7 +19128,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19325,7 +19334,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19403,7 +19412,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88">
         <v>1.64</v>
@@ -19531,7 +19540,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19609,10 +19618,10 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ89">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19737,7 +19746,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19943,7 +19952,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20355,7 +20364,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20436,7 +20445,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ93">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR93">
         <v>1.66</v>
@@ -20561,7 +20570,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20767,7 +20776,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20845,7 +20854,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ95">
         <v>1.42</v>
@@ -20973,7 +20982,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21051,7 +21060,7 @@
         <v>2.4</v>
       </c>
       <c r="AP96">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ96">
         <v>2.09</v>
@@ -21591,7 +21600,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21797,7 +21806,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -22003,7 +22012,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22209,7 +22218,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22415,7 +22424,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22493,7 +22502,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ103">
         <v>1.55</v>
@@ -22827,7 +22836,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22908,7 +22917,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ105">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR105">
         <v>1.93</v>
@@ -23445,7 +23454,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23523,10 +23532,10 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ108">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR108">
         <v>1.61</v>
@@ -23651,7 +23660,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23729,7 +23738,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ109">
         <v>0.83</v>
@@ -24063,7 +24072,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24141,7 +24150,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ111">
         <v>1.42</v>
@@ -24347,10 +24356,10 @@
         <v>2.67</v>
       </c>
       <c r="AP112">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ112">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR112">
         <v>1.59</v>
@@ -24553,10 +24562,10 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ113">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.89</v>
@@ -24681,7 +24690,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25093,7 +25102,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25299,7 +25308,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25586,7 +25595,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ118">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR118">
         <v>1.58</v>
@@ -25711,7 +25720,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26329,7 +26338,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26535,7 +26544,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26947,7 +26956,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27359,7 +27368,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27437,7 +27446,7 @@
         <v>1.17</v>
       </c>
       <c r="AP127">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ127">
         <v>1.42</v>
@@ -27565,7 +27574,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27646,7 +27655,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ128">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27977,7 +27986,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28055,7 +28064,7 @@
         <v>1.17</v>
       </c>
       <c r="AP130">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ130">
         <v>1.17</v>
@@ -28389,7 +28398,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28467,7 +28476,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ132">
         <v>1.27</v>
@@ -28801,7 +28810,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28882,7 +28891,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ134">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR134">
         <v>1.7</v>
@@ -29007,7 +29016,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29085,7 +29094,7 @@
         <v>1.5</v>
       </c>
       <c r="AP135">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ135">
         <v>1.18</v>
@@ -29213,7 +29222,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29419,7 +29428,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29625,7 +29634,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29909,7 +29918,7 @@
         <v>1.43</v>
       </c>
       <c r="AP139">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ139">
         <v>1.17</v>
@@ -30037,7 +30046,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30243,7 +30252,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30324,7 +30333,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ141">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR141">
         <v>1.53</v>
@@ -31145,7 +31154,7 @@
         <v>0.63</v>
       </c>
       <c r="AP145">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ145">
         <v>0.75</v>
@@ -31351,7 +31360,7 @@
         <v>1.86</v>
       </c>
       <c r="AP146">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ146">
         <v>1.55</v>
@@ -31557,7 +31566,7 @@
         <v>0.25</v>
       </c>
       <c r="AP147">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ147">
         <v>0.6899999999999999</v>
@@ -31891,7 +31900,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31972,7 +31981,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ149">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR149">
         <v>1.41</v>
@@ -32097,7 +32106,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32509,7 +32518,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32796,7 +32805,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ153">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR153">
         <v>1.63</v>
@@ -33127,7 +33136,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33620,7 +33629,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ157">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR157">
         <v>1.39</v>
@@ -33745,7 +33754,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34029,7 +34038,7 @@
         <v>2.25</v>
       </c>
       <c r="AP159">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ159">
         <v>2.09</v>
@@ -34157,7 +34166,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34363,7 +34372,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34775,7 +34784,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -34853,10 +34862,10 @@
         <v>0.75</v>
       </c>
       <c r="AP163">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ163">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR163">
         <v>1.52</v>
@@ -35062,7 +35071,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ164">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR164">
         <v>1.72</v>
@@ -35187,7 +35196,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35265,7 +35274,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ165">
         <v>0.83</v>
@@ -35677,10 +35686,10 @@
         <v>2.33</v>
       </c>
       <c r="AP167">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ167">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -36298,7 +36307,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ170">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36423,7 +36432,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36629,7 +36638,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36707,7 +36716,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ172">
         <v>1.5</v>
@@ -37453,7 +37462,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37737,7 +37746,7 @@
         <v>1.44</v>
       </c>
       <c r="AP177">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ177">
         <v>1.18</v>
@@ -38071,7 +38080,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38483,7 +38492,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38689,7 +38698,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -38767,7 +38776,7 @@
         <v>1.1</v>
       </c>
       <c r="AP182">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ182">
         <v>1.25</v>
@@ -38973,10 +38982,10 @@
         <v>2.2</v>
       </c>
       <c r="AP183">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ183">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR183">
         <v>2.02</v>
@@ -39179,7 +39188,7 @@
         <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ184">
         <v>0.83</v>
@@ -39307,7 +39316,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39388,7 +39397,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ185">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR185">
         <v>1.95</v>
@@ -39719,7 +39728,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40337,7 +40346,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40543,7 +40552,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40621,10 +40630,10 @@
         <v>0.4</v>
       </c>
       <c r="AP191">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ191">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR191">
         <v>1.48</v>
@@ -41161,7 +41170,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41573,7 +41582,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41779,7 +41788,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -41857,7 +41866,7 @@
         <v>1.7</v>
       </c>
       <c r="AP197">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ197">
         <v>1.64</v>
@@ -42063,7 +42072,7 @@
         <v>0.82</v>
       </c>
       <c r="AP198">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ198">
         <v>0.75</v>
@@ -42191,7 +42200,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -43015,7 +43024,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43221,7 +43230,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43427,7 +43436,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -44251,7 +44260,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44408,6 +44417,830 @@
       </c>
       <c r="BP209">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7450863</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45723.6875</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>71</v>
+      </c>
+      <c r="H210" t="s">
+        <v>73</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>2</v>
+      </c>
+      <c r="O210" t="s">
+        <v>133</v>
+      </c>
+      <c r="P210" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q210">
+        <v>3.6</v>
+      </c>
+      <c r="R210">
+        <v>2.05</v>
+      </c>
+      <c r="S210">
+        <v>2.75</v>
+      </c>
+      <c r="T210">
+        <v>1.35</v>
+      </c>
+      <c r="U210">
+        <v>2.9</v>
+      </c>
+      <c r="V210">
+        <v>2.7</v>
+      </c>
+      <c r="W210">
+        <v>1.4</v>
+      </c>
+      <c r="X210">
+        <v>7.4</v>
+      </c>
+      <c r="Y210">
+        <v>1.1</v>
+      </c>
+      <c r="Z210">
+        <v>3.03</v>
+      </c>
+      <c r="AA210">
+        <v>3.27</v>
+      </c>
+      <c r="AB210">
+        <v>2.3</v>
+      </c>
+      <c r="AC210">
+        <v>1.05</v>
+      </c>
+      <c r="AD210">
+        <v>7.8</v>
+      </c>
+      <c r="AE210">
+        <v>1.23</v>
+      </c>
+      <c r="AF210">
+        <v>3.62</v>
+      </c>
+      <c r="AG210">
+        <v>1.89</v>
+      </c>
+      <c r="AH210">
+        <v>1.85</v>
+      </c>
+      <c r="AI210">
+        <v>1.67</v>
+      </c>
+      <c r="AJ210">
+        <v>2.05</v>
+      </c>
+      <c r="AK210">
+        <v>1.33</v>
+      </c>
+      <c r="AL210">
+        <v>1.28</v>
+      </c>
+      <c r="AM210">
+        <v>1.25</v>
+      </c>
+      <c r="AN210">
+        <v>0.91</v>
+      </c>
+      <c r="AO210">
+        <v>1</v>
+      </c>
+      <c r="AP210">
+        <v>0.92</v>
+      </c>
+      <c r="AQ210">
+        <v>1</v>
+      </c>
+      <c r="AR210">
+        <v>1.54</v>
+      </c>
+      <c r="AS210">
+        <v>1.46</v>
+      </c>
+      <c r="AT210">
+        <v>3</v>
+      </c>
+      <c r="AU210">
+        <v>5</v>
+      </c>
+      <c r="AV210">
+        <v>6</v>
+      </c>
+      <c r="AW210">
+        <v>11</v>
+      </c>
+      <c r="AX210">
+        <v>9</v>
+      </c>
+      <c r="AY210">
+        <v>23</v>
+      </c>
+      <c r="AZ210">
+        <v>18</v>
+      </c>
+      <c r="BA210">
+        <v>13</v>
+      </c>
+      <c r="BB210">
+        <v>6</v>
+      </c>
+      <c r="BC210">
+        <v>19</v>
+      </c>
+      <c r="BD210">
+        <v>2.2</v>
+      </c>
+      <c r="BE210">
+        <v>6.4</v>
+      </c>
+      <c r="BF210">
+        <v>1.82</v>
+      </c>
+      <c r="BG210">
+        <v>1.36</v>
+      </c>
+      <c r="BH210">
+        <v>2.75</v>
+      </c>
+      <c r="BI210">
+        <v>1.63</v>
+      </c>
+      <c r="BJ210">
+        <v>2.06</v>
+      </c>
+      <c r="BK210">
+        <v>2.02</v>
+      </c>
+      <c r="BL210">
+        <v>1.65</v>
+      </c>
+      <c r="BM210">
+        <v>2.63</v>
+      </c>
+      <c r="BN210">
+        <v>1.4</v>
+      </c>
+      <c r="BO210">
+        <v>3.45</v>
+      </c>
+      <c r="BP210">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7450855</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45724.44791666666</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>75</v>
+      </c>
+      <c r="H211" t="s">
+        <v>81</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>2</v>
+      </c>
+      <c r="N211">
+        <v>3</v>
+      </c>
+      <c r="O211" t="s">
+        <v>143</v>
+      </c>
+      <c r="P211" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q211">
+        <v>2.45</v>
+      </c>
+      <c r="R211">
+        <v>2.1</v>
+      </c>
+      <c r="S211">
+        <v>4.33</v>
+      </c>
+      <c r="T211">
+        <v>1.4</v>
+      </c>
+      <c r="U211">
+        <v>2.75</v>
+      </c>
+      <c r="V211">
+        <v>2.75</v>
+      </c>
+      <c r="W211">
+        <v>1.4</v>
+      </c>
+      <c r="X211">
+        <v>6.5</v>
+      </c>
+      <c r="Y211">
+        <v>1.08</v>
+      </c>
+      <c r="Z211">
+        <v>1.95</v>
+      </c>
+      <c r="AA211">
+        <v>3.2</v>
+      </c>
+      <c r="AB211">
+        <v>4.1</v>
+      </c>
+      <c r="AC211">
+        <v>1.07</v>
+      </c>
+      <c r="AD211">
+        <v>8</v>
+      </c>
+      <c r="AE211">
+        <v>1.33</v>
+      </c>
+      <c r="AF211">
+        <v>3.3</v>
+      </c>
+      <c r="AG211">
+        <v>1.87</v>
+      </c>
+      <c r="AH211">
+        <v>1.87</v>
+      </c>
+      <c r="AI211">
+        <v>1.75</v>
+      </c>
+      <c r="AJ211">
+        <v>1.95</v>
+      </c>
+      <c r="AK211">
+        <v>1.22</v>
+      </c>
+      <c r="AL211">
+        <v>1.28</v>
+      </c>
+      <c r="AM211">
+        <v>1.77</v>
+      </c>
+      <c r="AN211">
+        <v>1.25</v>
+      </c>
+      <c r="AO211">
+        <v>0.82</v>
+      </c>
+      <c r="AP211">
+        <v>1.15</v>
+      </c>
+      <c r="AQ211">
+        <v>1</v>
+      </c>
+      <c r="AR211">
+        <v>1.62</v>
+      </c>
+      <c r="AS211">
+        <v>1.4</v>
+      </c>
+      <c r="AT211">
+        <v>3.02</v>
+      </c>
+      <c r="AU211">
+        <v>3</v>
+      </c>
+      <c r="AV211">
+        <v>4</v>
+      </c>
+      <c r="AW211">
+        <v>3</v>
+      </c>
+      <c r="AX211">
+        <v>9</v>
+      </c>
+      <c r="AY211">
+        <v>9</v>
+      </c>
+      <c r="AZ211">
+        <v>16</v>
+      </c>
+      <c r="BA211">
+        <v>5</v>
+      </c>
+      <c r="BB211">
+        <v>7</v>
+      </c>
+      <c r="BC211">
+        <v>12</v>
+      </c>
+      <c r="BD211">
+        <v>1.65</v>
+      </c>
+      <c r="BE211">
+        <v>6.4</v>
+      </c>
+      <c r="BF211">
+        <v>2.5</v>
+      </c>
+      <c r="BG211">
+        <v>1.38</v>
+      </c>
+      <c r="BH211">
+        <v>2.65</v>
+      </c>
+      <c r="BI211">
+        <v>1.65</v>
+      </c>
+      <c r="BJ211">
+        <v>2.02</v>
+      </c>
+      <c r="BK211">
+        <v>2.06</v>
+      </c>
+      <c r="BL211">
+        <v>1.63</v>
+      </c>
+      <c r="BM211">
+        <v>2.65</v>
+      </c>
+      <c r="BN211">
+        <v>1.38</v>
+      </c>
+      <c r="BO211">
+        <v>3.55</v>
+      </c>
+      <c r="BP211">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7450861</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45724.5625</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>84</v>
+      </c>
+      <c r="H212" t="s">
+        <v>86</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>3</v>
+      </c>
+      <c r="N212">
+        <v>3</v>
+      </c>
+      <c r="O212" t="s">
+        <v>95</v>
+      </c>
+      <c r="P212" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q212">
+        <v>3.65</v>
+      </c>
+      <c r="R212">
+        <v>1.91</v>
+      </c>
+      <c r="S212">
+        <v>3.1</v>
+      </c>
+      <c r="T212">
+        <v>1.53</v>
+      </c>
+      <c r="U212">
+        <v>2.35</v>
+      </c>
+      <c r="V212">
+        <v>3.55</v>
+      </c>
+      <c r="W212">
+        <v>1.25</v>
+      </c>
+      <c r="X212">
+        <v>8.9</v>
+      </c>
+      <c r="Y212">
+        <v>1.01</v>
+      </c>
+      <c r="Z212">
+        <v>3</v>
+      </c>
+      <c r="AA212">
+        <v>3.21</v>
+      </c>
+      <c r="AB212">
+        <v>2.35</v>
+      </c>
+      <c r="AC212">
+        <v>1.09</v>
+      </c>
+      <c r="AD212">
+        <v>7</v>
+      </c>
+      <c r="AE212">
+        <v>1.5</v>
+      </c>
+      <c r="AF212">
+        <v>2.3</v>
+      </c>
+      <c r="AG212">
+        <v>2.94</v>
+      </c>
+      <c r="AH212">
+        <v>1.35</v>
+      </c>
+      <c r="AI212">
+        <v>2.05</v>
+      </c>
+      <c r="AJ212">
+        <v>1.7</v>
+      </c>
+      <c r="AK212">
+        <v>1.53</v>
+      </c>
+      <c r="AL212">
+        <v>1.3</v>
+      </c>
+      <c r="AM212">
+        <v>1.38</v>
+      </c>
+      <c r="AN212">
+        <v>1.36</v>
+      </c>
+      <c r="AO212">
+        <v>2.27</v>
+      </c>
+      <c r="AP212">
+        <v>1.25</v>
+      </c>
+      <c r="AQ212">
+        <v>2.33</v>
+      </c>
+      <c r="AR212">
+        <v>1.62</v>
+      </c>
+      <c r="AS212">
+        <v>1.46</v>
+      </c>
+      <c r="AT212">
+        <v>3.08</v>
+      </c>
+      <c r="AU212">
+        <v>6</v>
+      </c>
+      <c r="AV212">
+        <v>9</v>
+      </c>
+      <c r="AW212">
+        <v>4</v>
+      </c>
+      <c r="AX212">
+        <v>1</v>
+      </c>
+      <c r="AY212">
+        <v>13</v>
+      </c>
+      <c r="AZ212">
+        <v>10</v>
+      </c>
+      <c r="BA212">
+        <v>2</v>
+      </c>
+      <c r="BB212">
+        <v>2</v>
+      </c>
+      <c r="BC212">
+        <v>4</v>
+      </c>
+      <c r="BD212">
+        <v>2.2</v>
+      </c>
+      <c r="BE212">
+        <v>6.25</v>
+      </c>
+      <c r="BF212">
+        <v>1.82</v>
+      </c>
+      <c r="BG212">
+        <v>1.52</v>
+      </c>
+      <c r="BH212">
+        <v>2.28</v>
+      </c>
+      <c r="BI212">
+        <v>1.88</v>
+      </c>
+      <c r="BJ212">
+        <v>1.76</v>
+      </c>
+      <c r="BK212">
+        <v>2.43</v>
+      </c>
+      <c r="BL212">
+        <v>1.46</v>
+      </c>
+      <c r="BM212">
+        <v>3.2</v>
+      </c>
+      <c r="BN212">
+        <v>1.27</v>
+      </c>
+      <c r="BO212">
+        <v>4.35</v>
+      </c>
+      <c r="BP212">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7450858</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45724.67708333334</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>76</v>
+      </c>
+      <c r="H213" t="s">
+        <v>78</v>
+      </c>
+      <c r="I213">
+        <v>2</v>
+      </c>
+      <c r="J213">
+        <v>1</v>
+      </c>
+      <c r="K213">
+        <v>3</v>
+      </c>
+      <c r="L213">
+        <v>3</v>
+      </c>
+      <c r="M213">
+        <v>1</v>
+      </c>
+      <c r="N213">
+        <v>4</v>
+      </c>
+      <c r="O213" t="s">
+        <v>232</v>
+      </c>
+      <c r="P213" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q213">
+        <v>1.9</v>
+      </c>
+      <c r="R213">
+        <v>2.35</v>
+      </c>
+      <c r="S213">
+        <v>6</v>
+      </c>
+      <c r="T213">
+        <v>1.3</v>
+      </c>
+      <c r="U213">
+        <v>3.2</v>
+      </c>
+      <c r="V213">
+        <v>2.4</v>
+      </c>
+      <c r="W213">
+        <v>1.5</v>
+      </c>
+      <c r="X213">
+        <v>5.25</v>
+      </c>
+      <c r="Y213">
+        <v>1.12</v>
+      </c>
+      <c r="Z213">
+        <v>1.5</v>
+      </c>
+      <c r="AA213">
+        <v>4.3</v>
+      </c>
+      <c r="AB213">
+        <v>5.9</v>
+      </c>
+      <c r="AC213">
+        <v>1.04</v>
+      </c>
+      <c r="AD213">
+        <v>10</v>
+      </c>
+      <c r="AE213">
+        <v>1.22</v>
+      </c>
+      <c r="AF213">
+        <v>4.2</v>
+      </c>
+      <c r="AG213">
+        <v>1.65</v>
+      </c>
+      <c r="AH213">
+        <v>2.05</v>
+      </c>
+      <c r="AI213">
+        <v>1.8</v>
+      </c>
+      <c r="AJ213">
+        <v>1.91</v>
+      </c>
+      <c r="AK213">
+        <v>1.1</v>
+      </c>
+      <c r="AL213">
+        <v>1.17</v>
+      </c>
+      <c r="AM213">
+        <v>2.65</v>
+      </c>
+      <c r="AN213">
+        <v>2.5</v>
+      </c>
+      <c r="AO213">
+        <v>0.45</v>
+      </c>
+      <c r="AP213">
+        <v>2.54</v>
+      </c>
+      <c r="AQ213">
+        <v>0.42</v>
+      </c>
+      <c r="AR213">
+        <v>1.92</v>
+      </c>
+      <c r="AS213">
+        <v>1.28</v>
+      </c>
+      <c r="AT213">
+        <v>3.2</v>
+      </c>
+      <c r="AU213">
+        <v>15</v>
+      </c>
+      <c r="AV213">
+        <v>5</v>
+      </c>
+      <c r="AW213">
+        <v>9</v>
+      </c>
+      <c r="AX213">
+        <v>6</v>
+      </c>
+      <c r="AY213">
+        <v>28</v>
+      </c>
+      <c r="AZ213">
+        <v>12</v>
+      </c>
+      <c r="BA213">
+        <v>5</v>
+      </c>
+      <c r="BB213">
+        <v>6</v>
+      </c>
+      <c r="BC213">
+        <v>11</v>
+      </c>
+      <c r="BD213">
+        <v>1.42</v>
+      </c>
+      <c r="BE213">
+        <v>6.75</v>
+      </c>
+      <c r="BF213">
+        <v>3.2</v>
+      </c>
+      <c r="BG213">
+        <v>1.35</v>
+      </c>
+      <c r="BH213">
+        <v>2.8</v>
+      </c>
+      <c r="BI213">
+        <v>1.61</v>
+      </c>
+      <c r="BJ213">
+        <v>2.08</v>
+      </c>
+      <c r="BK213">
+        <v>2</v>
+      </c>
+      <c r="BL213">
+        <v>1.66</v>
+      </c>
+      <c r="BM213">
+        <v>2.55</v>
+      </c>
+      <c r="BN213">
+        <v>1.41</v>
+      </c>
+      <c r="BO213">
+        <v>3.4</v>
+      </c>
+      <c r="BP213">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1002,6 +1002,9 @@
   <si>
     <t>['24', '70', '90+2']</t>
   </si>
+  <si>
+    <t>['48', '59']</t>
+  </si>
 </sst>
 </file>
 
@@ -1362,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2108,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -2523,7 +2526,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ6">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2935,7 +2938,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ8">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3553,7 +3556,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ11">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3756,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ12">
         <v>1.42</v>
@@ -4171,7 +4174,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ14">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4374,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15">
         <v>1.55</v>
@@ -5816,7 +5819,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ22">
         <v>2.33</v>
@@ -7055,7 +7058,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ28">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR28">
         <v>2.08</v>
@@ -7876,10 +7879,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ32">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR32">
         <v>1.13</v>
@@ -8288,7 +8291,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ34">
         <v>0.33</v>
@@ -8906,7 +8909,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ37">
         <v>1.42</v>
@@ -10554,7 +10557,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10760,7 +10763,7 @@
         <v>2.33</v>
       </c>
       <c r="AP46">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ46">
         <v>2.33</v>
@@ -11175,7 +11178,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ48">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR48">
         <v>0.96</v>
@@ -11381,7 +11384,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ49">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11584,10 +11587,10 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ50">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR50">
         <v>1.73</v>
@@ -14265,7 +14268,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ63">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -14468,7 +14471,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ64">
         <v>0.83</v>
@@ -14674,7 +14677,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -15089,7 +15092,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ67">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR67">
         <v>1.96</v>
@@ -15501,7 +15504,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ69">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -16734,7 +16737,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ75">
         <v>1.5</v>
@@ -17355,7 +17358,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR78">
         <v>1.53</v>
@@ -17767,7 +17770,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ80">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR80">
         <v>1.47</v>
@@ -17970,7 +17973,7 @@
         <v>0.25</v>
       </c>
       <c r="AP81">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18176,7 +18179,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ82">
         <v>0.83</v>
@@ -18797,7 +18800,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ85">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR85">
         <v>1.53</v>
@@ -19415,7 +19418,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR88">
         <v>1.53</v>
@@ -20030,7 +20033,7 @@
         <v>0.6</v>
       </c>
       <c r="AP91">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91">
         <v>1.25</v>
@@ -20651,7 +20654,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ94">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR94">
         <v>1.85</v>
@@ -21884,7 +21887,7 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ100">
         <v>1.18</v>
@@ -22299,7 +22302,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ102">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR102">
         <v>1.67</v>
@@ -22708,7 +22711,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ104">
         <v>0.33</v>
@@ -24771,7 +24774,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ114">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR114">
         <v>1.55</v>
@@ -25180,10 +25183,10 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ116">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR116">
         <v>1.38</v>
@@ -26419,7 +26422,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ122">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR122">
         <v>2.04</v>
@@ -26622,7 +26625,7 @@
         <v>2.5</v>
       </c>
       <c r="AP123">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ123">
         <v>2.09</v>
@@ -27034,7 +27037,7 @@
         <v>0.86</v>
       </c>
       <c r="AP125">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ125">
         <v>1.25</v>
@@ -28270,10 +28273,10 @@
         <v>0.71</v>
       </c>
       <c r="AP131">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ131">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28479,7 +28482,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ132">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR132">
         <v>1.49</v>
@@ -29712,7 +29715,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -31157,7 +31160,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ145">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR145">
         <v>1.63</v>
@@ -31772,7 +31775,7 @@
         <v>0.75</v>
       </c>
       <c r="AP148">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ148">
         <v>0.83</v>
@@ -31978,7 +31981,7 @@
         <v>2.25</v>
       </c>
       <c r="AP149">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ149">
         <v>2.33</v>
@@ -32187,7 +32190,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ150">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR150">
         <v>1.43</v>
@@ -32393,7 +32396,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ151">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR151">
         <v>1.81</v>
@@ -33420,7 +33423,7 @@
         <v>0.38</v>
       </c>
       <c r="AP156">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ156">
         <v>0.33</v>
@@ -33626,7 +33629,7 @@
         <v>0.5</v>
       </c>
       <c r="AP157">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ157">
         <v>0.42</v>
@@ -34247,7 +34250,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ160">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR160">
         <v>1.51</v>
@@ -35068,7 +35071,7 @@
         <v>0.44</v>
       </c>
       <c r="AP164">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ164">
         <v>0.42</v>
@@ -35895,7 +35898,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ168">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR168">
         <v>1.8</v>
@@ -36925,7 +36928,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ173">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR173">
         <v>1.71</v>
@@ -37131,7 +37134,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ174">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR174">
         <v>1.83</v>
@@ -38158,7 +38161,7 @@
         <v>2.11</v>
       </c>
       <c r="AP179">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ179">
         <v>2.09</v>
@@ -38364,7 +38367,7 @@
         <v>1.56</v>
       </c>
       <c r="AP180">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ180">
         <v>1.55</v>
@@ -38573,7 +38576,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ181">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR181">
         <v>1.46</v>
@@ -40012,7 +40015,7 @@
         <v>1.4</v>
       </c>
       <c r="AP188">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ188">
         <v>1.5</v>
@@ -40839,7 +40842,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ192">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR192">
         <v>1.67</v>
@@ -41248,7 +41251,7 @@
         <v>0.8</v>
       </c>
       <c r="AP194">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ194">
         <v>1</v>
@@ -41660,7 +41663,7 @@
         <v>0.55</v>
       </c>
       <c r="AP196">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ196">
         <v>0.6899999999999999</v>
@@ -41869,7 +41872,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ197">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR197">
         <v>1.68</v>
@@ -42075,7 +42078,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ198">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR198">
         <v>1.96</v>
@@ -45241,6 +45244,624 @@
       </c>
       <c r="BP213">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7450856</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45725.34375</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>72</v>
+      </c>
+      <c r="H214" t="s">
+        <v>83</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
+        <v>206</v>
+      </c>
+      <c r="P214" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q214">
+        <v>2.6</v>
+      </c>
+      <c r="R214">
+        <v>2.2</v>
+      </c>
+      <c r="S214">
+        <v>3.6</v>
+      </c>
+      <c r="T214">
+        <v>1.3</v>
+      </c>
+      <c r="U214">
+        <v>3.2</v>
+      </c>
+      <c r="V214">
+        <v>2.4</v>
+      </c>
+      <c r="W214">
+        <v>1.5</v>
+      </c>
+      <c r="X214">
+        <v>5.25</v>
+      </c>
+      <c r="Y214">
+        <v>1.12</v>
+      </c>
+      <c r="Z214">
+        <v>2.13</v>
+      </c>
+      <c r="AA214">
+        <v>3.63</v>
+      </c>
+      <c r="AB214">
+        <v>3.07</v>
+      </c>
+      <c r="AC214">
+        <v>1.04</v>
+      </c>
+      <c r="AD214">
+        <v>10</v>
+      </c>
+      <c r="AE214">
+        <v>1.22</v>
+      </c>
+      <c r="AF214">
+        <v>4.2</v>
+      </c>
+      <c r="AG214">
+        <v>1.6</v>
+      </c>
+      <c r="AH214">
+        <v>2.1</v>
+      </c>
+      <c r="AI214">
+        <v>1.53</v>
+      </c>
+      <c r="AJ214">
+        <v>2.35</v>
+      </c>
+      <c r="AK214">
+        <v>1.35</v>
+      </c>
+      <c r="AL214">
+        <v>1.22</v>
+      </c>
+      <c r="AM214">
+        <v>1.67</v>
+      </c>
+      <c r="AN214">
+        <v>1.45</v>
+      </c>
+      <c r="AO214">
+        <v>0.75</v>
+      </c>
+      <c r="AP214">
+        <v>1.58</v>
+      </c>
+      <c r="AQ214">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR214">
+        <v>1.68</v>
+      </c>
+      <c r="AS214">
+        <v>1.44</v>
+      </c>
+      <c r="AT214">
+        <v>3.12</v>
+      </c>
+      <c r="AU214">
+        <v>3</v>
+      </c>
+      <c r="AV214">
+        <v>0</v>
+      </c>
+      <c r="AW214">
+        <v>4</v>
+      </c>
+      <c r="AX214">
+        <v>14</v>
+      </c>
+      <c r="AY214">
+        <v>8</v>
+      </c>
+      <c r="AZ214">
+        <v>17</v>
+      </c>
+      <c r="BA214">
+        <v>3</v>
+      </c>
+      <c r="BB214">
+        <v>8</v>
+      </c>
+      <c r="BC214">
+        <v>11</v>
+      </c>
+      <c r="BD214">
+        <v>1.79</v>
+      </c>
+      <c r="BE214">
+        <v>6.4</v>
+      </c>
+      <c r="BF214">
+        <v>2.23</v>
+      </c>
+      <c r="BG214">
+        <v>1.32</v>
+      </c>
+      <c r="BH214">
+        <v>2.9</v>
+      </c>
+      <c r="BI214">
+        <v>1.56</v>
+      </c>
+      <c r="BJ214">
+        <v>2.18</v>
+      </c>
+      <c r="BK214">
+        <v>1.92</v>
+      </c>
+      <c r="BL214">
+        <v>1.73</v>
+      </c>
+      <c r="BM214">
+        <v>2.45</v>
+      </c>
+      <c r="BN214">
+        <v>1.45</v>
+      </c>
+      <c r="BO214">
+        <v>3.2</v>
+      </c>
+      <c r="BP214">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7450859</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45725.44791666666</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>80</v>
+      </c>
+      <c r="H215" t="s">
+        <v>87</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="N215">
+        <v>3</v>
+      </c>
+      <c r="O215" t="s">
+        <v>96</v>
+      </c>
+      <c r="P215" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q215">
+        <v>3.1</v>
+      </c>
+      <c r="R215">
+        <v>2.31</v>
+      </c>
+      <c r="S215">
+        <v>3.27</v>
+      </c>
+      <c r="T215">
+        <v>1.33</v>
+      </c>
+      <c r="U215">
+        <v>3.26</v>
+      </c>
+      <c r="V215">
+        <v>2.65</v>
+      </c>
+      <c r="W215">
+        <v>1.47</v>
+      </c>
+      <c r="X215">
+        <v>7</v>
+      </c>
+      <c r="Y215">
+        <v>1.1</v>
+      </c>
+      <c r="Z215">
+        <v>3.14</v>
+      </c>
+      <c r="AA215">
+        <v>3.09</v>
+      </c>
+      <c r="AB215">
+        <v>2.34</v>
+      </c>
+      <c r="AC215">
+        <v>1.05</v>
+      </c>
+      <c r="AD215">
+        <v>9.5</v>
+      </c>
+      <c r="AE215">
+        <v>1.25</v>
+      </c>
+      <c r="AF215">
+        <v>3.7</v>
+      </c>
+      <c r="AG215">
+        <v>1.92</v>
+      </c>
+      <c r="AH215">
+        <v>1.82</v>
+      </c>
+      <c r="AI215">
+        <v>1.62</v>
+      </c>
+      <c r="AJ215">
+        <v>2.2</v>
+      </c>
+      <c r="AK215">
+        <v>1.5</v>
+      </c>
+      <c r="AL215">
+        <v>1.25</v>
+      </c>
+      <c r="AM215">
+        <v>1.45</v>
+      </c>
+      <c r="AN215">
+        <v>1</v>
+      </c>
+      <c r="AO215">
+        <v>1.27</v>
+      </c>
+      <c r="AP215">
+        <v>0.92</v>
+      </c>
+      <c r="AQ215">
+        <v>1.42</v>
+      </c>
+      <c r="AR215">
+        <v>1.54</v>
+      </c>
+      <c r="AS215">
+        <v>1.34</v>
+      </c>
+      <c r="AT215">
+        <v>2.88</v>
+      </c>
+      <c r="AU215">
+        <v>4</v>
+      </c>
+      <c r="AV215">
+        <v>4</v>
+      </c>
+      <c r="AW215">
+        <v>17</v>
+      </c>
+      <c r="AX215">
+        <v>6</v>
+      </c>
+      <c r="AY215">
+        <v>30</v>
+      </c>
+      <c r="AZ215">
+        <v>12</v>
+      </c>
+      <c r="BA215">
+        <v>5</v>
+      </c>
+      <c r="BB215">
+        <v>4</v>
+      </c>
+      <c r="BC215">
+        <v>9</v>
+      </c>
+      <c r="BD215">
+        <v>2</v>
+      </c>
+      <c r="BE215">
+        <v>6.1</v>
+      </c>
+      <c r="BF215">
+        <v>2</v>
+      </c>
+      <c r="BG215">
+        <v>1.37</v>
+      </c>
+      <c r="BH215">
+        <v>2.7</v>
+      </c>
+      <c r="BI215">
+        <v>1.65</v>
+      </c>
+      <c r="BJ215">
+        <v>2.04</v>
+      </c>
+      <c r="BK215">
+        <v>1.85</v>
+      </c>
+      <c r="BL215">
+        <v>1.85</v>
+      </c>
+      <c r="BM215">
+        <v>2.65</v>
+      </c>
+      <c r="BN215">
+        <v>1.38</v>
+      </c>
+      <c r="BO215">
+        <v>3.45</v>
+      </c>
+      <c r="BP215">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7450862</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45725.5625</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>82</v>
+      </c>
+      <c r="H216" t="s">
+        <v>70</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
+        <v>95</v>
+      </c>
+      <c r="P216" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q216">
+        <v>3.6</v>
+      </c>
+      <c r="R216">
+        <v>2.15</v>
+      </c>
+      <c r="S216">
+        <v>2.62</v>
+      </c>
+      <c r="T216">
+        <v>1.33</v>
+      </c>
+      <c r="U216">
+        <v>3</v>
+      </c>
+      <c r="V216">
+        <v>2.45</v>
+      </c>
+      <c r="W216">
+        <v>1.48</v>
+      </c>
+      <c r="X216">
+        <v>5.5</v>
+      </c>
+      <c r="Y216">
+        <v>1.11</v>
+      </c>
+      <c r="Z216">
+        <v>3.15</v>
+      </c>
+      <c r="AA216">
+        <v>3.55</v>
+      </c>
+      <c r="AB216">
+        <v>2.12</v>
+      </c>
+      <c r="AC216">
+        <v>1.05</v>
+      </c>
+      <c r="AD216">
+        <v>9.5</v>
+      </c>
+      <c r="AE216">
+        <v>1.22</v>
+      </c>
+      <c r="AF216">
+        <v>4</v>
+      </c>
+      <c r="AG216">
+        <v>1.67</v>
+      </c>
+      <c r="AH216">
+        <v>2</v>
+      </c>
+      <c r="AI216">
+        <v>1.57</v>
+      </c>
+      <c r="AJ216">
+        <v>2.25</v>
+      </c>
+      <c r="AK216">
+        <v>1.65</v>
+      </c>
+      <c r="AL216">
+        <v>1.25</v>
+      </c>
+      <c r="AM216">
+        <v>1.35</v>
+      </c>
+      <c r="AN216">
+        <v>1.55</v>
+      </c>
+      <c r="AO216">
+        <v>1.64</v>
+      </c>
+      <c r="AP216">
+        <v>1.42</v>
+      </c>
+      <c r="AQ216">
+        <v>1.75</v>
+      </c>
+      <c r="AR216">
+        <v>1.42</v>
+      </c>
+      <c r="AS216">
+        <v>1.3</v>
+      </c>
+      <c r="AT216">
+        <v>2.72</v>
+      </c>
+      <c r="AU216">
+        <v>6</v>
+      </c>
+      <c r="AV216">
+        <v>3</v>
+      </c>
+      <c r="AW216">
+        <v>12</v>
+      </c>
+      <c r="AX216">
+        <v>6</v>
+      </c>
+      <c r="AY216">
+        <v>22</v>
+      </c>
+      <c r="AZ216">
+        <v>14</v>
+      </c>
+      <c r="BA216">
+        <v>13</v>
+      </c>
+      <c r="BB216">
+        <v>2</v>
+      </c>
+      <c r="BC216">
+        <v>15</v>
+      </c>
+      <c r="BD216">
+        <v>2.3</v>
+      </c>
+      <c r="BE216">
+        <v>6.5</v>
+      </c>
+      <c r="BF216">
+        <v>1.75</v>
+      </c>
+      <c r="BG216">
+        <v>1.34</v>
+      </c>
+      <c r="BH216">
+        <v>2.8</v>
+      </c>
+      <c r="BI216">
+        <v>1.6</v>
+      </c>
+      <c r="BJ216">
+        <v>2.12</v>
+      </c>
+      <c r="BK216">
+        <v>1.96</v>
+      </c>
+      <c r="BL216">
+        <v>1.7</v>
+      </c>
+      <c r="BM216">
+        <v>2.48</v>
+      </c>
+      <c r="BN216">
+        <v>1.44</v>
+      </c>
+      <c r="BO216">
+        <v>3.25</v>
+      </c>
+      <c r="BP216">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="331">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,9 @@
     <t>['21', '22', '58']</t>
   </si>
   <si>
+    <t>['-1', '-1', '-1']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1365,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2033,7 +2036,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2651,7 +2654,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3063,7 +3066,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3141,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9">
         <v>2.33</v>
@@ -3475,7 +3478,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3681,7 +3684,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3887,7 +3890,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4093,7 +4096,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4299,7 +4302,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4505,7 +4508,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4998,7 +5001,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ18">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5741,7 +5744,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6359,7 +6362,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6437,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ25">
         <v>1.25</v>
@@ -6565,7 +6568,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6771,7 +6774,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6977,7 +6980,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7389,7 +7392,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7801,7 +7804,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8007,7 +8010,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8088,7 +8091,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ33">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR33">
         <v>1.25</v>
@@ -8419,7 +8422,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -9037,7 +9040,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9243,7 +9246,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9861,7 +9864,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10479,7 +10482,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10685,7 +10688,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10969,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ47">
         <v>0.6899999999999999</v>
@@ -11097,7 +11100,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11509,7 +11512,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12002,7 +12005,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ52">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12333,7 +12336,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12539,7 +12542,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13157,7 +13160,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13363,7 +13366,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13569,7 +13572,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13775,7 +13778,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14265,7 +14268,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ63">
         <v>1.42</v>
@@ -14393,7 +14396,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14805,7 +14808,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -16122,7 +16125,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ72">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16247,7 +16250,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16453,7 +16456,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17689,7 +17692,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17767,7 +17770,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ80">
         <v>1.75</v>
@@ -18591,7 +18594,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ84">
         <v>0.33</v>
@@ -19131,7 +19134,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19337,7 +19340,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19543,7 +19546,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19749,7 +19752,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19955,7 +19958,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20367,7 +20370,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20573,7 +20576,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20779,7 +20782,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20985,7 +20988,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21478,7 +21481,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ98">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR98">
         <v>1.72</v>
@@ -21603,7 +21606,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21809,7 +21812,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21890,7 +21893,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ100">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR100">
         <v>1.26</v>
@@ -22015,7 +22018,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22093,7 +22096,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ101">
         <v>0.83</v>
@@ -22221,7 +22224,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22427,7 +22430,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22839,7 +22842,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23457,7 +23460,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23663,7 +23666,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24075,7 +24078,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24693,7 +24696,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25105,7 +25108,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25311,7 +25314,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25723,7 +25726,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -25801,7 +25804,7 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -26341,7 +26344,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26547,7 +26550,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26959,7 +26962,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27371,7 +27374,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27577,7 +27580,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27989,7 +27992,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28401,7 +28404,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28813,7 +28816,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29019,7 +29022,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29100,7 +29103,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ135">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR135">
         <v>1.91</v>
@@ -29225,7 +29228,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29431,7 +29434,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29637,7 +29640,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30049,7 +30052,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30255,7 +30258,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31903,7 +31906,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32109,7 +32112,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32521,7 +32524,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32602,7 +32605,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ152">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR152">
         <v>1.7</v>
@@ -32805,7 +32808,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -33139,7 +33142,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33757,7 +33760,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34169,7 +34172,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34375,7 +34378,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34456,7 +34459,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ161">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34787,7 +34790,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35199,7 +35202,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35483,7 +35486,7 @@
         <v>0.67</v>
       </c>
       <c r="AP166">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ166">
         <v>0.83</v>
@@ -36435,7 +36438,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36641,7 +36644,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37465,7 +37468,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37752,7 +37755,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ177">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR177">
         <v>1.53</v>
@@ -38083,7 +38086,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38495,7 +38498,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38701,7 +38704,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39319,7 +39322,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39731,7 +39734,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40349,7 +40352,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40555,7 +40558,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41173,7 +41176,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41460,7 +41463,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ195">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR195">
         <v>1.57</v>
@@ -41585,7 +41588,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41791,7 +41794,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42203,7 +42206,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42281,7 +42284,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ199">
         <v>1.17</v>
@@ -43027,7 +43030,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43233,7 +43236,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43439,7 +43442,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -44263,7 +44266,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44675,7 +44678,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44881,7 +44884,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -45499,7 +45502,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45705,7 +45708,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -45861,6 +45864,212 @@
         <v>3.25</v>
       </c>
       <c r="BP216">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7450860</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45726.625</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>77</v>
+      </c>
+      <c r="H217" t="s">
+        <v>74</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>3</v>
+      </c>
+      <c r="M217">
+        <v>3</v>
+      </c>
+      <c r="N217">
+        <v>6</v>
+      </c>
+      <c r="O217" t="s">
+        <v>233</v>
+      </c>
+      <c r="P217" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q217">
+        <v>4.06</v>
+      </c>
+      <c r="R217">
+        <v>2.37</v>
+      </c>
+      <c r="S217">
+        <v>2.55</v>
+      </c>
+      <c r="T217">
+        <v>1.33</v>
+      </c>
+      <c r="U217">
+        <v>3.25</v>
+      </c>
+      <c r="V217">
+        <v>2.58</v>
+      </c>
+      <c r="W217">
+        <v>1.49</v>
+      </c>
+      <c r="X217">
+        <v>6.5</v>
+      </c>
+      <c r="Y217">
+        <v>1.11</v>
+      </c>
+      <c r="Z217">
+        <v>3.73</v>
+      </c>
+      <c r="AA217">
+        <v>3.78</v>
+      </c>
+      <c r="AB217">
+        <v>1.86</v>
+      </c>
+      <c r="AC217">
+        <v>1.04</v>
+      </c>
+      <c r="AD217">
+        <v>10</v>
+      </c>
+      <c r="AE217">
+        <v>1.22</v>
+      </c>
+      <c r="AF217">
+        <v>4</v>
+      </c>
+      <c r="AG217">
+        <v>1.67</v>
+      </c>
+      <c r="AH217">
+        <v>2</v>
+      </c>
+      <c r="AI217">
+        <v>1.62</v>
+      </c>
+      <c r="AJ217">
+        <v>2.2</v>
+      </c>
+      <c r="AK217">
+        <v>1.8</v>
+      </c>
+      <c r="AL217">
+        <v>1.22</v>
+      </c>
+      <c r="AM217">
+        <v>1.28</v>
+      </c>
+      <c r="AN217">
+        <v>1.64</v>
+      </c>
+      <c r="AO217">
+        <v>1.18</v>
+      </c>
+      <c r="AP217">
+        <v>1.58</v>
+      </c>
+      <c r="AQ217">
+        <v>1.17</v>
+      </c>
+      <c r="AR217">
+        <v>1.64</v>
+      </c>
+      <c r="AS217">
+        <v>1.49</v>
+      </c>
+      <c r="AT217">
+        <v>3.13</v>
+      </c>
+      <c r="AU217">
+        <v>6</v>
+      </c>
+      <c r="AV217">
+        <v>4</v>
+      </c>
+      <c r="AW217">
+        <v>4</v>
+      </c>
+      <c r="AX217">
+        <v>14</v>
+      </c>
+      <c r="AY217">
+        <v>10</v>
+      </c>
+      <c r="AZ217">
+        <v>18</v>
+      </c>
+      <c r="BA217">
+        <v>4</v>
+      </c>
+      <c r="BB217">
+        <v>6</v>
+      </c>
+      <c r="BC217">
+        <v>10</v>
+      </c>
+      <c r="BD217">
+        <v>2.55</v>
+      </c>
+      <c r="BE217">
+        <v>6.4</v>
+      </c>
+      <c r="BF217">
+        <v>1.65</v>
+      </c>
+      <c r="BG217">
+        <v>1.33</v>
+      </c>
+      <c r="BH217">
+        <v>2.9</v>
+      </c>
+      <c r="BI217">
+        <v>1.58</v>
+      </c>
+      <c r="BJ217">
+        <v>2.14</v>
+      </c>
+      <c r="BK217">
+        <v>1.85</v>
+      </c>
+      <c r="BL217">
+        <v>1.85</v>
+      </c>
+      <c r="BM217">
+        <v>2.48</v>
+      </c>
+      <c r="BN217">
+        <v>1.44</v>
+      </c>
+      <c r="BO217">
+        <v>3.3</v>
+      </c>
+      <c r="BP217">
         <v>1.26</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -46019,10 +46019,10 @@
         <v>14</v>
       </c>
       <c r="AY217">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ217">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BA217">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="335">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -718,6 +718,12 @@
     <t>['-1', '-1', '-1']</t>
   </si>
   <si>
+    <t>['36', '71']</t>
+  </si>
+  <si>
+    <t>['45+2', '45+7', '82', '84', '90+6']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1007,6 +1013,12 @@
   </si>
   <si>
     <t>['48', '59']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
+    <t>['5', '11']</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1911,7 +1923,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ3">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2036,7 +2048,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2320,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ5">
         <v>1.25</v>
@@ -2654,7 +2666,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3066,7 +3078,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3478,7 +3490,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3684,7 +3696,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3890,7 +3902,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4096,7 +4108,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4174,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ14">
         <v>1.75</v>
@@ -4302,7 +4314,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4508,7 +4520,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5207,7 +5219,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ19">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5744,7 +5756,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6237,7 +6249,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ24">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR24">
         <v>1.69</v>
@@ -6362,7 +6374,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6568,7 +6580,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6774,7 +6786,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6980,7 +6992,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7058,7 +7070,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ28">
         <v>1.42</v>
@@ -7392,7 +7404,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7473,7 +7485,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ30">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR30">
         <v>0.86</v>
@@ -7676,7 +7688,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ31">
         <v>0.42</v>
@@ -7804,7 +7816,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8010,7 +8022,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8422,7 +8434,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8709,7 +8721,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ36">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR36">
         <v>1.51</v>
@@ -9040,7 +9052,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9121,7 +9133,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ38">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR38">
         <v>1.85</v>
@@ -9246,7 +9258,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9530,7 +9542,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ40">
         <v>0.83</v>
@@ -9864,7 +9876,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10482,7 +10494,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10688,7 +10700,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11100,7 +11112,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11512,7 +11524,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12336,7 +12348,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12542,7 +12554,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13160,7 +13172,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13238,10 +13250,10 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ58">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR58">
         <v>1.71</v>
@@ -13366,7 +13378,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13447,7 +13459,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ59">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR59">
         <v>1.38</v>
@@ -13572,7 +13584,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13778,7 +13790,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13856,7 +13868,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ61">
         <v>0.33</v>
@@ -14396,7 +14408,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14808,7 +14820,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15916,7 +15928,7 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ71">
         <v>1.25</v>
@@ -16122,7 +16134,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ72">
         <v>1.17</v>
@@ -16250,7 +16262,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16331,7 +16343,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ73">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR73">
         <v>1.47</v>
@@ -16456,7 +16468,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16537,7 +16549,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ74">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -17692,7 +17704,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -19134,7 +19146,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19340,7 +19352,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19546,7 +19558,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19752,7 +19764,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19958,7 +19970,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20245,7 +20257,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -20370,7 +20382,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20448,7 +20460,7 @@
         <v>2.6</v>
       </c>
       <c r="AP93">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ93">
         <v>2.33</v>
@@ -20576,7 +20588,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20782,7 +20794,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20988,7 +21000,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21069,7 +21081,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ96">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21272,7 +21284,7 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ97">
         <v>1.5</v>
@@ -21606,7 +21618,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21812,7 +21824,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -22018,7 +22030,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22224,7 +22236,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22430,7 +22442,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22842,7 +22854,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23332,7 +23344,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ107">
         <v>0.6899999999999999</v>
@@ -23460,7 +23472,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23666,7 +23678,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23747,7 +23759,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ109">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -23950,7 +23962,7 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ110">
         <v>0.6899999999999999</v>
@@ -24078,7 +24090,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24696,7 +24708,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25108,7 +25120,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25314,7 +25326,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25726,7 +25738,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26216,7 +26228,7 @@
         <v>1.43</v>
       </c>
       <c r="AP121">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ121">
         <v>1.5</v>
@@ -26344,7 +26356,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26550,7 +26562,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26631,7 +26643,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ123">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR123">
         <v>1.23</v>
@@ -26962,7 +26974,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27374,7 +27386,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27580,7 +27592,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27658,7 +27670,7 @@
         <v>0.5</v>
       </c>
       <c r="AP128">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -27867,7 +27879,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ129">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR129">
         <v>1.39</v>
@@ -27992,7 +28004,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28404,7 +28416,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28816,7 +28828,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29022,7 +29034,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29228,7 +29240,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29434,7 +29446,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29640,7 +29652,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30052,7 +30064,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30133,7 +30145,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ140">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR140">
         <v>1.69</v>
@@ -30258,7 +30270,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30336,7 +30348,7 @@
         <v>0.14</v>
       </c>
       <c r="AP141">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ141">
         <v>0.42</v>
@@ -31781,7 +31793,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ148">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR148">
         <v>1.73</v>
@@ -31906,7 +31918,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32112,7 +32124,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32396,7 +32408,7 @@
         <v>2.14</v>
       </c>
       <c r="AP151">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ151">
         <v>1.75</v>
@@ -32524,7 +32536,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33014,7 +33026,7 @@
         <v>1.25</v>
       </c>
       <c r="AP154">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ154">
         <v>1.17</v>
@@ -33142,7 +33154,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33760,7 +33772,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34047,7 +34059,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ159">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR159">
         <v>1.47</v>
@@ -34172,7 +34184,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34378,7 +34390,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34790,7 +34802,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35202,7 +35214,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35489,7 +35501,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ166">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR166">
         <v>1.68</v>
@@ -35898,7 +35910,7 @@
         <v>0.67</v>
       </c>
       <c r="AP168">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ168">
         <v>0.6899999999999999</v>
@@ -36438,7 +36450,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36644,7 +36656,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37134,7 +37146,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ174">
         <v>1.42</v>
@@ -37340,7 +37352,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ175">
         <v>0.33</v>
@@ -37468,7 +37480,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -38086,7 +38098,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38167,7 +38179,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ179">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR179">
         <v>1.4</v>
@@ -38498,7 +38510,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38704,7 +38716,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39322,7 +39334,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39734,7 +39746,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40352,7 +40364,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40433,7 +40445,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ190">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR190">
         <v>1.75</v>
@@ -40558,7 +40570,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41176,7 +41188,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41460,7 +41472,7 @@
         <v>1.3</v>
       </c>
       <c r="AP195">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ195">
         <v>1.17</v>
@@ -41588,7 +41600,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41794,7 +41806,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42206,7 +42218,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42490,7 +42502,7 @@
         <v>0.82</v>
       </c>
       <c r="AP200">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ200">
         <v>0.83</v>
@@ -42699,7 +42711,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ201">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AR201">
         <v>1.93</v>
@@ -43030,7 +43042,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43108,7 +43120,7 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ203">
         <v>1.55</v>
@@ -43236,7 +43248,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43442,7 +43454,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -44141,7 +44153,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ208">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR208">
         <v>1.66</v>
@@ -44266,7 +44278,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44678,7 +44690,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44884,7 +44896,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -45502,7 +45514,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45708,7 +45720,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -46071,6 +46083,418 @@
       </c>
       <c r="BP217">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7450869</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45730.58333333334</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>81</v>
+      </c>
+      <c r="H218" t="s">
+        <v>80</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>2</v>
+      </c>
+      <c r="L218">
+        <v>2</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>3</v>
+      </c>
+      <c r="O218" t="s">
+        <v>234</v>
+      </c>
+      <c r="P218" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q218">
+        <v>2.55</v>
+      </c>
+      <c r="R218">
+        <v>2.15</v>
+      </c>
+      <c r="S218">
+        <v>3.75</v>
+      </c>
+      <c r="T218">
+        <v>1.33</v>
+      </c>
+      <c r="U218">
+        <v>3</v>
+      </c>
+      <c r="V218">
+        <v>2.45</v>
+      </c>
+      <c r="W218">
+        <v>1.47</v>
+      </c>
+      <c r="X218">
+        <v>6</v>
+      </c>
+      <c r="Y218">
+        <v>1.11</v>
+      </c>
+      <c r="Z218">
+        <v>1.7</v>
+      </c>
+      <c r="AA218">
+        <v>3.72</v>
+      </c>
+      <c r="AB218">
+        <v>4.7</v>
+      </c>
+      <c r="AC218">
+        <v>1.05</v>
+      </c>
+      <c r="AD218">
+        <v>9.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.25</v>
+      </c>
+      <c r="AF218">
+        <v>3.75</v>
+      </c>
+      <c r="AG218">
+        <v>1.7</v>
+      </c>
+      <c r="AH218">
+        <v>1.95</v>
+      </c>
+      <c r="AI218">
+        <v>1.62</v>
+      </c>
+      <c r="AJ218">
+        <v>2.15</v>
+      </c>
+      <c r="AK218">
+        <v>1.29</v>
+      </c>
+      <c r="AL218">
+        <v>1.29</v>
+      </c>
+      <c r="AM218">
+        <v>1.75</v>
+      </c>
+      <c r="AN218">
+        <v>1.33</v>
+      </c>
+      <c r="AO218">
+        <v>0.83</v>
+      </c>
+      <c r="AP218">
+        <v>1.46</v>
+      </c>
+      <c r="AQ218">
+        <v>0.77</v>
+      </c>
+      <c r="AR218">
+        <v>1.64</v>
+      </c>
+      <c r="AS218">
+        <v>1.36</v>
+      </c>
+      <c r="AT218">
+        <v>3</v>
+      </c>
+      <c r="AU218">
+        <v>8</v>
+      </c>
+      <c r="AV218">
+        <v>4</v>
+      </c>
+      <c r="AW218">
+        <v>6</v>
+      </c>
+      <c r="AX218">
+        <v>5</v>
+      </c>
+      <c r="AY218">
+        <v>17</v>
+      </c>
+      <c r="AZ218">
+        <v>11</v>
+      </c>
+      <c r="BA218">
+        <v>5</v>
+      </c>
+      <c r="BB218">
+        <v>2</v>
+      </c>
+      <c r="BC218">
+        <v>7</v>
+      </c>
+      <c r="BD218">
+        <v>1.76</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>2.3</v>
+      </c>
+      <c r="BG218">
+        <v>1.35</v>
+      </c>
+      <c r="BH218">
+        <v>2.8</v>
+      </c>
+      <c r="BI218">
+        <v>1.6</v>
+      </c>
+      <c r="BJ218">
+        <v>2.12</v>
+      </c>
+      <c r="BK218">
+        <v>1.97</v>
+      </c>
+      <c r="BL218">
+        <v>1.68</v>
+      </c>
+      <c r="BM218">
+        <v>2.55</v>
+      </c>
+      <c r="BN218">
+        <v>1.42</v>
+      </c>
+      <c r="BO218">
+        <v>3.3</v>
+      </c>
+      <c r="BP218">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7450867</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45730.6875</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>73</v>
+      </c>
+      <c r="H219" t="s">
+        <v>75</v>
+      </c>
+      <c r="I219">
+        <v>2</v>
+      </c>
+      <c r="J219">
+        <v>2</v>
+      </c>
+      <c r="K219">
+        <v>4</v>
+      </c>
+      <c r="L219">
+        <v>5</v>
+      </c>
+      <c r="M219">
+        <v>2</v>
+      </c>
+      <c r="N219">
+        <v>7</v>
+      </c>
+      <c r="O219" t="s">
+        <v>235</v>
+      </c>
+      <c r="P219" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q219">
+        <v>2.35</v>
+      </c>
+      <c r="R219">
+        <v>2.1</v>
+      </c>
+      <c r="S219">
+        <v>4.5</v>
+      </c>
+      <c r="T219">
+        <v>1.37</v>
+      </c>
+      <c r="U219">
+        <v>2.8</v>
+      </c>
+      <c r="V219">
+        <v>2.6</v>
+      </c>
+      <c r="W219">
+        <v>1.43</v>
+      </c>
+      <c r="X219">
+        <v>6.5</v>
+      </c>
+      <c r="Y219">
+        <v>1.1</v>
+      </c>
+      <c r="Z219">
+        <v>1.74</v>
+      </c>
+      <c r="AA219">
+        <v>3.45</v>
+      </c>
+      <c r="AB219">
+        <v>4.9</v>
+      </c>
+      <c r="AC219">
+        <v>1.06</v>
+      </c>
+      <c r="AD219">
+        <v>8.5</v>
+      </c>
+      <c r="AE219">
+        <v>1.3</v>
+      </c>
+      <c r="AF219">
+        <v>3.45</v>
+      </c>
+      <c r="AG219">
+        <v>1.87</v>
+      </c>
+      <c r="AH219">
+        <v>1.87</v>
+      </c>
+      <c r="AI219">
+        <v>1.78</v>
+      </c>
+      <c r="AJ219">
+        <v>1.9</v>
+      </c>
+      <c r="AK219">
+        <v>1.2</v>
+      </c>
+      <c r="AL219">
+        <v>1.29</v>
+      </c>
+      <c r="AM219">
+        <v>1.93</v>
+      </c>
+      <c r="AN219">
+        <v>2.33</v>
+      </c>
+      <c r="AO219">
+        <v>2.09</v>
+      </c>
+      <c r="AP219">
+        <v>2.38</v>
+      </c>
+      <c r="AQ219">
+        <v>1.92</v>
+      </c>
+      <c r="AR219">
+        <v>1.79</v>
+      </c>
+      <c r="AS219">
+        <v>1.55</v>
+      </c>
+      <c r="AT219">
+        <v>3.34</v>
+      </c>
+      <c r="AU219">
+        <v>9</v>
+      </c>
+      <c r="AV219">
+        <v>6</v>
+      </c>
+      <c r="AW219">
+        <v>8</v>
+      </c>
+      <c r="AX219">
+        <v>4</v>
+      </c>
+      <c r="AY219">
+        <v>17</v>
+      </c>
+      <c r="AZ219">
+        <v>10</v>
+      </c>
+      <c r="BA219">
+        <v>5</v>
+      </c>
+      <c r="BB219">
+        <v>0</v>
+      </c>
+      <c r="BC219">
+        <v>5</v>
+      </c>
+      <c r="BD219">
+        <v>1.58</v>
+      </c>
+      <c r="BE219">
+        <v>6.5</v>
+      </c>
+      <c r="BF219">
+        <v>2.65</v>
+      </c>
+      <c r="BG219">
+        <v>1.38</v>
+      </c>
+      <c r="BH219">
+        <v>2.65</v>
+      </c>
+      <c r="BI219">
+        <v>1.65</v>
+      </c>
+      <c r="BJ219">
+        <v>2.02</v>
+      </c>
+      <c r="BK219">
+        <v>2.07</v>
+      </c>
+      <c r="BL219">
+        <v>1.63</v>
+      </c>
+      <c r="BM219">
+        <v>2.65</v>
+      </c>
+      <c r="BN219">
+        <v>1.38</v>
+      </c>
+      <c r="BO219">
+        <v>3.65</v>
+      </c>
+      <c r="BP219">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -724,6 +724,15 @@
     <t>['45+2', '45+7', '82', '84', '90+6']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['25', '50', '53', '64']</t>
+  </si>
+  <si>
+    <t>['60']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -943,9 +952,6 @@
     <t>['12', '63']</t>
   </si>
   <si>
-    <t>['13']</t>
-  </si>
-  <si>
     <t>['32', '74']</t>
   </si>
   <si>
@@ -1019,6 +1025,9 @@
   </si>
   <si>
     <t>['5', '11']</t>
+  </si>
+  <si>
+    <t>['9', '72', '77', '90']</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2048,7 +2057,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2666,7 +2675,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3078,7 +3087,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3362,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ10">
         <v>0.83</v>
@@ -3490,7 +3499,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3696,7 +3705,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3777,7 +3786,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ12">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3902,7 +3911,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3980,10 +3989,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR13">
         <v>1.41</v>
@@ -4108,7 +4117,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4314,7 +4323,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4392,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ15">
         <v>1.55</v>
@@ -4520,7 +4529,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4807,7 +4816,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ17">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5628,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -5756,7 +5765,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6374,7 +6383,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6580,7 +6589,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6786,7 +6795,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6992,7 +7001,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7404,7 +7413,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7816,7 +7825,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8022,7 +8031,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8306,10 +8315,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ34">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR34">
         <v>1.4</v>
@@ -8434,7 +8443,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8515,7 +8524,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ35">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR35">
         <v>1.34</v>
@@ -8927,7 +8936,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ37">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR37">
         <v>1.91</v>
@@ -9052,7 +9061,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9258,7 +9267,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9876,7 +9885,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10160,7 +10169,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ43">
         <v>2.33</v>
@@ -10366,7 +10375,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44">
         <v>1.5</v>
@@ -10494,7 +10503,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10572,7 +10581,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10700,7 +10709,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11112,7 +11121,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11524,7 +11533,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12348,7 +12357,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12554,7 +12563,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12632,7 +12641,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ55">
         <v>1.55</v>
@@ -13047,7 +13056,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR57">
         <v>1.6</v>
@@ -13172,7 +13181,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13378,7 +13387,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13456,7 +13465,7 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ59">
         <v>0.77</v>
@@ -13584,7 +13593,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13665,7 +13674,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ60">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -13790,7 +13799,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13871,7 +13880,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ61">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR61">
         <v>1.79</v>
@@ -14408,7 +14417,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14820,7 +14829,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -16262,7 +16271,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16468,7 +16477,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16752,7 +16761,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ75">
         <v>1.5</v>
@@ -16958,10 +16967,10 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ76">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR76">
         <v>1.53</v>
@@ -17164,10 +17173,10 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ77">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR77">
         <v>1.21</v>
@@ -17579,7 +17588,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ79">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR79">
         <v>1.89</v>
@@ -17704,7 +17713,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18609,7 +18618,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ84">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR84">
         <v>1.58</v>
@@ -19146,7 +19155,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19352,7 +19361,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19558,7 +19567,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19764,7 +19773,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19845,7 +19854,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ90">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.39</v>
@@ -19970,7 +19979,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20048,7 +20057,7 @@
         <v>0.6</v>
       </c>
       <c r="AP91">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ91">
         <v>1.25</v>
@@ -20254,7 +20263,7 @@
         <v>0.8</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ92">
         <v>0.77</v>
@@ -20382,7 +20391,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20588,7 +20597,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20666,7 +20675,7 @@
         <v>0.2</v>
       </c>
       <c r="AP94">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ94">
         <v>0.6899999999999999</v>
@@ -20794,7 +20803,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20875,7 +20884,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ95">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -21000,7 +21009,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21618,7 +21627,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21824,7 +21833,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -22030,7 +22039,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22236,7 +22245,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22442,7 +22451,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22729,7 +22738,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ104">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -22854,7 +22863,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22932,7 +22941,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ105">
         <v>0.42</v>
@@ -23472,7 +23481,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23678,7 +23687,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24090,7 +24099,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24171,7 +24180,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ111">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR111">
         <v>1.46</v>
@@ -24708,7 +24717,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24786,7 +24795,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ114">
         <v>0.6899999999999999</v>
@@ -25120,7 +25129,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25198,7 +25207,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ116">
         <v>1.42</v>
@@ -25326,7 +25335,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25407,7 +25416,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ117">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR117">
         <v>1.54</v>
@@ -25738,7 +25747,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26356,7 +26365,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26434,7 +26443,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ122">
         <v>1.75</v>
@@ -26562,7 +26571,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26974,7 +26983,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27261,7 +27270,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ126">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR126">
         <v>1.67</v>
@@ -27386,7 +27395,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27467,7 +27476,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ127">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -27592,7 +27601,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -28004,7 +28013,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28085,7 +28094,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ130">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR130">
         <v>1.6</v>
@@ -28288,7 +28297,7 @@
         <v>0.71</v>
       </c>
       <c r="AP131">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ131">
         <v>0.6899999999999999</v>
@@ -28416,7 +28425,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28700,7 +28709,7 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ133">
         <v>0.6899999999999999</v>
@@ -28828,7 +28837,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29034,7 +29043,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29240,7 +29249,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29321,7 +29330,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ136">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29446,7 +29455,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29527,7 +29536,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ137">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR137">
         <v>1.82</v>
@@ -29652,7 +29661,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29939,7 +29948,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ139">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR139">
         <v>1.94</v>
@@ -30064,7 +30073,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30270,7 +30279,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30760,7 +30769,7 @@
         <v>1.38</v>
       </c>
       <c r="AP143">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ143">
         <v>1.5</v>
@@ -31918,7 +31927,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -31996,7 +32005,7 @@
         <v>2.25</v>
       </c>
       <c r="AP149">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ149">
         <v>2.33</v>
@@ -32124,7 +32133,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32536,7 +32545,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32614,7 +32623,7 @@
         <v>1.29</v>
       </c>
       <c r="AP152">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ152">
         <v>1.17</v>
@@ -33029,7 +33038,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ154">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR154">
         <v>1.51</v>
@@ -33154,7 +33163,7 @@
         <v>198</v>
       </c>
       <c r="P155" t="s">
-        <v>309</v>
+        <v>236</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33232,7 +33241,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ155">
         <v>1.55</v>
@@ -33441,7 +33450,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ156">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR156">
         <v>1.39</v>
@@ -33644,7 +33653,7 @@
         <v>0.5</v>
       </c>
       <c r="AP157">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ157">
         <v>0.42</v>
@@ -33772,7 +33781,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -33853,7 +33862,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ158">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR158">
         <v>1.55</v>
@@ -34184,7 +34193,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34390,7 +34399,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34802,7 +34811,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35214,7 +35223,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36116,7 +36125,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP169">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ169">
         <v>0.6899999999999999</v>
@@ -36450,7 +36459,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36656,7 +36665,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36940,7 +36949,7 @@
         <v>1.89</v>
       </c>
       <c r="AP173">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ173">
         <v>1.75</v>
@@ -37355,7 +37364,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ175">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR175">
         <v>1.56</v>
@@ -37480,7 +37489,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37561,7 +37570,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ176">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR176">
         <v>1.63</v>
@@ -37973,7 +37982,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ178">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR178">
         <v>1.4</v>
@@ -38098,7 +38107,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38176,7 +38185,7 @@
         <v>2.11</v>
       </c>
       <c r="AP179">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ179">
         <v>1.92</v>
@@ -38510,7 +38519,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38716,7 +38725,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39334,7 +39343,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39412,7 +39421,7 @@
         <v>0.9</v>
       </c>
       <c r="AP185">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39746,7 +39755,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -39824,7 +39833,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP187">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ187">
         <v>1</v>
@@ -40239,7 +40248,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ189">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR189">
         <v>1.82</v>
@@ -40364,7 +40373,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40570,7 +40579,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41063,7 +41072,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ193">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR193">
         <v>1.41</v>
@@ -41188,7 +41197,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41266,7 +41275,7 @@
         <v>0.8</v>
       </c>
       <c r="AP194">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ194">
         <v>1</v>
@@ -41600,7 +41609,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41806,7 +41815,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42218,7 +42227,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42299,7 +42308,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ199">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR199">
         <v>1.65</v>
@@ -42708,7 +42717,7 @@
         <v>2</v>
       </c>
       <c r="AP201">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ201">
         <v>1.92</v>
@@ -42914,7 +42923,7 @@
         <v>1.09</v>
       </c>
       <c r="AP202">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ202">
         <v>1.25</v>
@@ -43042,7 +43051,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43248,7 +43257,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43454,7 +43463,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -43535,7 +43544,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ205">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR205">
         <v>1.46</v>
@@ -43741,7 +43750,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ206">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR206">
         <v>1.66</v>
@@ -43947,7 +43956,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ207">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR207">
         <v>1.81</v>
@@ -44278,7 +44287,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44690,7 +44699,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44896,7 +44905,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -45514,7 +45523,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45720,7 +45729,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -45798,7 +45807,7 @@
         <v>1.64</v>
       </c>
       <c r="AP216">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ216">
         <v>1.75</v>
@@ -46132,7 +46141,7 @@
         <v>234</v>
       </c>
       <c r="P218" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q218">
         <v>2.55</v>
@@ -46338,7 +46347,7 @@
         <v>235</v>
       </c>
       <c r="P219" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q219">
         <v>2.35</v>
@@ -46443,7 +46452,7 @@
         <v>4</v>
       </c>
       <c r="AY219">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ219">
         <v>10</v>
@@ -46495,6 +46504,624 @@
       </c>
       <c r="BP219">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7450871</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45731.44791666666</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>78</v>
+      </c>
+      <c r="H220" t="s">
+        <v>71</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>4</v>
+      </c>
+      <c r="N220">
+        <v>5</v>
+      </c>
+      <c r="O220" t="s">
+        <v>236</v>
+      </c>
+      <c r="P220" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q220">
+        <v>2.88</v>
+      </c>
+      <c r="R220">
+        <v>2.1</v>
+      </c>
+      <c r="S220">
+        <v>3.75</v>
+      </c>
+      <c r="T220">
+        <v>1.4</v>
+      </c>
+      <c r="U220">
+        <v>2.75</v>
+      </c>
+      <c r="V220">
+        <v>3</v>
+      </c>
+      <c r="W220">
+        <v>1.36</v>
+      </c>
+      <c r="X220">
+        <v>9</v>
+      </c>
+      <c r="Y220">
+        <v>1.07</v>
+      </c>
+      <c r="Z220">
+        <v>2.18</v>
+      </c>
+      <c r="AA220">
+        <v>3.23</v>
+      </c>
+      <c r="AB220">
+        <v>3.31</v>
+      </c>
+      <c r="AC220">
+        <v>1.04</v>
+      </c>
+      <c r="AD220">
+        <v>9</v>
+      </c>
+      <c r="AE220">
+        <v>1.3</v>
+      </c>
+      <c r="AF220">
+        <v>3.3</v>
+      </c>
+      <c r="AG220">
+        <v>1.95</v>
+      </c>
+      <c r="AH220">
+        <v>1.79</v>
+      </c>
+      <c r="AI220">
+        <v>1.8</v>
+      </c>
+      <c r="AJ220">
+        <v>1.95</v>
+      </c>
+      <c r="AK220">
+        <v>1.36</v>
+      </c>
+      <c r="AL220">
+        <v>1.31</v>
+      </c>
+      <c r="AM220">
+        <v>1.6</v>
+      </c>
+      <c r="AN220">
+        <v>1.5</v>
+      </c>
+      <c r="AO220">
+        <v>0.33</v>
+      </c>
+      <c r="AP220">
+        <v>1.38</v>
+      </c>
+      <c r="AQ220">
+        <v>0.54</v>
+      </c>
+      <c r="AR220">
+        <v>1.63</v>
+      </c>
+      <c r="AS220">
+        <v>1.32</v>
+      </c>
+      <c r="AT220">
+        <v>2.95</v>
+      </c>
+      <c r="AU220">
+        <v>5</v>
+      </c>
+      <c r="AV220">
+        <v>12</v>
+      </c>
+      <c r="AW220">
+        <v>4</v>
+      </c>
+      <c r="AX220">
+        <v>6</v>
+      </c>
+      <c r="AY220">
+        <v>11</v>
+      </c>
+      <c r="AZ220">
+        <v>23</v>
+      </c>
+      <c r="BA220">
+        <v>6</v>
+      </c>
+      <c r="BB220">
+        <v>4</v>
+      </c>
+      <c r="BC220">
+        <v>10</v>
+      </c>
+      <c r="BD220">
+        <v>1.67</v>
+      </c>
+      <c r="BE220">
+        <v>8.5</v>
+      </c>
+      <c r="BF220">
+        <v>2.45</v>
+      </c>
+      <c r="BG220">
+        <v>1.21</v>
+      </c>
+      <c r="BH220">
+        <v>3.58</v>
+      </c>
+      <c r="BI220">
+        <v>1.47</v>
+      </c>
+      <c r="BJ220">
+        <v>2.62</v>
+      </c>
+      <c r="BK220">
+        <v>1.79</v>
+      </c>
+      <c r="BL220">
+        <v>2.01</v>
+      </c>
+      <c r="BM220">
+        <v>2.25</v>
+      </c>
+      <c r="BN220">
+        <v>1.62</v>
+      </c>
+      <c r="BO220">
+        <v>2.92</v>
+      </c>
+      <c r="BP220">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7450864</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45731.5625</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>87</v>
+      </c>
+      <c r="H221" t="s">
+        <v>77</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>4</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>4</v>
+      </c>
+      <c r="O221" t="s">
+        <v>237</v>
+      </c>
+      <c r="P221" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q221">
+        <v>2.6</v>
+      </c>
+      <c r="R221">
+        <v>2.2</v>
+      </c>
+      <c r="S221">
+        <v>4.33</v>
+      </c>
+      <c r="T221">
+        <v>1.36</v>
+      </c>
+      <c r="U221">
+        <v>3</v>
+      </c>
+      <c r="V221">
+        <v>2.75</v>
+      </c>
+      <c r="W221">
+        <v>1.4</v>
+      </c>
+      <c r="X221">
+        <v>7</v>
+      </c>
+      <c r="Y221">
+        <v>1.1</v>
+      </c>
+      <c r="Z221">
+        <v>2.17</v>
+      </c>
+      <c r="AA221">
+        <v>3.36</v>
+      </c>
+      <c r="AB221">
+        <v>3.21</v>
+      </c>
+      <c r="AC221">
+        <v>1.02</v>
+      </c>
+      <c r="AD221">
+        <v>11</v>
+      </c>
+      <c r="AE221">
+        <v>1.22</v>
+      </c>
+      <c r="AF221">
+        <v>4</v>
+      </c>
+      <c r="AG221">
+        <v>1.85</v>
+      </c>
+      <c r="AH221">
+        <v>1.89</v>
+      </c>
+      <c r="AI221">
+        <v>1.75</v>
+      </c>
+      <c r="AJ221">
+        <v>2</v>
+      </c>
+      <c r="AK221">
+        <v>1.33</v>
+      </c>
+      <c r="AL221">
+        <v>1.28</v>
+      </c>
+      <c r="AM221">
+        <v>1.68</v>
+      </c>
+      <c r="AN221">
+        <v>1.67</v>
+      </c>
+      <c r="AO221">
+        <v>1.42</v>
+      </c>
+      <c r="AP221">
+        <v>1.77</v>
+      </c>
+      <c r="AQ221">
+        <v>1.31</v>
+      </c>
+      <c r="AR221">
+        <v>1.97</v>
+      </c>
+      <c r="AS221">
+        <v>1.37</v>
+      </c>
+      <c r="AT221">
+        <v>3.34</v>
+      </c>
+      <c r="AU221">
+        <v>12</v>
+      </c>
+      <c r="AV221">
+        <v>2</v>
+      </c>
+      <c r="AW221">
+        <v>6</v>
+      </c>
+      <c r="AX221">
+        <v>5</v>
+      </c>
+      <c r="AY221">
+        <v>20</v>
+      </c>
+      <c r="AZ221">
+        <v>10</v>
+      </c>
+      <c r="BA221">
+        <v>3</v>
+      </c>
+      <c r="BB221">
+        <v>11</v>
+      </c>
+      <c r="BC221">
+        <v>14</v>
+      </c>
+      <c r="BD221">
+        <v>1.55</v>
+      </c>
+      <c r="BE221">
+        <v>9</v>
+      </c>
+      <c r="BF221">
+        <v>2.7</v>
+      </c>
+      <c r="BG221">
+        <v>1.19</v>
+      </c>
+      <c r="BH221">
+        <v>3.8</v>
+      </c>
+      <c r="BI221">
+        <v>1.39</v>
+      </c>
+      <c r="BJ221">
+        <v>2.67</v>
+      </c>
+      <c r="BK221">
+        <v>1.72</v>
+      </c>
+      <c r="BL221">
+        <v>2.09</v>
+      </c>
+      <c r="BM221">
+        <v>2.17</v>
+      </c>
+      <c r="BN221">
+        <v>1.68</v>
+      </c>
+      <c r="BO221">
+        <v>2.81</v>
+      </c>
+      <c r="BP221">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7450872</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45731.67708333334</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>82</v>
+      </c>
+      <c r="H222" t="s">
+        <v>72</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>1</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>238</v>
+      </c>
+      <c r="P222" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q222">
+        <v>3.1</v>
+      </c>
+      <c r="R222">
+        <v>2.2</v>
+      </c>
+      <c r="S222">
+        <v>3.4</v>
+      </c>
+      <c r="T222">
+        <v>1.4</v>
+      </c>
+      <c r="U222">
+        <v>2.75</v>
+      </c>
+      <c r="V222">
+        <v>2.75</v>
+      </c>
+      <c r="W222">
+        <v>1.4</v>
+      </c>
+      <c r="X222">
+        <v>8</v>
+      </c>
+      <c r="Y222">
+        <v>1.08</v>
+      </c>
+      <c r="Z222">
+        <v>2.5</v>
+      </c>
+      <c r="AA222">
+        <v>3.06</v>
+      </c>
+      <c r="AB222">
+        <v>2.91</v>
+      </c>
+      <c r="AC222">
+        <v>1.03</v>
+      </c>
+      <c r="AD222">
+        <v>10</v>
+      </c>
+      <c r="AE222">
+        <v>1.25</v>
+      </c>
+      <c r="AF222">
+        <v>3.75</v>
+      </c>
+      <c r="AG222">
+        <v>1.8</v>
+      </c>
+      <c r="AH222">
+        <v>1.94</v>
+      </c>
+      <c r="AI222">
+        <v>1.67</v>
+      </c>
+      <c r="AJ222">
+        <v>2.1</v>
+      </c>
+      <c r="AK222">
+        <v>1.44</v>
+      </c>
+      <c r="AL222">
+        <v>1.32</v>
+      </c>
+      <c r="AM222">
+        <v>1.49</v>
+      </c>
+      <c r="AN222">
+        <v>1.42</v>
+      </c>
+      <c r="AO222">
+        <v>1.17</v>
+      </c>
+      <c r="AP222">
+        <v>1.54</v>
+      </c>
+      <c r="AQ222">
+        <v>1.08</v>
+      </c>
+      <c r="AR222">
+        <v>1.48</v>
+      </c>
+      <c r="AS222">
+        <v>1.58</v>
+      </c>
+      <c r="AT222">
+        <v>3.06</v>
+      </c>
+      <c r="AU222">
+        <v>5</v>
+      </c>
+      <c r="AV222">
+        <v>4</v>
+      </c>
+      <c r="AW222">
+        <v>6</v>
+      </c>
+      <c r="AX222">
+        <v>15</v>
+      </c>
+      <c r="AY222">
+        <v>11</v>
+      </c>
+      <c r="AZ222">
+        <v>19</v>
+      </c>
+      <c r="BA222">
+        <v>3</v>
+      </c>
+      <c r="BB222">
+        <v>6</v>
+      </c>
+      <c r="BC222">
+        <v>9</v>
+      </c>
+      <c r="BD222">
+        <v>1.73</v>
+      </c>
+      <c r="BE222">
+        <v>8.5</v>
+      </c>
+      <c r="BF222">
+        <v>2.38</v>
+      </c>
+      <c r="BG222">
+        <v>1.2</v>
+      </c>
+      <c r="BH222">
+        <v>3.9</v>
+      </c>
+      <c r="BI222">
+        <v>1.35</v>
+      </c>
+      <c r="BJ222">
+        <v>2.74</v>
+      </c>
+      <c r="BK222">
+        <v>1.67</v>
+      </c>
+      <c r="BL222">
+        <v>2.16</v>
+      </c>
+      <c r="BM222">
+        <v>2.07</v>
+      </c>
+      <c r="BN222">
+        <v>1.72</v>
+      </c>
+      <c r="BO222">
+        <v>2.51</v>
+      </c>
+      <c r="BP222">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -47070,10 +47070,10 @@
         <v>15</v>
       </c>
       <c r="AY222">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ222">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA222">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="343">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,15 @@
     <t>['60']</t>
   </si>
   <si>
+    <t>['16', '61']</t>
+  </si>
+  <si>
+    <t>['10', '32', '47']</t>
+  </si>
+  <si>
+    <t>['31', '59']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1028,6 +1037,12 @@
   </si>
   <si>
     <t>['9', '72', '77', '90']</t>
+  </si>
+  <si>
+    <t>['50', '85']</t>
+  </si>
+  <si>
+    <t>['9']</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1723,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ2">
         <v>0.6899999999999999</v>
@@ -2057,7 +2072,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2344,7 +2359,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ5">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2675,7 +2690,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2756,7 +2771,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3087,7 +3102,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3499,7 +3514,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3577,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11">
         <v>1.42</v>
@@ -3705,7 +3720,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3911,7 +3926,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4117,7 +4132,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4323,7 +4338,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4404,7 +4419,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ15">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4529,7 +4544,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4607,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -5022,7 +5037,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ18">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5225,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ19">
         <v>1.92</v>
@@ -5431,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ20">
         <v>0.6899999999999999</v>
@@ -5765,7 +5780,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6049,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ23">
         <v>0.42</v>
@@ -6383,7 +6398,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6464,7 +6479,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ25">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR25">
         <v>1</v>
@@ -6589,7 +6604,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6670,7 +6685,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ26">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6795,7 +6810,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -7001,7 +7016,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7285,10 +7300,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ29">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR29">
         <v>2.17</v>
@@ -7413,7 +7428,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7825,7 +7840,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8031,7 +8046,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8109,10 +8124,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ33">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR33">
         <v>1.25</v>
@@ -8443,7 +8458,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8727,7 +8742,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ36">
         <v>0.77</v>
@@ -9061,7 +9076,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9139,7 +9154,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ38">
         <v>1.92</v>
@@ -9267,7 +9282,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9345,10 +9360,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ39">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR39">
         <v>1.41</v>
@@ -9760,7 +9775,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ41">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR41">
         <v>2.02</v>
@@ -9885,7 +9900,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10378,7 +10393,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -10503,7 +10518,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10709,7 +10724,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11121,7 +11136,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11533,7 +11548,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12026,7 +12041,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ52">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12357,7 +12372,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12435,10 +12450,10 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ54">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR54">
         <v>1.89</v>
@@ -12563,7 +12578,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12644,7 +12659,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ55">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR55">
         <v>1.29</v>
@@ -12847,10 +12862,10 @@
         <v>0.67</v>
       </c>
       <c r="AP56">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ56">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -13053,7 +13068,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ57">
         <v>1.08</v>
@@ -13181,7 +13196,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13387,7 +13402,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13593,7 +13608,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13799,7 +13814,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14083,7 +14098,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ62">
         <v>0.83</v>
@@ -14417,7 +14432,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14829,7 +14844,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15940,7 +15955,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ71">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16146,7 +16161,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ72">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16271,7 +16286,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16349,7 +16364,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ73">
         <v>1.92</v>
@@ -16477,7 +16492,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16555,7 +16570,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ74">
         <v>0.77</v>
@@ -16764,7 +16779,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ75">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -17379,7 +17394,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ78">
         <v>0.6899999999999999</v>
@@ -17713,7 +17728,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18409,7 +18424,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ83">
         <v>0.6899999999999999</v>
@@ -19027,7 +19042,7 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -19155,7 +19170,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19236,7 +19251,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ87">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -19361,7 +19376,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19567,7 +19582,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19773,7 +19788,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19851,7 +19866,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ90">
         <v>1.08</v>
@@ -19979,7 +19994,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20060,7 +20075,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ91">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20391,7 +20406,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20597,7 +20612,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20803,7 +20818,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21009,7 +21024,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21296,7 +21311,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ97">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21499,10 +21514,10 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ98">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR98">
         <v>1.72</v>
@@ -21627,7 +21642,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21708,7 +21723,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ99">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR99">
         <v>1.36</v>
@@ -21833,7 +21848,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21914,7 +21929,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ100">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR100">
         <v>1.26</v>
@@ -22039,7 +22054,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22245,7 +22260,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22323,7 +22338,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ102">
         <v>1.75</v>
@@ -22451,7 +22466,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22532,7 +22547,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ103">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR103">
         <v>1.6</v>
@@ -22863,7 +22878,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23147,7 +23162,7 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23481,7 +23496,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23687,7 +23702,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24099,7 +24114,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24717,7 +24732,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25001,10 +25016,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ115">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25129,7 +25144,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25335,7 +25350,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25619,7 +25634,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ118">
         <v>0.42</v>
@@ -25747,7 +25762,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26031,10 +26046,10 @@
         <v>2.17</v>
       </c>
       <c r="AP120">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR120">
         <v>1.38</v>
@@ -26240,7 +26255,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ121">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR121">
         <v>1.57</v>
@@ -26365,7 +26380,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26571,7 +26586,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26983,7 +26998,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27064,7 +27079,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ125">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR125">
         <v>1.75</v>
@@ -27267,7 +27282,7 @@
         <v>0.33</v>
       </c>
       <c r="AP126">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ126">
         <v>0.54</v>
@@ -27395,7 +27410,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27601,7 +27616,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -28013,7 +28028,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28425,7 +28440,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28837,7 +28852,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28915,7 +28930,7 @@
         <v>2.43</v>
       </c>
       <c r="AP134">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ134">
         <v>2.33</v>
@@ -29043,7 +29058,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29124,7 +29139,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ135">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR135">
         <v>1.91</v>
@@ -29249,7 +29264,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29327,7 +29342,7 @@
         <v>1.43</v>
       </c>
       <c r="AP136">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ136">
         <v>1.31</v>
@@ -29455,7 +29470,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29533,7 +29548,7 @@
         <v>0.29</v>
       </c>
       <c r="AP137">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ137">
         <v>0.54</v>
@@ -29661,7 +29676,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30073,7 +30088,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30279,7 +30294,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30563,10 +30578,10 @@
         <v>1.13</v>
       </c>
       <c r="AP142">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ142">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR142">
         <v>1.61</v>
@@ -30772,7 +30787,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ143">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR143">
         <v>1.98</v>
@@ -30975,7 +30990,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ144">
         <v>0.83</v>
@@ -31390,7 +31405,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ146">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR146">
         <v>1.5</v>
@@ -31927,7 +31942,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32133,7 +32148,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32545,7 +32560,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32626,7 +32641,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ152">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR152">
         <v>1.7</v>
@@ -33244,7 +33259,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ155">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR155">
         <v>1.98</v>
@@ -33781,7 +33796,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -33859,7 +33874,7 @@
         <v>1.63</v>
       </c>
       <c r="AP158">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ158">
         <v>1.31</v>
@@ -34193,7 +34208,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34271,7 +34286,7 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ160">
         <v>1.75</v>
@@ -34399,7 +34414,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34477,10 +34492,10 @@
         <v>1.25</v>
       </c>
       <c r="AP161">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ161">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34811,7 +34826,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35223,7 +35238,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -36331,7 +36346,7 @@
         <v>1</v>
       </c>
       <c r="AP170">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36459,7 +36474,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36540,7 +36555,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ171">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR171">
         <v>1.72</v>
@@ -36665,7 +36680,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36746,7 +36761,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ172">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR172">
         <v>1.47</v>
@@ -37489,7 +37504,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37567,7 +37582,7 @@
         <v>1.22</v>
       </c>
       <c r="AP176">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ176">
         <v>1.08</v>
@@ -37776,7 +37791,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ177">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR177">
         <v>1.53</v>
@@ -38107,7 +38122,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38394,7 +38409,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ180">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR180">
         <v>1.4</v>
@@ -38519,7 +38534,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38597,7 +38612,7 @@
         <v>0.6</v>
       </c>
       <c r="AP181">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ181">
         <v>0.6899999999999999</v>
@@ -38725,7 +38740,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -38806,7 +38821,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ182">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR182">
         <v>1.68</v>
@@ -39343,7 +39358,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39755,7 +39770,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40042,7 +40057,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ188">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR188">
         <v>1.73</v>
@@ -40245,7 +40260,7 @@
         <v>1.4</v>
       </c>
       <c r="AP189">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ189">
         <v>1.31</v>
@@ -40373,7 +40388,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40451,7 +40466,7 @@
         <v>0.7</v>
       </c>
       <c r="AP190">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ190">
         <v>0.77</v>
@@ -40579,7 +40594,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40863,7 +40878,7 @@
         <v>1.4</v>
       </c>
       <c r="AP192">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ192">
         <v>1.42</v>
@@ -41197,7 +41212,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41484,7 +41499,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ195">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR195">
         <v>1.57</v>
@@ -41609,7 +41624,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41815,7 +41830,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42227,7 +42242,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42926,7 +42941,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ202">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR202">
         <v>1.62</v>
@@ -43051,7 +43066,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43132,7 +43147,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ203">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR203">
         <v>1.8</v>
@@ -43257,7 +43272,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43335,10 +43350,10 @@
         <v>1.36</v>
       </c>
       <c r="AP204">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ204">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR204">
         <v>1.84</v>
@@ -43463,7 +43478,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -43541,7 +43556,7 @@
         <v>1.27</v>
       </c>
       <c r="AP205">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ205">
         <v>1.31</v>
@@ -43953,7 +43968,7 @@
         <v>1.27</v>
       </c>
       <c r="AP207">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ207">
         <v>1.08</v>
@@ -44159,7 +44174,7 @@
         <v>0.91</v>
       </c>
       <c r="AP208">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ208">
         <v>0.77</v>
@@ -44287,7 +44302,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44699,7 +44714,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44905,7 +44920,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -45523,7 +45538,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45729,7 +45744,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -46016,7 +46031,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ217">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR217">
         <v>1.64</v>
@@ -46141,7 +46156,7 @@
         <v>234</v>
       </c>
       <c r="P218" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q218">
         <v>2.55</v>
@@ -46347,7 +46362,7 @@
         <v>235</v>
       </c>
       <c r="P219" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q219">
         <v>2.35</v>
@@ -46553,7 +46568,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q220">
         <v>2.88</v>
@@ -47122,6 +47137,830 @@
       </c>
       <c r="BP222">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7450868</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45732.34375</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>79</v>
+      </c>
+      <c r="H223" t="s">
+        <v>84</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>2</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>3</v>
+      </c>
+      <c r="O223" t="s">
+        <v>239</v>
+      </c>
+      <c r="P223" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q223">
+        <v>4.5</v>
+      </c>
+      <c r="R223">
+        <v>1.95</v>
+      </c>
+      <c r="S223">
+        <v>2.88</v>
+      </c>
+      <c r="T223">
+        <v>1.53</v>
+      </c>
+      <c r="U223">
+        <v>2.38</v>
+      </c>
+      <c r="V223">
+        <v>3.75</v>
+      </c>
+      <c r="W223">
+        <v>1.25</v>
+      </c>
+      <c r="X223">
+        <v>11</v>
+      </c>
+      <c r="Y223">
+        <v>1.05</v>
+      </c>
+      <c r="Z223">
+        <v>3.41</v>
+      </c>
+      <c r="AA223">
+        <v>3.15</v>
+      </c>
+      <c r="AB223">
+        <v>2.18</v>
+      </c>
+      <c r="AC223">
+        <v>1.09</v>
+      </c>
+      <c r="AD223">
+        <v>6.5</v>
+      </c>
+      <c r="AE223">
+        <v>1.45</v>
+      </c>
+      <c r="AF223">
+        <v>2.6</v>
+      </c>
+      <c r="AG223">
+        <v>2.37</v>
+      </c>
+      <c r="AH223">
+        <v>1.48</v>
+      </c>
+      <c r="AI223">
+        <v>2.05</v>
+      </c>
+      <c r="AJ223">
+        <v>1.7</v>
+      </c>
+      <c r="AK223">
+        <v>1.68</v>
+      </c>
+      <c r="AL223">
+        <v>1.33</v>
+      </c>
+      <c r="AM223">
+        <v>1.28</v>
+      </c>
+      <c r="AN223">
+        <v>1.18</v>
+      </c>
+      <c r="AO223">
+        <v>1.5</v>
+      </c>
+      <c r="AP223">
+        <v>1.33</v>
+      </c>
+      <c r="AQ223">
+        <v>1.38</v>
+      </c>
+      <c r="AR223">
+        <v>1.42</v>
+      </c>
+      <c r="AS223">
+        <v>1.4</v>
+      </c>
+      <c r="AT223">
+        <v>2.82</v>
+      </c>
+      <c r="AU223">
+        <v>5</v>
+      </c>
+      <c r="AV223">
+        <v>7</v>
+      </c>
+      <c r="AW223">
+        <v>4</v>
+      </c>
+      <c r="AX223">
+        <v>11</v>
+      </c>
+      <c r="AY223">
+        <v>11</v>
+      </c>
+      <c r="AZ223">
+        <v>21</v>
+      </c>
+      <c r="BA223">
+        <v>1</v>
+      </c>
+      <c r="BB223">
+        <v>12</v>
+      </c>
+      <c r="BC223">
+        <v>13</v>
+      </c>
+      <c r="BD223">
+        <v>2.2</v>
+      </c>
+      <c r="BE223">
+        <v>8.5</v>
+      </c>
+      <c r="BF223">
+        <v>1.8</v>
+      </c>
+      <c r="BG223">
+        <v>1.21</v>
+      </c>
+      <c r="BH223">
+        <v>3.58</v>
+      </c>
+      <c r="BI223">
+        <v>1.48</v>
+      </c>
+      <c r="BJ223">
+        <v>2.58</v>
+      </c>
+      <c r="BK223">
+        <v>1.8</v>
+      </c>
+      <c r="BL223">
+        <v>2</v>
+      </c>
+      <c r="BM223">
+        <v>2.25</v>
+      </c>
+      <c r="BN223">
+        <v>1.62</v>
+      </c>
+      <c r="BO223">
+        <v>2.92</v>
+      </c>
+      <c r="BP223">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7450866</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45732.44791666666</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>83</v>
+      </c>
+      <c r="H224" t="s">
+        <v>85</v>
+      </c>
+      <c r="I224">
+        <v>1</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>1</v>
+      </c>
+      <c r="N224">
+        <v>2</v>
+      </c>
+      <c r="O224" t="s">
+        <v>143</v>
+      </c>
+      <c r="P224" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q224">
+        <v>2.88</v>
+      </c>
+      <c r="R224">
+        <v>2.05</v>
+      </c>
+      <c r="S224">
+        <v>4</v>
+      </c>
+      <c r="T224">
+        <v>1.44</v>
+      </c>
+      <c r="U224">
+        <v>2.63</v>
+      </c>
+      <c r="V224">
+        <v>3.4</v>
+      </c>
+      <c r="W224">
+        <v>1.3</v>
+      </c>
+      <c r="X224">
+        <v>10</v>
+      </c>
+      <c r="Y224">
+        <v>1.06</v>
+      </c>
+      <c r="Z224">
+        <v>2</v>
+      </c>
+      <c r="AA224">
+        <v>3.35</v>
+      </c>
+      <c r="AB224">
+        <v>3.67</v>
+      </c>
+      <c r="AC224">
+        <v>1.05</v>
+      </c>
+      <c r="AD224">
+        <v>8.5</v>
+      </c>
+      <c r="AE224">
+        <v>1.35</v>
+      </c>
+      <c r="AF224">
+        <v>3</v>
+      </c>
+      <c r="AG224">
+        <v>1.94</v>
+      </c>
+      <c r="AH224">
+        <v>1.8</v>
+      </c>
+      <c r="AI224">
+        <v>1.95</v>
+      </c>
+      <c r="AJ224">
+        <v>1.8</v>
+      </c>
+      <c r="AK224">
+        <v>1.29</v>
+      </c>
+      <c r="AL224">
+        <v>1.31</v>
+      </c>
+      <c r="AM224">
+        <v>1.72</v>
+      </c>
+      <c r="AN224">
+        <v>1.18</v>
+      </c>
+      <c r="AO224">
+        <v>1.25</v>
+      </c>
+      <c r="AP224">
+        <v>1.17</v>
+      </c>
+      <c r="AQ224">
+        <v>1.23</v>
+      </c>
+      <c r="AR224">
+        <v>1.84</v>
+      </c>
+      <c r="AS224">
+        <v>1.37</v>
+      </c>
+      <c r="AT224">
+        <v>3.21</v>
+      </c>
+      <c r="AU224">
+        <v>3</v>
+      </c>
+      <c r="AV224">
+        <v>3</v>
+      </c>
+      <c r="AW224">
+        <v>2</v>
+      </c>
+      <c r="AX224">
+        <v>6</v>
+      </c>
+      <c r="AY224">
+        <v>6</v>
+      </c>
+      <c r="AZ224">
+        <v>11</v>
+      </c>
+      <c r="BA224">
+        <v>7</v>
+      </c>
+      <c r="BB224">
+        <v>8</v>
+      </c>
+      <c r="BC224">
+        <v>15</v>
+      </c>
+      <c r="BD224">
+        <v>1.55</v>
+      </c>
+      <c r="BE224">
+        <v>9</v>
+      </c>
+      <c r="BF224">
+        <v>2.7</v>
+      </c>
+      <c r="BG224">
+        <v>1.18</v>
+      </c>
+      <c r="BH224">
+        <v>4</v>
+      </c>
+      <c r="BI224">
+        <v>1.32</v>
+      </c>
+      <c r="BJ224">
+        <v>2.88</v>
+      </c>
+      <c r="BK224">
+        <v>1.61</v>
+      </c>
+      <c r="BL224">
+        <v>2.25</v>
+      </c>
+      <c r="BM224">
+        <v>2</v>
+      </c>
+      <c r="BN224">
+        <v>1.79</v>
+      </c>
+      <c r="BO224">
+        <v>2.53</v>
+      </c>
+      <c r="BP224">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7450870</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45732.5625</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>86</v>
+      </c>
+      <c r="H225" t="s">
+        <v>74</v>
+      </c>
+      <c r="I225">
+        <v>2</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>2</v>
+      </c>
+      <c r="L225">
+        <v>3</v>
+      </c>
+      <c r="M225">
+        <v>2</v>
+      </c>
+      <c r="N225">
+        <v>5</v>
+      </c>
+      <c r="O225" t="s">
+        <v>240</v>
+      </c>
+      <c r="P225" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q225">
+        <v>2.88</v>
+      </c>
+      <c r="R225">
+        <v>2.1</v>
+      </c>
+      <c r="S225">
+        <v>4</v>
+      </c>
+      <c r="T225">
+        <v>1.44</v>
+      </c>
+      <c r="U225">
+        <v>2.63</v>
+      </c>
+      <c r="V225">
+        <v>3.25</v>
+      </c>
+      <c r="W225">
+        <v>1.33</v>
+      </c>
+      <c r="X225">
+        <v>9</v>
+      </c>
+      <c r="Y225">
+        <v>1.07</v>
+      </c>
+      <c r="Z225">
+        <v>2.18</v>
+      </c>
+      <c r="AA225">
+        <v>3.19</v>
+      </c>
+      <c r="AB225">
+        <v>3.35</v>
+      </c>
+      <c r="AC225">
+        <v>1.05</v>
+      </c>
+      <c r="AD225">
+        <v>8.5</v>
+      </c>
+      <c r="AE225">
+        <v>1.35</v>
+      </c>
+      <c r="AF225">
+        <v>3</v>
+      </c>
+      <c r="AG225">
+        <v>2.05</v>
+      </c>
+      <c r="AH225">
+        <v>1.65</v>
+      </c>
+      <c r="AI225">
+        <v>1.91</v>
+      </c>
+      <c r="AJ225">
+        <v>1.91</v>
+      </c>
+      <c r="AK225">
+        <v>1.26</v>
+      </c>
+      <c r="AL225">
+        <v>1.31</v>
+      </c>
+      <c r="AM225">
+        <v>1.75</v>
+      </c>
+      <c r="AN225">
+        <v>1.75</v>
+      </c>
+      <c r="AO225">
+        <v>1.17</v>
+      </c>
+      <c r="AP225">
+        <v>1.85</v>
+      </c>
+      <c r="AQ225">
+        <v>1.08</v>
+      </c>
+      <c r="AR225">
+        <v>1.64</v>
+      </c>
+      <c r="AS225">
+        <v>1.52</v>
+      </c>
+      <c r="AT225">
+        <v>3.16</v>
+      </c>
+      <c r="AU225">
+        <v>6</v>
+      </c>
+      <c r="AV225">
+        <v>7</v>
+      </c>
+      <c r="AW225">
+        <v>9</v>
+      </c>
+      <c r="AX225">
+        <v>3</v>
+      </c>
+      <c r="AY225">
+        <v>19</v>
+      </c>
+      <c r="AZ225">
+        <v>12</v>
+      </c>
+      <c r="BA225">
+        <v>7</v>
+      </c>
+      <c r="BB225">
+        <v>5</v>
+      </c>
+      <c r="BC225">
+        <v>12</v>
+      </c>
+      <c r="BD225">
+        <v>1.83</v>
+      </c>
+      <c r="BE225">
+        <v>8</v>
+      </c>
+      <c r="BF225">
+        <v>2.2</v>
+      </c>
+      <c r="BG225">
+        <v>1.31</v>
+      </c>
+      <c r="BH225">
+        <v>2.92</v>
+      </c>
+      <c r="BI225">
+        <v>1.63</v>
+      </c>
+      <c r="BJ225">
+        <v>2.22</v>
+      </c>
+      <c r="BK225">
+        <v>2.03</v>
+      </c>
+      <c r="BL225">
+        <v>1.76</v>
+      </c>
+      <c r="BM225">
+        <v>2.67</v>
+      </c>
+      <c r="BN225">
+        <v>1.39</v>
+      </c>
+      <c r="BO225">
+        <v>3.58</v>
+      </c>
+      <c r="BP225">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7450865</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45732.67708333334</v>
+      </c>
+      <c r="F226">
+        <v>25</v>
+      </c>
+      <c r="G226" t="s">
+        <v>70</v>
+      </c>
+      <c r="H226" t="s">
+        <v>76</v>
+      </c>
+      <c r="I226">
+        <v>1</v>
+      </c>
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="K226">
+        <v>2</v>
+      </c>
+      <c r="L226">
+        <v>2</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>3</v>
+      </c>
+      <c r="O226" t="s">
+        <v>241</v>
+      </c>
+      <c r="P226" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q226">
+        <v>3.2</v>
+      </c>
+      <c r="R226">
+        <v>2.25</v>
+      </c>
+      <c r="S226">
+        <v>3.2</v>
+      </c>
+      <c r="T226">
+        <v>1.36</v>
+      </c>
+      <c r="U226">
+        <v>3</v>
+      </c>
+      <c r="V226">
+        <v>2.63</v>
+      </c>
+      <c r="W226">
+        <v>1.44</v>
+      </c>
+      <c r="X226">
+        <v>7</v>
+      </c>
+      <c r="Y226">
+        <v>1.1</v>
+      </c>
+      <c r="Z226">
+        <v>2.5</v>
+      </c>
+      <c r="AA226">
+        <v>3.5</v>
+      </c>
+      <c r="AB226">
+        <v>2.6</v>
+      </c>
+      <c r="AC226">
+        <v>1.02</v>
+      </c>
+      <c r="AD226">
+        <v>11</v>
+      </c>
+      <c r="AE226">
+        <v>1.2</v>
+      </c>
+      <c r="AF226">
+        <v>4.2</v>
+      </c>
+      <c r="AG226">
+        <v>1.67</v>
+      </c>
+      <c r="AH226">
+        <v>2</v>
+      </c>
+      <c r="AI226">
+        <v>1.62</v>
+      </c>
+      <c r="AJ226">
+        <v>2.2</v>
+      </c>
+      <c r="AK226">
+        <v>1.52</v>
+      </c>
+      <c r="AL226">
+        <v>1.3</v>
+      </c>
+      <c r="AM226">
+        <v>1.44</v>
+      </c>
+      <c r="AN226">
+        <v>2.25</v>
+      </c>
+      <c r="AO226">
+        <v>1.55</v>
+      </c>
+      <c r="AP226">
+        <v>2.31</v>
+      </c>
+      <c r="AQ226">
+        <v>1.42</v>
+      </c>
+      <c r="AR226">
+        <v>1.8</v>
+      </c>
+      <c r="AS226">
+        <v>1.36</v>
+      </c>
+      <c r="AT226">
+        <v>3.16</v>
+      </c>
+      <c r="AU226">
+        <v>3</v>
+      </c>
+      <c r="AV226">
+        <v>2</v>
+      </c>
+      <c r="AW226">
+        <v>7</v>
+      </c>
+      <c r="AX226">
+        <v>12</v>
+      </c>
+      <c r="AY226">
+        <v>13</v>
+      </c>
+      <c r="AZ226">
+        <v>20</v>
+      </c>
+      <c r="BA226">
+        <v>0</v>
+      </c>
+      <c r="BB226">
+        <v>4</v>
+      </c>
+      <c r="BC226">
+        <v>4</v>
+      </c>
+      <c r="BD226">
+        <v>1.85</v>
+      </c>
+      <c r="BE226">
+        <v>8.5</v>
+      </c>
+      <c r="BF226">
+        <v>2.15</v>
+      </c>
+      <c r="BG226">
+        <v>1.2</v>
+      </c>
+      <c r="BH226">
+        <v>3.68</v>
+      </c>
+      <c r="BI226">
+        <v>1.41</v>
+      </c>
+      <c r="BJ226">
+        <v>2.6</v>
+      </c>
+      <c r="BK226">
+        <v>1.72</v>
+      </c>
+      <c r="BL226">
+        <v>2.1</v>
+      </c>
+      <c r="BM226">
+        <v>2.15</v>
+      </c>
+      <c r="BN226">
+        <v>1.69</v>
+      </c>
+      <c r="BO226">
+        <v>2.88</v>
+      </c>
+      <c r="BP226">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -47300,10 +47300,10 @@
         <v>1</v>
       </c>
       <c r="BB223">
+        <v>11</v>
+      </c>
+      <c r="BC223">
         <v>12</v>
-      </c>
-      <c r="BC223">
-        <v>13</v>
       </c>
       <c r="BD223">
         <v>2.2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="348">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -742,6 +742,15 @@
     <t>['31', '59']</t>
   </si>
   <si>
+    <t>['44', '45+4', '50']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['11', '64', '90+4']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1043,6 +1052,12 @@
   </si>
   <si>
     <t>['9']</t>
+  </si>
+  <si>
+    <t>['7', '22']</t>
+  </si>
+  <si>
+    <t>['16']</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1741,7 +1756,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ2">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1944,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ3">
         <v>0.77</v>
@@ -2072,7 +2087,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2562,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6">
         <v>0.6899999999999999</v>
@@ -2690,7 +2705,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2768,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7">
         <v>1.38</v>
@@ -3102,7 +3117,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3389,7 +3404,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ10">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3514,7 +3529,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3720,7 +3735,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3798,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12">
         <v>1.31</v>
@@ -3926,7 +3941,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4132,7 +4147,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4213,7 +4228,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ14">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4338,7 +4353,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4419,7 +4434,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ15">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4544,7 +4559,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -4828,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ17">
         <v>0.54</v>
@@ -5449,7 +5464,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ20">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR20">
         <v>0.84</v>
@@ -5780,7 +5795,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6398,7 +6413,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6604,7 +6619,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6682,7 +6697,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26">
         <v>1.38</v>
@@ -6810,7 +6825,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6888,10 +6903,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ27">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>0.72</v>
@@ -7016,7 +7031,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7303,7 +7318,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ29">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR29">
         <v>2.17</v>
@@ -7428,7 +7443,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7840,7 +7855,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7918,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ32">
         <v>0.6899999999999999</v>
@@ -8046,7 +8061,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8458,7 +8473,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8536,7 +8551,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ35">
         <v>1.08</v>
@@ -9076,7 +9091,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9282,7 +9297,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9363,7 +9378,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ39">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR39">
         <v>1.41</v>
@@ -9569,7 +9584,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ40">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9772,7 +9787,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ41">
         <v>1.23</v>
@@ -9900,7 +9915,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9978,7 +9993,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -10518,7 +10533,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10724,7 +10739,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -10802,7 +10817,7 @@
         <v>2.33</v>
       </c>
       <c r="AP46">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ46">
         <v>2.33</v>
@@ -11011,7 +11026,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ47">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR47">
         <v>1.43</v>
@@ -11136,7 +11151,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11214,7 +11229,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ48">
         <v>1.42</v>
@@ -11420,7 +11435,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ49">
         <v>0.6899999999999999</v>
@@ -11548,7 +11563,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11629,7 +11644,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ50">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR50">
         <v>1.73</v>
@@ -12038,7 +12053,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ52">
         <v>1.08</v>
@@ -12372,7 +12387,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12578,7 +12593,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12659,7 +12674,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ55">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR55">
         <v>1.29</v>
@@ -13196,7 +13211,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13402,7 +13417,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13608,7 +13623,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13686,7 +13701,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ60">
         <v>1.31</v>
@@ -13814,7 +13829,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14101,7 +14116,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ62">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.9</v>
@@ -14432,7 +14447,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14513,7 +14528,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ64">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.8</v>
@@ -14716,7 +14731,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14844,7 +14859,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -14922,7 +14937,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -15131,7 +15146,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ67">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR67">
         <v>1.96</v>
@@ -15334,10 +15349,10 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ68">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR68">
         <v>1.44</v>
@@ -15746,7 +15761,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ70">
         <v>2.33</v>
@@ -16286,7 +16301,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16492,7 +16507,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17728,7 +17743,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17809,7 +17824,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ80">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR80">
         <v>1.47</v>
@@ -18218,10 +18233,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ82">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR82">
         <v>1.3</v>
@@ -18427,7 +18442,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ83">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR83">
         <v>1.5</v>
@@ -18836,7 +18851,7 @@
         <v>0.8</v>
       </c>
       <c r="AP85">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ85">
         <v>1.42</v>
@@ -19170,7 +19185,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19251,7 +19266,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ87">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR87">
         <v>1.27</v>
@@ -19376,7 +19391,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19454,10 +19469,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ88">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR88">
         <v>1.53</v>
@@ -19582,7 +19597,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19660,7 +19675,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ89">
         <v>0.42</v>
@@ -19788,7 +19803,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19994,7 +20009,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20406,7 +20421,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20612,7 +20627,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20818,7 +20833,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21024,7 +21039,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21102,7 +21117,7 @@
         <v>2.4</v>
       </c>
       <c r="AP96">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ96">
         <v>1.92</v>
@@ -21642,7 +21657,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21848,7 +21863,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21926,7 +21941,7 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ100">
         <v>1.08</v>
@@ -22054,7 +22069,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22135,7 +22150,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ101">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR101">
         <v>1.68</v>
@@ -22260,7 +22275,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22341,7 +22356,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ102">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR102">
         <v>1.67</v>
@@ -22466,7 +22481,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22544,10 +22559,10 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ103">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR103">
         <v>1.6</v>
@@ -22878,7 +22893,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23371,7 +23386,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ107">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR107">
         <v>1.56</v>
@@ -23496,7 +23511,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23574,7 +23589,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
         <v>0.42</v>
@@ -23702,7 +23717,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23780,7 +23795,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ109">
         <v>0.77</v>
@@ -23989,7 +24004,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ110">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR110">
         <v>1.69</v>
@@ -24114,7 +24129,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24192,7 +24207,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ111">
         <v>1.31</v>
@@ -24398,7 +24413,7 @@
         <v>2.67</v>
       </c>
       <c r="AP112">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ112">
         <v>2.33</v>
@@ -24732,7 +24747,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25144,7 +25159,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25350,7 +25365,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25428,7 +25443,7 @@
         <v>1.4</v>
       </c>
       <c r="AP117">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ117">
         <v>1.08</v>
@@ -25762,7 +25777,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26049,7 +26064,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR120">
         <v>1.38</v>
@@ -26380,7 +26395,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26461,7 +26476,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ122">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR122">
         <v>2.04</v>
@@ -26586,7 +26601,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26664,7 +26679,7 @@
         <v>2.5</v>
       </c>
       <c r="AP123">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ123">
         <v>1.92</v>
@@ -26870,10 +26885,10 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ124">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.68</v>
@@ -26998,7 +27013,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27410,7 +27425,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27488,7 +27503,7 @@
         <v>1.17</v>
       </c>
       <c r="AP127">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ127">
         <v>1.31</v>
@@ -27616,7 +27631,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -28028,7 +28043,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28106,7 +28121,7 @@
         <v>1.17</v>
       </c>
       <c r="AP130">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ130">
         <v>1.08</v>
@@ -28440,7 +28455,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28518,7 +28533,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ132">
         <v>1.42</v>
@@ -28727,7 +28742,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ133">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR133">
         <v>1.65</v>
@@ -28852,7 +28867,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29058,7 +29073,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29264,7 +29279,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29470,7 +29485,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29676,7 +29691,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29754,7 +29769,7 @@
         <v>0.14</v>
       </c>
       <c r="AP138">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -30088,7 +30103,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30166,7 +30181,7 @@
         <v>2.57</v>
       </c>
       <c r="AP140">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ140">
         <v>1.92</v>
@@ -30294,7 +30309,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30993,7 +31008,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ144">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.48</v>
@@ -31196,7 +31211,7 @@
         <v>0.63</v>
       </c>
       <c r="AP145">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ145">
         <v>0.6899999999999999</v>
@@ -31402,10 +31417,10 @@
         <v>1.86</v>
       </c>
       <c r="AP146">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ146">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR146">
         <v>1.5</v>
@@ -31608,10 +31623,10 @@
         <v>0.25</v>
       </c>
       <c r="AP147">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ147">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR147">
         <v>1.42</v>
@@ -31942,7 +31957,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32148,7 +32163,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32435,7 +32450,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ151">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR151">
         <v>1.81</v>
@@ -32560,7 +32575,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33259,7 +33274,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ155">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR155">
         <v>1.98</v>
@@ -33462,7 +33477,7 @@
         <v>0.38</v>
       </c>
       <c r="AP156">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ156">
         <v>0.54</v>
@@ -33796,7 +33811,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34080,7 +34095,7 @@
         <v>2.25</v>
       </c>
       <c r="AP159">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ159">
         <v>1.92</v>
@@ -34208,7 +34223,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34289,7 +34304,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ160">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR160">
         <v>1.51</v>
@@ -34414,7 +34429,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34826,7 +34841,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -34904,7 +34919,7 @@
         <v>0.75</v>
       </c>
       <c r="AP163">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ163">
         <v>1</v>
@@ -35238,7 +35253,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35319,7 +35334,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ165">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR165">
         <v>2.02</v>
@@ -35728,7 +35743,7 @@
         <v>2.33</v>
       </c>
       <c r="AP167">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ167">
         <v>2.33</v>
@@ -36143,7 +36158,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ169">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR169">
         <v>1.91</v>
@@ -36474,7 +36489,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36552,7 +36567,7 @@
         <v>1.11</v>
       </c>
       <c r="AP171">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ171">
         <v>1.23</v>
@@ -36680,7 +36695,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36758,7 +36773,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ172">
         <v>1.38</v>
@@ -36967,7 +36982,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ173">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR173">
         <v>1.71</v>
@@ -37504,7 +37519,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37788,7 +37803,7 @@
         <v>1.44</v>
       </c>
       <c r="AP177">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ177">
         <v>1.08</v>
@@ -38122,7 +38137,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38406,10 +38421,10 @@
         <v>1.56</v>
       </c>
       <c r="AP180">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ180">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR180">
         <v>1.4</v>
@@ -38534,7 +38549,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38740,7 +38755,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -38818,7 +38833,7 @@
         <v>1.1</v>
       </c>
       <c r="AP182">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ182">
         <v>1.23</v>
@@ -39230,10 +39245,10 @@
         <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ184">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR184">
         <v>1.49</v>
@@ -39358,7 +39373,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39642,10 +39657,10 @@
         <v>0.6</v>
       </c>
       <c r="AP186">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ186">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR186">
         <v>1.66</v>
@@ -39770,7 +39785,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40388,7 +40403,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40594,7 +40609,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40672,7 +40687,7 @@
         <v>0.4</v>
       </c>
       <c r="AP191">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ191">
         <v>0.42</v>
@@ -41212,7 +41227,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41624,7 +41639,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41702,10 +41717,10 @@
         <v>0.55</v>
       </c>
       <c r="AP196">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ196">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR196">
         <v>1.46</v>
@@ -41830,7 +41845,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -41908,10 +41923,10 @@
         <v>1.7</v>
       </c>
       <c r="AP197">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ197">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR197">
         <v>1.68</v>
@@ -42242,7 +42257,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42529,7 +42544,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ200">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR200">
         <v>1.6</v>
@@ -43066,7 +43081,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43147,7 +43162,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ203">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR203">
         <v>1.8</v>
@@ -43272,7 +43287,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43478,7 +43493,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -43762,7 +43777,7 @@
         <v>0.36</v>
       </c>
       <c r="AP206">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ206">
         <v>0.54</v>
@@ -44302,7 +44317,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44383,7 +44398,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ209">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR209">
         <v>1.41</v>
@@ -44586,7 +44601,7 @@
         <v>1</v>
       </c>
       <c r="AP210">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ210">
         <v>1</v>
@@ -44714,7 +44729,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44792,7 +44807,7 @@
         <v>0.82</v>
       </c>
       <c r="AP211">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ211">
         <v>1</v>
@@ -44920,7 +44935,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -44998,7 +45013,7 @@
         <v>2.27</v>
       </c>
       <c r="AP212">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ212">
         <v>2.33</v>
@@ -45538,7 +45553,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45616,7 +45631,7 @@
         <v>1.27</v>
       </c>
       <c r="AP215">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ215">
         <v>1.42</v>
@@ -45744,7 +45759,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -45825,7 +45840,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ216">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR216">
         <v>1.42</v>
@@ -46156,7 +46171,7 @@
         <v>234</v>
       </c>
       <c r="P218" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q218">
         <v>2.55</v>
@@ -46362,7 +46377,7 @@
         <v>235</v>
       </c>
       <c r="P219" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q219">
         <v>2.35</v>
@@ -46568,7 +46583,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q220">
         <v>2.88</v>
@@ -47598,7 +47613,7 @@
         <v>240</v>
       </c>
       <c r="P225" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q225">
         <v>2.88</v>
@@ -47804,7 +47819,7 @@
         <v>241</v>
       </c>
       <c r="P226" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q226">
         <v>3.2</v>
@@ -47885,7 +47900,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ226">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR226">
         <v>1.8</v>
@@ -47961,6 +47976,1036 @@
       </c>
       <c r="BP226">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7450880</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>84</v>
+      </c>
+      <c r="H227" t="s">
+        <v>82</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>2</v>
+      </c>
+      <c r="K227">
+        <v>2</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+      <c r="M227">
+        <v>2</v>
+      </c>
+      <c r="N227">
+        <v>2</v>
+      </c>
+      <c r="O227" t="s">
+        <v>95</v>
+      </c>
+      <c r="P227" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q227">
+        <v>2.63</v>
+      </c>
+      <c r="R227">
+        <v>2</v>
+      </c>
+      <c r="S227">
+        <v>5</v>
+      </c>
+      <c r="T227">
+        <v>1.5</v>
+      </c>
+      <c r="U227">
+        <v>2.5</v>
+      </c>
+      <c r="V227">
+        <v>3.5</v>
+      </c>
+      <c r="W227">
+        <v>1.29</v>
+      </c>
+      <c r="X227">
+        <v>11</v>
+      </c>
+      <c r="Y227">
+        <v>1.05</v>
+      </c>
+      <c r="Z227">
+        <v>1.8</v>
+      </c>
+      <c r="AA227">
+        <v>3.33</v>
+      </c>
+      <c r="AB227">
+        <v>4.7</v>
+      </c>
+      <c r="AC227">
+        <v>0</v>
+      </c>
+      <c r="AD227">
+        <v>0</v>
+      </c>
+      <c r="AE227">
+        <v>0</v>
+      </c>
+      <c r="AF227">
+        <v>0</v>
+      </c>
+      <c r="AG227">
+        <v>2.2</v>
+      </c>
+      <c r="AH227">
+        <v>1.55</v>
+      </c>
+      <c r="AI227">
+        <v>2.1</v>
+      </c>
+      <c r="AJ227">
+        <v>1.67</v>
+      </c>
+      <c r="AK227">
+        <v>0</v>
+      </c>
+      <c r="AL227">
+        <v>0</v>
+      </c>
+      <c r="AM227">
+        <v>0</v>
+      </c>
+      <c r="AN227">
+        <v>1.25</v>
+      </c>
+      <c r="AO227">
+        <v>0.83</v>
+      </c>
+      <c r="AP227">
+        <v>1.15</v>
+      </c>
+      <c r="AQ227">
+        <v>1</v>
+      </c>
+      <c r="AR227">
+        <v>1.59</v>
+      </c>
+      <c r="AS227">
+        <v>1.39</v>
+      </c>
+      <c r="AT227">
+        <v>2.98</v>
+      </c>
+      <c r="AU227">
+        <v>7</v>
+      </c>
+      <c r="AV227">
+        <v>4</v>
+      </c>
+      <c r="AW227">
+        <v>6</v>
+      </c>
+      <c r="AX227">
+        <v>9</v>
+      </c>
+      <c r="AY227">
+        <v>13</v>
+      </c>
+      <c r="AZ227">
+        <v>15</v>
+      </c>
+      <c r="BA227">
+        <v>6</v>
+      </c>
+      <c r="BB227">
+        <v>2</v>
+      </c>
+      <c r="BC227">
+        <v>8</v>
+      </c>
+      <c r="BD227">
+        <v>0</v>
+      </c>
+      <c r="BE227">
+        <v>0</v>
+      </c>
+      <c r="BF227">
+        <v>0</v>
+      </c>
+      <c r="BG227">
+        <v>0</v>
+      </c>
+      <c r="BH227">
+        <v>0</v>
+      </c>
+      <c r="BI227">
+        <v>0</v>
+      </c>
+      <c r="BJ227">
+        <v>0</v>
+      </c>
+      <c r="BK227">
+        <v>0</v>
+      </c>
+      <c r="BL227">
+        <v>0</v>
+      </c>
+      <c r="BM227">
+        <v>0</v>
+      </c>
+      <c r="BN227">
+        <v>0</v>
+      </c>
+      <c r="BO227">
+        <v>0</v>
+      </c>
+      <c r="BP227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7450878</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45744.6875</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>74</v>
+      </c>
+      <c r="H228" t="s">
+        <v>73</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>0</v>
+      </c>
+      <c r="O228" t="s">
+        <v>95</v>
+      </c>
+      <c r="P228" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q228">
+        <v>2.5</v>
+      </c>
+      <c r="R228">
+        <v>2.3</v>
+      </c>
+      <c r="S228">
+        <v>4</v>
+      </c>
+      <c r="T228">
+        <v>1.3</v>
+      </c>
+      <c r="U228">
+        <v>3.4</v>
+      </c>
+      <c r="V228">
+        <v>2.5</v>
+      </c>
+      <c r="W228">
+        <v>1.5</v>
+      </c>
+      <c r="X228">
+        <v>6</v>
+      </c>
+      <c r="Y228">
+        <v>1.13</v>
+      </c>
+      <c r="Z228">
+        <v>1.95</v>
+      </c>
+      <c r="AA228">
+        <v>3.68</v>
+      </c>
+      <c r="AB228">
+        <v>3.5</v>
+      </c>
+      <c r="AC228">
+        <v>0</v>
+      </c>
+      <c r="AD228">
+        <v>0</v>
+      </c>
+      <c r="AE228">
+        <v>0</v>
+      </c>
+      <c r="AF228">
+        <v>0</v>
+      </c>
+      <c r="AG228">
+        <v>1.6</v>
+      </c>
+      <c r="AH228">
+        <v>2.1</v>
+      </c>
+      <c r="AI228">
+        <v>1.57</v>
+      </c>
+      <c r="AJ228">
+        <v>2.25</v>
+      </c>
+      <c r="AK228">
+        <v>0</v>
+      </c>
+      <c r="AL228">
+        <v>0</v>
+      </c>
+      <c r="AM228">
+        <v>0</v>
+      </c>
+      <c r="AN228">
+        <v>2.17</v>
+      </c>
+      <c r="AO228">
+        <v>1</v>
+      </c>
+      <c r="AP228">
+        <v>2.08</v>
+      </c>
+      <c r="AQ228">
+        <v>1</v>
+      </c>
+      <c r="AR228">
+        <v>1.7</v>
+      </c>
+      <c r="AS228">
+        <v>1.51</v>
+      </c>
+      <c r="AT228">
+        <v>3.21</v>
+      </c>
+      <c r="AU228">
+        <v>6</v>
+      </c>
+      <c r="AV228">
+        <v>4</v>
+      </c>
+      <c r="AW228">
+        <v>6</v>
+      </c>
+      <c r="AX228">
+        <v>8</v>
+      </c>
+      <c r="AY228">
+        <v>16</v>
+      </c>
+      <c r="AZ228">
+        <v>16</v>
+      </c>
+      <c r="BA228">
+        <v>8</v>
+      </c>
+      <c r="BB228">
+        <v>5</v>
+      </c>
+      <c r="BC228">
+        <v>13</v>
+      </c>
+      <c r="BD228">
+        <v>0</v>
+      </c>
+      <c r="BE228">
+        <v>0</v>
+      </c>
+      <c r="BF228">
+        <v>0</v>
+      </c>
+      <c r="BG228">
+        <v>0</v>
+      </c>
+      <c r="BH228">
+        <v>0</v>
+      </c>
+      <c r="BI228">
+        <v>0</v>
+      </c>
+      <c r="BJ228">
+        <v>0</v>
+      </c>
+      <c r="BK228">
+        <v>2.25</v>
+      </c>
+      <c r="BL228">
+        <v>0</v>
+      </c>
+      <c r="BM228">
+        <v>0</v>
+      </c>
+      <c r="BN228">
+        <v>0</v>
+      </c>
+      <c r="BO228">
+        <v>0</v>
+      </c>
+      <c r="BP228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7450873</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45745.44791666666</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>75</v>
+      </c>
+      <c r="H229" t="s">
+        <v>79</v>
+      </c>
+      <c r="I229">
+        <v>2</v>
+      </c>
+      <c r="J229">
+        <v>1</v>
+      </c>
+      <c r="K229">
+        <v>3</v>
+      </c>
+      <c r="L229">
+        <v>3</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>4</v>
+      </c>
+      <c r="O229" t="s">
+        <v>242</v>
+      </c>
+      <c r="P229" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q229">
+        <v>2.3</v>
+      </c>
+      <c r="R229">
+        <v>2.2</v>
+      </c>
+      <c r="S229">
+        <v>5</v>
+      </c>
+      <c r="T229">
+        <v>1.4</v>
+      </c>
+      <c r="U229">
+        <v>2.75</v>
+      </c>
+      <c r="V229">
+        <v>2.75</v>
+      </c>
+      <c r="W229">
+        <v>1.4</v>
+      </c>
+      <c r="X229">
+        <v>8</v>
+      </c>
+      <c r="Y229">
+        <v>1.08</v>
+      </c>
+      <c r="Z229">
+        <v>1.65</v>
+      </c>
+      <c r="AA229">
+        <v>3.92</v>
+      </c>
+      <c r="AB229">
+        <v>4.75</v>
+      </c>
+      <c r="AC229">
+        <v>0</v>
+      </c>
+      <c r="AD229">
+        <v>0</v>
+      </c>
+      <c r="AE229">
+        <v>0</v>
+      </c>
+      <c r="AF229">
+        <v>0</v>
+      </c>
+      <c r="AG229">
+        <v>1.87</v>
+      </c>
+      <c r="AH229">
+        <v>1.87</v>
+      </c>
+      <c r="AI229">
+        <v>1.91</v>
+      </c>
+      <c r="AJ229">
+        <v>1.91</v>
+      </c>
+      <c r="AK229">
+        <v>0</v>
+      </c>
+      <c r="AL229">
+        <v>0</v>
+      </c>
+      <c r="AM229">
+        <v>0</v>
+      </c>
+      <c r="AN229">
+        <v>1.15</v>
+      </c>
+      <c r="AO229">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP229">
+        <v>1.29</v>
+      </c>
+      <c r="AQ229">
+        <v>0.64</v>
+      </c>
+      <c r="AR229">
+        <v>1.58</v>
+      </c>
+      <c r="AS229">
+        <v>1.05</v>
+      </c>
+      <c r="AT229">
+        <v>2.63</v>
+      </c>
+      <c r="AU229">
+        <v>4</v>
+      </c>
+      <c r="AV229">
+        <v>5</v>
+      </c>
+      <c r="AW229">
+        <v>13</v>
+      </c>
+      <c r="AX229">
+        <v>2</v>
+      </c>
+      <c r="AY229">
+        <v>24</v>
+      </c>
+      <c r="AZ229">
+        <v>9</v>
+      </c>
+      <c r="BA229">
+        <v>5</v>
+      </c>
+      <c r="BB229">
+        <v>4</v>
+      </c>
+      <c r="BC229">
+        <v>9</v>
+      </c>
+      <c r="BD229">
+        <v>0</v>
+      </c>
+      <c r="BE229">
+        <v>0</v>
+      </c>
+      <c r="BF229">
+        <v>0</v>
+      </c>
+      <c r="BG229">
+        <v>0</v>
+      </c>
+      <c r="BH229">
+        <v>0</v>
+      </c>
+      <c r="BI229">
+        <v>0</v>
+      </c>
+      <c r="BJ229">
+        <v>0</v>
+      </c>
+      <c r="BK229">
+        <v>2.1</v>
+      </c>
+      <c r="BL229">
+        <v>0</v>
+      </c>
+      <c r="BM229">
+        <v>0</v>
+      </c>
+      <c r="BN229">
+        <v>0</v>
+      </c>
+      <c r="BO229">
+        <v>0</v>
+      </c>
+      <c r="BP229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7450877</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45745.5625</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>80</v>
+      </c>
+      <c r="H230" t="s">
+        <v>70</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>1</v>
+      </c>
+      <c r="O230" t="s">
+        <v>243</v>
+      </c>
+      <c r="P230" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q230">
+        <v>3.5</v>
+      </c>
+      <c r="R230">
+        <v>2.25</v>
+      </c>
+      <c r="S230">
+        <v>2.88</v>
+      </c>
+      <c r="T230">
+        <v>1.33</v>
+      </c>
+      <c r="U230">
+        <v>3.25</v>
+      </c>
+      <c r="V230">
+        <v>2.63</v>
+      </c>
+      <c r="W230">
+        <v>1.44</v>
+      </c>
+      <c r="X230">
+        <v>6.5</v>
+      </c>
+      <c r="Y230">
+        <v>1.11</v>
+      </c>
+      <c r="Z230">
+        <v>2.91</v>
+      </c>
+      <c r="AA230">
+        <v>3.58</v>
+      </c>
+      <c r="AB230">
+        <v>2.24</v>
+      </c>
+      <c r="AC230">
+        <v>0</v>
+      </c>
+      <c r="AD230">
+        <v>0</v>
+      </c>
+      <c r="AE230">
+        <v>0</v>
+      </c>
+      <c r="AF230">
+        <v>0</v>
+      </c>
+      <c r="AG230">
+        <v>1.65</v>
+      </c>
+      <c r="AH230">
+        <v>2.05</v>
+      </c>
+      <c r="AI230">
+        <v>1.57</v>
+      </c>
+      <c r="AJ230">
+        <v>2.25</v>
+      </c>
+      <c r="AK230">
+        <v>0</v>
+      </c>
+      <c r="AL230">
+        <v>0</v>
+      </c>
+      <c r="AM230">
+        <v>0</v>
+      </c>
+      <c r="AN230">
+        <v>0.92</v>
+      </c>
+      <c r="AO230">
+        <v>1.75</v>
+      </c>
+      <c r="AP230">
+        <v>1.08</v>
+      </c>
+      <c r="AQ230">
+        <v>1.62</v>
+      </c>
+      <c r="AR230">
+        <v>1.6</v>
+      </c>
+      <c r="AS230">
+        <v>1.28</v>
+      </c>
+      <c r="AT230">
+        <v>2.88</v>
+      </c>
+      <c r="AU230">
+        <v>6</v>
+      </c>
+      <c r="AV230">
+        <v>3</v>
+      </c>
+      <c r="AW230">
+        <v>6</v>
+      </c>
+      <c r="AX230">
+        <v>12</v>
+      </c>
+      <c r="AY230">
+        <v>13</v>
+      </c>
+      <c r="AZ230">
+        <v>21</v>
+      </c>
+      <c r="BA230">
+        <v>3</v>
+      </c>
+      <c r="BB230">
+        <v>11</v>
+      </c>
+      <c r="BC230">
+        <v>14</v>
+      </c>
+      <c r="BD230">
+        <v>0</v>
+      </c>
+      <c r="BE230">
+        <v>0</v>
+      </c>
+      <c r="BF230">
+        <v>0</v>
+      </c>
+      <c r="BG230">
+        <v>0</v>
+      </c>
+      <c r="BH230">
+        <v>0</v>
+      </c>
+      <c r="BI230">
+        <v>0</v>
+      </c>
+      <c r="BJ230">
+        <v>0</v>
+      </c>
+      <c r="BK230">
+        <v>2.38</v>
+      </c>
+      <c r="BL230">
+        <v>0</v>
+      </c>
+      <c r="BM230">
+        <v>0</v>
+      </c>
+      <c r="BN230">
+        <v>0</v>
+      </c>
+      <c r="BO230">
+        <v>0</v>
+      </c>
+      <c r="BP230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7450881</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45745.67708333334</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>71</v>
+      </c>
+      <c r="H231" t="s">
+        <v>76</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>2</v>
+      </c>
+      <c r="L231">
+        <v>3</v>
+      </c>
+      <c r="M231">
+        <v>1</v>
+      </c>
+      <c r="N231">
+        <v>4</v>
+      </c>
+      <c r="O231" t="s">
+        <v>244</v>
+      </c>
+      <c r="P231" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q231">
+        <v>4</v>
+      </c>
+      <c r="R231">
+        <v>2.1</v>
+      </c>
+      <c r="S231">
+        <v>2.75</v>
+      </c>
+      <c r="T231">
+        <v>1.4</v>
+      </c>
+      <c r="U231">
+        <v>2.75</v>
+      </c>
+      <c r="V231">
+        <v>3</v>
+      </c>
+      <c r="W231">
+        <v>1.36</v>
+      </c>
+      <c r="X231">
+        <v>9</v>
+      </c>
+      <c r="Y231">
+        <v>1.07</v>
+      </c>
+      <c r="Z231">
+        <v>3.6</v>
+      </c>
+      <c r="AA231">
+        <v>3.32</v>
+      </c>
+      <c r="AB231">
+        <v>2.04</v>
+      </c>
+      <c r="AC231">
+        <v>0</v>
+      </c>
+      <c r="AD231">
+        <v>0</v>
+      </c>
+      <c r="AE231">
+        <v>0</v>
+      </c>
+      <c r="AF231">
+        <v>0</v>
+      </c>
+      <c r="AG231">
+        <v>1.92</v>
+      </c>
+      <c r="AH231">
+        <v>1.82</v>
+      </c>
+      <c r="AI231">
+        <v>1.8</v>
+      </c>
+      <c r="AJ231">
+        <v>1.95</v>
+      </c>
+      <c r="AK231">
+        <v>0</v>
+      </c>
+      <c r="AL231">
+        <v>0</v>
+      </c>
+      <c r="AM231">
+        <v>0</v>
+      </c>
+      <c r="AN231">
+        <v>0.92</v>
+      </c>
+      <c r="AO231">
+        <v>1.42</v>
+      </c>
+      <c r="AP231">
+        <v>1.08</v>
+      </c>
+      <c r="AQ231">
+        <v>1.31</v>
+      </c>
+      <c r="AR231">
+        <v>1.56</v>
+      </c>
+      <c r="AS231">
+        <v>1.39</v>
+      </c>
+      <c r="AT231">
+        <v>2.95</v>
+      </c>
+      <c r="AU231">
+        <v>7</v>
+      </c>
+      <c r="AV231">
+        <v>4</v>
+      </c>
+      <c r="AW231">
+        <v>11</v>
+      </c>
+      <c r="AX231">
+        <v>8</v>
+      </c>
+      <c r="AY231">
+        <v>21</v>
+      </c>
+      <c r="AZ231">
+        <v>15</v>
+      </c>
+      <c r="BA231">
+        <v>6</v>
+      </c>
+      <c r="BB231">
+        <v>5</v>
+      </c>
+      <c r="BC231">
+        <v>11</v>
+      </c>
+      <c r="BD231">
+        <v>0</v>
+      </c>
+      <c r="BE231">
+        <v>0</v>
+      </c>
+      <c r="BF231">
+        <v>0</v>
+      </c>
+      <c r="BG231">
+        <v>0</v>
+      </c>
+      <c r="BH231">
+        <v>0</v>
+      </c>
+      <c r="BI231">
+        <v>0</v>
+      </c>
+      <c r="BJ231">
+        <v>0</v>
+      </c>
+      <c r="BK231">
+        <v>2.38</v>
+      </c>
+      <c r="BL231">
+        <v>0</v>
+      </c>
+      <c r="BM231">
+        <v>0</v>
+      </c>
+      <c r="BN231">
+        <v>0</v>
+      </c>
+      <c r="BO231">
+        <v>0</v>
+      </c>
+      <c r="BP231">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="353">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,15 @@
     <t>['11', '64', '90+4']</t>
   </si>
   <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['28', '49', '60', '82']</t>
+  </si>
+  <si>
+    <t>['38', '90+11']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1058,6 +1067,12 @@
   </si>
   <si>
     <t>['16']</t>
+  </si>
+  <si>
+    <t>['10', '75', '90+4']</t>
+  </si>
+  <si>
+    <t>['51']</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2087,7 +2102,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2165,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2705,7 +2720,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2992,7 +3007,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ8">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3117,7 +3132,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3195,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ9">
         <v>2.33</v>
@@ -3529,7 +3544,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3610,7 +3625,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ11">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3735,7 +3750,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3941,7 +3956,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4147,7 +4162,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4353,7 +4368,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4559,7 +4574,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5049,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ18">
         <v>1.08</v>
@@ -5795,7 +5810,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5873,7 +5888,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ22">
         <v>2.33</v>
@@ -6082,7 +6097,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ23">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR23">
         <v>2.07</v>
@@ -6413,7 +6428,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6491,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ25">
         <v>1.23</v>
@@ -6619,7 +6634,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6825,7 +6840,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -7031,7 +7046,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7112,7 +7127,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ28">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR28">
         <v>2.08</v>
@@ -7443,7 +7458,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7521,7 +7536,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ30">
         <v>1.92</v>
@@ -7730,7 +7745,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ31">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR31">
         <v>1.66</v>
@@ -7855,7 +7870,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8061,7 +8076,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8473,7 +8488,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8963,7 +8978,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ37">
         <v>1.31</v>
@@ -9091,7 +9106,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9297,7 +9312,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9915,7 +9930,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9996,7 +10011,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR42">
         <v>1.4</v>
@@ -10533,7 +10548,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10614,7 +10629,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR45">
         <v>1.15</v>
@@ -10739,7 +10754,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11023,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ47">
         <v>0.64</v>
@@ -11151,7 +11166,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11232,7 +11247,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ48">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR48">
         <v>0.96</v>
@@ -11563,7 +11578,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11641,7 +11656,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ50">
         <v>1.62</v>
@@ -12259,10 +12274,10 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ53">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR53">
         <v>1.28</v>
@@ -12387,7 +12402,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12593,7 +12608,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13211,7 +13226,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13417,7 +13432,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13623,7 +13638,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13829,7 +13844,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14319,10 +14334,10 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ63">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -14447,7 +14462,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14525,7 +14540,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14734,7 +14749,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR65">
         <v>1.09</v>
@@ -14859,7 +14874,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15555,7 +15570,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ69">
         <v>0.6899999999999999</v>
@@ -16301,7 +16316,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16507,7 +16522,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17743,7 +17758,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17821,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ80">
         <v>1.62</v>
@@ -18027,7 +18042,7 @@
         <v>0.25</v>
       </c>
       <c r="AP81">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18645,7 +18660,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ84">
         <v>0.54</v>
@@ -18854,7 +18869,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ85">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR85">
         <v>1.53</v>
@@ -19060,7 +19075,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR86">
         <v>1.54</v>
@@ -19185,7 +19200,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19263,7 +19278,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ87">
         <v>1.31</v>
@@ -19391,7 +19406,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19597,7 +19612,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19678,7 +19693,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ89">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19803,7 +19818,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -20009,7 +20024,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20421,7 +20436,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20627,7 +20642,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20833,7 +20848,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21039,7 +21054,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21657,7 +21672,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21735,7 +21750,7 @@
         <v>1.17</v>
       </c>
       <c r="AP99">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ99">
         <v>1.38</v>
@@ -21863,7 +21878,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -22069,7 +22084,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22147,7 +22162,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22275,7 +22290,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22481,7 +22496,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22765,7 +22780,7 @@
         <v>0.2</v>
       </c>
       <c r="AP104">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ104">
         <v>0.54</v>
@@ -22893,7 +22908,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22974,7 +22989,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ105">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR105">
         <v>1.93</v>
@@ -23511,7 +23526,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23592,7 +23607,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ108">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR108">
         <v>1.61</v>
@@ -23717,7 +23732,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24129,7 +24144,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24622,7 +24637,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR113">
         <v>1.89</v>
@@ -24747,7 +24762,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25159,7 +25174,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25240,7 +25255,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ116">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR116">
         <v>1.38</v>
@@ -25365,7 +25380,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25652,7 +25667,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ118">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR118">
         <v>1.58</v>
@@ -25777,7 +25792,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -25855,7 +25870,7 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -26395,7 +26410,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26601,7 +26616,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -27013,7 +27028,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27091,7 +27106,7 @@
         <v>0.86</v>
       </c>
       <c r="AP125">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ125">
         <v>1.23</v>
@@ -27425,7 +27440,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27631,7 +27646,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27712,7 +27727,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27915,7 +27930,7 @@
         <v>0.71</v>
       </c>
       <c r="AP129">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ129">
         <v>0.77</v>
@@ -28043,7 +28058,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28455,7 +28470,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28536,7 +28551,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ132">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR132">
         <v>1.49</v>
@@ -28867,7 +28882,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29073,7 +29088,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29279,7 +29294,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29485,7 +29500,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29691,7 +29706,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30103,7 +30118,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30309,7 +30324,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30390,7 +30405,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ141">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR141">
         <v>1.53</v>
@@ -31829,7 +31844,7 @@
         <v>0.75</v>
       </c>
       <c r="AP148">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ148">
         <v>0.77</v>
@@ -31957,7 +31972,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32163,7 +32178,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32241,10 +32256,10 @@
         <v>1.38</v>
       </c>
       <c r="AP150">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ150">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR150">
         <v>1.43</v>
@@ -32575,7 +32590,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32859,10 +32874,10 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ153">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR153">
         <v>1.63</v>
@@ -33686,7 +33701,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ157">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR157">
         <v>1.39</v>
@@ -33811,7 +33826,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34223,7 +34238,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34429,7 +34444,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34713,7 +34728,7 @@
         <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ162">
         <v>1</v>
@@ -34841,7 +34856,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -34922,7 +34937,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ163">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR163">
         <v>1.52</v>
@@ -35125,10 +35140,10 @@
         <v>0.44</v>
       </c>
       <c r="AP164">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ164">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR164">
         <v>1.72</v>
@@ -35253,7 +35268,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35537,7 +35552,7 @@
         <v>0.67</v>
       </c>
       <c r="AP166">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ166">
         <v>0.77</v>
@@ -36364,7 +36379,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ170">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36489,7 +36504,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36695,7 +36710,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37188,7 +37203,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ174">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR174">
         <v>1.83</v>
@@ -37519,7 +37534,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -38009,7 +38024,7 @@
         <v>1.56</v>
       </c>
       <c r="AP178">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ178">
         <v>1.31</v>
@@ -38137,7 +38152,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38549,7 +38564,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38755,7 +38770,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39373,7 +39388,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39454,7 +39469,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ185">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR185">
         <v>1.95</v>
@@ -39785,7 +39800,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40069,7 +40084,7 @@
         <v>1.4</v>
       </c>
       <c r="AP188">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ188">
         <v>1.38</v>
@@ -40403,7 +40418,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40609,7 +40624,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40690,7 +40705,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ191">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR191">
         <v>1.48</v>
@@ -40896,7 +40911,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ192">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR192">
         <v>1.67</v>
@@ -41099,7 +41114,7 @@
         <v>0.4</v>
       </c>
       <c r="AP193">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ193">
         <v>0.54</v>
@@ -41227,7 +41242,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41639,7 +41654,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41845,7 +41860,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42257,7 +42272,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42335,7 +42350,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ199">
         <v>1.08</v>
@@ -43081,7 +43096,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43287,7 +43302,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43493,7 +43508,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -44317,7 +44332,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44395,7 +44410,7 @@
         <v>0.75</v>
       </c>
       <c r="AP209">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ209">
         <v>0.64</v>
@@ -44729,7 +44744,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44810,7 +44825,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ211">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR211">
         <v>1.62</v>
@@ -44935,7 +44950,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -45222,7 +45237,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ213">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR213">
         <v>1.92</v>
@@ -45425,7 +45440,7 @@
         <v>0.75</v>
       </c>
       <c r="AP214">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ214">
         <v>0.6899999999999999</v>
@@ -45553,7 +45568,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45634,7 +45649,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ215">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR215">
         <v>1.54</v>
@@ -45759,7 +45774,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -46043,7 +46058,7 @@
         <v>1.18</v>
       </c>
       <c r="AP217">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ217">
         <v>1.08</v>
@@ -46171,7 +46186,7 @@
         <v>234</v>
       </c>
       <c r="P218" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q218">
         <v>2.55</v>
@@ -46377,7 +46392,7 @@
         <v>235</v>
       </c>
       <c r="P219" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q219">
         <v>2.35</v>
@@ -46583,7 +46598,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q220">
         <v>2.88</v>
@@ -47613,7 +47628,7 @@
         <v>240</v>
       </c>
       <c r="P225" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q225">
         <v>2.88</v>
@@ -47819,7 +47834,7 @@
         <v>241</v>
       </c>
       <c r="P226" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q226">
         <v>3.2</v>
@@ -48025,7 +48040,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48437,7 +48452,7 @@
         <v>242</v>
       </c>
       <c r="P229" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q229">
         <v>2.3</v>
@@ -49005,6 +49020,624 @@
         <v>0</v>
       </c>
       <c r="BP231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7450876</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45746.30208333334</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>85</v>
+      </c>
+      <c r="H232" t="s">
+        <v>81</v>
+      </c>
+      <c r="I232">
+        <v>1</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>2</v>
+      </c>
+      <c r="L232">
+        <v>1</v>
+      </c>
+      <c r="M232">
+        <v>3</v>
+      </c>
+      <c r="N232">
+        <v>4</v>
+      </c>
+      <c r="O232" t="s">
+        <v>245</v>
+      </c>
+      <c r="P232" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q232">
+        <v>3.1</v>
+      </c>
+      <c r="R232">
+        <v>2.05</v>
+      </c>
+      <c r="S232">
+        <v>3.75</v>
+      </c>
+      <c r="T232">
+        <v>1.44</v>
+      </c>
+      <c r="U232">
+        <v>2.63</v>
+      </c>
+      <c r="V232">
+        <v>3.25</v>
+      </c>
+      <c r="W232">
+        <v>1.33</v>
+      </c>
+      <c r="X232">
+        <v>10</v>
+      </c>
+      <c r="Y232">
+        <v>1.06</v>
+      </c>
+      <c r="Z232">
+        <v>2.35</v>
+      </c>
+      <c r="AA232">
+        <v>3.15</v>
+      </c>
+      <c r="AB232">
+        <v>3.06</v>
+      </c>
+      <c r="AC232">
+        <v>0</v>
+      </c>
+      <c r="AD232">
+        <v>0</v>
+      </c>
+      <c r="AE232">
+        <v>0</v>
+      </c>
+      <c r="AF232">
+        <v>0</v>
+      </c>
+      <c r="AG232">
+        <v>2</v>
+      </c>
+      <c r="AH232">
+        <v>1.65</v>
+      </c>
+      <c r="AI232">
+        <v>1.8</v>
+      </c>
+      <c r="AJ232">
+        <v>1.95</v>
+      </c>
+      <c r="AK232">
+        <v>0</v>
+      </c>
+      <c r="AL232">
+        <v>0</v>
+      </c>
+      <c r="AM232">
+        <v>0</v>
+      </c>
+      <c r="AN232">
+        <v>1.42</v>
+      </c>
+      <c r="AO232">
+        <v>1</v>
+      </c>
+      <c r="AP232">
+        <v>1.31</v>
+      </c>
+      <c r="AQ232">
+        <v>1.15</v>
+      </c>
+      <c r="AR232">
+        <v>1.48</v>
+      </c>
+      <c r="AS232">
+        <v>1.41</v>
+      </c>
+      <c r="AT232">
+        <v>2.89</v>
+      </c>
+      <c r="AU232">
+        <v>4</v>
+      </c>
+      <c r="AV232">
+        <v>4</v>
+      </c>
+      <c r="AW232">
+        <v>7</v>
+      </c>
+      <c r="AX232">
+        <v>2</v>
+      </c>
+      <c r="AY232">
+        <v>13</v>
+      </c>
+      <c r="AZ232">
+        <v>6</v>
+      </c>
+      <c r="BA232">
+        <v>8</v>
+      </c>
+      <c r="BB232">
+        <v>5</v>
+      </c>
+      <c r="BC232">
+        <v>13</v>
+      </c>
+      <c r="BD232">
+        <v>0</v>
+      </c>
+      <c r="BE232">
+        <v>0</v>
+      </c>
+      <c r="BF232">
+        <v>0</v>
+      </c>
+      <c r="BG232">
+        <v>0</v>
+      </c>
+      <c r="BH232">
+        <v>0</v>
+      </c>
+      <c r="BI232">
+        <v>0</v>
+      </c>
+      <c r="BJ232">
+        <v>0</v>
+      </c>
+      <c r="BK232">
+        <v>2.2</v>
+      </c>
+      <c r="BL232">
+        <v>0</v>
+      </c>
+      <c r="BM232">
+        <v>0</v>
+      </c>
+      <c r="BN232">
+        <v>0</v>
+      </c>
+      <c r="BO232">
+        <v>0</v>
+      </c>
+      <c r="BP232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7450879</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45746.40625</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>77</v>
+      </c>
+      <c r="H233" t="s">
+        <v>78</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="L233">
+        <v>4</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="N233">
+        <v>5</v>
+      </c>
+      <c r="O233" t="s">
+        <v>246</v>
+      </c>
+      <c r="P233" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q233">
+        <v>2.75</v>
+      </c>
+      <c r="R233">
+        <v>2.3</v>
+      </c>
+      <c r="S233">
+        <v>3.6</v>
+      </c>
+      <c r="T233">
+        <v>1.33</v>
+      </c>
+      <c r="U233">
+        <v>3.25</v>
+      </c>
+      <c r="V233">
+        <v>2.5</v>
+      </c>
+      <c r="W233">
+        <v>1.5</v>
+      </c>
+      <c r="X233">
+        <v>6.5</v>
+      </c>
+      <c r="Y233">
+        <v>1.11</v>
+      </c>
+      <c r="Z233">
+        <v>2.12</v>
+      </c>
+      <c r="AA233">
+        <v>3.5</v>
+      </c>
+      <c r="AB233">
+        <v>3.2</v>
+      </c>
+      <c r="AC233">
+        <v>0</v>
+      </c>
+      <c r="AD233">
+        <v>0</v>
+      </c>
+      <c r="AE233">
+        <v>0</v>
+      </c>
+      <c r="AF233">
+        <v>0</v>
+      </c>
+      <c r="AG233">
+        <v>1.61</v>
+      </c>
+      <c r="AH233">
+        <v>2.05</v>
+      </c>
+      <c r="AI233">
+        <v>1.57</v>
+      </c>
+      <c r="AJ233">
+        <v>2.25</v>
+      </c>
+      <c r="AK233">
+        <v>0</v>
+      </c>
+      <c r="AL233">
+        <v>0</v>
+      </c>
+      <c r="AM233">
+        <v>0</v>
+      </c>
+      <c r="AN233">
+        <v>1.58</v>
+      </c>
+      <c r="AO233">
+        <v>0.42</v>
+      </c>
+      <c r="AP233">
+        <v>1.69</v>
+      </c>
+      <c r="AQ233">
+        <v>0.38</v>
+      </c>
+      <c r="AR233">
+        <v>1.63</v>
+      </c>
+      <c r="AS233">
+        <v>1.28</v>
+      </c>
+      <c r="AT233">
+        <v>2.91</v>
+      </c>
+      <c r="AU233">
+        <v>8</v>
+      </c>
+      <c r="AV233">
+        <v>8</v>
+      </c>
+      <c r="AW233">
+        <v>7</v>
+      </c>
+      <c r="AX233">
+        <v>9</v>
+      </c>
+      <c r="AY233">
+        <v>19</v>
+      </c>
+      <c r="AZ233">
+        <v>19</v>
+      </c>
+      <c r="BA233">
+        <v>3</v>
+      </c>
+      <c r="BB233">
+        <v>6</v>
+      </c>
+      <c r="BC233">
+        <v>9</v>
+      </c>
+      <c r="BD233">
+        <v>0</v>
+      </c>
+      <c r="BE233">
+        <v>0</v>
+      </c>
+      <c r="BF233">
+        <v>0</v>
+      </c>
+      <c r="BG233">
+        <v>0</v>
+      </c>
+      <c r="BH233">
+        <v>0</v>
+      </c>
+      <c r="BI233">
+        <v>0</v>
+      </c>
+      <c r="BJ233">
+        <v>0</v>
+      </c>
+      <c r="BK233">
+        <v>2.1</v>
+      </c>
+      <c r="BL233">
+        <v>0</v>
+      </c>
+      <c r="BM233">
+        <v>0</v>
+      </c>
+      <c r="BN233">
+        <v>0</v>
+      </c>
+      <c r="BO233">
+        <v>0</v>
+      </c>
+      <c r="BP233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7450874</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45746.52083333334</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>72</v>
+      </c>
+      <c r="H234" t="s">
+        <v>87</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>3</v>
+      </c>
+      <c r="O234" t="s">
+        <v>247</v>
+      </c>
+      <c r="P234" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q234">
+        <v>2.88</v>
+      </c>
+      <c r="R234">
+        <v>2.2</v>
+      </c>
+      <c r="S234">
+        <v>3.6</v>
+      </c>
+      <c r="T234">
+        <v>1.36</v>
+      </c>
+      <c r="U234">
+        <v>3</v>
+      </c>
+      <c r="V234">
+        <v>2.75</v>
+      </c>
+      <c r="W234">
+        <v>1.4</v>
+      </c>
+      <c r="X234">
+        <v>8</v>
+      </c>
+      <c r="Y234">
+        <v>1.08</v>
+      </c>
+      <c r="Z234">
+        <v>2.21</v>
+      </c>
+      <c r="AA234">
+        <v>3.41</v>
+      </c>
+      <c r="AB234">
+        <v>3.07</v>
+      </c>
+      <c r="AC234">
+        <v>0</v>
+      </c>
+      <c r="AD234">
+        <v>0</v>
+      </c>
+      <c r="AE234">
+        <v>0</v>
+      </c>
+      <c r="AF234">
+        <v>0</v>
+      </c>
+      <c r="AG234">
+        <v>1.8</v>
+      </c>
+      <c r="AH234">
+        <v>1.94</v>
+      </c>
+      <c r="AI234">
+        <v>1.7</v>
+      </c>
+      <c r="AJ234">
+        <v>2.05</v>
+      </c>
+      <c r="AK234">
+        <v>0</v>
+      </c>
+      <c r="AL234">
+        <v>0</v>
+      </c>
+      <c r="AM234">
+        <v>0</v>
+      </c>
+      <c r="AN234">
+        <v>1.58</v>
+      </c>
+      <c r="AO234">
+        <v>1.42</v>
+      </c>
+      <c r="AP234">
+        <v>1.69</v>
+      </c>
+      <c r="AQ234">
+        <v>1.31</v>
+      </c>
+      <c r="AR234">
+        <v>1.63</v>
+      </c>
+      <c r="AS234">
+        <v>1.33</v>
+      </c>
+      <c r="AT234">
+        <v>2.96</v>
+      </c>
+      <c r="AU234">
+        <v>5</v>
+      </c>
+      <c r="AV234">
+        <v>8</v>
+      </c>
+      <c r="AW234">
+        <v>9</v>
+      </c>
+      <c r="AX234">
+        <v>9</v>
+      </c>
+      <c r="AY234">
+        <v>16</v>
+      </c>
+      <c r="AZ234">
+        <v>21</v>
+      </c>
+      <c r="BA234">
+        <v>4</v>
+      </c>
+      <c r="BB234">
+        <v>9</v>
+      </c>
+      <c r="BC234">
+        <v>13</v>
+      </c>
+      <c r="BD234">
+        <v>0</v>
+      </c>
+      <c r="BE234">
+        <v>0</v>
+      </c>
+      <c r="BF234">
+        <v>0</v>
+      </c>
+      <c r="BG234">
+        <v>0</v>
+      </c>
+      <c r="BH234">
+        <v>0</v>
+      </c>
+      <c r="BI234">
+        <v>0</v>
+      </c>
+      <c r="BJ234">
+        <v>0</v>
+      </c>
+      <c r="BK234">
+        <v>2.1</v>
+      </c>
+      <c r="BL234">
+        <v>0</v>
+      </c>
+      <c r="BM234">
+        <v>0</v>
+      </c>
+      <c r="BN234">
+        <v>0</v>
+      </c>
+      <c r="BO234">
+        <v>0</v>
+      </c>
+      <c r="BP234">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="354">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1074,6 +1074,9 @@
   <si>
     <t>['51']</t>
   </si>
+  <si>
+    <t>['77', '90+3']</t>
+  </si>
 </sst>
 </file>
 
@@ -1434,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3213,7 +3216,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ9">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4652,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -5476,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ20">
         <v>0.64</v>
@@ -5891,7 +5894,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ22">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR22">
         <v>2.03</v>
@@ -9390,7 +9393,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ39">
         <v>1.31</v>
@@ -10217,7 +10220,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ43">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10835,7 +10838,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ46">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR46">
         <v>1.21</v>
@@ -13098,7 +13101,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ57">
         <v>1.08</v>
@@ -15779,7 +15782,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ70">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -19072,7 +19075,7 @@
         <v>0.75</v>
       </c>
       <c r="AP86">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ86">
         <v>1.15</v>
@@ -20517,7 +20520,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ93">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR93">
         <v>1.66</v>
@@ -22368,7 +22371,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ102">
         <v>1.62</v>
@@ -24431,7 +24434,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ112">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR112">
         <v>1.59</v>
@@ -27312,7 +27315,7 @@
         <v>0.33</v>
       </c>
       <c r="AP126">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ126">
         <v>0.54</v>
@@ -28963,7 +28966,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ134">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR134">
         <v>1.7</v>
@@ -29372,7 +29375,7 @@
         <v>1.43</v>
       </c>
       <c r="AP136">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ136">
         <v>1.31</v>
@@ -32053,7 +32056,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ149">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR149">
         <v>1.41</v>
@@ -34522,7 +34525,7 @@
         <v>1.25</v>
       </c>
       <c r="AP161">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ161">
         <v>1.08</v>
@@ -35761,7 +35764,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ167">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -39057,7 +39060,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ183">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR183">
         <v>2.02</v>
@@ -40496,7 +40499,7 @@
         <v>0.7</v>
       </c>
       <c r="AP190">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ190">
         <v>0.77</v>
@@ -43380,7 +43383,7 @@
         <v>1.36</v>
       </c>
       <c r="AP204">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ204">
         <v>1.38</v>
@@ -45031,7 +45034,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ212">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR212">
         <v>1.62</v>
@@ -47500,7 +47503,7 @@
         <v>1.25</v>
       </c>
       <c r="AP224">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ224">
         <v>1.23</v>
@@ -49639,6 +49642,212 @@
       </c>
       <c r="BP234">
         <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7450875</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>83</v>
+      </c>
+      <c r="H235" t="s">
+        <v>86</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>2</v>
+      </c>
+      <c r="N235">
+        <v>2</v>
+      </c>
+      <c r="O235" t="s">
+        <v>95</v>
+      </c>
+      <c r="P235" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q235">
+        <v>4.33</v>
+      </c>
+      <c r="R235">
+        <v>2.05</v>
+      </c>
+      <c r="S235">
+        <v>2.75</v>
+      </c>
+      <c r="T235">
+        <v>1.44</v>
+      </c>
+      <c r="U235">
+        <v>2.63</v>
+      </c>
+      <c r="V235">
+        <v>3.25</v>
+      </c>
+      <c r="W235">
+        <v>1.33</v>
+      </c>
+      <c r="X235">
+        <v>10</v>
+      </c>
+      <c r="Y235">
+        <v>1.06</v>
+      </c>
+      <c r="Z235">
+        <v>3.77</v>
+      </c>
+      <c r="AA235">
+        <v>3.21</v>
+      </c>
+      <c r="AB235">
+        <v>2.03</v>
+      </c>
+      <c r="AC235">
+        <v>1.07</v>
+      </c>
+      <c r="AD235">
+        <v>8</v>
+      </c>
+      <c r="AE235">
+        <v>1.38</v>
+      </c>
+      <c r="AF235">
+        <v>3</v>
+      </c>
+      <c r="AG235">
+        <v>2.05</v>
+      </c>
+      <c r="AH235">
+        <v>1.65</v>
+      </c>
+      <c r="AI235">
+        <v>1.95</v>
+      </c>
+      <c r="AJ235">
+        <v>1.8</v>
+      </c>
+      <c r="AK235">
+        <v>1.85</v>
+      </c>
+      <c r="AL235">
+        <v>1.31</v>
+      </c>
+      <c r="AM235">
+        <v>1.23</v>
+      </c>
+      <c r="AN235">
+        <v>1.17</v>
+      </c>
+      <c r="AO235">
+        <v>2.33</v>
+      </c>
+      <c r="AP235">
+        <v>1.08</v>
+      </c>
+      <c r="AQ235">
+        <v>2.38</v>
+      </c>
+      <c r="AR235">
+        <v>1.76</v>
+      </c>
+      <c r="AS235">
+        <v>1.46</v>
+      </c>
+      <c r="AT235">
+        <v>3.22</v>
+      </c>
+      <c r="AU235">
+        <v>3</v>
+      </c>
+      <c r="AV235">
+        <v>7</v>
+      </c>
+      <c r="AW235">
+        <v>7</v>
+      </c>
+      <c r="AX235">
+        <v>14</v>
+      </c>
+      <c r="AY235">
+        <v>12</v>
+      </c>
+      <c r="AZ235">
+        <v>29</v>
+      </c>
+      <c r="BA235">
+        <v>4</v>
+      </c>
+      <c r="BB235">
+        <v>12</v>
+      </c>
+      <c r="BC235">
+        <v>16</v>
+      </c>
+      <c r="BD235">
+        <v>2.15</v>
+      </c>
+      <c r="BE235">
+        <v>8.5</v>
+      </c>
+      <c r="BF235">
+        <v>1.85</v>
+      </c>
+      <c r="BG235">
+        <v>1.2</v>
+      </c>
+      <c r="BH235">
+        <v>3.68</v>
+      </c>
+      <c r="BI235">
+        <v>1.41</v>
+      </c>
+      <c r="BJ235">
+        <v>2.6</v>
+      </c>
+      <c r="BK235">
+        <v>1.77</v>
+      </c>
+      <c r="BL235">
+        <v>1.93</v>
+      </c>
+      <c r="BM235">
+        <v>2.19</v>
+      </c>
+      <c r="BN235">
+        <v>1.57</v>
+      </c>
+      <c r="BO235">
+        <v>2.88</v>
+      </c>
+      <c r="BP235">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="356">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,12 @@
     <t>['38', '90+11']</t>
   </si>
   <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['39', '45+2']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1437,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP235"/>
+  <dimension ref="A1:BP237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1980,7 +1986,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ3">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2105,7 +2111,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2723,7 +2729,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3135,7 +3141,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3419,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3547,7 +3553,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3753,7 +3759,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3959,7 +3965,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4037,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ13">
         <v>1.08</v>
@@ -4165,7 +4171,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4371,7 +4377,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4449,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ15">
         <v>1.31</v>
@@ -4577,7 +4583,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5276,7 +5282,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ19">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5813,7 +5819,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6306,7 +6312,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ24">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR24">
         <v>1.69</v>
@@ -6431,7 +6437,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6637,7 +6643,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6843,7 +6849,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -7049,7 +7055,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7461,7 +7467,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7542,7 +7548,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ30">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR30">
         <v>0.86</v>
@@ -7873,7 +7879,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8079,7 +8085,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8363,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ34">
         <v>0.54</v>
@@ -8491,7 +8497,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8778,7 +8784,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ36">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR36">
         <v>1.51</v>
@@ -9109,7 +9115,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9190,7 +9196,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ38">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR38">
         <v>1.85</v>
@@ -9315,7 +9321,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9933,7 +9939,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10423,7 +10429,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ44">
         <v>1.38</v>
@@ -10551,7 +10557,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10629,7 +10635,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ45">
         <v>1.15</v>
@@ -10757,7 +10763,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11169,7 +11175,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11581,7 +11587,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12405,7 +12411,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12611,7 +12617,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12689,7 +12695,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ55">
         <v>1.31</v>
@@ -13229,7 +13235,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13310,7 +13316,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ58">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR58">
         <v>1.71</v>
@@ -13435,7 +13441,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13516,7 +13522,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ59">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR59">
         <v>1.38</v>
@@ -13641,7 +13647,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13847,7 +13853,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14465,7 +14471,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14877,7 +14883,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -16319,7 +16325,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16400,7 +16406,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ73">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR73">
         <v>1.47</v>
@@ -16525,7 +16531,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16606,7 +16612,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ74">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -16809,7 +16815,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ75">
         <v>1.38</v>
@@ -17221,7 +17227,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ77">
         <v>1.31</v>
@@ -17761,7 +17767,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -19203,7 +19209,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19409,7 +19415,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19615,7 +19621,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19821,7 +19827,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -20027,7 +20033,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20105,7 +20111,7 @@
         <v>0.6</v>
       </c>
       <c r="AP91">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ91">
         <v>1.23</v>
@@ -20311,10 +20317,10 @@
         <v>0.8</v>
       </c>
       <c r="AP92">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ92">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -20439,7 +20445,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20645,7 +20651,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20851,7 +20857,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21057,7 +21063,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21138,7 +21144,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ96">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21675,7 +21681,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21881,7 +21887,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -22087,7 +22093,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22293,7 +22299,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22499,7 +22505,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22911,7 +22917,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23529,7 +23535,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23735,7 +23741,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -23816,7 +23822,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ109">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -24147,7 +24153,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24765,7 +24771,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24843,7 +24849,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ114">
         <v>0.6899999999999999</v>
@@ -25177,7 +25183,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25255,7 +25261,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ116">
         <v>1.31</v>
@@ -25383,7 +25389,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25795,7 +25801,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26413,7 +26419,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26619,7 +26625,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -26700,7 +26706,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ123">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR123">
         <v>1.23</v>
@@ -27031,7 +27037,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27443,7 +27449,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27649,7 +27655,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27936,7 +27942,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ129">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR129">
         <v>1.39</v>
@@ -28061,7 +28067,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28345,7 +28351,7 @@
         <v>0.71</v>
       </c>
       <c r="AP131">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ131">
         <v>0.6899999999999999</v>
@@ -28473,7 +28479,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28757,7 +28763,7 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ133">
         <v>0.64</v>
@@ -28885,7 +28891,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29091,7 +29097,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29297,7 +29303,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29503,7 +29509,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29709,7 +29715,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30121,7 +30127,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30202,7 +30208,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ140">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR140">
         <v>1.69</v>
@@ -30327,7 +30333,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31850,7 +31856,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ148">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR148">
         <v>1.73</v>
@@ -31975,7 +31981,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32053,7 +32059,7 @@
         <v>2.25</v>
       </c>
       <c r="AP149">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ149">
         <v>2.38</v>
@@ -32181,7 +32187,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32593,7 +32599,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32671,7 +32677,7 @@
         <v>1.29</v>
       </c>
       <c r="AP152">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -33701,7 +33707,7 @@
         <v>0.5</v>
       </c>
       <c r="AP157">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ157">
         <v>0.38</v>
@@ -33829,7 +33835,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34116,7 +34122,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ159">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR159">
         <v>1.47</v>
@@ -34241,7 +34247,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34447,7 +34453,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34859,7 +34865,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35271,7 +35277,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35558,7 +35564,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ166">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR166">
         <v>1.68</v>
@@ -36507,7 +36513,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36713,7 +36719,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36997,7 +37003,7 @@
         <v>1.89</v>
       </c>
       <c r="AP173">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ173">
         <v>1.62</v>
@@ -37537,7 +37543,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -38155,7 +38161,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38233,10 +38239,10 @@
         <v>2.11</v>
       </c>
       <c r="AP179">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ179">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR179">
         <v>1.4</v>
@@ -38567,7 +38573,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38773,7 +38779,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39391,7 +39397,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39803,7 +39809,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -39881,7 +39887,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP187">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ187">
         <v>1</v>
@@ -40421,7 +40427,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40502,7 +40508,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ190">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR190">
         <v>1.75</v>
@@ -40627,7 +40633,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41245,7 +41251,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41323,7 +41329,7 @@
         <v>0.8</v>
       </c>
       <c r="AP194">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ194">
         <v>1</v>
@@ -41657,7 +41663,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41863,7 +41869,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42275,7 +42281,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42768,7 +42774,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ201">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR201">
         <v>1.93</v>
@@ -42971,7 +42977,7 @@
         <v>1.09</v>
       </c>
       <c r="AP202">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ202">
         <v>1.23</v>
@@ -43099,7 +43105,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43305,7 +43311,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43511,7 +43517,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -44210,7 +44216,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ208">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR208">
         <v>1.66</v>
@@ -44335,7 +44341,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44747,7 +44753,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44953,7 +44959,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -45571,7 +45577,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45777,7 +45783,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -45855,7 +45861,7 @@
         <v>1.64</v>
       </c>
       <c r="AP216">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ216">
         <v>1.62</v>
@@ -46189,7 +46195,7 @@
         <v>234</v>
       </c>
       <c r="P218" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q218">
         <v>2.55</v>
@@ -46270,7 +46276,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ218">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR218">
         <v>1.64</v>
@@ -46395,7 +46401,7 @@
         <v>235</v>
       </c>
       <c r="P219" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q219">
         <v>2.35</v>
@@ -46476,7 +46482,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ219">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR219">
         <v>1.79</v>
@@ -46601,7 +46607,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q220">
         <v>2.88</v>
@@ -46679,7 +46685,7 @@
         <v>0.33</v>
       </c>
       <c r="AP220">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ220">
         <v>0.54</v>
@@ -47091,7 +47097,7 @@
         <v>1.17</v>
       </c>
       <c r="AP222">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ222">
         <v>1.08</v>
@@ -47631,7 +47637,7 @@
         <v>240</v>
       </c>
       <c r="P225" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q225">
         <v>2.88</v>
@@ -47837,7 +47843,7 @@
         <v>241</v>
       </c>
       <c r="P226" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q226">
         <v>3.2</v>
@@ -48043,7 +48049,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48455,7 +48461,7 @@
         <v>242</v>
       </c>
       <c r="P229" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q229">
         <v>2.3</v>
@@ -49073,7 +49079,7 @@
         <v>245</v>
       </c>
       <c r="P232" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49279,7 +49285,7 @@
         <v>246</v>
       </c>
       <c r="P233" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q233">
         <v>2.75</v>
@@ -49485,7 +49491,7 @@
         <v>247</v>
       </c>
       <c r="P234" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49691,7 +49697,7 @@
         <v>95</v>
       </c>
       <c r="P235" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q235">
         <v>4.33</v>
@@ -49848,6 +49854,418 @@
       </c>
       <c r="BP235">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7450888</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45751.54166666666</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>78</v>
+      </c>
+      <c r="H236" t="s">
+        <v>75</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>1</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="N236">
+        <v>2</v>
+      </c>
+      <c r="O236" t="s">
+        <v>248</v>
+      </c>
+      <c r="P236" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q236">
+        <v>3.1</v>
+      </c>
+      <c r="R236">
+        <v>2.2</v>
+      </c>
+      <c r="S236">
+        <v>3.4</v>
+      </c>
+      <c r="T236">
+        <v>1.4</v>
+      </c>
+      <c r="U236">
+        <v>2.75</v>
+      </c>
+      <c r="V236">
+        <v>2.75</v>
+      </c>
+      <c r="W236">
+        <v>1.4</v>
+      </c>
+      <c r="X236">
+        <v>8</v>
+      </c>
+      <c r="Y236">
+        <v>1.08</v>
+      </c>
+      <c r="Z236">
+        <v>2.41</v>
+      </c>
+      <c r="AA236">
+        <v>3.28</v>
+      </c>
+      <c r="AB236">
+        <v>2.86</v>
+      </c>
+      <c r="AC236">
+        <v>1.06</v>
+      </c>
+      <c r="AD236">
+        <v>8.5</v>
+      </c>
+      <c r="AE236">
+        <v>1.3</v>
+      </c>
+      <c r="AF236">
+        <v>3.45</v>
+      </c>
+      <c r="AG236">
+        <v>1.87</v>
+      </c>
+      <c r="AH236">
+        <v>1.87</v>
+      </c>
+      <c r="AI236">
+        <v>1.7</v>
+      </c>
+      <c r="AJ236">
+        <v>2.05</v>
+      </c>
+      <c r="AK236">
+        <v>1.43</v>
+      </c>
+      <c r="AL236">
+        <v>1.3</v>
+      </c>
+      <c r="AM236">
+        <v>1.52</v>
+      </c>
+      <c r="AN236">
+        <v>1.38</v>
+      </c>
+      <c r="AO236">
+        <v>1.92</v>
+      </c>
+      <c r="AP236">
+        <v>1.36</v>
+      </c>
+      <c r="AQ236">
+        <v>1.85</v>
+      </c>
+      <c r="AR236">
+        <v>1.6</v>
+      </c>
+      <c r="AS236">
+        <v>1.53</v>
+      </c>
+      <c r="AT236">
+        <v>3.13</v>
+      </c>
+      <c r="AU236">
+        <v>6</v>
+      </c>
+      <c r="AV236">
+        <v>8</v>
+      </c>
+      <c r="AW236">
+        <v>4</v>
+      </c>
+      <c r="AX236">
+        <v>10</v>
+      </c>
+      <c r="AY236">
+        <v>11</v>
+      </c>
+      <c r="AZ236">
+        <v>19</v>
+      </c>
+      <c r="BA236">
+        <v>7</v>
+      </c>
+      <c r="BB236">
+        <v>3</v>
+      </c>
+      <c r="BC236">
+        <v>10</v>
+      </c>
+      <c r="BD236">
+        <v>1.94</v>
+      </c>
+      <c r="BE236">
+        <v>6.4</v>
+      </c>
+      <c r="BF236">
+        <v>2.07</v>
+      </c>
+      <c r="BG236">
+        <v>1.33</v>
+      </c>
+      <c r="BH236">
+        <v>2.88</v>
+      </c>
+      <c r="BI236">
+        <v>1.58</v>
+      </c>
+      <c r="BJ236">
+        <v>2.14</v>
+      </c>
+      <c r="BK236">
+        <v>1.95</v>
+      </c>
+      <c r="BL236">
+        <v>1.71</v>
+      </c>
+      <c r="BM236">
+        <v>2.48</v>
+      </c>
+      <c r="BN236">
+        <v>1.43</v>
+      </c>
+      <c r="BO236">
+        <v>3.3</v>
+      </c>
+      <c r="BP236">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7450889</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45751.64583333334</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>82</v>
+      </c>
+      <c r="H237" t="s">
+        <v>80</v>
+      </c>
+      <c r="I237">
+        <v>2</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>2</v>
+      </c>
+      <c r="L237">
+        <v>2</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>2</v>
+      </c>
+      <c r="O237" t="s">
+        <v>249</v>
+      </c>
+      <c r="P237" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q237">
+        <v>2.75</v>
+      </c>
+      <c r="R237">
+        <v>2.3</v>
+      </c>
+      <c r="S237">
+        <v>3.6</v>
+      </c>
+      <c r="T237">
+        <v>1.33</v>
+      </c>
+      <c r="U237">
+        <v>3.25</v>
+      </c>
+      <c r="V237">
+        <v>2.5</v>
+      </c>
+      <c r="W237">
+        <v>1.5</v>
+      </c>
+      <c r="X237">
+        <v>6.5</v>
+      </c>
+      <c r="Y237">
+        <v>1.11</v>
+      </c>
+      <c r="Z237">
+        <v>2.32</v>
+      </c>
+      <c r="AA237">
+        <v>3.33</v>
+      </c>
+      <c r="AB237">
+        <v>2.95</v>
+      </c>
+      <c r="AC237">
+        <v>1.05</v>
+      </c>
+      <c r="AD237">
+        <v>9.5</v>
+      </c>
+      <c r="AE237">
+        <v>1.22</v>
+      </c>
+      <c r="AF237">
+        <v>4.2</v>
+      </c>
+      <c r="AG237">
+        <v>1.8</v>
+      </c>
+      <c r="AH237">
+        <v>1.94</v>
+      </c>
+      <c r="AI237">
+        <v>1.57</v>
+      </c>
+      <c r="AJ237">
+        <v>2.25</v>
+      </c>
+      <c r="AK237">
+        <v>1.34</v>
+      </c>
+      <c r="AL237">
+        <v>1.28</v>
+      </c>
+      <c r="AM237">
+        <v>1.68</v>
+      </c>
+      <c r="AN237">
+        <v>1.54</v>
+      </c>
+      <c r="AO237">
+        <v>0.77</v>
+      </c>
+      <c r="AP237">
+        <v>1.64</v>
+      </c>
+      <c r="AQ237">
+        <v>0.71</v>
+      </c>
+      <c r="AR237">
+        <v>1.47</v>
+      </c>
+      <c r="AS237">
+        <v>1.34</v>
+      </c>
+      <c r="AT237">
+        <v>2.81</v>
+      </c>
+      <c r="AU237">
+        <v>8</v>
+      </c>
+      <c r="AV237">
+        <v>4</v>
+      </c>
+      <c r="AW237">
+        <v>5</v>
+      </c>
+      <c r="AX237">
+        <v>5</v>
+      </c>
+      <c r="AY237">
+        <v>16</v>
+      </c>
+      <c r="AZ237">
+        <v>10</v>
+      </c>
+      <c r="BA237">
+        <v>4</v>
+      </c>
+      <c r="BB237">
+        <v>5</v>
+      </c>
+      <c r="BC237">
+        <v>9</v>
+      </c>
+      <c r="BD237">
+        <v>1.66</v>
+      </c>
+      <c r="BE237">
+        <v>6.5</v>
+      </c>
+      <c r="BF237">
+        <v>2.48</v>
+      </c>
+      <c r="BG237">
+        <v>1.33</v>
+      </c>
+      <c r="BH237">
+        <v>2.88</v>
+      </c>
+      <c r="BI237">
+        <v>1.58</v>
+      </c>
+      <c r="BJ237">
+        <v>2.15</v>
+      </c>
+      <c r="BK237">
+        <v>1.96</v>
+      </c>
+      <c r="BL237">
+        <v>1.7</v>
+      </c>
+      <c r="BM237">
+        <v>2.5</v>
+      </c>
+      <c r="BN237">
+        <v>1.43</v>
+      </c>
+      <c r="BO237">
+        <v>3.25</v>
+      </c>
+      <c r="BP237">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -766,6 +766,12 @@
     <t>['39', '45+2']</t>
   </si>
   <si>
+    <t>['20']</t>
+  </si>
+  <si>
+    <t>['30', '83']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1052,9 +1058,6 @@
   </si>
   <si>
     <t>['48', '59']</t>
-  </si>
-  <si>
-    <t>['20']</t>
   </si>
   <si>
     <t>['5', '11']</t>
@@ -1443,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP237"/>
+  <dimension ref="A1:BP240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1983,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ3">
         <v>0.71</v>
@@ -2111,7 +2114,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2398,7 +2401,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ5">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2604,7 +2607,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ6">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2729,7 +2732,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3013,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ8">
         <v>1.31</v>
@@ -3141,7 +3144,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3553,7 +3556,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3759,7 +3762,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3840,7 +3843,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ12">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3965,7 +3968,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4171,7 +4174,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4249,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ14">
         <v>1.62</v>
@@ -4377,7 +4380,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4583,7 +4586,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5819,7 +5822,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6309,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ24">
         <v>0.71</v>
@@ -6437,7 +6440,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6518,7 +6521,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ25">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR25">
         <v>1</v>
@@ -6643,7 +6646,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6849,7 +6852,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -7055,7 +7058,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7133,7 +7136,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ28">
         <v>1.31</v>
@@ -7467,7 +7470,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7879,7 +7882,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7960,7 +7963,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ32">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR32">
         <v>1.13</v>
@@ -8085,7 +8088,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8497,7 +8500,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8990,7 +8993,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ37">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR37">
         <v>1.91</v>
@@ -9115,7 +9118,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9321,7 +9324,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9811,10 +9814,10 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ41">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR41">
         <v>2.02</v>
@@ -9939,7 +9942,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10557,7 +10560,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10763,7 +10766,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11175,7 +11178,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11462,7 +11465,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ49">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11587,7 +11590,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -11871,7 +11874,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -12077,7 +12080,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ52">
         <v>1.08</v>
@@ -12411,7 +12414,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12617,7 +12620,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -12904,7 +12907,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ56">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -13235,7 +13238,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13313,7 +13316,7 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ58">
         <v>1.85</v>
@@ -13441,7 +13444,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13647,7 +13650,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13728,7 +13731,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ60">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR60">
         <v>1.47</v>
@@ -13853,7 +13856,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -14471,7 +14474,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14883,7 +14886,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -15167,7 +15170,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ67">
         <v>1.62</v>
@@ -15582,7 +15585,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ69">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR69">
         <v>1.25</v>
@@ -15991,10 +15994,10 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16325,7 +16328,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16531,7 +16534,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -17230,7 +17233,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ77">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR77">
         <v>1.21</v>
@@ -17436,7 +17439,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ78">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR78">
         <v>1.53</v>
@@ -17639,7 +17642,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ79">
         <v>0.54</v>
@@ -17767,7 +17770,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -19209,7 +19212,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19415,7 +19418,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19621,7 +19624,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19827,7 +19830,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -20033,7 +20036,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20114,7 +20117,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ91">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20445,7 +20448,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20523,7 +20526,7 @@
         <v>2.6</v>
       </c>
       <c r="AP93">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ93">
         <v>2.38</v>
@@ -20651,7 +20654,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20732,7 +20735,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ94">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR94">
         <v>1.85</v>
@@ -20857,7 +20860,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20935,10 +20938,10 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ95">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR95">
         <v>1.94</v>
@@ -21063,7 +21066,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21141,7 +21144,7 @@
         <v>2.4</v>
       </c>
       <c r="AP96">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ96">
         <v>1.85</v>
@@ -21681,7 +21684,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21887,7 +21890,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -22093,7 +22096,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22299,7 +22302,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22505,7 +22508,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22917,7 +22920,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -23407,7 +23410,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ107">
         <v>0.64</v>
@@ -23535,7 +23538,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23613,7 +23616,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ108">
         <v>0.38</v>
@@ -23741,7 +23744,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24153,7 +24156,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24234,7 +24237,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ111">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR111">
         <v>1.46</v>
@@ -24437,7 +24440,7 @@
         <v>2.67</v>
       </c>
       <c r="AP112">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ112">
         <v>2.38</v>
@@ -24643,7 +24646,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ113">
         <v>1.15</v>
@@ -24771,7 +24774,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -24852,7 +24855,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ114">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR114">
         <v>1.55</v>
@@ -25058,7 +25061,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ115">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25183,7 +25186,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25389,7 +25392,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25801,7 +25804,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26291,7 +26294,7 @@
         <v>1.43</v>
       </c>
       <c r="AP121">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ121">
         <v>1.38</v>
@@ -26419,7 +26422,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26625,7 +26628,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -27037,7 +27040,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27118,7 +27121,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ125">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR125">
         <v>1.75</v>
@@ -27449,7 +27452,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27530,7 +27533,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ127">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -27655,7 +27658,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -28067,7 +28070,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28354,7 +28357,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ131">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28479,7 +28482,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28557,7 +28560,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ132">
         <v>1.31</v>
@@ -28891,7 +28894,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -29097,7 +29100,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29175,7 +29178,7 @@
         <v>1.5</v>
       </c>
       <c r="AP135">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ135">
         <v>1.08</v>
@@ -29303,7 +29306,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29384,7 +29387,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ136">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29509,7 +29512,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29715,7 +29718,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -29999,7 +30002,7 @@
         <v>1.43</v>
       </c>
       <c r="AP139">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ139">
         <v>1.08</v>
@@ -30127,7 +30130,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30333,7 +30336,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30411,7 +30414,7 @@
         <v>0.14</v>
       </c>
       <c r="AP141">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ141">
         <v>0.38</v>
@@ -30620,7 +30623,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ142">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR142">
         <v>1.61</v>
@@ -31238,7 +31241,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ145">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR145">
         <v>1.63</v>
@@ -31647,7 +31650,7 @@
         <v>0.25</v>
       </c>
       <c r="AP147">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ147">
         <v>0.64</v>
@@ -31981,7 +31984,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32187,7 +32190,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32599,7 +32602,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -33089,7 +33092,7 @@
         <v>1.25</v>
       </c>
       <c r="AP154">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ154">
         <v>1.08</v>
@@ -33835,7 +33838,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -33916,7 +33919,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ158">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR158">
         <v>1.55</v>
@@ -34247,7 +34250,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34453,7 +34456,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34865,7 +34868,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -34943,7 +34946,7 @@
         <v>0.75</v>
       </c>
       <c r="AP163">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ163">
         <v>1.15</v>
@@ -35277,7 +35280,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35355,7 +35358,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ165">
         <v>1</v>
@@ -35976,7 +35979,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ168">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR168">
         <v>1.8</v>
@@ -36513,7 +36516,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36594,7 +36597,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ171">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR171">
         <v>1.72</v>
@@ -36719,7 +36722,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36797,7 +36800,7 @@
         <v>1.22</v>
       </c>
       <c r="AP172">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ172">
         <v>1.38</v>
@@ -37415,7 +37418,7 @@
         <v>0.33</v>
       </c>
       <c r="AP175">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ175">
         <v>0.54</v>
@@ -37543,7 +37546,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -38036,7 +38039,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ178">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR178">
         <v>1.4</v>
@@ -38161,7 +38164,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38573,7 +38576,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38654,7 +38657,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ181">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR181">
         <v>1.46</v>
@@ -38779,7 +38782,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -38860,7 +38863,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ182">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR182">
         <v>1.68</v>
@@ -39063,7 +39066,7 @@
         <v>2.2</v>
       </c>
       <c r="AP183">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ183">
         <v>2.38</v>
@@ -39269,7 +39272,7 @@
         <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ184">
         <v>1</v>
@@ -39397,7 +39400,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39809,7 +39812,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40302,7 +40305,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ189">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR189">
         <v>1.82</v>
@@ -40427,7 +40430,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40633,7 +40636,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41251,7 +41254,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41535,7 +41538,7 @@
         <v>1.3</v>
       </c>
       <c r="AP195">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ195">
         <v>1.08</v>
@@ -41663,7 +41666,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41869,7 +41872,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42153,10 +42156,10 @@
         <v>0.82</v>
       </c>
       <c r="AP198">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ198">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR198">
         <v>1.96</v>
@@ -42281,7 +42284,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42565,7 +42568,7 @@
         <v>0.82</v>
       </c>
       <c r="AP200">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ200">
         <v>1</v>
@@ -42980,7 +42983,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ202">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR202">
         <v>1.62</v>
@@ -43105,7 +43108,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43311,7 +43314,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43517,7 +43520,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -43598,7 +43601,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ205">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR205">
         <v>1.46</v>
@@ -44341,7 +44344,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44625,7 +44628,7 @@
         <v>1</v>
       </c>
       <c r="AP210">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ210">
         <v>1</v>
@@ -44753,7 +44756,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44959,7 +44962,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -45243,7 +45246,7 @@
         <v>0.45</v>
       </c>
       <c r="AP213">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ213">
         <v>0.38</v>
@@ -45452,7 +45455,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ214">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR214">
         <v>1.68</v>
@@ -45577,7 +45580,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45783,7 +45786,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -46195,7 +46198,7 @@
         <v>234</v>
       </c>
       <c r="P218" t="s">
-        <v>346</v>
+        <v>250</v>
       </c>
       <c r="Q218">
         <v>2.55</v>
@@ -46273,7 +46276,7 @@
         <v>0.83</v>
       </c>
       <c r="AP218">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ218">
         <v>0.71</v>
@@ -46401,7 +46404,7 @@
         <v>235</v>
       </c>
       <c r="P219" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q219">
         <v>2.35</v>
@@ -46607,7 +46610,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q220">
         <v>2.88</v>
@@ -46894,7 +46897,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ221">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR221">
         <v>1.97</v>
@@ -47512,7 +47515,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ224">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR224">
         <v>1.84</v>
@@ -47637,7 +47640,7 @@
         <v>240</v>
       </c>
       <c r="P225" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q225">
         <v>2.88</v>
@@ -47843,7 +47846,7 @@
         <v>241</v>
       </c>
       <c r="P226" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q226">
         <v>3.2</v>
@@ -48049,7 +48052,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48461,7 +48464,7 @@
         <v>242</v>
       </c>
       <c r="P229" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q229">
         <v>2.3</v>
@@ -48951,7 +48954,7 @@
         <v>1.42</v>
       </c>
       <c r="AP231">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ231">
         <v>1.31</v>
@@ -49079,7 +49082,7 @@
         <v>245</v>
       </c>
       <c r="P232" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49285,7 +49288,7 @@
         <v>246</v>
       </c>
       <c r="P233" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q233">
         <v>2.75</v>
@@ -49491,7 +49494,7 @@
         <v>247</v>
       </c>
       <c r="P234" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49697,7 +49700,7 @@
         <v>95</v>
       </c>
       <c r="P235" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q235">
         <v>4.33</v>
@@ -50266,6 +50269,624 @@
       </c>
       <c r="BP237">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7450887</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45752.40625</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>81</v>
+      </c>
+      <c r="H238" t="s">
+        <v>83</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>1</v>
+      </c>
+      <c r="K238">
+        <v>1</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>1</v>
+      </c>
+      <c r="O238" t="s">
+        <v>95</v>
+      </c>
+      <c r="P238" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q238">
+        <v>3</v>
+      </c>
+      <c r="R238">
+        <v>2.2</v>
+      </c>
+      <c r="S238">
+        <v>3.6</v>
+      </c>
+      <c r="T238">
+        <v>1.4</v>
+      </c>
+      <c r="U238">
+        <v>2.75</v>
+      </c>
+      <c r="V238">
+        <v>3</v>
+      </c>
+      <c r="W238">
+        <v>1.36</v>
+      </c>
+      <c r="X238">
+        <v>8</v>
+      </c>
+      <c r="Y238">
+        <v>1.08</v>
+      </c>
+      <c r="Z238">
+        <v>2.21</v>
+      </c>
+      <c r="AA238">
+        <v>3.23</v>
+      </c>
+      <c r="AB238">
+        <v>3.23</v>
+      </c>
+      <c r="AC238">
+        <v>1.01</v>
+      </c>
+      <c r="AD238">
+        <v>8.5</v>
+      </c>
+      <c r="AE238">
+        <v>1.33</v>
+      </c>
+      <c r="AF238">
+        <v>3.39</v>
+      </c>
+      <c r="AG238">
+        <v>1.85</v>
+      </c>
+      <c r="AH238">
+        <v>1.89</v>
+      </c>
+      <c r="AI238">
+        <v>1.75</v>
+      </c>
+      <c r="AJ238">
+        <v>2</v>
+      </c>
+      <c r="AK238">
+        <v>1.3</v>
+      </c>
+      <c r="AL238">
+        <v>1.34</v>
+      </c>
+      <c r="AM238">
+        <v>1.77</v>
+      </c>
+      <c r="AN238">
+        <v>1.46</v>
+      </c>
+      <c r="AO238">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP238">
+        <v>1.36</v>
+      </c>
+      <c r="AQ238">
+        <v>0.86</v>
+      </c>
+      <c r="AR238">
+        <v>1.65</v>
+      </c>
+      <c r="AS238">
+        <v>1.45</v>
+      </c>
+      <c r="AT238">
+        <v>3.1</v>
+      </c>
+      <c r="AU238">
+        <v>6</v>
+      </c>
+      <c r="AV238">
+        <v>5</v>
+      </c>
+      <c r="AW238">
+        <v>9</v>
+      </c>
+      <c r="AX238">
+        <v>8</v>
+      </c>
+      <c r="AY238">
+        <v>17</v>
+      </c>
+      <c r="AZ238">
+        <v>15</v>
+      </c>
+      <c r="BA238">
+        <v>7</v>
+      </c>
+      <c r="BB238">
+        <v>5</v>
+      </c>
+      <c r="BC238">
+        <v>12</v>
+      </c>
+      <c r="BD238">
+        <v>1.7</v>
+      </c>
+      <c r="BE238">
+        <v>6.8</v>
+      </c>
+      <c r="BF238">
+        <v>2.7</v>
+      </c>
+      <c r="BG238">
+        <v>0</v>
+      </c>
+      <c r="BH238">
+        <v>0</v>
+      </c>
+      <c r="BI238">
+        <v>1.25</v>
+      </c>
+      <c r="BJ238">
+        <v>3.28</v>
+      </c>
+      <c r="BK238">
+        <v>1.53</v>
+      </c>
+      <c r="BL238">
+        <v>2.43</v>
+      </c>
+      <c r="BM238">
+        <v>1.88</v>
+      </c>
+      <c r="BN238">
+        <v>1.92</v>
+      </c>
+      <c r="BO238">
+        <v>2.34</v>
+      </c>
+      <c r="BP238">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7450890</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45752.52083333334</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>71</v>
+      </c>
+      <c r="H239" t="s">
+        <v>77</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>1</v>
+      </c>
+      <c r="N239">
+        <v>2</v>
+      </c>
+      <c r="O239" t="s">
+        <v>250</v>
+      </c>
+      <c r="P239" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q239">
+        <v>2.63</v>
+      </c>
+      <c r="R239">
+        <v>2.25</v>
+      </c>
+      <c r="S239">
+        <v>4</v>
+      </c>
+      <c r="T239">
+        <v>1.36</v>
+      </c>
+      <c r="U239">
+        <v>3</v>
+      </c>
+      <c r="V239">
+        <v>2.63</v>
+      </c>
+      <c r="W239">
+        <v>1.44</v>
+      </c>
+      <c r="X239">
+        <v>7</v>
+      </c>
+      <c r="Y239">
+        <v>1.1</v>
+      </c>
+      <c r="Z239">
+        <v>2.05</v>
+      </c>
+      <c r="AA239">
+        <v>3.33</v>
+      </c>
+      <c r="AB239">
+        <v>3.55</v>
+      </c>
+      <c r="AC239">
+        <v>0</v>
+      </c>
+      <c r="AD239">
+        <v>0</v>
+      </c>
+      <c r="AE239">
+        <v>1.21</v>
+      </c>
+      <c r="AF239">
+        <v>4.61</v>
+      </c>
+      <c r="AG239">
+        <v>1.98</v>
+      </c>
+      <c r="AH239">
+        <v>1.77</v>
+      </c>
+      <c r="AI239">
+        <v>1.67</v>
+      </c>
+      <c r="AJ239">
+        <v>2.1</v>
+      </c>
+      <c r="AK239">
+        <v>1.21</v>
+      </c>
+      <c r="AL239">
+        <v>1.27</v>
+      </c>
+      <c r="AM239">
+        <v>2.17</v>
+      </c>
+      <c r="AN239">
+        <v>1.08</v>
+      </c>
+      <c r="AO239">
+        <v>1.31</v>
+      </c>
+      <c r="AP239">
+        <v>1.07</v>
+      </c>
+      <c r="AQ239">
+        <v>1.29</v>
+      </c>
+      <c r="AR239">
+        <v>1.6</v>
+      </c>
+      <c r="AS239">
+        <v>1.37</v>
+      </c>
+      <c r="AT239">
+        <v>2.97</v>
+      </c>
+      <c r="AU239">
+        <v>5</v>
+      </c>
+      <c r="AV239">
+        <v>5</v>
+      </c>
+      <c r="AW239">
+        <v>6</v>
+      </c>
+      <c r="AX239">
+        <v>15</v>
+      </c>
+      <c r="AY239">
+        <v>15</v>
+      </c>
+      <c r="AZ239">
+        <v>28</v>
+      </c>
+      <c r="BA239">
+        <v>2</v>
+      </c>
+      <c r="BB239">
+        <v>8</v>
+      </c>
+      <c r="BC239">
+        <v>10</v>
+      </c>
+      <c r="BD239">
+        <v>1.68</v>
+      </c>
+      <c r="BE239">
+        <v>6.7</v>
+      </c>
+      <c r="BF239">
+        <v>2.77</v>
+      </c>
+      <c r="BG239">
+        <v>0</v>
+      </c>
+      <c r="BH239">
+        <v>0</v>
+      </c>
+      <c r="BI239">
+        <v>1.45</v>
+      </c>
+      <c r="BJ239">
+        <v>2.65</v>
+      </c>
+      <c r="BK239">
+        <v>1.73</v>
+      </c>
+      <c r="BL239">
+        <v>2.08</v>
+      </c>
+      <c r="BM239">
+        <v>2.13</v>
+      </c>
+      <c r="BN239">
+        <v>1.7</v>
+      </c>
+      <c r="BO239">
+        <v>2.54</v>
+      </c>
+      <c r="BP239">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7450884</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45752.63541666666</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>76</v>
+      </c>
+      <c r="H240" t="s">
+        <v>85</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>2</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>2</v>
+      </c>
+      <c r="O240" t="s">
+        <v>251</v>
+      </c>
+      <c r="P240" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q240">
+        <v>2.05</v>
+      </c>
+      <c r="R240">
+        <v>2.38</v>
+      </c>
+      <c r="S240">
+        <v>6</v>
+      </c>
+      <c r="T240">
+        <v>1.36</v>
+      </c>
+      <c r="U240">
+        <v>3</v>
+      </c>
+      <c r="V240">
+        <v>2.63</v>
+      </c>
+      <c r="W240">
+        <v>1.44</v>
+      </c>
+      <c r="X240">
+        <v>7</v>
+      </c>
+      <c r="Y240">
+        <v>1.1</v>
+      </c>
+      <c r="Z240">
+        <v>1.46</v>
+      </c>
+      <c r="AA240">
+        <v>4.3</v>
+      </c>
+      <c r="AB240">
+        <v>6.6</v>
+      </c>
+      <c r="AC240">
+        <v>1.01</v>
+      </c>
+      <c r="AD240">
+        <v>8.5</v>
+      </c>
+      <c r="AE240">
+        <v>1.37</v>
+      </c>
+      <c r="AF240">
+        <v>3.19</v>
+      </c>
+      <c r="AG240">
+        <v>1.77</v>
+      </c>
+      <c r="AH240">
+        <v>1.98</v>
+      </c>
+      <c r="AI240">
+        <v>1.95</v>
+      </c>
+      <c r="AJ240">
+        <v>1.8</v>
+      </c>
+      <c r="AK240">
+        <v>1.14</v>
+      </c>
+      <c r="AL240">
+        <v>1.26</v>
+      </c>
+      <c r="AM240">
+        <v>2.53</v>
+      </c>
+      <c r="AN240">
+        <v>2.54</v>
+      </c>
+      <c r="AO240">
+        <v>1.23</v>
+      </c>
+      <c r="AP240">
+        <v>2.57</v>
+      </c>
+      <c r="AQ240">
+        <v>1.14</v>
+      </c>
+      <c r="AR240">
+        <v>2</v>
+      </c>
+      <c r="AS240">
+        <v>1.36</v>
+      </c>
+      <c r="AT240">
+        <v>3.36</v>
+      </c>
+      <c r="AU240">
+        <v>5</v>
+      </c>
+      <c r="AV240">
+        <v>6</v>
+      </c>
+      <c r="AW240">
+        <v>9</v>
+      </c>
+      <c r="AX240">
+        <v>11</v>
+      </c>
+      <c r="AY240">
+        <v>18</v>
+      </c>
+      <c r="AZ240">
+        <v>20</v>
+      </c>
+      <c r="BA240">
+        <v>5</v>
+      </c>
+      <c r="BB240">
+        <v>6</v>
+      </c>
+      <c r="BC240">
+        <v>11</v>
+      </c>
+      <c r="BD240">
+        <v>1.43</v>
+      </c>
+      <c r="BE240">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF240">
+        <v>3.36</v>
+      </c>
+      <c r="BG240">
+        <v>0</v>
+      </c>
+      <c r="BH240">
+        <v>0</v>
+      </c>
+      <c r="BI240">
+        <v>1.35</v>
+      </c>
+      <c r="BJ240">
+        <v>2.74</v>
+      </c>
+      <c r="BK240">
+        <v>1.68</v>
+      </c>
+      <c r="BL240">
+        <v>2.15</v>
+      </c>
+      <c r="BM240">
+        <v>2.09</v>
+      </c>
+      <c r="BN240">
+        <v>1.71</v>
+      </c>
+      <c r="BO240">
+        <v>2.67</v>
+      </c>
+      <c r="BP240">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="359">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,15 @@
     <t>['30', '83']</t>
   </si>
   <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['45+6', '49', '82', '87']</t>
+  </si>
+  <si>
     <t>['24', '37']</t>
   </si>
   <si>
@@ -1006,9 +1015,6 @@
     <t>['52']</t>
   </si>
   <si>
-    <t>['22']</t>
-  </si>
-  <si>
     <t>['14', '26', '85']</t>
   </si>
   <si>
@@ -1043,9 +1049,6 @@
   </si>
   <si>
     <t>['32', '68', '85']</t>
-  </si>
-  <si>
-    <t>['8']</t>
   </si>
   <si>
     <t>['17']</t>
@@ -1085,6 +1088,9 @@
   </si>
   <si>
     <t>['77', '90+3']</t>
+  </si>
+  <si>
+    <t>['58', '67']</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1780,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ2">
         <v>0.64</v>
@@ -2114,7 +2120,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2398,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ5">
         <v>1.14</v>
@@ -2732,7 +2738,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2813,7 +2819,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3144,7 +3150,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -3556,7 +3562,7 @@
         <v>97</v>
       </c>
       <c r="P11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -3762,7 +3768,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -3968,7 +3974,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4049,7 +4055,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ13">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>1.41</v>
@@ -4174,7 +4180,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -4380,7 +4386,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
@@ -4586,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q16">
         <v>3.5</v>
@@ -5079,7 +5085,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ18">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5694,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -5822,7 +5828,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -6106,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ23">
         <v>0.38</v>
@@ -6440,7 +6446,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6646,7 +6652,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -6727,7 +6733,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6852,7 +6858,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -7058,7 +7064,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7470,7 +7476,7 @@
         <v>95</v>
       </c>
       <c r="P30" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q30">
         <v>3.1</v>
@@ -7754,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ31">
         <v>0.38</v>
@@ -7882,7 +7888,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8088,7 +8094,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q33">
         <v>4.75</v>
@@ -8169,7 +8175,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ33">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR33">
         <v>1.25</v>
@@ -8500,7 +8506,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -8581,7 +8587,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ35">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.34</v>
@@ -9118,7 +9124,7 @@
         <v>115</v>
       </c>
       <c r="P38" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q38">
         <v>2.25</v>
@@ -9196,7 +9202,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ38">
         <v>1.85</v>
@@ -9324,7 +9330,7 @@
         <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9608,7 +9614,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -9942,7 +9948,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10226,7 +10232,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ43">
         <v>2.38</v>
@@ -10435,7 +10441,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ44">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -10560,7 +10566,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10766,7 +10772,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -11178,7 +11184,7 @@
         <v>122</v>
       </c>
       <c r="P48" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11590,7 +11596,7 @@
         <v>123</v>
       </c>
       <c r="P50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q50">
         <v>3.2</v>
@@ -12083,7 +12089,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ52">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12414,7 +12420,7 @@
         <v>95</v>
       </c>
       <c r="P54" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12495,7 +12501,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ54">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR54">
         <v>1.89</v>
@@ -12620,7 +12626,7 @@
         <v>95</v>
       </c>
       <c r="P55" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q55">
         <v>4.75</v>
@@ -13113,7 +13119,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ57">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.6</v>
@@ -13238,7 +13244,7 @@
         <v>128</v>
       </c>
       <c r="P58" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13444,7 +13450,7 @@
         <v>129</v>
       </c>
       <c r="P59" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q59">
         <v>2.5</v>
@@ -13522,7 +13528,7 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ59">
         <v>0.71</v>
@@ -13650,7 +13656,7 @@
         <v>130</v>
       </c>
       <c r="P60" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q60">
         <v>2.2</v>
@@ -13856,7 +13862,7 @@
         <v>131</v>
       </c>
       <c r="P61" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q61">
         <v>2.63</v>
@@ -13934,7 +13940,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ61">
         <v>0.54</v>
@@ -14140,7 +14146,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14474,7 +14480,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q64">
         <v>2.88</v>
@@ -14886,7 +14892,7 @@
         <v>135</v>
       </c>
       <c r="P66" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -16200,10 +16206,10 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ72">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16328,7 +16334,7 @@
         <v>141</v>
       </c>
       <c r="P73" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16534,7 +16540,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q74">
         <v>2.38</v>
@@ -16612,7 +16618,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ74">
         <v>0.71</v>
@@ -16821,7 +16827,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ75">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -17024,10 +17030,10 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ76">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.53</v>
@@ -17770,7 +17776,7 @@
         <v>95</v>
       </c>
       <c r="P80" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -19212,7 +19218,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -19418,7 +19424,7 @@
         <v>95</v>
       </c>
       <c r="P88" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q88">
         <v>2.6</v>
@@ -19624,7 +19630,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19830,7 +19836,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q90">
         <v>3.6</v>
@@ -19911,7 +19917,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ90">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.39</v>
@@ -20036,7 +20042,7 @@
         <v>95</v>
       </c>
       <c r="P91" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q91">
         <v>2.6</v>
@@ -20448,7 +20454,7 @@
         <v>95</v>
       </c>
       <c r="P93" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q93">
         <v>4.33</v>
@@ -20654,7 +20660,7 @@
         <v>95</v>
       </c>
       <c r="P94" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20732,7 +20738,7 @@
         <v>0.2</v>
       </c>
       <c r="AP94">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ94">
         <v>0.86</v>
@@ -20860,7 +20866,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21066,7 +21072,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21350,10 +21356,10 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ97">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21556,10 +21562,10 @@
         <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ98">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR98">
         <v>1.72</v>
@@ -21684,7 +21690,7 @@
         <v>95</v>
       </c>
       <c r="P99" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q99">
         <v>4</v>
@@ -21765,7 +21771,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ99">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR99">
         <v>1.36</v>
@@ -21890,7 +21896,7 @@
         <v>95</v>
       </c>
       <c r="P100" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q100">
         <v>4.5</v>
@@ -21971,7 +21977,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ100">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR100">
         <v>1.26</v>
@@ -22096,7 +22102,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -22302,7 +22308,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22508,7 +22514,7 @@
         <v>95</v>
       </c>
       <c r="P103" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q103">
         <v>3.4</v>
@@ -22920,7 +22926,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -22998,7 +23004,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ105">
         <v>0.38</v>
@@ -23538,7 +23544,7 @@
         <v>164</v>
       </c>
       <c r="P108" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23744,7 +23750,7 @@
         <v>165</v>
       </c>
       <c r="P109" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q109">
         <v>2.05</v>
@@ -24028,7 +24034,7 @@
         <v>0.33</v>
       </c>
       <c r="AP110">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ110">
         <v>0.64</v>
@@ -24156,7 +24162,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q111">
         <v>2.5</v>
@@ -24774,7 +24780,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q114">
         <v>3.1</v>
@@ -25058,7 +25064,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ115">
         <v>1.14</v>
@@ -25186,7 +25192,7 @@
         <v>95</v>
       </c>
       <c r="P116" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25392,7 +25398,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q117">
         <v>2.2</v>
@@ -25473,7 +25479,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ117">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR117">
         <v>1.54</v>
@@ -25804,7 +25810,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q119">
         <v>3.6</v>
@@ -26297,7 +26303,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ121">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR121">
         <v>1.57</v>
@@ -26422,7 +26428,7 @@
         <v>95</v>
       </c>
       <c r="P122" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26500,7 +26506,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ122">
         <v>1.62</v>
@@ -26628,7 +26634,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
@@ -27040,7 +27046,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -27452,7 +27458,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q127">
         <v>2.5</v>
@@ -27658,7 +27664,7 @@
         <v>95</v>
       </c>
       <c r="P128" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q128">
         <v>2.2</v>
@@ -27736,7 +27742,7 @@
         <v>0.5</v>
       </c>
       <c r="AP128">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ128">
         <v>1.15</v>
@@ -28070,7 +28076,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -28151,7 +28157,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ130">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR130">
         <v>1.6</v>
@@ -28482,7 +28488,7 @@
         <v>95</v>
       </c>
       <c r="P132" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q132">
         <v>3.1</v>
@@ -28894,7 +28900,7 @@
         <v>183</v>
       </c>
       <c r="P134" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q134">
         <v>3.75</v>
@@ -28972,7 +28978,7 @@
         <v>2.43</v>
       </c>
       <c r="AP134">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ134">
         <v>2.38</v>
@@ -29100,7 +29106,7 @@
         <v>184</v>
       </c>
       <c r="P135" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q135">
         <v>3</v>
@@ -29181,7 +29187,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ135">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR135">
         <v>1.91</v>
@@ -29306,7 +29312,7 @@
         <v>109</v>
       </c>
       <c r="P136" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q136">
         <v>2.75</v>
@@ -29512,7 +29518,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q137">
         <v>2.3</v>
@@ -29590,7 +29596,7 @@
         <v>0.29</v>
       </c>
       <c r="AP137">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ137">
         <v>0.54</v>
@@ -29718,7 +29724,7 @@
         <v>95</v>
       </c>
       <c r="P138" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q138">
         <v>4</v>
@@ -30005,7 +30011,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ139">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.94</v>
@@ -30130,7 +30136,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q140">
         <v>2.1</v>
@@ -30336,7 +30342,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30826,10 +30832,10 @@
         <v>1.38</v>
       </c>
       <c r="AP143">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ143">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR143">
         <v>1.98</v>
@@ -31984,7 +31990,7 @@
         <v>193</v>
       </c>
       <c r="P149" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32190,7 +32196,7 @@
         <v>194</v>
       </c>
       <c r="P150" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32474,7 +32480,7 @@
         <v>2.14</v>
       </c>
       <c r="AP151">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ151">
         <v>1.62</v>
@@ -32602,7 +32608,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32683,7 +32689,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR152">
         <v>1.7</v>
@@ -33095,7 +33101,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ154">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR154">
         <v>1.51</v>
@@ -33298,7 +33304,7 @@
         <v>1.75</v>
       </c>
       <c r="AP155">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ155">
         <v>1.31</v>
@@ -33838,7 +33844,7 @@
         <v>201</v>
       </c>
       <c r="P158" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q158">
         <v>2.1</v>
@@ -34250,7 +34256,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q160">
         <v>4.5</v>
@@ -34456,7 +34462,7 @@
         <v>95</v>
       </c>
       <c r="P161" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34537,7 +34543,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ161">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34868,7 +34874,7 @@
         <v>203</v>
       </c>
       <c r="P163" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -35280,7 +35286,7 @@
         <v>205</v>
       </c>
       <c r="P165" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q165">
         <v>2.05</v>
@@ -35976,7 +35982,7 @@
         <v>0.67</v>
       </c>
       <c r="AP168">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ168">
         <v>0.86</v>
@@ -36182,7 +36188,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP169">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ169">
         <v>0.64</v>
@@ -36388,7 +36394,7 @@
         <v>1</v>
       </c>
       <c r="AP170">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ170">
         <v>1.15</v>
@@ -36516,7 +36522,7 @@
         <v>209</v>
       </c>
       <c r="P171" t="s">
-        <v>330</v>
+        <v>252</v>
       </c>
       <c r="Q171">
         <v>2.1</v>
@@ -36722,7 +36728,7 @@
         <v>149</v>
       </c>
       <c r="P172" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36803,7 +36809,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ172">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR172">
         <v>1.47</v>
@@ -37212,7 +37218,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ174">
         <v>1.31</v>
@@ -37546,7 +37552,7 @@
         <v>213</v>
       </c>
       <c r="P176" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q176">
         <v>1.93</v>
@@ -37627,7 +37633,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ176">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR176">
         <v>1.63</v>
@@ -37833,7 +37839,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ177">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR177">
         <v>1.53</v>
@@ -38164,7 +38170,7 @@
         <v>177</v>
       </c>
       <c r="P179" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q179">
         <v>3.25</v>
@@ -38576,7 +38582,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q181">
         <v>3.5</v>
@@ -38782,7 +38788,7 @@
         <v>215</v>
       </c>
       <c r="P182" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q182">
         <v>2.55</v>
@@ -39400,7 +39406,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q185">
         <v>2.44</v>
@@ -39478,7 +39484,7 @@
         <v>0.9</v>
       </c>
       <c r="AP185">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ185">
         <v>1.15</v>
@@ -39812,7 +39818,7 @@
         <v>93</v>
       </c>
       <c r="P187" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q187">
         <v>3.66</v>
@@ -40099,7 +40105,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ188">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR188">
         <v>1.73</v>
@@ -40302,7 +40308,7 @@
         <v>1.4</v>
       </c>
       <c r="AP189">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ189">
         <v>1.29</v>
@@ -40430,7 +40436,7 @@
         <v>220</v>
       </c>
       <c r="P190" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q190">
         <v>2.5</v>
@@ -40636,7 +40642,7 @@
         <v>221</v>
       </c>
       <c r="P191" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41254,7 +41260,7 @@
         <v>95</v>
       </c>
       <c r="P194" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q194">
         <v>3.56</v>
@@ -41541,7 +41547,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ195">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR195">
         <v>1.57</v>
@@ -41666,7 +41672,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q196">
         <v>2.95</v>
@@ -41872,7 +41878,7 @@
         <v>224</v>
       </c>
       <c r="P197" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -42284,7 +42290,7 @@
         <v>226</v>
       </c>
       <c r="P199" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q199">
         <v>3</v>
@@ -42365,7 +42371,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ199">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR199">
         <v>1.65</v>
@@ -42774,7 +42780,7 @@
         <v>2</v>
       </c>
       <c r="AP201">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ201">
         <v>1.85</v>
@@ -43108,7 +43114,7 @@
         <v>95</v>
       </c>
       <c r="P203" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q203">
         <v>2.95</v>
@@ -43186,7 +43192,7 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ203">
         <v>1.31</v>
@@ -43314,7 +43320,7 @@
         <v>95</v>
       </c>
       <c r="P204" t="s">
-        <v>343</v>
+        <v>253</v>
       </c>
       <c r="Q204">
         <v>3.3</v>
@@ -43395,7 +43401,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ204">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR204">
         <v>1.84</v>
@@ -43520,7 +43526,7 @@
         <v>95</v>
       </c>
       <c r="P205" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -44010,10 +44016,10 @@
         <v>1.27</v>
       </c>
       <c r="AP207">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ207">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR207">
         <v>1.81</v>
@@ -44344,7 +44350,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -44756,7 +44762,7 @@
         <v>143</v>
       </c>
       <c r="P211" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q211">
         <v>2.45</v>
@@ -44962,7 +44968,7 @@
         <v>95</v>
       </c>
       <c r="P212" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q212">
         <v>3.65</v>
@@ -45580,7 +45586,7 @@
         <v>96</v>
       </c>
       <c r="P215" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
@@ -45786,7 +45792,7 @@
         <v>95</v>
       </c>
       <c r="P216" t="s">
-        <v>343</v>
+        <v>253</v>
       </c>
       <c r="Q216">
         <v>3.6</v>
@@ -46073,7 +46079,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ217">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR217">
         <v>1.64</v>
@@ -46404,7 +46410,7 @@
         <v>235</v>
       </c>
       <c r="P219" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q219">
         <v>2.35</v>
@@ -46482,7 +46488,7 @@
         <v>2.09</v>
       </c>
       <c r="AP219">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ219">
         <v>1.85</v>
@@ -46610,7 +46616,7 @@
         <v>236</v>
       </c>
       <c r="P220" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q220">
         <v>2.88</v>
@@ -46894,7 +46900,7 @@
         <v>1.42</v>
       </c>
       <c r="AP221">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ221">
         <v>1.29</v>
@@ -47103,7 +47109,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ222">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR222">
         <v>1.48</v>
@@ -47309,7 +47315,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ223">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR223">
         <v>1.42</v>
@@ -47640,7 +47646,7 @@
         <v>240</v>
       </c>
       <c r="P225" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q225">
         <v>2.88</v>
@@ -47721,7 +47727,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ225">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR225">
         <v>1.64</v>
@@ -47846,7 +47852,7 @@
         <v>241</v>
       </c>
       <c r="P226" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q226">
         <v>3.2</v>
@@ -47924,7 +47930,7 @@
         <v>1.55</v>
       </c>
       <c r="AP226">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ226">
         <v>1.31</v>
@@ -48052,7 +48058,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48464,7 +48470,7 @@
         <v>242</v>
       </c>
       <c r="P229" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q229">
         <v>2.3</v>
@@ -49082,7 +49088,7 @@
         <v>245</v>
       </c>
       <c r="P232" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49288,7 +49294,7 @@
         <v>246</v>
       </c>
       <c r="P233" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q233">
         <v>2.75</v>
@@ -49494,7 +49500,7 @@
         <v>247</v>
       </c>
       <c r="P234" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49700,7 +49706,7 @@
         <v>95</v>
       </c>
       <c r="P235" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q235">
         <v>4.33</v>
@@ -50318,7 +50324,7 @@
         <v>95</v>
       </c>
       <c r="P238" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q238">
         <v>3</v>
@@ -50524,7 +50530,7 @@
         <v>250</v>
       </c>
       <c r="P239" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q239">
         <v>2.63</v>
@@ -50887,6 +50893,624 @@
       </c>
       <c r="BP240">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7450883</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45753.30208333334</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>70</v>
+      </c>
+      <c r="H241" t="s">
+        <v>84</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>1</v>
+      </c>
+      <c r="M241">
+        <v>1</v>
+      </c>
+      <c r="N241">
+        <v>2</v>
+      </c>
+      <c r="O241" t="s">
+        <v>252</v>
+      </c>
+      <c r="P241" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q241">
+        <v>2.75</v>
+      </c>
+      <c r="R241">
+        <v>2.05</v>
+      </c>
+      <c r="S241">
+        <v>4.33</v>
+      </c>
+      <c r="T241">
+        <v>1.44</v>
+      </c>
+      <c r="U241">
+        <v>2.63</v>
+      </c>
+      <c r="V241">
+        <v>3.4</v>
+      </c>
+      <c r="W241">
+        <v>1.3</v>
+      </c>
+      <c r="X241">
+        <v>10</v>
+      </c>
+      <c r="Y241">
+        <v>1.06</v>
+      </c>
+      <c r="Z241">
+        <v>2.04</v>
+      </c>
+      <c r="AA241">
+        <v>3.23</v>
+      </c>
+      <c r="AB241">
+        <v>3.71</v>
+      </c>
+      <c r="AC241">
+        <v>1.07</v>
+      </c>
+      <c r="AD241">
+        <v>8</v>
+      </c>
+      <c r="AE241">
+        <v>1.38</v>
+      </c>
+      <c r="AF241">
+        <v>3</v>
+      </c>
+      <c r="AG241">
+        <v>2</v>
+      </c>
+      <c r="AH241">
+        <v>1.67</v>
+      </c>
+      <c r="AI241">
+        <v>1.95</v>
+      </c>
+      <c r="AJ241">
+        <v>1.8</v>
+      </c>
+      <c r="AK241">
+        <v>1.25</v>
+      </c>
+      <c r="AL241">
+        <v>1.25</v>
+      </c>
+      <c r="AM241">
+        <v>1.75</v>
+      </c>
+      <c r="AN241">
+        <v>2.31</v>
+      </c>
+      <c r="AO241">
+        <v>1.38</v>
+      </c>
+      <c r="AP241">
+        <v>2.21</v>
+      </c>
+      <c r="AQ241">
+        <v>1.36</v>
+      </c>
+      <c r="AR241">
+        <v>1.75</v>
+      </c>
+      <c r="AS241">
+        <v>1.48</v>
+      </c>
+      <c r="AT241">
+        <v>3.23</v>
+      </c>
+      <c r="AU241">
+        <v>5</v>
+      </c>
+      <c r="AV241">
+        <v>4</v>
+      </c>
+      <c r="AW241">
+        <v>6</v>
+      </c>
+      <c r="AX241">
+        <v>3</v>
+      </c>
+      <c r="AY241">
+        <v>12</v>
+      </c>
+      <c r="AZ241">
+        <v>9</v>
+      </c>
+      <c r="BA241">
+        <v>5</v>
+      </c>
+      <c r="BB241">
+        <v>4</v>
+      </c>
+      <c r="BC241">
+        <v>9</v>
+      </c>
+      <c r="BD241">
+        <v>1.64</v>
+      </c>
+      <c r="BE241">
+        <v>6.5</v>
+      </c>
+      <c r="BF241">
+        <v>2.55</v>
+      </c>
+      <c r="BG241">
+        <v>1.3</v>
+      </c>
+      <c r="BH241">
+        <v>3.05</v>
+      </c>
+      <c r="BI241">
+        <v>1.53</v>
+      </c>
+      <c r="BJ241">
+        <v>2.25</v>
+      </c>
+      <c r="BK241">
+        <v>1.87</v>
+      </c>
+      <c r="BL241">
+        <v>1.77</v>
+      </c>
+      <c r="BM241">
+        <v>2.35</v>
+      </c>
+      <c r="BN241">
+        <v>1.48</v>
+      </c>
+      <c r="BO241">
+        <v>3.05</v>
+      </c>
+      <c r="BP241">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7450882</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45753.40625</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>87</v>
+      </c>
+      <c r="H242" t="s">
+        <v>74</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>1</v>
+      </c>
+      <c r="L242">
+        <v>1</v>
+      </c>
+      <c r="M242">
+        <v>2</v>
+      </c>
+      <c r="N242">
+        <v>3</v>
+      </c>
+      <c r="O242" t="s">
+        <v>253</v>
+      </c>
+      <c r="P242" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q242">
+        <v>3.5</v>
+      </c>
+      <c r="R242">
+        <v>2.25</v>
+      </c>
+      <c r="S242">
+        <v>2.88</v>
+      </c>
+      <c r="T242">
+        <v>1.33</v>
+      </c>
+      <c r="U242">
+        <v>3.25</v>
+      </c>
+      <c r="V242">
+        <v>2.63</v>
+      </c>
+      <c r="W242">
+        <v>1.44</v>
+      </c>
+      <c r="X242">
+        <v>7</v>
+      </c>
+      <c r="Y242">
+        <v>1.1</v>
+      </c>
+      <c r="Z242">
+        <v>3.26</v>
+      </c>
+      <c r="AA242">
+        <v>3.55</v>
+      </c>
+      <c r="AB242">
+        <v>2.07</v>
+      </c>
+      <c r="AC242">
+        <v>1.05</v>
+      </c>
+      <c r="AD242">
+        <v>9.5</v>
+      </c>
+      <c r="AE242">
+        <v>1.28</v>
+      </c>
+      <c r="AF242">
+        <v>3.65</v>
+      </c>
+      <c r="AG242">
+        <v>1.79</v>
+      </c>
+      <c r="AH242">
+        <v>1.95</v>
+      </c>
+      <c r="AI242">
+        <v>1.62</v>
+      </c>
+      <c r="AJ242">
+        <v>2.2</v>
+      </c>
+      <c r="AK242">
+        <v>1.7</v>
+      </c>
+      <c r="AL242">
+        <v>1.25</v>
+      </c>
+      <c r="AM242">
+        <v>1.3</v>
+      </c>
+      <c r="AN242">
+        <v>1.77</v>
+      </c>
+      <c r="AO242">
+        <v>1.08</v>
+      </c>
+      <c r="AP242">
+        <v>1.64</v>
+      </c>
+      <c r="AQ242">
+        <v>1.21</v>
+      </c>
+      <c r="AR242">
+        <v>2.01</v>
+      </c>
+      <c r="AS242">
+        <v>1.52</v>
+      </c>
+      <c r="AT242">
+        <v>3.53</v>
+      </c>
+      <c r="AU242">
+        <v>6</v>
+      </c>
+      <c r="AV242">
+        <v>3</v>
+      </c>
+      <c r="AW242">
+        <v>8</v>
+      </c>
+      <c r="AX242">
+        <v>2</v>
+      </c>
+      <c r="AY242">
+        <v>16</v>
+      </c>
+      <c r="AZ242">
+        <v>6</v>
+      </c>
+      <c r="BA242">
+        <v>5</v>
+      </c>
+      <c r="BB242">
+        <v>5</v>
+      </c>
+      <c r="BC242">
+        <v>10</v>
+      </c>
+      <c r="BD242">
+        <v>2.33</v>
+      </c>
+      <c r="BE242">
+        <v>6.4</v>
+      </c>
+      <c r="BF242">
+        <v>1.74</v>
+      </c>
+      <c r="BG242">
+        <v>1.35</v>
+      </c>
+      <c r="BH242">
+        <v>2.8</v>
+      </c>
+      <c r="BI242">
+        <v>1.6</v>
+      </c>
+      <c r="BJ242">
+        <v>2.1</v>
+      </c>
+      <c r="BK242">
+        <v>2</v>
+      </c>
+      <c r="BL242">
+        <v>1.68</v>
+      </c>
+      <c r="BM242">
+        <v>2.55</v>
+      </c>
+      <c r="BN242">
+        <v>1.42</v>
+      </c>
+      <c r="BO242">
+        <v>3.3</v>
+      </c>
+      <c r="BP242">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7450885</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45753.52083333334</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>73</v>
+      </c>
+      <c r="H243" t="s">
+        <v>72</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
+      </c>
+      <c r="L243">
+        <v>4</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>4</v>
+      </c>
+      <c r="O243" t="s">
+        <v>254</v>
+      </c>
+      <c r="P243" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q243">
+        <v>2.3</v>
+      </c>
+      <c r="R243">
+        <v>2.38</v>
+      </c>
+      <c r="S243">
+        <v>4.33</v>
+      </c>
+      <c r="T243">
+        <v>1.3</v>
+      </c>
+      <c r="U243">
+        <v>3.4</v>
+      </c>
+      <c r="V243">
+        <v>2.38</v>
+      </c>
+      <c r="W243">
+        <v>1.53</v>
+      </c>
+      <c r="X243">
+        <v>6</v>
+      </c>
+      <c r="Y243">
+        <v>1.13</v>
+      </c>
+      <c r="Z243">
+        <v>1.76</v>
+      </c>
+      <c r="AA243">
+        <v>3.93</v>
+      </c>
+      <c r="AB243">
+        <v>4.1</v>
+      </c>
+      <c r="AC243">
+        <v>1.04</v>
+      </c>
+      <c r="AD243">
+        <v>10</v>
+      </c>
+      <c r="AE243">
+        <v>1.2</v>
+      </c>
+      <c r="AF243">
+        <v>4.33</v>
+      </c>
+      <c r="AG243">
+        <v>1.57</v>
+      </c>
+      <c r="AH243">
+        <v>2.15</v>
+      </c>
+      <c r="AI243">
+        <v>1.57</v>
+      </c>
+      <c r="AJ243">
+        <v>2.25</v>
+      </c>
+      <c r="AK243">
+        <v>1.22</v>
+      </c>
+      <c r="AL243">
+        <v>1.2</v>
+      </c>
+      <c r="AM243">
+        <v>1.95</v>
+      </c>
+      <c r="AN243">
+        <v>2.38</v>
+      </c>
+      <c r="AO243">
+        <v>1.08</v>
+      </c>
+      <c r="AP243">
+        <v>2.43</v>
+      </c>
+      <c r="AQ243">
+        <v>1</v>
+      </c>
+      <c r="AR243">
+        <v>1.82</v>
+      </c>
+      <c r="AS243">
+        <v>1.6</v>
+      </c>
+      <c r="AT243">
+        <v>3.42</v>
+      </c>
+      <c r="AU243">
+        <v>9</v>
+      </c>
+      <c r="AV243">
+        <v>0</v>
+      </c>
+      <c r="AW243">
+        <v>10</v>
+      </c>
+      <c r="AX243">
+        <v>7</v>
+      </c>
+      <c r="AY243">
+        <v>23</v>
+      </c>
+      <c r="AZ243">
+        <v>10</v>
+      </c>
+      <c r="BA243">
+        <v>6</v>
+      </c>
+      <c r="BB243">
+        <v>4</v>
+      </c>
+      <c r="BC243">
+        <v>10</v>
+      </c>
+      <c r="BD243">
+        <v>1.46</v>
+      </c>
+      <c r="BE243">
+        <v>9.4</v>
+      </c>
+      <c r="BF243">
+        <v>3.18</v>
+      </c>
+      <c r="BG243">
+        <v>1.21</v>
+      </c>
+      <c r="BH243">
+        <v>3.65</v>
+      </c>
+      <c r="BI243">
+        <v>1.27</v>
+      </c>
+      <c r="BJ243">
+        <v>3.14</v>
+      </c>
+      <c r="BK243">
+        <v>1.53</v>
+      </c>
+      <c r="BL243">
+        <v>2.43</v>
+      </c>
+      <c r="BM243">
+        <v>1.88</v>
+      </c>
+      <c r="BN243">
+        <v>1.92</v>
+      </c>
+      <c r="BO243">
+        <v>2.34</v>
+      </c>
+      <c r="BP243">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Poland Ekstraklasa_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="360">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1092,6 +1092,9 @@
   <si>
     <t>['58', '67']</t>
   </si>
+  <si>
+    <t>['28']</t>
+  </si>
 </sst>
 </file>
 
@@ -1452,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP243"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3231,7 +3234,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ9">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3640,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ11">
         <v>1.31</v>
@@ -5909,7 +5912,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ22">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR22">
         <v>2.03</v>
@@ -8172,7 +8175,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ33">
         <v>1.21</v>
@@ -8790,7 +8793,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ36">
         <v>0.71</v>
@@ -10235,7 +10238,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ43">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR43">
         <v>1.8</v>
@@ -10853,7 +10856,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ46">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR46">
         <v>1.21</v>
@@ -12910,7 +12913,7 @@
         <v>0.67</v>
       </c>
       <c r="AP56">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ56">
         <v>1.14</v>
@@ -15797,7 +15800,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ70">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -16412,7 +16415,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ73">
         <v>1.85</v>
@@ -19914,7 +19917,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20535,7 +20538,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ93">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR93">
         <v>1.66</v>
@@ -24449,7 +24452,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ112">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR112">
         <v>1.59</v>
@@ -26094,7 +26097,7 @@
         <v>2.17</v>
       </c>
       <c r="AP120">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ120">
         <v>1.31</v>
@@ -28981,7 +28984,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ134">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR134">
         <v>1.7</v>
@@ -31038,7 +31041,7 @@
         <v>1.13</v>
       </c>
       <c r="AP144">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -32071,7 +32074,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ149">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR149">
         <v>1.41</v>
@@ -34334,7 +34337,7 @@
         <v>2</v>
       </c>
       <c r="AP160">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ160">
         <v>1.62</v>
@@ -35779,7 +35782,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ167">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -38660,7 +38663,7 @@
         <v>0.6</v>
       </c>
       <c r="AP181">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ181">
         <v>0.86</v>
@@ -39075,7 +39078,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ183">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR183">
         <v>2.02</v>
@@ -43604,7 +43607,7 @@
         <v>1.27</v>
       </c>
       <c r="AP205">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ205">
         <v>1.29</v>
@@ -45049,7 +45052,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ212">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR212">
         <v>1.62</v>
@@ -47312,7 +47315,7 @@
         <v>1.5</v>
       </c>
       <c r="AP223">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ223">
         <v>1.36</v>
@@ -49787,7 +49790,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ235">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR235">
         <v>1.76</v>
@@ -51511,6 +51514,212 @@
       </c>
       <c r="BP243">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7450886</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45754.58333333334</v>
+      </c>
+      <c r="F244">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>79</v>
+      </c>
+      <c r="H244" t="s">
+        <v>86</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>1</v>
+      </c>
+      <c r="K244">
+        <v>1</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244">
+        <v>2</v>
+      </c>
+      <c r="O244" t="s">
+        <v>212</v>
+      </c>
+      <c r="P244" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q244">
+        <v>5.5</v>
+      </c>
+      <c r="R244">
+        <v>2.2</v>
+      </c>
+      <c r="S244">
+        <v>2.3</v>
+      </c>
+      <c r="T244">
+        <v>1.4</v>
+      </c>
+      <c r="U244">
+        <v>2.75</v>
+      </c>
+      <c r="V244">
+        <v>3</v>
+      </c>
+      <c r="W244">
+        <v>1.36</v>
+      </c>
+      <c r="X244">
+        <v>8</v>
+      </c>
+      <c r="Y244">
+        <v>1.08</v>
+      </c>
+      <c r="Z244">
+        <v>5.5</v>
+      </c>
+      <c r="AA244">
+        <v>3.84</v>
+      </c>
+      <c r="AB244">
+        <v>1.59</v>
+      </c>
+      <c r="AC244">
+        <v>1.04</v>
+      </c>
+      <c r="AD244">
+        <v>9</v>
+      </c>
+      <c r="AE244">
+        <v>1.3</v>
+      </c>
+      <c r="AF244">
+        <v>3.25</v>
+      </c>
+      <c r="AG244">
+        <v>1.95</v>
+      </c>
+      <c r="AH244">
+        <v>1.79</v>
+      </c>
+      <c r="AI244">
+        <v>1.95</v>
+      </c>
+      <c r="AJ244">
+        <v>1.8</v>
+      </c>
+      <c r="AK244">
+        <v>2.1</v>
+      </c>
+      <c r="AL244">
+        <v>1.26</v>
+      </c>
+      <c r="AM244">
+        <v>1.17</v>
+      </c>
+      <c r="AN244">
+        <v>1.33</v>
+      </c>
+      <c r="AO244">
+        <v>2.38</v>
+      </c>
+      <c r="AP244">
+        <v>1.31</v>
+      </c>
+      <c r="AQ244">
+        <v>2.29</v>
+      </c>
+      <c r="AR244">
+        <v>1.41</v>
+      </c>
+      <c r="AS244">
+        <v>1.55</v>
+      </c>
+      <c r="AT244">
+        <v>2.96</v>
+      </c>
+      <c r="AU244">
+        <v>4</v>
+      </c>
+      <c r="AV244">
+        <v>5</v>
+      </c>
+      <c r="AW244">
+        <v>7</v>
+      </c>
+      <c r="AX244">
+        <v>11</v>
+      </c>
+      <c r="AY244">
+        <v>15</v>
+      </c>
+      <c r="AZ244">
+        <v>19</v>
+      </c>
+      <c r="BA244">
+        <v>5</v>
+      </c>
+      <c r="BB244">
+        <v>4</v>
+      </c>
+      <c r="BC244">
+        <v>9</v>
+      </c>
+      <c r="BD244">
+        <v>3.46</v>
+      </c>
+      <c r="BE244">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF244">
+        <v>1.41</v>
+      </c>
+      <c r="BG244">
+        <v>1.21</v>
+      </c>
+      <c r="BH244">
+        <v>3.58</v>
+      </c>
+      <c r="BI244">
+        <v>1.42</v>
+      </c>
+      <c r="BJ244">
+        <v>2.57</v>
+      </c>
+      <c r="BK244">
+        <v>1.75</v>
+      </c>
+      <c r="BL244">
+        <v>2.04</v>
+      </c>
+      <c r="BM244">
+        <v>2.18</v>
+      </c>
+      <c r="BN244">
+        <v>1.65</v>
+      </c>
+      <c r="BO244">
+        <v>2.92</v>
+      </c>
+      <c r="BP244">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>
